--- a/output/rrl_matrix.xlsx
+++ b/output/rrl_matrix.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S45"/>
+  <dimension ref="A1:S49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="19" customWidth="1" min="16" max="16"/>
     <col width="27" customWidth="1" min="17" max="17"/>
-    <col width="13" customWidth="1" min="18" max="18"/>
+    <col width="18" customWidth="1" min="18" max="18"/>
     <col width="60" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
@@ -636,17 +636,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>af7fc167eb9a6103</t>
+          <t>786b0581c04bbb7a</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Business Simulation in the Context of Emerging Technologies the SPEE Case Study</t>
+          <t>Artificial intelligence in higher education: a bibliometric analysis of research trends (2015–2024)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Sequeira, G.; Pereira, R.; Cossa, G.; Pinto, A.; Roque, L.</t>
+          <t>Mittal, N.; Batra, G.; Sijariya, R.</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -659,22 +659,17 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lecture notes in computer science</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Springer Science+Business Media</t>
+          <t>International Conference on Artificial Intelligence in Education</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>book-chapter</t>
+          <t>article</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10.1007/978-3-032-20129-4_24</t>
+          <t>10.1108/aiie-04-2025-0076</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -684,7 +679,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -697,47 +692,48 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>hybrid</t>
-        </is>
-      </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026/af7fc167eb9a6103.pdf</t>
+          <t>2026/786b0581c04bbb7a.pdf</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>dean_provided,s2</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>This study analyzed the factors to consider for updating business simulation systems within the context of digital transformation driven by emerging technologies. To achieve this, a qualitative research approach was adopted, focusing on the Business Practices and Entrepreneurship System (SPEE), the leading business simulator in Mozambique, to identify critical factors for its modernization. The investigation, conducted as a single case study, incorporated a literature review, document analysis, and interviews, which revealed five key dimensions: realism, multidisciplinary approach, communication and interaction, ease of use and support, and accessibility and scalability. The research concluded that the most significant factors include the complexity of the local market, automation and operational efficiency, the level of digital literacy and technological infrastructure, the anticipation of future scenarios, and the enhancement of user experience. These findings suggest that integrating emerging technologies such as Artificial Intelligence (AI), Blockchain, and Virtual Reality (VR) could enhance realism, adaptability, and user engagement. Additionally, hybrid solutions combining online and offline accessibility were recommended to address technological infrastructure limitations in developing countries. The study provides practical guidelines for aligning SPEE with contemporary educational and market demands, reinforcing its relevance in higher education.</t>
+          <t xml:space="preserve">
+ Previous research on Artificial Intelligence in Education (AIEd) has predominantly focused on specific tools and outcomes. Few studies provide data-driven insights into its evolution, particularly in the period after the launch of ChatGPT. This study addresses this gap through a bibliometric analysis of publications on Artificial Intelligence in Higher Education from 2015 to 2024, mapping research output, collaboration patterns, and citation trends.
+ A total of 1,671 peer-reviewed journal articles indexed in Scopus were analyzed based on the PRISMA framework. Using performance analysis and scientific mapping, the study examined the AIEd research landscape to offer document, author, country, institution, and keyword-level insights.
+ The publications depict a 67% annual growth rate, especially after 2022, with output tripling from 353 in 2023 to 927 in 2024, coinciding with the release of ChatGPT. Most highly cited articles focus on generative AI, signifying a thematic shift towards AI-driven academic concerns like academic integrity, assessment challenges, and AI ethics.
+ The findings can guide universities in implementing AI literacy initiatives, embedding ethical safeguards, and shaping evidence-based institutional and policy frameworks for responsible AI integration.
+ This study captures the trajectory of AI in higher education over the past decade. It highlights a significant thematic shift in research following the emergence of ChatGPT, which has not yet been comprehensively assessed. The findings of the study are poised to shape the direction of future research in the field.
+</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>5237174bb1448508</t>
+          <t>281df417f101e592</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Deploying Generative-AI-Powered Multimodal Intelligence for Bespoke English Language Instruction: A Cross-Disciplinary Case Study in 21st-Century Higher Education</t>
+          <t>Artificial intelligence in higher education: faculty empowerment or future workplace stress</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Raj, D.; Anuradha, G.; Kavitha, V.; Shalini, K.; Steffi, R.; Mathew, D.</t>
+          <t>Soomro, S.; Fan, M.; Soomro, S.; Sohu, J.; Shaikh, S.; Kherazi, F.</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -750,22 +746,17 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Communications in computer and information science</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Springer Science+Business Media</t>
+          <t>Learning Futures and Emerging Technologies</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>book-chapter</t>
+          <t>article</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10.1007/978-3-032-17300-3_14</t>
+          <t>10.1108/lfet-06-2025-0077</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -788,47 +779,47 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>hybrid</t>
-        </is>
-      </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026/5237174bb1448508.pdf</t>
+          <t>2026/281df417f101e592.pdf</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>dean_provided,s2</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>Abstract This study examines the use of generative artificial intelligence and multimodal analytics to create a more personalised experience of English language instruction for the pertinent diverse learners in higher education institutions. Using a large major research university as the site of an extensive case study, and with a sizeable contingent of disciplinary English as a Second Language (ESL) instructors, who worked at the behest of the principal investigator, unquestioningly, for 12 months, the discipline-agnostic experimental classroom was populated with upward of 200 ESL students, each of whom was subject to varying degrees and types of private AI supervision. The study makes a substantial contribution to research on educational technologies by establishing a robust framework for integrating multimodal AI into education. It is clear that the comfortable pedagogical fit of AI in language education is the result of: (1) fostering instructor agency through careful and inclusive planning; (2) placing personnel training at the center of implementation efforts; (3) enacting strong support throughout all levels of the institution; and (4) keeping the ethics of AI use at the forefront of decision-making.</t>
+          <t xml:space="preserve">
+ This research paper aims to investigate the impact of artificial intelligence adoption (AIA) on workplace well-being (WWB) in Pakistani higher education institutions (HEIs) with a focus on the mediating roles of job autonomy (JA) and work–life balance (WLB) and the moderating effect of training (T).
+ Applying cross-sectional survey research, the data were gathered from 462 Faculty members within Pakistani HEIs. Constructs were measured using validated scales. The analysis used structural equation modeling (SEM) to test direct, mediating and moderating relationships among variables.
+ AI adoption was found to affect faculty workplace well-being significantly. Although AI increases efficiency and flexibility, it entails risks of work intensification and decreased job control. Job autonomy and work–life balance partially mediate the AIA–WWB relation. Moreover, training significantly moderates the relationship between AI adoption and job autonomy.
+ To the best of the authors’ knowledge, this analysis provides one of the first empirical considerations of AI’s implications on faculty well-being. It extends SDT by integrating it into AI adoption research and highlights how psychological needs interact with digital transformation in academic environments.
+</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>26c869f88b616e34</t>
+          <t>8ab99685bf611427</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Efficacy of Selected Generative AI Systems in Assessing Discourse Coherence, Pragmatic Competence, Collocational Competence, and Figurative Language</t>
+          <t>Artificial intelligence in higher education: stakeholder perceptions and policy implications</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Prajapati, A.; Teraiya, A.; Vaghela, K.</t>
+          <t>Lawrence, S.</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -841,22 +832,22 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Communications in computer and information science</t>
+          <t>Journal of Applied Research in Higher Education</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Springer Science+Business Media</t>
+          <t>Babeș-Bolyai University</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>book-chapter</t>
+          <t>article</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10.1007/978-3-032-17300-3_10</t>
+          <t>10.1108/jarhe-10-2025-0872</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -877,49 +868,51 @@
       <c r="M5" t="inlineStr">
         <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>hybrid</t>
         </is>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026/26c869f88b616e34.pdf</t>
+          <t>2026/8ab99685bf611427.pdf</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>dean_provided,s2</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>Abstract Artificial Intelligence (AI) is rapidly transforming language education, functioning not merely as an automation tool but as a catalyst for understanding, accuracy, and individualized learning. Nonetheless, despite the extensive integration of AI in education, comprehension of its efficacy in assessing language proficiency, particularly these four parameters, discourse coherence, pragmatic competence, collocational competence, and figurative language, remains largely underexplored from the perspective of integrating AI. Consequently, capacity to embed AI driven formative assessments for enhanced feedback can be insightful. The present study assesses the efficacy of five leading generative AI systems namely GPT-4, Gemini, DeepSeek, Copilot, and Claude Sonnet 4, through standardised dialogues that encompass four linguistic criteria, discourse coherence, pragmatic competence, collocational competence, and figurative language. language. The dialogues constructed by students as a part of a classroom activity are assessed through each AI tool will through CEFR based 5-point rubrics. The study of this evaluation, aims to explore how effectively and precisely these AI tools process the specific language inputs deliver the feedback that aids learners in improving expression, increasing their clarity, and enriching their contextual comprehension. The findings of this study will benefit teachers, curriculum developers and language learners by offering evidence-based insights into which generative AI systems can be utilised for the improvement, accuracy and learner autonomy in higher education and EFL domains.</t>
+          <t xml:space="preserve">
+ This study aims to examine stakeholder perceptions of artificial intelligence (AI) at a small regional comprehensive university in the southern United States to inform the development of ethical, transparent and inclusive institutional policies. Guided by an integrated conceptual framework, the study explored how stakeholder role and age influence perceptions of AI and identified perceived training and policy gaps related to responsible AI use.
+ Guided by the technology acceptance model, diffusion of innovations theory, the ethical decision-making framework and social constructivism, the study employed an exploratory survey design (n = 248) combining Likert-scale items and open-ended responses. Quantitative data were analyzed using descriptive and nonparametric statistics, and qualitative data were examined through thematic analysis to capture both patterns and contextual insights.
+ Results revealed significant differences in AI perceptions by role and age. Students were highly accepting of AI for learning and efficiency, whereas faculty and administrators expressed greater concern about academic integrity, privacy and ethical use. Staff responses were mixed, emphasizing workflow efficiency alongside ethical and governance-related risks. Across groups, participants highlighted the need for clearer guidelines and structured training to support responsible AI adoption.
+ The single-institution, cross-sectional design may limit transferability. Future research could extend these findings through multi-institutional, longitudinal or qualitative studies that further examine evolving AI governance and practice.
+ Findings provide actionable guidance for developing AI policies, professional learning and governance structures that promote transparency, accountability, and equitable access while respecting institutional context.
+ This study contributes a multi-stakeholder empirical analysis of AI perceptions within a single institutional context, guided by an integrated conceptual framework to inform ethical policy, governance and practice in higher education.
+</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2e7b056c99eebd67</t>
+          <t>af7fc167eb9a6103</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Enhancing Agile Workflows with AI-Driven, Sustainability-Aware Requirements Engineering: A Design Science Approach</t>
+          <t>Business Simulation in the Context of Emerging Technologies the SPEE Case Study</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Weerakoon, O.; Oyedeji, S.; Samad, M.; Abubakar, A.; Ishan, A.; Shayan, M.; Mäkilä, T.; Kaila, E.</t>
+          <t>Sequeira, G.; Pereira, R.; Cossa, G.; Pinto, A.; Roque, L.</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -932,7 +925,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lecture notes in business information processing</t>
+          <t>Lecture notes in computer science</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -947,7 +940,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10.1007/978-3-032-14518-5_17</t>
+          <t>10.1007/978-3-032-20129-4_24</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -983,7 +976,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026/2e7b056c99eebd67.pdf</t>
+          <t>2026/af7fc167eb9a6103.pdf</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -993,24 +986,24 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>Generative AI presents growing opportunities across various fields, including Requirements Engineering (RE). RE, which is the backbone of software projects, drives the entire product development toward respective business goals. However, sustainability is not considered a primary need during the requirement elicitation, and as a result, software engineers are usually unable to envision the sustainability impacts of the products they build. To explore this gap, we introduce Reqwire, an AI-driven, sustainability-aware multi-agent system that (i) generates user stories from software requirement documents, (ii) enriches them with sustainability attributes, and (iii) integrates with common agile project management tools, like Jira. The system consists of specialized agents, namely as root, distributor, user story generator, and Jira. We followed a Design Science Research (DSR) approach under seven iterative cycles, incorporating feedback from an industry partner and academia to design and evaluate the Reqwire workflow. Our results indicate that Reqwire reduces manual effort by generating structured user stories, estimating story points, and assigning sustainability tags across five sustainability dimensions: environmental, economic, social, individual, and technical. The multi-agent-based framework enables integration with third-party tools, supporting consistent, systematic project tracking. Reqwire shows promise for enhancing agile workflows and promoting sustainable software practices from initial test rounds with the client.</t>
+          <t>This study analyzed the factors to consider for updating business simulation systems within the context of digital transformation driven by emerging technologies. To achieve this, a qualitative research approach was adopted, focusing on the Business Practices and Entrepreneurship System (SPEE), the leading business simulator in Mozambique, to identify critical factors for its modernization. The investigation, conducted as a single case study, incorporated a literature review, document analysis, and interviews, which revealed five key dimensions: realism, multidisciplinary approach, communication and interaction, ease of use and support, and accessibility and scalability. The research concluded that the most significant factors include the complexity of the local market, automation and operational efficiency, the level of digital literacy and technological infrastructure, the anticipation of future scenarios, and the enhancement of user experience. These findings suggest that integrating emerging technologies such as Artificial Intelligence (AI), Blockchain, and Virtual Reality (VR) could enhance realism, adaptability, and user engagement. Additionally, hybrid solutions combining online and offline accessibility were recommended to address technological infrastructure limitations in developing countries. The study provides practical guidelines for aligning SPEE with contemporary educational and market demands, reinforcing its relevance in higher education.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>19da11449909222f</t>
+          <t>5237174bb1448508</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Narrative AI Strategies for Media, Ethics and Higher Education Impulse Perspectives from Practice Based Media Education</t>
+          <t>Deploying Generative-AI-Powered Multimodal Intelligence for Bespoke English Language Instruction: A Cross-Disciplinary Case Study in 21st-Century Higher Education</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Simon, M.; Khafif, D.</t>
+          <t>Raj, D.; Anuradha, G.; Kavitha, V.; Shalini, K.; Steffi, R.; Mathew, D.</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -1023,7 +1016,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lecture notes in business information processing</t>
+          <t>Communications in computer and information science</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1038,7 +1031,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10.1007/978-3-032-14518-5_18</t>
+          <t>10.1007/978-3-032-17300-3_14</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1070,11 +1063,11 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026/19da11449909222f.pdf</t>
+          <t>2026/5237174bb1448508.pdf</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1084,24 +1077,24 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>The transformation of narrative creation, authorship, and authenticity in the age of Generative AI is not merely a technological shift, but a cultural, epistemic, and ethical realignment. This paper argues that this transformation requires a threefold competence profile—technical proficiency, narrative design capability, and ethical reflexivity—cultivated in both higher education and corporate practice. This motive connects interdisciplinary teaching with strategic implications for communication, marketing, and oragnisational governance, bridging theory and real-world applications.</t>
+          <t>Abstract This study examines the use of generative artificial intelligence and multimodal analytics to create a more personalised experience of English language instruction for the pertinent diverse learners in higher education institutions. Using a large major research university as the site of an extensive case study, and with a sizeable contingent of disciplinary English as a Second Language (ESL) instructors, who worked at the behest of the principal investigator, unquestioningly, for 12 months, the discipline-agnostic experimental classroom was populated with upward of 200 ESL students, each of whom was subject to varying degrees and types of private AI supervision. The study makes a substantial contribution to research on educational technologies by establishing a robust framework for integrating multimodal AI into education. It is clear that the comfortable pedagogical fit of AI in language education is the result of: (1) fostering instructor agency through careful and inclusive planning; (2) placing personnel training at the center of implementation efforts; (3) enacting strong support throughout all levels of the institution; and (4) keeping the ethics of AI use at the forefront of decision-making.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>bde689abecf48b32</t>
+          <t>26c869f88b616e34</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Practical Adoption of Green Coding: A Comparative Study Across Organizations in Finland and Globally</t>
+          <t>Efficacy of Selected Generative AI Systems in Assessing Discourse Coherence, Pragmatic Competence, Collocational Competence, and Figurative Language</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Moktan, I.; Khan, M.; Oyedeji, S.; Puonti, M.; Adisa, M.; Porras, J.</t>
+          <t>Prajapati, A.; Teraiya, A.; Vaghela, K.</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1114,7 +1107,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lecture notes in business information processing</t>
+          <t>Communications in computer and information science</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1129,7 +1122,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10.1007/978-3-032-14518-5_28</t>
+          <t>10.1007/978-3-032-17300-3_10</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1161,11 +1154,11 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026/bde689abecf48b32.pdf</t>
+          <t>2026/26c869f88b616e34.pdf</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1175,28 +1168,28 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>As the environmental impact of digital technologies gains increasing attention, green coding has emerged as a critical aspect of green software engineering. This study investigates the practical adoption of green coding practices in organizations in Finland and globally to understand how they approach green coding in their software-development workflow. This study adopts a qualitative research methodology, combining a systematic literature review and semi-structured interviews. Key findings indicate that while organizations adhere to academic-recommended coding practices such as caching, lazy loading, asynchronous processing, microservices, and content/UI optimization, industry prioritization often depends on business needs, with less emphasis on energy-efficient programming languages or priority in green coding, especially in organizations outside the EU. Interestingly, in larger organizations, such as banks, green coding initiatives are mostly driven from the bottom up and led by software engineers. This reflects a positive change. However, innovative academic proposals, such as large language model (LLM)-based assistants for recommending green libraries, remain prototypes without industrial adoption. While LLM-based assistants show potential in recommending greener libraries, their current energy demand raises questions about net sustainability. Future research should evaluate their carbon trade-offs to ensure these tools contribute positively to sustainability goals. This study underscores the need for closer collaboration between academia and industry to promote the practical adoption of effective tools, along with standardized guidelines and sustainability-oriented education, to enable the wider adoption of green coding practices.</t>
+          <t>Abstract Artificial Intelligence (AI) is rapidly transforming language education, functioning not merely as an automation tool but as a catalyst for understanding, accuracy, and individualized learning. Nonetheless, despite the extensive integration of AI in education, comprehension of its efficacy in assessing language proficiency, particularly these four parameters, discourse coherence, pragmatic competence, collocational competence, and figurative language, remains largely underexplored from the perspective of integrating AI. Consequently, capacity to embed AI driven formative assessments for enhanced feedback can be insightful. The present study assesses the efficacy of five leading generative AI systems namely GPT-4, Gemini, DeepSeek, Copilot, and Claude Sonnet 4, through standardised dialogues that encompass four linguistic criteria, discourse coherence, pragmatic competence, collocational competence, and figurative language. language. The dialogues constructed by students as a part of a classroom activity are assessed through each AI tool will through CEFR based 5-point rubrics. The study of this evaluation, aims to explore how effectively and precisely these AI tools process the specific language inputs deliver the feedback that aids learners in improving expression, increasing their clarity, and enriching their contextual comprehension. The findings of this study will benefit teachers, curriculum developers and language learners by offering evidence-based insights into which generative AI systems can be utilised for the improvement, accuracy and learner autonomy in higher education and EFL domains.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>c6a4accaccaeb577</t>
+          <t>2e7b056c99eebd67</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Capacity Building in Livestock Breeding and Genetic Improvement in Achieving UN Sustainable Development Goals for Africa</t>
+          <t>Enhancing Agile Workflows with AI-Driven, Sustainability-Aware Requirements Engineering: A Design Science Approach</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Tiambo, C.; Opoola, O.; Okpeku, M.; Houaga, I.; Touko, B.; Dessie, T.</t>
+          <t>Weerakoon, O.; Oyedeji, S.; Samad, M.; Abubakar, A.; Ishan, A.; Shayan, M.; Mäkilä, T.; Kaila, E.</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1205,12 +1198,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sustainable development goals series</t>
+          <t>Lecture notes in business information processing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Springer International Publishing</t>
+          <t>Springer Science+Business Media</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1220,7 +1213,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-92076-9_28</t>
+          <t>10.1007/978-3-032-14518-5_17</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1252,11 +1245,11 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2025/c6a4accaccaeb577.pdf</t>
+          <t>2026/2e7b056c99eebd67.pdf</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -1266,28 +1259,28 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>Abstract To achieve the Sustainable Development Goals of the United Nations (UN-SDGs) in Africa, livestock breeding efficiency is a prerequisite. Human capital in the form of professional, managerial, and technical skills, improved policies and institutional operation are the key enablers of performance for the smallholder livestock sector. Capacity building is central to guarantee African livestock efficiency along the value chains and ultimately transformed livelihoods. Currently, animal breeding and genetic improvement in Africa are constrained by a serious human and institutional capacity gap. The Livestock Development Strategy for Africa (LiDESA) seeks to transform the livestock sector for accelerated and equitable growth and for enhanced contribution to socio-economic development. Sustainable livestock development in Africa could be better realized through the development of customized capacity building strategies targeting (1) relevant participatory breeding education, hands-on training, efficient technical assistance, and collaborations / partnerships aiming to address farmers’ present and future challenges, (2) enabling breeding systems for sustainable productivity, resilience of breeds, and animal seed stock management, and (3) market-led breeding solutions that are attractive for the younger and future generations. Challenges facing capacity building in livestock breeding in Africa vary between and within stakeholders of specific value chains, and farmers lack training and suitable support programmes for their breeding activities. Beyond the lack of skilled human resources, financial capacity to enforce legislation and policies in Animal Genetic Resources (AnGR) that may lead to the design and implementation of conservation and breeding programmes is a major limiting factor in most African countries. Currently, animal breeding programmes may not thrive, unless a new cohort of breeders, infrastructures, and policies are in place and backed by long-term investment plans. The main loopholes of the desired revolution reside in the current gaps and limitations of higher education and professional trainings, in terms of human resources, infrastructure, curricular content, research, and cooperation. The required capacity development could also be through people-centred community-based breeding programmes (CBBP), training of trainers, and continuous education with major inputs/roles by agricultural training institutions (e.g. Pan African University), the African Union InterAfrican Bureau for Animal Genetics Resources (AU-IBAR) and the African Animal Breeding Network (AABNet), in the form of collaborations for teaching, research, and outreach. Key capacity building intervention areas needing attention are: (1) Conservation and restoration of local animal genetic diversity, their improvement and dissemination of elite locally adapted and farmers-preferred genetics, and preservation of their natural habitat; (2) Demand-led capacity development in modern livestock breeding techniques; (3) Sustainable intensification of livestock farming practices; (4) Adaptation to extreme environmental conditions and livestock emergency guidelines and standards (LEGS); (5) Breeding for animal welfare, adaptability, and biosafety; (6) Big Data and artificial intelligence for smart farming and livestock breeding programmes; and (7) Infrastructural development and policies’ integration for technology uptake.</t>
+          <t>Generative AI presents growing opportunities across various fields, including Requirements Engineering (RE). RE, which is the backbone of software projects, drives the entire product development toward respective business goals. However, sustainability is not considered a primary need during the requirement elicitation, and as a result, software engineers are usually unable to envision the sustainability impacts of the products they build. To explore this gap, we introduce Reqwire, an AI-driven, sustainability-aware multi-agent system that (i) generates user stories from software requirement documents, (ii) enriches them with sustainability attributes, and (iii) integrates with common agile project management tools, like Jira. The system consists of specialized agents, namely as root, distributor, user story generator, and Jira. We followed a Design Science Research (DSR) approach under seven iterative cycles, incorporating feedback from an industry partner and academia to design and evaluate the Reqwire workflow. Our results indicate that Reqwire reduces manual effort by generating structured user stories, estimating story points, and assigning sustainability tags across five sustainability dimensions: environmental, economic, social, individual, and technical. The multi-agent-based framework enables integration with third-party tools, supporting consistent, systematic project tracking. Reqwire shows promise for enhancing agile workflows and promoting sustainable software practices from initial test rounds with the client.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>262fa18a25cef7c6</t>
+          <t>19da11449909222f</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Catastrophic Computation. On the Impossibility of Sustainable Artificial Intelligence</t>
+          <t>Narrative AI Strategies for Media, Ethics and Higher Education Impulse Perspectives from Practice Based Media Education</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Rehak, R.</t>
+          <t>Simon, M.; Khafif, D.</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1296,7 +1289,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lecture notes in computer science</t>
+          <t>Lecture notes in business information processing</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1311,7 +1304,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>10.1007/978-3-032-11108-1_8</t>
+          <t>10.1007/978-3-032-14518-5_18</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1347,7 +1340,7 @@
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2025/262fa18a25cef7c6.pdf</t>
+          <t>2026/19da11449909222f.pdf</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -1357,28 +1350,28 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>Artificial intelligence (AI) is currently considered a sustainability “game-changer” within and outside of academia. I argue that while there are indeed many sustainability-related use cases for AI, they are likely to have more overall drawbacks than benefits. To substantiate this claim, I differentiate three ‘AI materialities’ of the AI supply chain: first the literal materiality (e.g. water, cobalt, lithium, energy consumption etc.), second, the informational materiality (e.g. lots of data and centralised control necessary), and third, the social materiality (e.g. exploitative data work, communities harm by waste and pollution). In all materialities, effects are especially devastating for the global south while benefiting the global north. A second strong claim regarding sustainable AI circles around so-called apolitical optimisation (e.g. regarding city traffic), however the optimisation criteria (e.g. cars, bikes, emissions, commute time, health) are purely political and have to be collectively negotiated before applying AI optimisation. Hence, sustainable AI, in principle, cannot break the glass ceiling of transformation and might even distract from necessary societal change. To address that I propose to stop ‘unformation gathering’ and to apply the ‘small is beautiful’ principle. This aims to contribute to an informed academic and collective negotiation on how to (not) integrate AI into the sustainability project while avoiding to reproduce the status quo by serving hegemonic interests between useful AI use cases, techno-utopian salvation narratives, technology-centred efficiency paradigms, the exploitative and extractivist character of AI and concepts of digital degrowth. In order to discuss sustainable AI, this article draws from insights by critical data and algorithm studies, STS, transformative sustainability science, critical computer science, and public interest theory.</t>
+          <t>The transformation of narrative creation, authorship, and authenticity in the age of Generative AI is not merely a technological shift, but a cultural, epistemic, and ethical realignment. This paper argues that this transformation requires a threefold competence profile—technical proficiency, narrative design capability, and ethical reflexivity—cultivated in both higher education and corporate practice. This motive connects interdisciplinary teaching with strategic implications for communication, marketing, and oragnisational governance, bridging theory and real-world applications.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ca3c5062dc813e4f</t>
+          <t>bde689abecf48b32</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Comparative Analysis of Generative AI Performance in University Programming Courses</t>
+          <t>Practical Adoption of Green Coding: A Comparative Study Across Organizations in Finland and Globally</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Suomalainen, E.; Vanhala, E.; Ikonen, J.</t>
+          <t>Moktan, I.; Khan, M.; Oyedeji, S.; Puonti, M.; Adisa, M.; Porras, J.</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1402,7 +1395,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>10.1007/978-3-032-14518-5_16</t>
+          <t>10.1007/978-3-032-14518-5_28</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1434,38 +1427,38 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2025/ca3c5062dc813e4f.pdf</t>
+          <t>2026/bde689abecf48b32.pdf</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>openalex,s2</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>Generative artificial intelligence (GenAI) has had an impact on university education and also to the software industry. This can be seen in many different courses where GenAIs can complete exercises, exams, and even whole courses by themselves. This study aims to find out how effectively different GenAI tools can complete exercises in programming courses. Our objective is to find how GenAI’s performance varies across courses and what differences there are in results between multiple GenAI tools. During the study, five programming courses were evaluated using five different GenAI tools. These tools were able to solve 43–90% of programming assignments and 80–100% of quizzes. In practice, the result is that any of the selected GenAIs could have been used to pass the majority of all the tested course parts. Results indicate that we have to rethink how courses’ tasks are designed and that courses need to have an element where learning is verified in a controlled environment to verify that we are educating software professionals for the industry.</t>
+          <t>As the environmental impact of digital technologies gains increasing attention, green coding has emerged as a critical aspect of green software engineering. This study investigates the practical adoption of green coding practices in organizations in Finland and globally to understand how they approach green coding in their software-development workflow. This study adopts a qualitative research methodology, combining a systematic literature review and semi-structured interviews. Key findings indicate that while organizations adhere to academic-recommended coding practices such as caching, lazy loading, asynchronous processing, microservices, and content/UI optimization, industry prioritization often depends on business needs, with less emphasis on energy-efficient programming languages or priority in green coding, especially in organizations outside the EU. Interestingly, in larger organizations, such as banks, green coding initiatives are mostly driven from the bottom up and led by software engineers. This reflects a positive change. However, innovative academic proposals, such as large language model (LLM)-based assistants for recommending green libraries, remain prototypes without industrial adoption. While LLM-based assistants show potential in recommending greener libraries, their current energy demand raises questions about net sustainability. Future research should evaluate their carbon trade-offs to ensure these tools contribute positively to sustainability goals. This study underscores the need for closer collaboration between academia and industry to promote the practical adoption of effective tools, along with standardized guidelines and sustainability-oriented education, to enable the wider adoption of green coding practices.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>82ca847ef02116ef</t>
+          <t>c6a4accaccaeb577</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Digital Twin for Datacenter: HPC4AI UniTO Case Study</t>
+          <t>Capacity Building in Livestock Breeding and Genetic Improvement in Achieving UN Sustainable Development Goals for Africa</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Vaccaro, V.; Birke, R.; Meschini, S.; Tagliabue, L.; Rabellino, S.; Legazpi, P.; Andinucci, M.</t>
+          <t>Tiambo, C.; Opoola, O.; Okpeku, M.; Houaga, I.; Touko, B.; Dessie, T.</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1478,12 +1471,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lecture notes in civil engineering</t>
+          <t>Sustainable development goals series</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Springer Nature</t>
+          <t>Springer International Publishing</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1493,7 +1486,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10.1007/978-3-032-09040-9_9</t>
+          <t>10.1007/978-3-031-92076-9_28</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1525,11 +1518,11 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2025/82ca847ef02116ef.pdf</t>
+          <t>2025/c6a4accaccaeb577.pdf</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1539,24 +1532,24 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>Abstract The HPC4AI (High-Performance Computing for Artificial Intelligence) datacenter at the University of Turin’s Computer Science Department was established to meet the rapidly growing computational demands of interdisciplinary AI research. HPC4AI innovates by redefining the traditional roles of Cloud and High-Performance Computing (HPC) systems, where the Cloud provides a modern interface for HPC, and HPC acts as an accelerator for Cloud applications. To date, it has supported over 40 research projects spanning diverse fields such as astronomy, medicine, and human sciences. Additionally, HPC4AI serves as a research and development platform for exploring, developing, and testing novel datacenter technologies. It features a variety of experimental computing platforms and the first prototype of a two-phase evaporative server cooling system. This work outlines the operational management of HPC4AI, highlighting challenges, lessons learned, and key opportunities related to digital twins for datacenters.</t>
+          <t>Abstract To achieve the Sustainable Development Goals of the United Nations (UN-SDGs) in Africa, livestock breeding efficiency is a prerequisite. Human capital in the form of professional, managerial, and technical skills, improved policies and institutional operation are the key enablers of performance for the smallholder livestock sector. Capacity building is central to guarantee African livestock efficiency along the value chains and ultimately transformed livelihoods. Currently, animal breeding and genetic improvement in Africa are constrained by a serious human and institutional capacity gap. The Livestock Development Strategy for Africa (LiDESA) seeks to transform the livestock sector for accelerated and equitable growth and for enhanced contribution to socio-economic development. Sustainable livestock development in Africa could be better realized through the development of customized capacity building strategies targeting (1) relevant participatory breeding education, hands-on training, efficient technical assistance, and collaborations / partnerships aiming to address farmers’ present and future challenges, (2) enabling breeding systems for sustainable productivity, resilience of breeds, and animal seed stock management, and (3) market-led breeding solutions that are attractive for the younger and future generations. Challenges facing capacity building in livestock breeding in Africa vary between and within stakeholders of specific value chains, and farmers lack training and suitable support programmes for their breeding activities. Beyond the lack of skilled human resources, financial capacity to enforce legislation and policies in Animal Genetic Resources (AnGR) that may lead to the design and implementation of conservation and breeding programmes is a major limiting factor in most African countries. Currently, animal breeding programmes may not thrive, unless a new cohort of breeders, infrastructures, and policies are in place and backed by long-term investment plans. The main loopholes of the desired revolution reside in the current gaps and limitations of higher education and professional trainings, in terms of human resources, infrastructure, curricular content, research, and cooperation. The required capacity development could also be through people-centred community-based breeding programmes (CBBP), training of trainers, and continuous education with major inputs/roles by agricultural training institutions (e.g. Pan African University), the African Union InterAfrican Bureau for Animal Genetics Resources (AU-IBAR) and the African Animal Breeding Network (AABNet), in the form of collaborations for teaching, research, and outreach. Key capacity building intervention areas needing attention are: (1) Conservation and restoration of local animal genetic diversity, their improvement and dissemination of elite locally adapted and farmers-preferred genetics, and preservation of their natural habitat; (2) Demand-led capacity development in modern livestock breeding techniques; (3) Sustainable intensification of livestock farming practices; (4) Adaptation to extreme environmental conditions and livestock emergency guidelines and standards (LEGS); (5) Breeding for animal welfare, adaptability, and biosafety; (6) Big Data and artificial intelligence for smart farming and livestock breeding programmes; and (7) Infrastructural development and policies’ integration for technology uptake.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>b070f5d42bca7df6</t>
+          <t>262fa18a25cef7c6</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Generative AI in Simulation-Based Test Environments for Large-Scale Cyber-Physical Systems: An Industrial Study</t>
+          <t>Catastrophic Computation. On the Impossibility of Sustainable Artificial Intelligence</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sadrnezhaad, M.; López, J.; Mårtensson, T.; Varró, D.</t>
+          <t>Rehak, R.</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1584,7 +1577,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>10.1007/978-3-032-12089-2_13</t>
+          <t>10.1007/978-3-032-11108-1_8</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1609,7 +1602,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="O13" t="n">
@@ -1620,34 +1613,34 @@
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2025/b070f5d42bca7df6.pdf</t>
+          <t>2025/262fa18a25cef7c6.pdf</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>openalex,s2</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>Quality assurance for large-scale cyber-physical systems relies on sophisticated test activities using complex test environments investigated with the help of numerous types of simulators. As these systems grow, extensive resources are required to develop and maintain simulation models of hardware and software components, as well as physical environments. Meanwhile, recent advances in generative AI have led to tools that can produce executable test cases for software systems, offering potential benefits such as reducing manual efforts or increasing test coverage. However, the application of generative AI techniques to simulation-based testing of large-scale cyber-physical systems remains underexplored. To better understand this gap, this study captures practitioners'perspectives on leveraging generative AI, based on a cross-company workshop with six organizations. Our contribution is twofold: (1) detailed, experience-based insights into challenges faced by engineers, and (2) a research agenda comprising three high-priority directions: (a) AI-generated scenarios and environment models, (b) simulators and AI in CI/CD pipelines, and (c) trustworthiness in generative AI for simulation. While participants acknowledged substantial potential, they also highlighted unresolved challenges. By detailing these issues, the paper aims to guide future academia-industry collaboration towards the responsible adoption of generative AI in simulation-based testing.</t>
+          <t>Artificial intelligence (AI) is currently considered a sustainability “game-changer” within and outside of academia. I argue that while there are indeed many sustainability-related use cases for AI, they are likely to have more overall drawbacks than benefits. To substantiate this claim, I differentiate three ‘AI materialities’ of the AI supply chain: first the literal materiality (e.g. water, cobalt, lithium, energy consumption etc.), second, the informational materiality (e.g. lots of data and centralised control necessary), and third, the social materiality (e.g. exploitative data work, communities harm by waste and pollution). In all materialities, effects are especially devastating for the global south while benefiting the global north. A second strong claim regarding sustainable AI circles around so-called apolitical optimisation (e.g. regarding city traffic), however the optimisation criteria (e.g. cars, bikes, emissions, commute time, health) are purely political and have to be collectively negotiated before applying AI optimisation. Hence, sustainable AI, in principle, cannot break the glass ceiling of transformation and might even distract from necessary societal change. To address that I propose to stop ‘unformation gathering’ and to apply the ‘small is beautiful’ principle. This aims to contribute to an informed academic and collective negotiation on how to (not) integrate AI into the sustainability project while avoiding to reproduce the status quo by serving hegemonic interests between useful AI use cases, techno-utopian salvation narratives, technology-centred efficiency paradigms, the exploitative and extractivist character of AI and concepts of digital degrowth. In order to discuss sustainable AI, this article draws from insights by critical data and algorithm studies, STS, transformative sustainability science, critical computer science, and public interest theory.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>d9d8ca8edb1d6ec5</t>
+          <t>ca3c5062dc813e4f</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Integrating Artificial Intelligence with Gamification Techniques to Enhance Student Motivation and Engagement</t>
+          <t>Comparative Analysis of Generative AI Performance in University Programming Courses</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Choustoulakis, E.; Athanasopoulou, P.; Pollalis, Y.; Nikoloudakis, D.</t>
+          <t>Suomalainen, E.; Vanhala, E.; Ikonen, J.</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1660,12 +1653,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Springer proceedings in business and economics</t>
+          <t>Lecture notes in business information processing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Springer International Publishing</t>
+          <t>Springer Science+Business Media</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1675,7 +1668,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-81962-9_58</t>
+          <t>10.1007/978-3-032-14518-5_16</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1704,41 +1697,41 @@
         </is>
       </c>
       <c r="O14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2025/d9d8ca8edb1d6ec5.pdf</t>
+          <t>2025/ca3c5062dc813e4f.pdf</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>openalex,s2</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>Abstract This study investigated the integration of Artificial Intelligence (AI) with gamification techniques to enhance student motivation, engagement, and academic performance in management education. A non-probability sample of 200 undergraduate students from Greece was randomly assigned to one of two groups: an experimental group that experienced AI-driven gamification, or a control group that followed traditional instructional methods. Quantitative analysis revealed that students in the experimental group demonstrated a statistically significant increase in active participation and a statistically significant improvement in course completion rates compared to the control group. This was complemented by significant enhancements in academic performance, with final grades showing a notable difference. The AI-driven gamified environment, which included personalized challenges and real-time feedback, effectively boosted engagement and academic outcomes. Qualitative feedback from students indicated that the AI system’s ability to adapt to individual learning needs was particularly valued. Students appreciated the personalized support, which helped them stay on track and better understand complex concepts. The study highlights the potential of combining AI with gamification to create a more interactive and tailored educational experience, addressing diverse learning needs and preferences. These findings highlight the transformative impact of AI-driven gamification on management education and emphasize the critical role of courses in integrating these innovative methods. They also suggest avenues for future research to further optimize these approaches, enhancing both educational practices and student outcomes in management training.</t>
+          <t>Generative artificial intelligence (GenAI) has had an impact on university education and also to the software industry. This can be seen in many different courses where GenAIs can complete exercises, exams, and even whole courses by themselves. This study aims to find out how effectively different GenAI tools can complete exercises in programming courses. Our objective is to find how GenAI’s performance varies across courses and what differences there are in results between multiple GenAI tools. During the study, five programming courses were evaluated using five different GenAI tools. These tools were able to solve 43–90% of programming assignments and 80–100% of quizzes. In practice, the result is that any of the selected GenAIs could have been used to pass the majority of all the tested course parts. Results indicate that we have to rethink how courses’ tasks are designed and that courses need to have an element where learning is verified in a controlled environment to verify that we are educating software professionals for the industry.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>6adfc8932d140131</t>
+          <t>82ca847ef02116ef</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Micro-degree Artificial Intelligence and Society</t>
+          <t>Digital Twin for Datacenter: HPC4AI UniTO Case Study</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Lasser, J.; Pfiffner, M.</t>
+          <t>Vaccaro, V.; Birke, R.; Meschini, S.; Tagliabue, L.; Rabellino, S.; Legazpi, P.; Andinucci, M.</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1751,12 +1744,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lecture notes in computer science</t>
+          <t>Lecture notes in civil engineering</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Springer Science+Business Media</t>
+          <t>Springer Nature</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1766,7 +1759,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10.1007/978-3-032-11108-1_21</t>
+          <t>10.1007/978-3-032-09040-9_9</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1802,7 +1795,7 @@
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2025/6adfc8932d140131.pdf</t>
+          <t>2025/82ca847ef02116ef.pdf</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -1812,24 +1805,24 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>We introduce the micro-degree “Artificial Intelligence and Society” developed by the University of Graz, a novel interdisciplinary program designed to bridge the gap between technical AI knowledge and its broader societal implications. Recognising the rapid permeation of AI into all aspects of life and the limitations of traditional educational systems in addressing this transformation, the target audience of the micro-degree is both students enrolled in traditional university degrees as well as the existing workforce. The 16 ECTS curriculum, spanning two semesters, covers the technical foundations of AI systems alongside their ethical, legal, economic, and educational impacts. It features a modular structure with basic knowledge lectures, hands-on application courses – including a mandatory technical AI course and electives in ethics, law, economics, and education –, and practicals where students implement AI-based solutions to real-world problems. Here, we describe the structure and content of the micro-degree, including the learning objectives of the individual degree modules. We also provide Open Educational Resources used for teaching the (mandatory) lecture and hands-on course on the technical foundations of artificial intelligence. This micro-degree represents a crucial step towards fostering digital humanism by enabling individuals to confidently understand, apply, and shape AI’s role in society.</t>
+          <t>Abstract The HPC4AI (High-Performance Computing for Artificial Intelligence) datacenter at the University of Turin’s Computer Science Department was established to meet the rapidly growing computational demands of interdisciplinary AI research. HPC4AI innovates by redefining the traditional roles of Cloud and High-Performance Computing (HPC) systems, where the Cloud provides a modern interface for HPC, and HPC acts as an accelerator for Cloud applications. To date, it has supported over 40 research projects spanning diverse fields such as astronomy, medicine, and human sciences. Additionally, HPC4AI serves as a research and development platform for exploring, developing, and testing novel datacenter technologies. It features a variety of experimental computing platforms and the first prototype of a two-phase evaporative server cooling system. This work outlines the operational management of HPC4AI, highlighting challenges, lessons learned, and key opportunities related to digital twins for datacenters.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>36a4fda0d7a39cf4</t>
+          <t>b070f5d42bca7df6</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Reconsidering Requirements Engineering: Human–AI Collaboration in AI-Native Software Development</t>
+          <t>Generative AI in Simulation-Based Test Environments for Large-Scale Cyber-Physical Systems: An Industrial Study</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Abbasi, M.; Ihantola, P.; Mikkonen, T.; Mäkitalo, N.</t>
+          <t>Sadrnezhaad, M.; López, J.; Mårtensson, T.; Varró, D.</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1857,7 +1850,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10.1007/978-3-032-04190-6_11</t>
+          <t>10.1007/978-3-032-12089-2_13</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1886,14 +1879,14 @@
         </is>
       </c>
       <c r="O16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
         <v>2</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2025/36a4fda0d7a39cf4.pdf</t>
+          <t>2025/b070f5d42bca7df6.pdf</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -1903,24 +1896,24 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>Requirement Engineering (RE) is the foundation of successful software development. In RE, the goal is to ensure that implemented systems satisfy stakeholder needs through rigorous requirements elicitation, validation, and evaluation processes. Despite its critical role, RE continues to face persistent challenges, such as ambiguity, conflicting stakeholder needs, and the complexity of managing evolving requirements. A common view is that Artificial Intelligence (AI) has the potential to streamline the RE process, resulting in improved efficiency, accuracy, and management actions. However, using AI also introduces new concerns, such as ethical issues, biases, and lack of transparency. This paper explores how AI can enhance traditional RE practices by automating labor-intensive tasks, supporting requirement prioritization, and facilitating collaboration between stakeholders and AI systems. The paper also describes the opportunities and challenges that AI brings to RE. In particular, the vision calls for ethical practices in AI, along with a much-enhanced collaboration between academia and industry professionals. The focus should be on creating not only powerful but also trustworthy and practical AI solutions ready to adapt to the fast-paced world of software development.</t>
+          <t>Quality assurance for large-scale cyber-physical systems relies on sophisticated test activities using complex test environments investigated with the help of numerous types of simulators. As these systems grow, extensive resources are required to develop and maintain simulation models of hardware and software components, as well as physical environments. Meanwhile, recent advances in generative AI have led to tools that can produce executable test cases for software systems, offering potential benefits such as reducing manual efforts or increasing test coverage. However, the application of generative AI techniques to simulation-based testing of large-scale cyber-physical systems remains underexplored. To better understand this gap, this study captures practitioners'perspectives on leveraging generative AI, based on a cross-company workshop with six organizations. Our contribution is twofold: (1) detailed, experience-based insights into challenges faced by engineers, and (2) a research agenda comprising three high-priority directions: (a) AI-generated scenarios and environment models, (b) simulators and AI in CI/CD pipelines, and (c) trustworthiness in generative AI for simulation. While participants acknowledged substantial potential, they also highlighted unresolved challenges. By detailing these issues, the paper aims to guide future academia-industry collaboration towards the responsible adoption of generative AI in simulation-based testing.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>e8ba15cc7545622a</t>
+          <t>d9d8ca8edb1d6ec5</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Shape Computation Research at the University of Sydney</t>
+          <t>Integrating Artificial Intelligence with Gamification Techniques to Enhance Student Motivation and Engagement</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Gero, J.</t>
+          <t>Choustoulakis, E.; Athanasopoulou, P.; Pollalis, Y.; Nikoloudakis, D.</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1933,7 +1926,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mathematics and the built environment</t>
+          <t>Springer proceedings in business and economics</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1948,7 +1941,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-81623-9_15</t>
+          <t>10.1007/978-3-031-81962-9_58</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1977,14 +1970,14 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P17" t="n">
         <v>2</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2025/e8ba15cc7545622a.pdf</t>
+          <t>2025/d9d8ca8edb1d6ec5.pdf</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1994,24 +1987,24 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>This chapter provides a brief overview of the shape computation research at the University of Sydney that was carried out over a 35-year period, between 1977 and 2012, referencing 17 Ph.D theses that discuss shape computation during that period. The chapter draws distinctions between shape computation using shape grammars and other approaches that parallel, supplement and diverge from shape grammars. It introduces a variety of methods for shape computation, including those based on infinite maximal lines, artificial intelligence, learning representations, learning generation rules, logic models, qualitative representation, qualitative reasoning, algebraic representation, shape semantics, situated learning, and shape interpretation.</t>
+          <t>Abstract This study investigated the integration of Artificial Intelligence (AI) with gamification techniques to enhance student motivation, engagement, and academic performance in management education. A non-probability sample of 200 undergraduate students from Greece was randomly assigned to one of two groups: an experimental group that experienced AI-driven gamification, or a control group that followed traditional instructional methods. Quantitative analysis revealed that students in the experimental group demonstrated a statistically significant increase in active participation and a statistically significant improvement in course completion rates compared to the control group. This was complemented by significant enhancements in academic performance, with final grades showing a notable difference. The AI-driven gamified environment, which included personalized challenges and real-time feedback, effectively boosted engagement and academic outcomes. Qualitative feedback from students indicated that the AI system’s ability to adapt to individual learning needs was particularly valued. Students appreciated the personalized support, which helped them stay on track and better understand complex concepts. The study highlights the potential of combining AI with gamification to create a more interactive and tailored educational experience, addressing diverse learning needs and preferences. These findings highlight the transformative impact of AI-driven gamification on management education and emphasize the critical role of courses in integrating these innovative methods. They also suggest avenues for future research to further optimize these approaches, enhancing both educational practices and student outcomes in management training.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>fd9e23c6c69b4a0f</t>
+          <t>6adfc8932d140131</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>The Future of Cybersecurity at Sea: Human vs Human or AI vs AI?</t>
+          <t>Micro-degree Artificial Intelligence and Society</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Alop, A.</t>
+          <t>Lasser, J.; Pfiffner, M.</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -2024,12 +2017,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Signals and communication technology</t>
+          <t>Lecture notes in computer science</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Springer Vienna</t>
+          <t>Springer Science+Business Media</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -2039,7 +2032,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-87290-7_1</t>
+          <t>10.1007/978-3-032-11108-1_21</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2075,7 +2068,7 @@
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2025/fd9e23c6c69b4a0f.pdf</t>
+          <t>2025/6adfc8932d140131.pdf</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -2085,24 +2078,24 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>The digitalization of all areas of activity, including maritime, today is characterized, among other things, by two powerful influencing factors: on the one hand, artificial intelligence (AI) increasingly taking over the most important functions and develops very quickly, and on the other hand, threats and risks related to cybersecurity. The common belief, which is hard to argue against, is that the first factor is positive, because it contributes to developments, and the second is undoubtedly negative, because it hinders developments and can even inhibit them; from here, it is easy to conclude that in order to continue and accelerate progress, the positive aspects of the first factor must be contributed in every way and the fight against the effects of the second factor must be undertaken. But how realistic and consistently achievable are these two goals in interaction? True, in the light of the developments of the last years and even months, it seems that the AI “train” has started its impressive journey at high speed, and nothing can stop it. At the same time, continuing the allegory, there is still a “wagon” of cyber threats attached to this “train,” and getting rid of it or even defeating it to a sufficient extent seems problematic, at least now. The author of this chapter expresses an estimated opinion that as long as people fight against each other on both sides of the “cyber war” (“bad” guys against “good” ones), it is so to say war of attrition, where no glorious victory awaits either side. It seems to the author that it is possible to change the situation and achieve victory over the “bad” guys only if the AI itself takes over its own protection. Whether and to what extent this is possible is one of the main topics of this chapter. In the author’s opinion, there can be any truth behind this only if the AI acquires a large part of the characteristics unique to humans (values, moral principles, emotions, etc.), thanks to which it would be possible to be guided by the specific laws or rules of behavior of the AI. As a classic example, the so-called three laws of robotics, formulated by the American science fiction writer Isaac Asimov about 80 years ago, are based on the principle of avoiding harm to humans (Anderson, Asimov’s “Three Laws of Robotics” and machine metaethics, University of Connecticut, Dept. of Philosophy, Stamford, CT, https://cdn.aaai.org/Symposia/Fall/2005/FS-05-06/FS05-06-002.pdf ). In this chapter, we have analyzed whether such AI developments are possible at all and what threats and difficulties this entails in turn.</t>
+          <t>We introduce the micro-degree “Artificial Intelligence and Society” developed by the University of Graz, a novel interdisciplinary program designed to bridge the gap between technical AI knowledge and its broader societal implications. Recognising the rapid permeation of AI into all aspects of life and the limitations of traditional educational systems in addressing this transformation, the target audience of the micro-degree is both students enrolled in traditional university degrees as well as the existing workforce. The 16 ECTS curriculum, spanning two semesters, covers the technical foundations of AI systems alongside their ethical, legal, economic, and educational impacts. It features a modular structure with basic knowledge lectures, hands-on application courses – including a mandatory technical AI course and electives in ethics, law, economics, and education –, and practicals where students implement AI-based solutions to real-world problems. Here, we describe the structure and content of the micro-degree, including the learning objectives of the individual degree modules. We also provide Open Educational Resources used for teaching the (mandatory) lecture and hands-on course on the technical foundations of artificial intelligence. This micro-degree represents a crucial step towards fostering digital humanism by enabling individuals to confidently understand, apply, and shape AI’s role in society.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>dd8a0e8d30483815</t>
+          <t>03aa44aa607b0e73</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>The Impact of AI Tools on Universities’ Educational Strategies and Student Success: Sultan Qaboos University and Qatar University as a Case Study</t>
+          <t>Proposal of a framework to enhance the adoption of artificial intelligence in higher education considering sustainable development: a hybrid Lawshe-TOPSIS approach</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Al-Awadhi, T.; Al-Balushi, A.; Abdullah, M.; Abulibdeh, A.</t>
+          <t>Fernandes, R.; Nagata, V.; Filho, W.; Rampasso, I.; Ávila, L.; Silva, J.; Anholon, R.; Martins, V.</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2115,22 +2108,22 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Gulf Studies</t>
+          <t>International Journal of Educational Management</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Springer Nature</t>
+          <t>Emerald Publishing Limited</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>book-chapter</t>
+          <t>article</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>10.1007/978-981-97-9667-0_9</t>
+          <t>10.1108/ijem-08-2024-0441</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2151,49 +2144,50 @@
       <c r="M19" t="inlineStr">
         <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>hybrid</t>
         </is>
       </c>
       <c r="O19" t="n">
         <v>1</v>
       </c>
       <c r="P19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2025/dd8a0e8d30483815.pdf</t>
+          <t>2025/03aa44aa607b0e73.pdf</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>dean_provided,s2</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>Abstract Sultan Qaboos University (SQU) and Qatar University (QU) are working to adopt short- and long-term plans to ensure leadership in teaching and learning, scientific research, and community service at regional and international levels. Modern technologies, especially artificial intelligence (AI), play an important role in our lives, providing realistic opportunities to accelerate business implementation and improve the final value of work. AI plays a crucial role in taking education and research to the next level, transforming the way these organisations work and make decisions. AI can improve the traditional work of educational institutions and transform the understanding of their complexity. However, challenges remain in various aspects, whether related to the nature of our work or to the AI technologies themselves. This is still a great opportunity for every HEI. Therefore, this paper aims to analyse the potential of AI to accelerate the implementation of the strategic plans of the two universities.</t>
+          <t xml:space="preserve">
+ The main objective of this study was to propose a framework to enhance the adoption of artificial intelligence (AI) in higher education, considering sustainable development in the context of an emerging economy country.
+ The method adopted was a literature review and a survey conducted with higher education faculty members from Brazilian universities. Through an electronic questionnaire, 71 responses were collected. The data were analyzed using a hybrid Lawshe-TOPSIS approach.
+ As a result, the validated framework highlights six challenges related to the adoption of AI in higher education and nine ordered benefits of AI adoption, with the most significant for the analyzed context being the ability to process large amounts of data; sustainable solutions for industry, commerce and the economy; adaptive teaching strategies and greater scientific assistance for students and faculty.
+ The article contributes to the literature by filling a research gap and provides insights for higher education institution managers regarding AI adoption in this mode of education.
+ The research underscores the importance of aligning technological initiatives with sustainable development goals, providing a structured guide.
+</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>ccacb2251f5b4e56</t>
+          <t>36a4fda0d7a39cf4</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Thinking Along the Lines Generated by GenAI? A Systematic Mapping Study on Academic Writing</t>
+          <t>Reconsidering Requirements Engineering: Human–AI Collaboration in AI-Native Software Development</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Kaczkó, É.; Ivanjek, L.; Norz, L.; Ammenwerth, E.</t>
+          <t>Abbasi, M.; Ihantola, P.; Mikkonen, T.; Mäkitalo, N.</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2221,7 +2215,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10.1007/978-3-032-11108-1_35</t>
+          <t>10.1007/978-3-032-04190-6_11</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2246,49 +2240,49 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>hybrid</t>
+          <t>green</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P20" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2025/ccacb2251f5b4e56.pdf</t>
+          <t>2025/36a4fda0d7a39cf4.pdf</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>openalex,s2</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>The advent of generative AI (GenAI) tools in higher education challenges fundamental assumptions about academic authorship, students’ cognitive development and how writing cultivates critical thinking (CT). This systematic mapping study synthesized emerging research on how GenAI is reshaping the relationship between academic writing and CT in higher education. Drawing on 25 peer-reviewed studies published between 2023 and 2025, we analyzed conceptualizations of CT and academic writing, identified pedagogical approaches, and examined the use of GenAI tools across a range of disciplines, educational levels, and geographic contexts. Findings revealed that interest in the use of GenAI in academic writing is global and spans all disciplines and higher educational levels. However, only a minority of studies drew on robust theoretical frameworks. CT was conceptualized predominantly within a cognitive skills paradigm, while broader understandings linked to criticality and critical pedagogy were largely absent. Pedagogical models were rare and mostly untested, and educators’ perspectives were underrepresented. While GenAI was seen as supporting writing processes, its potential to foster or hinder CT remained contested. Future research should broaden conceptual foundations, include educator perspectives, and prioritize pedagogical design and evaluation. Rethinking academic writing as a transformative practice may require moving beyond the cognitive paradigm towards more participatory and ethically grounded approaches to CT.</t>
+          <t>Requirement Engineering (RE) is the foundation of successful software development. In RE, the goal is to ensure that implemented systems satisfy stakeholder needs through rigorous requirements elicitation, validation, and evaluation processes. Despite its critical role, RE continues to face persistent challenges, such as ambiguity, conflicting stakeholder needs, and the complexity of managing evolving requirements. A common view is that Artificial Intelligence (AI) has the potential to streamline the RE process, resulting in improved efficiency, accuracy, and management actions. However, using AI also introduces new concerns, such as ethical issues, biases, and lack of transparency. This paper explores how AI can enhance traditional RE practices by automating labor-intensive tasks, supporting requirement prioritization, and facilitating collaboration between stakeholders and AI systems. The paper also describes the opportunities and challenges that AI brings to RE. In particular, the vision calls for ethical practices in AI, along with a much-enhanced collaboration between academia and industry professionals. The focus should be on creating not only powerful but also trustworthy and practical AI solutions ready to adapt to the fast-paced world of software development.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>bebfc35847a401fc</t>
+          <t>e8ba15cc7545622a</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Characteristics of Romanian Online Recruitment Websites and Students’ Use</t>
+          <t>Shape Computation Research at the University of Sydney</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mardache, A.; Balasescu, M.</t>
+          <t>Gero, J.</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -2297,7 +2291,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Springer proceedings in business and economics</t>
+          <t>Mathematics and the built environment</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2312,7 +2306,7 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-51038-0_76</t>
+          <t>10.1007/978-3-031-81623-9_15</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2348,7 +2342,7 @@
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2024/bebfc35847a401fc.pdf</t>
+          <t>2025/e8ba15cc7545622a.pdf</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2358,28 +2352,28 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>Abstract Technology has increasingly changed the way human resource (HR) function achieves its goals. Organizations seek agile employees who can cope with continuous changes in a complex and uncertain environment. Effective recruitment is closely related to talent management, as organizations are interested in attracting talented people who can give a competitive advantage for the organization. The use of technology and artificial intelligence in recruitment will increasingly enable the creation of profiles that help organizations attract the best candidates for vacancies. In this context, due to its multiple advantages both for organizations and candidates, online recruitment is increasingly being used. However, it is important to be aware of the various problems associated with online recruitment and to find solutions in solving them. In this study, we conducted a content analysis of ten of the most popular recruitment websites in Romania, according to a wide range of criteria concerning the jobs on offer, but also the features of the sites. Moreover, we also conducted an exploratory survey (with a sample of 200 students) in order to identify the perception and use of these recruitment websites by students and recent university graduates. Recruitment websites are more and more complex and offer diverse and useful tools for users. Some of them already use artificial intelligence to help users identify the most compatible job. Students and recent university graduates predominantly use such websites when they are looking for a job.</t>
+          <t>This chapter provides a brief overview of the shape computation research at the University of Sydney that was carried out over a 35-year period, between 1977 and 2012, referencing 17 Ph.D theses that discuss shape computation during that period. The chapter draws distinctions between shape computation using shape grammars and other approaches that parallel, supplement and diverge from shape grammars. It introduces a variety of methods for shape computation, including those based on infinite maximal lines, artificial intelligence, learning representations, learning generation rules, logic models, qualitative representation, qualitative reasoning, algebraic representation, shape semantics, situated learning, and shape interpretation.</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>323ecbe01d1cd744</t>
+          <t>fd9e23c6c69b4a0f</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Last Tendencies in Acquiring Text Competence in the Field of Tourism. The Case of Chatbots and AI</t>
+          <t>The Future of Cybersecurity at Sea: Human vs Human or AI vs AI?</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Madueño, M.</t>
+          <t>Alop, A.</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -2388,12 +2382,12 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Springer proceedings in business and economics</t>
+          <t>Signals and communication technology</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Springer International Publishing</t>
+          <t>Springer Vienna</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2403,7 +2397,7 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-52607-7_17</t>
+          <t>10.1007/978-3-031-87290-7_1</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2432,14 +2426,14 @@
         </is>
       </c>
       <c r="O22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
         <v>2</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2024/323ecbe01d1cd744.pdf</t>
+          <t>2025/fd9e23c6c69b4a0f.pdf</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -2449,28 +2443,28 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>Abstract Our aim is to propose the usage of generative Artificial Intelligence, hereafter AI, while lecturing, as a complement to the traditional methodology, to ease technological skills acquisition in the related AI. Widely spread in all aspects of cultural life and professional praxis worldwide, it is of key importance in the training of our professional to be. In Malaga University’s Degree of Tourism, in subjects dealing with English for tourism management, we shall concentrate on chatbots aided by AI, in order to make a literary review to see the state of the question and to reflect on the needed changes to implement these tools. We shall try to outline the characteristics, possibilities, advantages and disadvantages, and the influence on both students and lecturers alike of the usage of AI in chatbots to deal with outcoming texts. Direct interaction with the tools will be highlighted. Of key importance is training lecturers in the productive use of “prompt engineering”. To conclude, handling specialised texts in the field of tourism by means of chatbots might help lecturers’ awareness and responsibility for right use to obtain semi-specialised and specialised texts in the field of tourism in order to understand, extract and evaluate its pertinence.</t>
+          <t>The digitalization of all areas of activity, including maritime, today is characterized, among other things, by two powerful influencing factors: on the one hand, artificial intelligence (AI) increasingly taking over the most important functions and develops very quickly, and on the other hand, threats and risks related to cybersecurity. The common belief, which is hard to argue against, is that the first factor is positive, because it contributes to developments, and the second is undoubtedly negative, because it hinders developments and can even inhibit them; from here, it is easy to conclude that in order to continue and accelerate progress, the positive aspects of the first factor must be contributed in every way and the fight against the effects of the second factor must be undertaken. But how realistic and consistently achievable are these two goals in interaction? True, in the light of the developments of the last years and even months, it seems that the AI “train” has started its impressive journey at high speed, and nothing can stop it. At the same time, continuing the allegory, there is still a “wagon” of cyber threats attached to this “train,” and getting rid of it or even defeating it to a sufficient extent seems problematic, at least now. The author of this chapter expresses an estimated opinion that as long as people fight against each other on both sides of the “cyber war” (“bad” guys against “good” ones), it is so to say war of attrition, where no glorious victory awaits either side. It seems to the author that it is possible to change the situation and achieve victory over the “bad” guys only if the AI itself takes over its own protection. Whether and to what extent this is possible is one of the main topics of this chapter. In the author’s opinion, there can be any truth behind this only if the AI acquires a large part of the characteristics unique to humans (values, moral principles, emotions, etc.), thanks to which it would be possible to be guided by the specific laws or rules of behavior of the AI. As a classic example, the so-called three laws of robotics, formulated by the American science fiction writer Isaac Asimov about 80 years ago, are based on the principle of avoiding harm to humans (Anderson, Asimov’s “Three Laws of Robotics” and machine metaethics, University of Connecticut, Dept. of Philosophy, Stamford, CT, https://cdn.aaai.org/Symposia/Fall/2005/FS-05-06/FS05-06-002.pdf ). In this chapter, we have analyzed whether such AI developments are possible at all and what threats and difficulties this entails in turn.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>e799f9736c02ac60</t>
+          <t>dd8a0e8d30483815</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Overcoming the Long Shadow of the Past: Defense AI in Japan</t>
+          <t>The Impact of AI Tools on Universities’ Educational Strategies and Student Success: Sultan Qaboos University and Qatar University as a Case Study</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Tsuchiya, M.</t>
+          <t>Al-Awadhi, T.; Al-Balushi, A.; Abdullah, M.; Abulibdeh, A.</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -2479,12 +2473,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Contributions to security and defence studies</t>
+          <t>Gulf Studies</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Springer International Publishing</t>
+          <t>Springer Nature</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2494,7 +2488,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-58649-1_22</t>
+          <t>10.1007/978-981-97-9667-0_9</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2523,14 +2517,14 @@
         </is>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2024/e799f9736c02ac60.pdf</t>
+          <t>2025/dd8a0e8d30483815.pdf</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -2540,28 +2534,28 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>Abstract Since the end of World War II, Japan has not had a full-fledged military, but only Self-Defense Forces (SDF) for the sole purpose of “exclusively defensive defense.” Hesitancy exists in society, especially in academia, to research and develop technologies that could be diverted to military use. This has created a long shadow of the past in which public opinion, strategic culture, and the academic-industrial ecosystem mutually reinforce each other not to directly address defense technologies, though Japan is often recognized as one of the most technologically advanced countries. However, with the recent deterioration of the national security environment around Japan, such hesitance is weakening, and research and development of technologies that can be applied to defense purposes is now being conducted, also in cooperation with partners like the United States, the United Kingdom, and others. Discussions about artificial intelligence (AI) for defense purposes began in earnest around 2022, with descriptions found in government and defense documents, and budget appropriations beginning to be made. However, the budget size is miniscule and no special organization for defense AI exists. In addition, there is no plan to use defense AI in earnest in defense operations, and it is merely positioned as one of the technologies that are attracting widespread attention. The defense industry is working on AI across the board, but Japan’s defense industry has a large proportion of civilian demand, and there are aspects of the industry that are not necessarily for defense use. If necessary, they will be applied to defense applications, but they are not actively promoted as AI for defense. Attempts to deepen the knowledge of AI among SDF personnel have only just begun.</t>
+          <t>Abstract Sultan Qaboos University (SQU) and Qatar University (QU) are working to adopt short- and long-term plans to ensure leadership in teaching and learning, scientific research, and community service at regional and international levels. Modern technologies, especially artificial intelligence (AI), play an important role in our lives, providing realistic opportunities to accelerate business implementation and improve the final value of work. AI plays a crucial role in taking education and research to the next level, transforming the way these organisations work and make decisions. AI can improve the traditional work of educational institutions and transform the understanding of their complexity. However, challenges remain in various aspects, whether related to the nature of our work or to the AI technologies themselves. This is still a great opportunity for every HEI. Therefore, this paper aims to analyse the potential of AI to accelerate the implementation of the strategic plans of the two universities.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>148d777c7af8aaae</t>
+          <t>ccacb2251f5b4e56</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Reimagining Extreme Event Scenarios: The Aesthetic Visualisation of Climate Uncertainty to Enhance Preparedness</t>
+          <t>Thinking Along the Lines Generated by GenAI? A Systematic Mapping Study on Academic Writing</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Favero, D.; Thurow, S.; Pagnucco, M.; Frohne, U.</t>
+          <t>Kaczkó, É.; Ivanjek, L.; Norz, L.; Ammenwerth, E.</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -2570,12 +2564,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Arts, research, innovation and society</t>
+          <t>Lecture notes in computer science</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Springer International Publishing</t>
+          <t>Springer Science+Business Media</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -2585,7 +2579,7 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-56114-6_2</t>
+          <t>10.1007/978-3-032-11108-1_35</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2617,11 +2611,11 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2024/148d777c7af8aaae.pdf</t>
+          <t>2025/ccacb2251f5b4e56.pdf</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -2631,24 +2625,24 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>Abstract Responding to the rapidly escalating climate emergency, this chapter outlines transformative multidisciplinary research centred on the visualisation of unpredictable extreme event scenarios. It proposes a unique, scientifically grounded artistic approach to one of the world’s most immediate challenges—preparing communities for extreme climate events, such as firestorms and flash floods. As preparedness is a function of prior threat experience, it argues that visualising threat scenarios in advance can be a key to surviving and adapting in an era of increasing climate instability. This approach can enable communities to viscerally experience and rehearse threat perception, situational awareness, adaptive decision making and dynamic response to unexpected life-threatening extreme events. Using experimental case studies at The University of New South Wales’s iCinema Research Centre and international benchmarks, this chapter explores how advances in immersive visualisation and artificial intelligence aesthetics can be integrated to provide a framework that enables the virtual prototyping of unforeseen geolocated climate scenarios to facilitate readiness in the face of accelerating climate uncertainty.</t>
+          <t>The advent of generative AI (GenAI) tools in higher education challenges fundamental assumptions about academic authorship, students’ cognitive development and how writing cultivates critical thinking (CT). This systematic mapping study synthesized emerging research on how GenAI is reshaping the relationship between academic writing and CT in higher education. Drawing on 25 peer-reviewed studies published between 2023 and 2025, we analyzed conceptualizations of CT and academic writing, identified pedagogical approaches, and examined the use of GenAI tools across a range of disciplines, educational levels, and geographic contexts. Findings revealed that interest in the use of GenAI in academic writing is global and spans all disciplines and higher educational levels. However, only a minority of studies drew on robust theoretical frameworks. CT was conceptualized predominantly within a cognitive skills paradigm, while broader understandings linked to criticality and critical pedagogy were largely absent. Pedagogical models were rare and mostly untested, and educators’ perspectives were underrepresented. While GenAI was seen as supporting writing processes, its potential to foster or hinder CT remained contested. Future research should broaden conceptual foundations, include educator perspectives, and prioritize pedagogical design and evaluation. Rethinking academic writing as a transformative practice may require moving beyond the cognitive paradigm towards more participatory and ethically grounded approaches to CT.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>5beff436c4263cda</t>
+          <t>bebfc35847a401fc</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Retrieval Augmented Large Language Model Chatbots in Higher Education: A Study on University Open Days</t>
+          <t>Characteristics of Romanian Online Recruitment Websites and Students’ Use</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Shanthakumar, A.; Fassihi-Tash, F.; Lotfi, A.; Bird, J.</t>
+          <t>Mardache, A.; Balasescu, M.</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -2661,12 +2655,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Advances in intelligent systems and computing</t>
+          <t>Springer proceedings in business and economics</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Springer Nature</t>
+          <t>Springer International Publishing</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -2676,7 +2670,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-78857-4_3</t>
+          <t>10.1007/978-3-031-51038-0_76</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2701,41 +2695,45 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="O25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2024/5beff436c4263cda.pdf</t>
+          <t>2024/bebfc35847a401fc.pdf</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>openalex,s2</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="n"/>
+          <t>openalex</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Technology has increasingly changed the way human resource (HR) function achieves its goals. Organizations seek agile employees who can cope with continuous changes in a complex and uncertain environment. Effective recruitment is closely related to talent management, as organizations are interested in attracting talented people who can give a competitive advantage for the organization. The use of technology and artificial intelligence in recruitment will increasingly enable the creation of profiles that help organizations attract the best candidates for vacancies. In this context, due to its multiple advantages both for organizations and candidates, online recruitment is increasingly being used. However, it is important to be aware of the various problems associated with online recruitment and to find solutions in solving them. In this study, we conducted a content analysis of ten of the most popular recruitment websites in Romania, according to a wide range of criteria concerning the jobs on offer, but also the features of the sites. Moreover, we also conducted an exploratory survey (with a sample of 200 students) in order to identify the perception and use of these recruitment websites by students and recent university graduates. Recruitment websites are more and more complex and offer diverse and useful tools for users. Some of them already use artificial intelligence to help users identify the most compatible job. Students and recent university graduates predominantly use such websites when they are looking for a job.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>a366da3974dd03f0</t>
+          <t>323ecbe01d1cd744</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Ruffle&amp;amp;Riley: Insights from Designing and Evaluating a Large Language Model-Based Conversational Tutoring System</t>
+          <t>Last Tendencies in Acquiring Text Competence in the Field of Tourism. The Case of Chatbots and AI</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Schmucker, R.; Xia, M.; Azaria, A.; Mitchell, T.</t>
+          <t>Madueño, M.</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -2748,12 +2746,12 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lecture notes in computer science</t>
+          <t>Springer proceedings in business and economics</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Springer Science+Business Media</t>
+          <t>Springer International Publishing</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2763,7 +2761,7 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-64302-6_6</t>
+          <t>10.1007/978-3-031-52607-7_17</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2792,14 +2790,14 @@
         </is>
       </c>
       <c r="O26" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="P26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2024/a366da3974dd03f0.pdf</t>
+          <t>2024/323ecbe01d1cd744.pdf</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -2809,24 +2807,24 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>Abstract Conversational tutoring systems (CTSs) offer learning experiences through interactions based on natural language. They are recognized for promoting cognitive engagement and improving learning outcomes, especially in reasoning tasks. Nonetheless, the cost associated with authoring CTS content is a major obstacle to widespread adoption and to research on effective instructional design. In this paper, we discuss and evaluate a novel type of CTS that leverages recent advances in large language models (LLMs) in two ways: First, the system enables AI-assisted content authoring by inducing an easily editable tutoring script automatically from a lesson text. Second, the system automates the script orchestration in a learning-by-teaching format via two LLM-based agents (Ruffle&amp;amp;Riley) acting as a student and a professor. The system allows for free-form conversations that follow the ITS-typical inner and outer loop structure. We evaluate Ruffle&amp;amp;Riley’s ability to support biology lessons in two between-subject online user studies ( $$N = 200$$ &lt;mml:math xmlns:mml="http://www.w3.org/1998/Math/MathML"&gt; &lt;mml:mrow&gt; &lt;mml:mi&gt;N&lt;/mml:mi&gt; &lt;mml:mo&gt;=&lt;/mml:mo&gt; &lt;mml:mn&gt;200&lt;/mml:mn&gt; &lt;/mml:mrow&gt; &lt;/mml:math&gt; ) comparing the system to simpler QA chatbots and reading activity. Analyzing system usage patterns, pre/post-test scores and user experience surveys, we find that Ruffle&amp;amp;Riley users report high levels of engagement, understanding and perceive the offered support as helpful. Even though Ruffle&amp;amp;Riley users require more time to complete the activity, we did not find significant differences in short-term learning gains over the reading activity. Our system architecture and user study provide various insights for designers of future CTSs. We further open-source our system to support ongoing research on effective instructional design of LLM-based learning technologies.</t>
+          <t>Abstract Our aim is to propose the usage of generative Artificial Intelligence, hereafter AI, while lecturing, as a complement to the traditional methodology, to ease technological skills acquisition in the related AI. Widely spread in all aspects of cultural life and professional praxis worldwide, it is of key importance in the training of our professional to be. In Malaga University’s Degree of Tourism, in subjects dealing with English for tourism management, we shall concentrate on chatbots aided by AI, in order to make a literary review to see the state of the question and to reflect on the needed changes to implement these tools. We shall try to outline the characteristics, possibilities, advantages and disadvantages, and the influence on both students and lecturers alike of the usage of AI in chatbots to deal with outcoming texts. Direct interaction with the tools will be highlighted. Of key importance is training lecturers in the productive use of “prompt engineering”. To conclude, handling specialised texts in the field of tourism by means of chatbots might help lecturers’ awareness and responsibility for right use to obtain semi-specialised and specialised texts in the field of tourism in order to understand, extract and evaluate its pertinence.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2c028fbe91e54d72</t>
+          <t>e799f9736c02ac60</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Survival of the Smartest? Defense AI in Ukraine</t>
+          <t>Overcoming the Long Shadow of the Past: Defense AI in Japan</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Goncharuk, V.</t>
+          <t>Tsuchiya, M.</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -2854,7 +2852,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-58649-1_17</t>
+          <t>10.1007/978-3-031-58649-1_22</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2883,14 +2881,14 @@
         </is>
       </c>
       <c r="O27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
         <v>2</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2024/2c028fbe91e54d72.pdf</t>
+          <t>2024/e799f9736c02ac60.pdf</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2900,28 +2898,28 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>Abstract Before Russia’s invasion in February 2022, Ukraine boasted a thriving ecosystem for producing artificial intelligence (AI) solutions, leading Eastern Europe in AI company numbers and hosting R&amp;amp;D offices of multinational giants like Amazon and Google. Despite this, Ukraine’s defense sector lagged in AI adoption due to a focus on traditional hardware. The conflict between Russia and Ukraine has transformed the situation, with both sides employing AI in geospatial intelligence, unmanned systems, military training, and cyber warfare, making this conflict the first to feature AI competition as a critical factor. Ukraine’s resilience during the war has relied on active use of awareness systems, volunteer initiatives, open-source platforms, and decentralized asset utilization. The government has begun systematically formulating defense AI policy initiatives and fostering a new ecosystem while civil IT companies shift focus towards dual-use products and talent acquisition in AI. Current defense AI development priorities include AI for unmanned systems, to combat disinformation and support cybersecurity and to advance logistics and mine detection. In parallel, the war has advanced closer cooperation between universities and the military sector, also in view of advancing training and developing AI-enhanced simulation-based training. Overall, the conflict serves as a testing ground for foreign AI developers, prompting reevaluation of regulatory assumptions and the need for war-proof defense AI solutions.</t>
+          <t>Abstract Since the end of World War II, Japan has not had a full-fledged military, but only Self-Defense Forces (SDF) for the sole purpose of “exclusively defensive defense.” Hesitancy exists in society, especially in academia, to research and develop technologies that could be diverted to military use. This has created a long shadow of the past in which public opinion, strategic culture, and the academic-industrial ecosystem mutually reinforce each other not to directly address defense technologies, though Japan is often recognized as one of the most technologically advanced countries. However, with the recent deterioration of the national security environment around Japan, such hesitance is weakening, and research and development of technologies that can be applied to defense purposes is now being conducted, also in cooperation with partners like the United States, the United Kingdom, and others. Discussions about artificial intelligence (AI) for defense purposes began in earnest around 2022, with descriptions found in government and defense documents, and budget appropriations beginning to be made. However, the budget size is miniscule and no special organization for defense AI exists. In addition, there is no plan to use defense AI in earnest in defense operations, and it is merely positioned as one of the technologies that are attracting widespread attention. The defense industry is working on AI across the board, but Japan’s defense industry has a large proportion of civilian demand, and there are aspects of the industry that are not necessarily for defense use. If necessary, they will be applied to defense applications, but they are not actively promoted as AI for defense. Attempts to deepen the knowledge of AI among SDF personnel have only just begun.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ae87b25ad2e4631c</t>
+          <t>148d777c7af8aaae</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Future of Learning and Education</t>
+          <t>Reimagining Extreme Event Scenarios: The Aesthetic Visualisation of Climate Uncertainty to Enhance Preparedness</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Varghese, S.</t>
+          <t>Favero, D.; Thurow, S.; Pagnucco, M.; Frohne, U.</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -2930,7 +2928,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Future of business and finance</t>
+          <t>Arts, research, innovation and society</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2945,7 +2943,7 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-36382-5_16</t>
+          <t>10.1007/978-3-031-56114-6_2</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2974,14 +2972,14 @@
         </is>
       </c>
       <c r="O28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P28" t="n">
         <v>2</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2023/ae87b25ad2e4631c.pdf</t>
+          <t>2024/148d777c7af8aaae.pdf</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -2991,28 +2989,28 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>Abstract According to “A Scorecard for Humanity,” a report from the Copenhagen Consensus Center, our world gains every time an individual is educated, and our world pays a price when people go illiterate. In the future, those regions and nations of the world that manage to educate its people would gain, whereas those that do not pay much attention to this crucial aspect would continue to suffer losses, hidden in plain sight. Hence, by 2050, we suggest that though the world would have made tremendous progress in basic education, illiteracy would persist with almost 500 million uneducated in the world. Illiteracy shall be most concentrated in the regions of Africa and South Asia, whereas most other nations would move toward a total eradication. However, there would also be a systemic change in the higher education sector across the globe, as the age cohort of 18 to 24 years in Europe would shrink, but in South Asia and Africa, this would continue to grow. There would also be a disruption of the current pedagogic and regimental learning systems toward flatter, flexible, and open systems based on research in learning sciences. Technology would also come by to play a larger role, where education would be driven by artificial intelligence (AI) and big data—resulting in complete personalization of curriculum and methodology focusing on each individual's minute needs.</t>
+          <t>Abstract Responding to the rapidly escalating climate emergency, this chapter outlines transformative multidisciplinary research centred on the visualisation of unpredictable extreme event scenarios. It proposes a unique, scientifically grounded artistic approach to one of the world’s most immediate challenges—preparing communities for extreme climate events, such as firestorms and flash floods. As preparedness is a function of prior threat experience, it argues that visualising threat scenarios in advance can be a key to surviving and adapting in an era of increasing climate instability. This approach can enable communities to viscerally experience and rehearse threat perception, situational awareness, adaptive decision making and dynamic response to unexpected life-threatening extreme events. Using experimental case studies at The University of New South Wales’s iCinema Research Centre and international benchmarks, this chapter explores how advances in immersive visualisation and artificial intelligence aesthetics can be integrated to provide a framework that enables the virtual prototyping of unforeseen geolocated climate scenarios to facilitate readiness in the face of accelerating climate uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2ad51015436ad076</t>
+          <t>5beff436c4263cda</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Investigating the Role of ChatGPT in Supporting Text-Based Programming Education for Students and Teachers</t>
+          <t>Retrieval Augmented Large Language Model Chatbots in Higher Education: A Study on University Open Days</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Wieser, M.; Schöffmann, K.; Stefanics, D.; Bollin, A.; Pasterk, S.</t>
+          <t>Shanthakumar, A.; Fassihi-Tash, F.; Lotfi, A.; Bird, J.</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -3021,12 +3019,12 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lecture notes in computer science</t>
+          <t>Advances in intelligent systems and computing</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Springer Science+Business Media</t>
+          <t>Springer Nature</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3036,7 +3034,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-44900-0_4</t>
+          <t>10.1007/978-3-031-78857-4_3</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3061,49 +3059,45 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>hybrid</t>
+          <t>green</t>
         </is>
       </c>
       <c r="O29" t="n">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="P29" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2023/2ad51015436ad076.pdf</t>
+          <t>2024/5beff436c4263cda.pdf</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>openalex</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="inlineStr">
-        <is>
-          <t>Abstract Teaching text-based programming poses significant challenges in both school and university contexts. This study explores the potential of ChatGPT as a sustainable didactic tool to support students, freshmen, and teachers. By focusing on a beginner’s course with examples also relevant to vocational schools, we investigated three research questions. First, the extent to which ChatGPT assists students in solving and understanding initial examples; secondly, the feasibility of teachers utilizing the chatbot for grading student solutions; and finally, the additional support ChatGPT provides in terms of teaching. Our findings demonstrate that ChatGPT offers valuable guidance for teachers in terms of assessment and grading and aids students in understanding and optimizing their solutions.</t>
-        </is>
-      </c>
+          <t>openalex,s2</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>135634b3c7c31d5d</t>
+          <t>a366da3974dd03f0</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Judicial Decision-Making in the Age of Artificial Intelligence</t>
+          <t>Ruffle&amp;amp;Riley: Insights from Designing and Evaluating a Large Language Model-Based Conversational Tutoring System</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Gravett, W.</t>
+          <t>Schmucker, R.; Xia, M.; Azaria, A.; Mitchell, T.</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -3112,12 +3106,12 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Law, governance and technology series</t>
+          <t>Lecture notes in computer science</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Springer International Publishing</t>
+          <t>Springer Science+Business Media</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3127,7 +3121,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-41264-6_15</t>
+          <t>10.1007/978-3-031-64302-6_6</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3156,14 +3150,14 @@
         </is>
       </c>
       <c r="O30" t="n">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="P30" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2023/135634b3c7c31d5d.pdf</t>
+          <t>2024/a366da3974dd03f0.pdf</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3173,28 +3167,28 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>Abstract Artificial intelligence (AI) has become a pervasive presence in almost every aspect of society and business: from assigning credit scores to people, to identifying the best candidates for an employment position, to ranking applicants for admission to university. One of the most striking innovations in the United States criminal justice system in the last three decades has been the introduction of risk-assessment software, powered by sophisticated algorithms, to predict whether individual offenders are likely to re-offend. The focus of this contribution is on the use of these risk-assessment tools in criminal sentencing. Apart from the broader social, ethical and legal considerations, to date, not much is known about how perceptions of technology influence cognition in decision-making, particularly in the legal context. What research does demonstrate is that humans are inclined to trust algorithms as objective, and, as such, as unobjectionable. This contribution examines two phenomena in this regard: (i) the “technology effect”—the human tendency towards excessive optimism when making decisions involving technology; and (ii) “automation bias”—the phenomenon whereby judges accept the recommendations of an automated decision-making system, and cease searching for confirmatory evidence, perhaps even transferring responsibility for decision-making onto the machine.</t>
+          <t>Abstract Conversational tutoring systems (CTSs) offer learning experiences through interactions based on natural language. They are recognized for promoting cognitive engagement and improving learning outcomes, especially in reasoning tasks. Nonetheless, the cost associated with authoring CTS content is a major obstacle to widespread adoption and to research on effective instructional design. In this paper, we discuss and evaluate a novel type of CTS that leverages recent advances in large language models (LLMs) in two ways: First, the system enables AI-assisted content authoring by inducing an easily editable tutoring script automatically from a lesson text. Second, the system automates the script orchestration in a learning-by-teaching format via two LLM-based agents (Ruffle&amp;amp;Riley) acting as a student and a professor. The system allows for free-form conversations that follow the ITS-typical inner and outer loop structure. We evaluate Ruffle&amp;amp;Riley’s ability to support biology lessons in two between-subject online user studies ( $$N = 200$$ &lt;mml:math xmlns:mml="http://www.w3.org/1998/Math/MathML"&gt; &lt;mml:mrow&gt; &lt;mml:mi&gt;N&lt;/mml:mi&gt; &lt;mml:mo&gt;=&lt;/mml:mo&gt; &lt;mml:mn&gt;200&lt;/mml:mn&gt; &lt;/mml:mrow&gt; &lt;/mml:math&gt; ) comparing the system to simpler QA chatbots and reading activity. Analyzing system usage patterns, pre/post-test scores and user experience surveys, we find that Ruffle&amp;amp;Riley users report high levels of engagement, understanding and perceive the offered support as helpful. Even though Ruffle&amp;amp;Riley users require more time to complete the activity, we did not find significant differences in short-term learning gains over the reading activity. Our system architecture and user study provide various insights for designers of future CTSs. We further open-source our system to support ongoing research on effective instructional design of LLM-based learning technologies.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>7947ac0d82ac46e9</t>
+          <t>2c028fbe91e54d72</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Metabolism in Crisis? A New Interplay Between Physiology and Ecology</t>
+          <t>Survival of the Smartest? Defense AI in Ukraine</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bognon-Küss, C.</t>
+          <t>Goncharuk, V.</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -3203,12 +3197,12 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>History, philosophy and theory of the life sciences</t>
+          <t>Contributions to security and defence studies</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Springer Nature (Netherlands)</t>
+          <t>Springer International Publishing</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3218,7 +3212,7 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-12604-8_11</t>
+          <t>10.1007/978-3-031-58649-1_17</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3247,14 +3241,14 @@
         </is>
       </c>
       <c r="O31" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="P31" t="n">
         <v>2</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2023/7947ac0d82ac46e9.pdf</t>
+          <t>2024/2c028fbe91e54d72.pdf</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3264,24 +3258,24 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>Abstract This chapter investigates the hybrid relationships between metabolism, broadly and a-historically understood as the set of processes through which alien matter is made homogeneous to that of the organism, and forms of vitalism from the eighteenth century on. While metabolic processes have long been modeled in a reductionist fashion as a straightforward function of repair and expansion of a given structure (either chemically, or mechanistically), a challenging vitalist view has characterized metabolism as a creative, organizing, vital faculty. I suggest that this tension was overcome in Claude Bernard’s works on “indirect nutrition”, in which nutrition, rightly conceived as a general vital phenomenon common to plants and animals, was both characterized as an instance of the general physico-chemical determinism of all phenomena and as the sign and condition of the “freedom and independence” of the organism with respect to the environment. I propose that Bernard’s theory of indirect nutrition was central in the elaboration of his general physiology and has, at the same time, underpinned a self-centered view of biological identity in which the organism creates itself continuously at the detriment of its external milieu . I further argue that this conception of biological individuality as metabolically constructed has since, and paradoxically, supported a view in which the organism appears as an autonomous and self-creating entity. I then contrast this classical view of the metabolic autonomy of the organism with the challenges raised by microbiome studies and suggest that these emerging fields contribute to sketch an ecological conception of the organism and its metabolism through the reconceptualization of its relationship with the environment. The recent focus on a “microbiota – host metabolism” axis contributes to shift the focus away from the classical concept of organism, somehow externalizing vitalism out of the autonomous individual in favor of an ecological, collaborative, and interactionist view of the living.</t>
+          <t>Abstract Before Russia’s invasion in February 2022, Ukraine boasted a thriving ecosystem for producing artificial intelligence (AI) solutions, leading Eastern Europe in AI company numbers and hosting R&amp;amp;D offices of multinational giants like Amazon and Google. Despite this, Ukraine’s defense sector lagged in AI adoption due to a focus on traditional hardware. The conflict between Russia and Ukraine has transformed the situation, with both sides employing AI in geospatial intelligence, unmanned systems, military training, and cyber warfare, making this conflict the first to feature AI competition as a critical factor. Ukraine’s resilience during the war has relied on active use of awareness systems, volunteer initiatives, open-source platforms, and decentralized asset utilization. The government has begun systematically formulating defense AI policy initiatives and fostering a new ecosystem while civil IT companies shift focus towards dual-use products and talent acquisition in AI. Current defense AI development priorities include AI for unmanned systems, to combat disinformation and support cybersecurity and to advance logistics and mine detection. In parallel, the war has advanced closer cooperation between universities and the military sector, also in view of advancing training and developing AI-enhanced simulation-based training. Overall, the conflict serves as a testing ground for foreign AI developers, prompting reevaluation of regulatory assumptions and the need for war-proof defense AI solutions.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>3827a11b5b949e39</t>
+          <t>ae87b25ad2e4631c</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Rebuilding After War and Genocide: Learning with and from Refugees in the Transnational Digital Classroom</t>
+          <t>Future of Learning and Education</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Brill-Carlat, M.; Höhn, M.</t>
+          <t>Varghese, S.</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -3294,7 +3288,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Political pedagogies</t>
+          <t>Future of business and finance</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3309,7 +3303,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-12350-4_22</t>
+          <t>10.1007/978-3-031-36382-5_16</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3338,14 +3332,14 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P32" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2023/3827a11b5b949e39.pdf</t>
+          <t>2023/ae87b25ad2e4631c.pdf</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3355,24 +3349,24 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>Abstract The Covid-19 emergency spurred a flurry of teaching innovations as higher education institutions turned to online or blended learning models, and as international collaborations have moved nearly entirely online. These circumstances inspired us to revisit the digital transatlantic seminar, “Germany 1945: History and Memory in Germany after WWII,” taught by Höhn in Spring 2018 to a group of seven Vassar students (Brill-Carlat among them) and six advanced high-school students—between the ages of 17 and 22—who had come to Berlin as asylum seekers from Syria, Iraq, and Afghanistan. The course dealt with history and memory of World War II and the Holocaust in Germany. As such, it reflected a core commitment of the Consortium on Forced Migration, Displacement, and Education (CFMDE), founded by Höhn at Vassar and partners (Bard, Bennington, Sarah Lawrence, the New School, and the Council for European Studies): the importance of providing opportunities for our undergraduate students to learn with and from refugees and displaced individuals if they are to understand and tackle the global, multidimensional challenges of forced migration. As institutional resistance to digital teaching necessarily vanished with the Covid-19 pandemic in Spring 2020 and the direction of future online-learning policies is up for debate, we revisit the 2018 class to examine lessons learned and how this project points the way to another digital venture: digitally “hosting” displaced scholars at liberal arts campuses.</t>
+          <t>Abstract According to “A Scorecard for Humanity,” a report from the Copenhagen Consensus Center, our world gains every time an individual is educated, and our world pays a price when people go illiterate. In the future, those regions and nations of the world that manage to educate its people would gain, whereas those that do not pay much attention to this crucial aspect would continue to suffer losses, hidden in plain sight. Hence, by 2050, we suggest that though the world would have made tremendous progress in basic education, illiteracy would persist with almost 500 million uneducated in the world. Illiteracy shall be most concentrated in the regions of Africa and South Asia, whereas most other nations would move toward a total eradication. However, there would also be a systemic change in the higher education sector across the globe, as the age cohort of 18 to 24 years in Europe would shrink, but in South Asia and Africa, this would continue to grow. There would also be a disruption of the current pedagogic and regimental learning systems toward flatter, flexible, and open systems based on research in learning sciences. Technology would also come by to play a larger role, where education would be driven by artificial intelligence (AI) and big data—resulting in complete personalization of curriculum and methodology focusing on each individual's minute needs.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>c81bf633e42c7f19</t>
+          <t>2ad51015436ad076</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Survey of AI Tool Usage in Programming Course: Early Observations</t>
+          <t>Investigating the Role of ChatGPT in Supporting Text-Based Programming Education for Students and Teachers</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Saari, M.; Rantanen, P.; Nurminen, M.; Kilamo, T.; Systä, K.; Abrahamsson, P.</t>
+          <t>Wieser, M.; Schöffmann, K.; Stefanics, D.; Bollin, A.; Pasterk, S.</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -3385,7 +3379,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lecture notes in business information processing</t>
+          <t>Lecture notes in computer science</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3400,7 +3394,7 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-48550-3_18</t>
+          <t>10.1007/978-3-031-44900-0_4</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3429,14 +3423,14 @@
         </is>
       </c>
       <c r="O33" t="n">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="P33" t="n">
         <v>2</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2023/c81bf633e42c7f19.pdf</t>
+          <t>2023/2ad51015436ad076.pdf</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -3446,24 +3440,24 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>Abstract This study explores the role of artificial intelligence (AI) in university teaching, with a focus on the teaching of programming. Despite the growing use of AI in education, both students and teachers often struggle to understand its role and implications. To address this gap, we conducted a survey of a wide group of students (n = 200) to assess their experiences and perspectives on the use of AI in programming education. The survey results suggest that AI is becoming increasingly involved in university teaching, particularly in the teaching of programming. However, students require guidance from teachers in order to use AI tools effectively in their studies. The study concludes that the goal of teaching programming should be to guide students in the responsible use of AI. Overall, the study highlights the need for greater awareness and understanding of AI in university teaching and the fact that teachers have an important role to play in providing guidance to students on the responsible use of AI tools.</t>
+          <t>Abstract Teaching text-based programming poses significant challenges in both school and university contexts. This study explores the potential of ChatGPT as a sustainable didactic tool to support students, freshmen, and teachers. By focusing on a beginner’s course with examples also relevant to vocational schools, we investigated three research questions. First, the extent to which ChatGPT assists students in solving and understanding initial examples; secondly, the feasibility of teachers utilizing the chatbot for grading student solutions; and finally, the additional support ChatGPT provides in terms of teaching. Our findings demonstrate that ChatGPT offers valuable guidance for teachers in terms of assessment and grading and aids students in understanding and optimizing their solutions.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>96a698008602b3d7</t>
+          <t>135634b3c7c31d5d</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>The Role of Educational Interventions in Facing Social Media Threats: Overarching Principles of the COURAGE Project</t>
+          <t>Judicial Decision-Making in the Age of Artificial Intelligence</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Taibi, D.; Börsting, J.; Hoppe, U.; Ognibene, D.; Hernández-Leo, D.; Eimler, S.; Kruschwitz, U.</t>
+          <t>Gravett, W.</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -3476,12 +3470,12 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Communications in computer and information science</t>
+          <t>Law, governance and technology series</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Springer Science+Business Media</t>
+          <t>Springer International Publishing</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -3491,7 +3485,7 @@
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-29800-4_25</t>
+          <t>10.1007/978-3-031-41264-6_15</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3520,14 +3514,14 @@
         </is>
       </c>
       <c r="O34" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="P34" t="n">
         <v>2</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2023/96a698008602b3d7.pdf</t>
+          <t>2023/135634b3c7c31d5d.pdf</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3537,42 +3531,42 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>Abstract Social media are offering new opportunities for communication and interaction way beyond what was possible only a few years ago. However, social media are also virtual spaces where young people are exposed to a variety of threats. Digital addiction, discrimination, hate speech, misinformation, polarization as well as manipulative influences of algorithms, body stereotyping, and cyberbullying are examples of challenges that find fertile ground on social media. Educators and students are not adequately prepared to face these challenges. To this aim, the COURAGE project, presented in this paper, introduces new tools and learning methodologies that can be adopted within higher education learning paths to train educators to deal with social media threats. The overarching principles of the COURAGE project leverage the most recent advances in the fields of artificial intelligence and in the educational domain paired with social and media psychological insights to support the development of the COURAGE ecosystem. The results of the experiments currently implemented with teachers and students of secondary schools as well as the impact of the COURAGE project on societal changes and ethical questions are presented and discussed.</t>
+          <t>Abstract Artificial intelligence (AI) has become a pervasive presence in almost every aspect of society and business: from assigning credit scores to people, to identifying the best candidates for an employment position, to ranking applicants for admission to university. One of the most striking innovations in the United States criminal justice system in the last three decades has been the introduction of risk-assessment software, powered by sophisticated algorithms, to predict whether individual offenders are likely to re-offend. The focus of this contribution is on the use of these risk-assessment tools in criminal sentencing. Apart from the broader social, ethical and legal considerations, to date, not much is known about how perceptions of technology influence cognition in decision-making, particularly in the legal context. What research does demonstrate is that humans are inclined to trust algorithms as objective, and, as such, as unobjectionable. This contribution examines two phenomena in this regard: (i) the “technology effect”—the human tendency towards excessive optimism when making decisions involving technology; and (ii) “automation bias”—the phenomenon whereby judges accept the recommendations of an automated decision-making system, and cease searching for confirmatory evidence, perhaps even transferring responsibility for decision-making onto the machine.</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>e3b815e1a83132e6</t>
+          <t>7947ac0d82ac46e9</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>About the Editor</t>
+          <t>Metabolism in Crisis? A New Interplay Between Physiology and Ecology</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>MBA, S.</t>
+          <t>Bognon-Küss, C.</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>pre_chatgpt</t>
+          <t>post_chatgpt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Digital Health</t>
+          <t>History, philosophy and theory of the life sciences</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>SAGE Publishing</t>
+          <t>Springer Nature (Netherlands)</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3582,7 +3576,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>10.36255/exon-publications-digital-health.editor</t>
+          <t>10.1007/978-3-031-12604-8_11</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3592,7 +3586,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3607,18 +3601,18 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="P35" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2022/e3b815e1a83132e6.pdf</t>
+          <t>2023/7947ac0d82ac46e9.pdf</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3628,42 +3622,42 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>Professor Simon Lin Linwood, MD, MBA, is the Chief Medical Information Officer at the UCR Health and UCR School of Medicine, Riverside, CA, USA. He obtained his executive education in Artificial Intelligence Strategy and Implementation from Harvard University. He was named Innovator of the Year by CHIME in 2018. He is a national thought leader on digital transformation and acknowledged for providing vision and leadership in information technology to drive business growth in large, complex, and highly distributed environments. He has supervised and mentored many PhD students on data-driven innovation in healthcare, such as deep learning for risk prediction in population health to control costs, and methods to reduce physician documentation burden. He received Mentor of the Year Award in 2016. His areas of expertise include digital transformation, data-driven innovation, data science, data lake, artificial intelligence, and natural language processing, among others. He has extensively published on digital health, artificial intelligence/machine learning, data science, clinical informatics, genome informatics.</t>
+          <t>Abstract This chapter investigates the hybrid relationships between metabolism, broadly and a-historically understood as the set of processes through which alien matter is made homogeneous to that of the organism, and forms of vitalism from the eighteenth century on. While metabolic processes have long been modeled in a reductionist fashion as a straightforward function of repair and expansion of a given structure (either chemically, or mechanistically), a challenging vitalist view has characterized metabolism as a creative, organizing, vital faculty. I suggest that this tension was overcome in Claude Bernard’s works on “indirect nutrition”, in which nutrition, rightly conceived as a general vital phenomenon common to plants and animals, was both characterized as an instance of the general physico-chemical determinism of all phenomena and as the sign and condition of the “freedom and independence” of the organism with respect to the environment. I propose that Bernard’s theory of indirect nutrition was central in the elaboration of his general physiology and has, at the same time, underpinned a self-centered view of biological identity in which the organism creates itself continuously at the detriment of its external milieu . I further argue that this conception of biological individuality as metabolically constructed has since, and paradoxically, supported a view in which the organism appears as an autonomous and self-creating entity. I then contrast this classical view of the metabolic autonomy of the organism with the challenges raised by microbiome studies and suggest that these emerging fields contribute to sketch an ecological conception of the organism and its metabolism through the reconceptualization of its relationship with the environment. The recent focus on a “microbiota – host metabolism” axis contributes to shift the focus away from the classical concept of organism, somehow externalizing vitalism out of the autonomous individual in favor of an ecological, collaborative, and interactionist view of the living.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>246ac766bd6d1c42</t>
+          <t>3827a11b5b949e39</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>List of Contributors</t>
+          <t>Rebuilding After War and Genocide: Learning with and from Refugees in the Transnational Digital Classroom</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Contributors, L.</t>
+          <t>Brill-Carlat, M.; Höhn, M.</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>pre_chatgpt</t>
+          <t>post_chatgpt</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Digital Health</t>
+          <t>Political pedagogies</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>SAGE Publishing</t>
+          <t>Springer International Publishing</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3673,7 +3667,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>10.36255/exon-publications-digital-health.contributors</t>
+          <t>10.1007/978-3-031-12350-4_22</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3683,7 +3677,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3698,7 +3692,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="O36" t="n">
@@ -3709,7 +3703,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2022/246ac766bd6d1c42.pdf</t>
+          <t>2023/3827a11b5b949e39.pdf</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3719,42 +3713,42 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>ABRAR-AHMAD ZULFIQAR, MDService de Médecine Interne, Diabète et Maladies métaboliques de la Clinique Médicale B, Hôpitaux Universitaires de Strasbourg et Equipe EA 3072 “Mitochondrie, Stress oxydant et Protection musculaire”, Faculté de Médecine-Université de Strasbourg, Strasbourg, France AIKO OSAWA, MD, PHDNational Center for Geriatrics and Gerontology, Aichi, Japan AMIR HAJJAM, PHDLaboratoire IRTES-SeT, Université de Technologie de Belfort-Montbéliard (UTBM), Belfort-Montbéliard, Belfort, France BRYONY MCGARRY, PHDPRECISE4Q, Predictive Modelling in Stroke, Technological University Dublin, Dublin, Ireland CEES TH. SMIT SIBINGA, MD, PHD, FRCP, FRCPATHIQM Consulting and University of Groningen, De Gast 46, 9801AE Zuidhorn, The Netherlands CLÁUDIA S. SOUSA, MDPulmonology Department, Central Hospital of Funchal, Portugal EMMANUEL ANDRÈS, MD, PHDLaboratoire IRTES-SeT, Université de Technologie de Belfort-Montbéliard (UTBM), Belfort-Montbéliard, Belfort, France EN-JU LIN, PHD, MPHResearch Information Solutions and Innovation, The Research Institute at Nationwide Children’s Hospital, Columbus, OH, USA ESRA ZIHNI, MSCPRECISE4Q, Predictive Modelling in Stroke, Technological University Dublin, Dublin, Ireland HIDENORI ARAI, MD, PHDNational Center for Geriatrics and Gerontology, Aichi, Japan IRVING D. KAPLAN, MDDepartment of Radiation Oncology, Beth Israel Deaconess Medical Center, Boston, MA, USA JENAY YUEN, BSKeck School of Medicine, University of Southern California, California, USA JESSAMINE P. WINER-JONES, PHDTriNetX, LLC, Cambridge, MA, USA JOHN KELLEHER, PHDPRECISE4Q, Predictive Modelling in Stroke, Technological University Dublin, Dublin, Ireland KATHARINE LAWRENCE, MD MPHNYU Grossman School of Medicine, Department of Population Health; NY, USA LIMOR APPELBAUM, MDDepartment of Radiation Oncology, Beth Israel Deaconess Medical Center, Boston, MA, USA MADELEINE SCHROEDER, MSResearch Information Solutions and Innovation, The Research Institute at Nationwide Children’s Hospital, Columbus, OH, USA MÁRIO MORAIS-ALMEIDA, MDAllergy Centre, CUF Descobertas Hospital, Lisboa, Portugal MARTIN RINARD, PHDComputer Science and Artificial Intelligence Laboratory, Massachusetts Institute of Technology, Cambridge, MA, USA MATVEY B. PALCHUK, MD, MSTriNetX, LLC, Cambridge, MA, USA MAURICE MARS, MBCHB, MDDepartment of TeleHealth, University of KwaZulu-Natal, Durban, South Africa MIGUEL T. BARBOSA, MDAllergy Centre, CUF Descobertas Hospital, Lisboa, Portugal MOHAMED HAJJAM, MDPredimed Technology, Schiltigheim, France RICHARD E. SCOTT, PHDDepartment of Community Health Sciences, University of Calgary, Calgary, Alberta, Canada SARAH PIKE, BAKeck School of Medicine, University of Southern California, California, USA SHINICHIRO MAESHIMA, MD, PHDKinjo University, Ishikawa, Japan SIMON LIN LINWOOD, MD, MBASchool of Medicine, University of California, Riverside, CA, USA STEVE KHACHIKYANDornsife College of Letters, Arts &amp;amp; Sciences, University of Southern California, California, USA STEVEN KUNDROT, BS, MBA&amp;nbsp;TriNetX, LLC, Cambridge, MA, USA SUDHA NALLASAMY, MDThe Vision Center at Children’s Hospital Los Angeles, California, USA; USC Roski Eye Institute, University of Southern California, California, USA YUNGUI HUANG, PHD, MBAResearch Information Solutions and Innovation, The Research Institute at Nationwide Children’s Hospital, Columbus, OH, USA</t>
+          <t>Abstract The Covid-19 emergency spurred a flurry of teaching innovations as higher education institutions turned to online or blended learning models, and as international collaborations have moved nearly entirely online. These circumstances inspired us to revisit the digital transatlantic seminar, “Germany 1945: History and Memory in Germany after WWII,” taught by Höhn in Spring 2018 to a group of seven Vassar students (Brill-Carlat among them) and six advanced high-school students—between the ages of 17 and 22—who had come to Berlin as asylum seekers from Syria, Iraq, and Afghanistan. The course dealt with history and memory of World War II and the Holocaust in Germany. As such, it reflected a core commitment of the Consortium on Forced Migration, Displacement, and Education (CFMDE), founded by Höhn at Vassar and partners (Bard, Bennington, Sarah Lawrence, the New School, and the Council for European Studies): the importance of providing opportunities for our undergraduate students to learn with and from refugees and displaced individuals if they are to understand and tackle the global, multidimensional challenges of forced migration. As institutional resistance to digital teaching necessarily vanished with the Covid-19 pandemic in Spring 2020 and the direction of future online-learning policies is up for debate, we revisit the 2018 class to examine lessons learned and how this project points the way to another digital venture: digitally “hosting” displaced scholars at liberal arts campuses.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>05cd11abf81f4c96</t>
+          <t>c81bf633e42c7f19</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Artificial Intelligence and Machine Learning: An Instructor’s Exoskeleton in the Future of Education</t>
+          <t>Survey of AI Tool Usage in Programming Course: Early Observations</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>August, S.; Tsaima, A.</t>
+          <t>Saari, M.; Rantanen, P.; Nurminen, M.; Kilamo, T.; Systä, K.; Abrahamsson, P.</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>pre_chatgpt</t>
+          <t>post_chatgpt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>SpringerBriefs in statistics</t>
+          <t>Lecture notes in business information processing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Springer International Publishing</t>
+          <t>Springer Science+Business Media</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3764,7 +3758,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10.1007/978-3-030-58948-6_5</t>
+          <t>10.1007/978-3-031-48550-3_18</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3793,59 +3787,59 @@
         </is>
       </c>
       <c r="O37" t="n">
-        <v>26</v>
+        <v>4</v>
       </c>
       <c r="P37" t="n">
         <v>2</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2021/05cd11abf81f4c96.pdf</t>
+          <t>2023/c81bf633e42c7f19.pdf</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
         <is>
-          <t>openalex,s2</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>Abstract The role of artificial intelligence in US education is expanding. As education moves toward providing customized learning paths, the use of artificial intelligence (AI) and machine learning (ML) algorithms in learning systems increases. This can be viewed as growing metaphorical exoskeletons for instructors, enabling them to provide a higher level of guidance, feedback, and autonomy to learners. In turn, the instructor gains time to sense student needs and support authentic learning experiences that go beyond what AI and ML can provide. Applications of AI-based education technology support learning through automated tutoring, personalizing learning, assessing student knowledge, and automating tasks normally performed by the instructor. This technology raises questions about how it is best used, what data provides evidence of the impact of AI and ML on learning, and future directions in interactive learning systems. Exploration of the use of AI and ML for both co-curricular and independent learnings in content presentation and instruction; interactions, communications, and discussions; learner activities; assessment and evaluation; and co-curricular opportunities provide guidance for future research.</t>
+          <t>Abstract This study explores the role of artificial intelligence (AI) in university teaching, with a focus on the teaching of programming. Despite the growing use of AI in education, both students and teachers often struggle to understand its role and implications. To address this gap, we conducted a survey of a wide group of students (n = 200) to assess their experiences and perspectives on the use of AI in programming education. The survey results suggest that AI is becoming increasingly involved in university teaching, particularly in the teaching of programming. However, students require guidance from teachers in order to use AI tools effectively in their studies. The study concludes that the goal of teaching programming should be to guide students in the responsible use of AI. Overall, the study highlights the need for greater awareness and understanding of AI in university teaching and the fact that teachers have an important role to play in providing guidance to students on the responsible use of AI tools.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>e4785c336fe78ec7</t>
+          <t>96a698008602b3d7</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Personalized and Adaptive Learning</t>
+          <t>The Role of Educational Interventions in Facing Social Media Threats: Overarching Principles of the COURAGE Project</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Taylor, D.; Yeung, M.; Bashet, A.</t>
+          <t>Taibi, D.; Börsting, J.; Hoppe, U.; Ognibene, D.; Hernández-Leo, D.; Eimler, S.; Kruschwitz, U.</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>pre_chatgpt</t>
+          <t>post_chatgpt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>SpringerBriefs in statistics</t>
+          <t>Communications in computer and information science</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Springer International Publishing</t>
+          <t>Springer Science+Business Media</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -3855,7 +3849,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>10.1007/978-3-030-58948-6_2</t>
+          <t>10.1007/978-3-031-29800-4_25</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3884,45 +3878,45 @@
         </is>
       </c>
       <c r="O38" t="n">
-        <v>136</v>
+        <v>6</v>
       </c>
       <c r="P38" t="n">
         <v>2</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2021/e4785c336fe78ec7.pdf</t>
+          <t>2023/96a698008602b3d7.pdf</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>openalex,s2</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>Abstract Personalized and adaptive learning has been touted to be one of the most promising emerging tools for increasing student learning and student success. Yet, the terms are neither precise nor clearly defined at this time, thus making it difficult for institutions of higher education to adopt and implement a learning approach using technology that is in its infancy and not clearly understood by those who will be utilizing it. One goal of this chapter is to define adaptive and personalized learning as it is used at this time in the hopes that as the technology evolves the promise of increased student learning can come to fruition. Adaptive learning personalizes learning by continuously evaluating each student’s performance in real time and creating an ever-changing individualized learning pathway as directed by artificial intelligence and machine learning, thus increasing learning and student satisfaction.</t>
+          <t>Abstract Social media are offering new opportunities for communication and interaction way beyond what was possible only a few years ago. However, social media are also virtual spaces where young people are exposed to a variety of threats. Digital addiction, discrimination, hate speech, misinformation, polarization as well as manipulative influences of algorithms, body stereotyping, and cyberbullying are examples of challenges that find fertile ground on social media. Educators and students are not adequately prepared to face these challenges. To this aim, the COURAGE project, presented in this paper, introduces new tools and learning methodologies that can be adopted within higher education learning paths to train educators to deal with social media threats. The overarching principles of the COURAGE project leverage the most recent advances in the fields of artificial intelligence and in the educational domain paired with social and media psychological insights to support the development of the COURAGE ecosystem. The results of the experiments currently implemented with teachers and students of secondary schools as well as the impact of the COURAGE project on societal changes and ethical questions are presented and discussed.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>085fa965ce157d51</t>
+          <t>e3b815e1a83132e6</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Robots as My Future Colleagues: Changing Attitudes Toward Collaborative Robots by Means of Experience-Based Workshops</t>
+          <t>About the Editor</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Leoste, J.; Viik, T.; López, J.; Kangur, M.; Vunder, V.; Mollard, Y.; Õun, T.; Tammo, H.; Paekivi, K.</t>
+          <t>MBA, S.</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -3931,12 +3925,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Smart innovation, systems and technologies</t>
+          <t>Digital Health</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Springer Nature</t>
+          <t>SAGE Publishing</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -3946,7 +3940,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>10.1007/978-981-16-3930-2_13</t>
+          <t>10.36255/exon-publications-digital-health.editor</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3956,7 +3950,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3971,18 +3965,18 @@
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>hybrid</t>
+          <t>gold</t>
         </is>
       </c>
       <c r="O39" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P39" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2021/085fa965ce157d51.pdf</t>
+          <t>2022/e3b815e1a83132e6.pdf</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -3992,28 +3986,28 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>Abstract Artificial intelligence-driven robots are increasingly being introduced in various workplaces. Research implies that people’s negative attitudes toward intelligent and collaborative robots might hinder their willingness to use them. We propose that interactive educational activities such as specialized workshops help people to overcome such negative attitudes. We designed a two-day workshop that introduced two quasi-industrial robots (Poppy Ergo Jr and ClearBot) to 16 university students. Students’ attitudes were qualitatively measured before and after the workshop. The results imply that the workshop helped students to increase their understanding of the nature of the intelligent collaborative robots. More precisely, robots became to be seen as empowering tools, rather than friends or enemies. Interestingly, there were significant gender differences, as the female participants had a greater tendency to view robots as animated objects. We concluded that specialized workshops effectively lead participants to become aware of various promising opportunities for their robotic co-workers in the possible future.</t>
+          <t>Professor Simon Lin Linwood, MD, MBA, is the Chief Medical Information Officer at the UCR Health and UCR School of Medicine, Riverside, CA, USA. He obtained his executive education in Artificial Intelligence Strategy and Implementation from Harvard University. He was named Innovator of the Year by CHIME in 2018. He is a national thought leader on digital transformation and acknowledged for providing vision and leadership in information technology to drive business growth in large, complex, and highly distributed environments. He has supervised and mentored many PhD students on data-driven innovation in healthcare, such as deep learning for risk prediction in population health to control costs, and methods to reduce physician documentation burden. He received Mentor of the Year Award in 2016. His areas of expertise include digital transformation, data-driven innovation, data science, data lake, artificial intelligence, and natural language processing, among others. He has extensively published on digital health, artificial intelligence/machine learning, data science, clinical informatics, genome informatics.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0141788f9ac5d7cb</t>
+          <t>246ac766bd6d1c42</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>University Student Surveys Using Chatbots: Artificial Intelligence Conversational Agents</t>
+          <t>List of Contributors</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Abbas, N.; Pickard, T.; Atwell, E.; Walker, A.</t>
+          <t>Contributors, L.</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -4022,12 +4016,12 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lecture notes in computer science</t>
+          <t>Digital Health</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Springer Science+Business Media</t>
+          <t>SAGE Publishing</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4037,7 +4031,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>10.1007/978-3-030-77943-6_10</t>
+          <t>10.36255/exon-publications-digital-health.contributors</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4047,7 +4041,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4062,45 +4056,49 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>gold</t>
         </is>
       </c>
       <c r="O40" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2021/0141788f9ac5d7cb.pdf</t>
+          <t>2022/246ac766bd6d1c42.pdf</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
         <is>
-          <t>openalex,s2</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="n"/>
+          <t>openalex</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>ABRAR-AHMAD ZULFIQAR, MDService de Médecine Interne, Diabète et Maladies métaboliques de la Clinique Médicale B, Hôpitaux Universitaires de Strasbourg et Equipe EA 3072 “Mitochondrie, Stress oxydant et Protection musculaire”, Faculté de Médecine-Université de Strasbourg, Strasbourg, France AIKO OSAWA, MD, PHDNational Center for Geriatrics and Gerontology, Aichi, Japan AMIR HAJJAM, PHDLaboratoire IRTES-SeT, Université de Technologie de Belfort-Montbéliard (UTBM), Belfort-Montbéliard, Belfort, France BRYONY MCGARRY, PHDPRECISE4Q, Predictive Modelling in Stroke, Technological University Dublin, Dublin, Ireland CEES TH. SMIT SIBINGA, MD, PHD, FRCP, FRCPATHIQM Consulting and University of Groningen, De Gast 46, 9801AE Zuidhorn, The Netherlands CLÁUDIA S. SOUSA, MDPulmonology Department, Central Hospital of Funchal, Portugal EMMANUEL ANDRÈS, MD, PHDLaboratoire IRTES-SeT, Université de Technologie de Belfort-Montbéliard (UTBM), Belfort-Montbéliard, Belfort, France EN-JU LIN, PHD, MPHResearch Information Solutions and Innovation, The Research Institute at Nationwide Children’s Hospital, Columbus, OH, USA ESRA ZIHNI, MSCPRECISE4Q, Predictive Modelling in Stroke, Technological University Dublin, Dublin, Ireland HIDENORI ARAI, MD, PHDNational Center for Geriatrics and Gerontology, Aichi, Japan IRVING D. KAPLAN, MDDepartment of Radiation Oncology, Beth Israel Deaconess Medical Center, Boston, MA, USA JENAY YUEN, BSKeck School of Medicine, University of Southern California, California, USA JESSAMINE P. WINER-JONES, PHDTriNetX, LLC, Cambridge, MA, USA JOHN KELLEHER, PHDPRECISE4Q, Predictive Modelling in Stroke, Technological University Dublin, Dublin, Ireland KATHARINE LAWRENCE, MD MPHNYU Grossman School of Medicine, Department of Population Health; NY, USA LIMOR APPELBAUM, MDDepartment of Radiation Oncology, Beth Israel Deaconess Medical Center, Boston, MA, USA MADELEINE SCHROEDER, MSResearch Information Solutions and Innovation, The Research Institute at Nationwide Children’s Hospital, Columbus, OH, USA MÁRIO MORAIS-ALMEIDA, MDAllergy Centre, CUF Descobertas Hospital, Lisboa, Portugal MARTIN RINARD, PHDComputer Science and Artificial Intelligence Laboratory, Massachusetts Institute of Technology, Cambridge, MA, USA MATVEY B. PALCHUK, MD, MSTriNetX, LLC, Cambridge, MA, USA MAURICE MARS, MBCHB, MDDepartment of TeleHealth, University of KwaZulu-Natal, Durban, South Africa MIGUEL T. BARBOSA, MDAllergy Centre, CUF Descobertas Hospital, Lisboa, Portugal MOHAMED HAJJAM, MDPredimed Technology, Schiltigheim, France RICHARD E. SCOTT, PHDDepartment of Community Health Sciences, University of Calgary, Calgary, Alberta, Canada SARAH PIKE, BAKeck School of Medicine, University of Southern California, California, USA SHINICHIRO MAESHIMA, MD, PHDKinjo University, Ishikawa, Japan SIMON LIN LINWOOD, MD, MBASchool of Medicine, University of California, Riverside, CA, USA STEVE KHACHIKYANDornsife College of Letters, Arts &amp;amp; Sciences, University of Southern California, California, USA STEVEN KUNDROT, BS, MBA&amp;nbsp;TriNetX, LLC, Cambridge, MA, USA SUDHA NALLASAMY, MDThe Vision Center at Children’s Hospital Los Angeles, California, USA; USC Roski Eye Institute, University of Southern California, California, USA YUNGUI HUANG, PHD, MBAResearch Information Solutions and Innovation, The Research Institute at Nationwide Children’s Hospital, Columbus, OH, USA</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>d0f022dbfc25bf9e</t>
+          <t>05cd11abf81f4c96</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>About the Book</t>
+          <t>Artificial Intelligence and Machine Learning: An Instructor’s Exoskeleton in the Future of Education</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bartneck, C.; Lütge, C.; Wagner, A.; Welsh, S.</t>
+          <t>August, S.; Tsaima, A.</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -4109,7 +4107,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SpringerBriefs in ethics</t>
+          <t>SpringerBriefs in statistics</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -4124,7 +4122,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>10.1007/978-3-030-51110-4_1</t>
+          <t>10.1007/978-3-030-58948-6_5</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4153,45 +4151,45 @@
         </is>
       </c>
       <c r="O41" t="n">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="P41" t="n">
         <v>2</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2020/d0f022dbfc25bf9e.pdf</t>
+          <t>2021/05cd11abf81f4c96.pdf</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>openalex,s2</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>This book provides an introduction into the ethics of robots and artificial intelligence. The book was written with university students, policy makers, and professionals in mind but should be accessible for most adults. The book is meant to provide balanced and, at times, conflicting viewpoints as to the benefits and deficits of AI through the lens of ethics. As discussed in the chapters that follow, ethical questions are often not cut and dry. Nations, communities, and individuals may have unique and important perspectives on these topics that should be heard and considered. While the voices that compose this book are our own, we have attempted to represent the views of the broader AI, robotics, and ethics communities.</t>
+          <t>Abstract The role of artificial intelligence in US education is expanding. As education moves toward providing customized learning paths, the use of artificial intelligence (AI) and machine learning (ML) algorithms in learning systems increases. This can be viewed as growing metaphorical exoskeletons for instructors, enabling them to provide a higher level of guidance, feedback, and autonomy to learners. In turn, the instructor gains time to sense student needs and support authentic learning experiences that go beyond what AI and ML can provide. Applications of AI-based education technology support learning through automated tutoring, personalizing learning, assessing student knowledge, and automating tasks normally performed by the instructor. This technology raises questions about how it is best used, what data provides evidence of the impact of AI and ML on learning, and future directions in interactive learning systems. Exploration of the use of AI and ML for both co-curricular and independent learnings in content presentation and instruction; interactions, communications, and discussions; learner activities; assessment and evaluation; and co-curricular opportunities provide guidance for future research.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>68c8ca7f7b8e293f</t>
+          <t>e4785c336fe78ec7</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Collaborative Innovation Between Shenzhen Municipal Government and Tsinghua University</t>
+          <t>Personalized and Adaptive Learning</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Kang, F.</t>
+          <t>Taylor, D.; Yeung, M.; Bashet, A.</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -4200,12 +4198,12 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Education in the Asia-Pacific region</t>
+          <t>SpringerBriefs in statistics</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Springer Nature</t>
+          <t>Springer International Publishing</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -4215,7 +4213,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10.1007/978-981-15-7018-6_20</t>
+          <t>10.1007/978-3-030-58948-6_2</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4244,14 +4242,14 @@
         </is>
       </c>
       <c r="O42" t="n">
-        <v>4</v>
+        <v>136</v>
       </c>
       <c r="P42" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2020/68c8ca7f7b8e293f.pdf</t>
+          <t>2021/e4785c336fe78ec7.pdf</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -4261,28 +4259,28 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>Global megatrendsGlobal megatrends—the rise of frontier technologies, the dramatic growth of information, sociopolitical landscape changes, and demographic changes—call for the need for ecosystem orchestration that requires collaboration. The People’s Republic of China has been heavily investing on Artificial Intelligence (AI) and Research and Development (R&amp;D) to become an innovation leader globally and to further leverage its position as a manufacturing powerhouse. The Chinese innovation ecosystemInnovation ecosystem has grown steadily in recent years as they tapped higher education and research institutes. University-research-industry linkagesUniversity-research-industry linkages have proven to be successful in achieving PRC’s innovation-driven endeavors as evidenced by the large number of firms and start-ups from such linkages have grown into large businesses and key technological leaders.</t>
+          <t>Abstract Personalized and adaptive learning has been touted to be one of the most promising emerging tools for increasing student learning and student success. Yet, the terms are neither precise nor clearly defined at this time, thus making it difficult for institutions of higher education to adopt and implement a learning approach using technology that is in its infancy and not clearly understood by those who will be utilizing it. One goal of this chapter is to define adaptive and personalized learning as it is used at this time in the hopes that as the technology evolves the promise of increased student learning can come to fruition. Adaptive learning personalizes learning by continuously evaluating each student’s performance in real time and creating an ever-changing individualized learning pathway as directed by artificial intelligence and machine learning, thus increasing learning and student satisfaction.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ccad16bc20847787</t>
+          <t>085fa965ce157d51</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Correction to: Predictive Policing in 2025: A Scenario</t>
+          <t>Robots as My Future Colleagues: Changing Attitudes Toward Collaborative Robots by Means of Experience-Based Workshops</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Macnish, K.; Wright, D.; Jiya, T.</t>
+          <t>Leoste, J.; Viik, T.; López, J.; Kangur, M.; Vunder, V.; Mollard, Y.; Õun, T.; Tammo, H.; Paekivi, K.</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -4291,12 +4289,12 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Advanced sciences and technologies for security applications</t>
+          <t>Smart innovation, systems and technologies</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Springer International Publishing</t>
+          <t>Springer Nature</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4306,7 +4304,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>10.1007/978-3-030-50613-1_9</t>
+          <t>10.1007/978-981-16-3930-2_13</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4335,45 +4333,45 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="P43" t="n">
         <v>2</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2020/ccad16bc20847787.pdf</t>
+          <t>2021/085fa965ce157d51.pdf</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>openalex,s2</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>Abstract Law enforcement authorities (LEAs) have begun using artificial intelligence and predictive policing applications that are likely to raise ethical, data protection, social, political and economic issues. This paper describes application of a new scenario methodology for identifying issues that emerging technologies are likely to raise in a future six or seven years hence, but that deserve policymakers’ attention now. It often takes policymakers that long to develop a new policy, consult with stakeholders and implement the policy. Thus, policymakers need a structured, but concise framework in order to understand the issues and their various implications. At the same time, they also prefer policies that have stakeholder support. These considerations led the University of Twente in the Netherlands and the UK’s Trilateral Research to develop the scenario that follows. It is structured with several headings that policymakers need to consider in order to move toward a desired future and avoidance of an undesired future.</t>
+          <t>Abstract Artificial intelligence-driven robots are increasingly being introduced in various workplaces. Research implies that people’s negative attitudes toward intelligent and collaborative robots might hinder their willingness to use them. We propose that interactive educational activities such as specialized workshops help people to overcome such negative attitudes. We designed a two-day workshop that introduced two quasi-industrial robots (Poppy Ergo Jr and ClearBot) to 16 university students. Students’ attitudes were qualitatively measured before and after the workshop. The results imply that the workshop helped students to increase their understanding of the nature of the intelligent collaborative robots. More precisely, robots became to be seen as empowering tools, rather than friends or enemies. Interestingly, there were significant gender differences, as the female participants had a greater tendency to view robots as animated objects. We concluded that specialized workshops effectively lead participants to become aware of various promising opportunities for their robotic co-workers in the possible future.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>e97796436a92a9c7</t>
+          <t>0141788f9ac5d7cb</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Creative Composition Problem: A Knowledge Graph Logical-Based AI Construction and Optimization Solution - Applied in Cecilia: An Architecture of a Digital Companion Artificial Intelligence (AI) Agent System Composer of Dialogue Scripts for Well-Being and Mental Health</t>
+          <t>University Student Surveys Using Chatbots: Artificial Intelligence Conversational Agents</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Galindo, M.; Moreno, L.</t>
+          <t>Abbas, N.; Pickard, T.; Atwell, E.; Walker, A.</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -4397,7 +4395,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>10.1007/978-3-030-72308-8_4</t>
+          <t>10.1007/978-3-030-77943-6_10</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4422,18 +4420,18 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>hybrid</t>
+          <t>green</t>
         </is>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="P44" t="n">
         <v>2</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2020/e97796436a92a9c7.pdf</t>
+          <t>2021/0141788f9ac5d7cb.pdf</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4441,26 +4439,22 @@
           <t>openalex,s2</t>
         </is>
       </c>
-      <c r="S44" s="2" t="inlineStr">
-        <is>
-          <t>Abstract Contribution of this work is to Define the Creative Composition Problem (CCP) for Human Well-being Optimization by Construction of Knowledge Graph using Knowledge Representation and logic-based Artificial Intelligence reasoning-planning where the computation of the Optimal Solution is achieved by Dynamic Programming or Logic Programming. The Creative Composition Problem is embedded within Cecilia: an architecture of a digital companion artificial intelligence agent system composer of dialogue scripts for Well-being and Mental Health. Where Cecilia Framework is instantiated in Well-being and Mental Health domain for optimal well-being development of first year university students. We define the ‘The Problem of Creating a Dialogue Composition (PCDC)’ and we propose a feasible and optimal solution of it. CCP is instantiated in this applied domain to solve PCDC optimizing the Mental Health and Well-being of the student. CCP as PCDC is applied to optimize maximizing the mental health of the student but also maximizing the smoothness, coherence, enjoyment and engagement each time the dialogue session is composed. Cecilia helps students to manage stress/anxiety to attempt the prevention of depression. Students can interact through the digital companion making questions and answers. While the system “learns” from the user it allows the user to learn from herself. Once the student discovers elements that were unnoticed by her, she will find a better way to improve when discovering her points of improvement.</t>
-        </is>
-      </c>
+      <c r="S44" s="2" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>4f278c8b9ba9d758</t>
+          <t>d0f022dbfc25bf9e</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Teaching Programming for Mathematical Scientists</t>
+          <t>About the Book</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Betteridge, J.; Chan, E.; Corless, R.; Davenport, J.; Grant, J.</t>
+          <t>Bartneck, C.; Lütge, C.; Wagner, A.; Welsh, S.</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -4473,12 +4467,12 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Mathematics education in the digital era</t>
+          <t>SpringerBriefs in ethics</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Springer Nature (Netherlands)</t>
+          <t>Springer International Publishing</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4488,7 +4482,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>10.1007/978-3-030-86909-0_12</t>
+          <t>10.1007/978-3-030-51110-4_1</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4513,26 +4507,390 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="O45" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="P45" t="n">
         <v>2</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
+          <t>2020/d0f022dbfc25bf9e.pdf</t>
+        </is>
+      </c>
+      <c r="R45" t="inlineStr">
+        <is>
+          <t>openalex</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>This book provides an introduction into the ethics of robots and artificial intelligence. The book was written with university students, policy makers, and professionals in mind but should be accessible for most adults. The book is meant to provide balanced and, at times, conflicting viewpoints as to the benefits and deficits of AI through the lens of ethics. As discussed in the chapters that follow, ethical questions are often not cut and dry. Nations, communities, and individuals may have unique and important perspectives on these topics that should be heard and considered. While the voices that compose this book are our own, we have attempted to represent the views of the broader AI, robotics, and ethics communities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>68c8ca7f7b8e293f</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Collaborative Innovation Between Shenzhen Municipal Government and Tsinghua University</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Kang, F.</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>pre_chatgpt</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Education in the Asia-Pacific region</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Springer Nature</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>book-chapter</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>10.1007/978-981-15-7018-6_20</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>4</v>
+      </c>
+      <c r="P46" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>2020/68c8ca7f7b8e293f.pdf</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>openalex,s2</t>
+        </is>
+      </c>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>Global megatrendsGlobal megatrends—the rise of frontier technologies, the dramatic growth of information, sociopolitical landscape changes, and demographic changes—call for the need for ecosystem orchestration that requires collaboration. The People’s Republic of China has been heavily investing on Artificial Intelligence (AI) and Research and Development (R&amp;D) to become an innovation leader globally and to further leverage its position as a manufacturing powerhouse. The Chinese innovation ecosystemInnovation ecosystem has grown steadily in recent years as they tapped higher education and research institutes. University-research-industry linkagesUniversity-research-industry linkages have proven to be successful in achieving PRC’s innovation-driven endeavors as evidenced by the large number of firms and start-ups from such linkages have grown into large businesses and key technological leaders.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>ccad16bc20847787</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Correction to: Predictive Policing in 2025: A Scenario</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Macnish, K.; Wright, D.; Jiya, T.</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>pre_chatgpt</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Advanced sciences and technologies for security applications</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Springer International Publishing</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>book-chapter</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-030-50613-1_9</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>10</v>
+      </c>
+      <c r="P47" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>2020/ccad16bc20847787.pdf</t>
+        </is>
+      </c>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>openalex,s2</t>
+        </is>
+      </c>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Law enforcement authorities (LEAs) have begun using artificial intelligence and predictive policing applications that are likely to raise ethical, data protection, social, political and economic issues. This paper describes application of a new scenario methodology for identifying issues that emerging technologies are likely to raise in a future six or seven years hence, but that deserve policymakers’ attention now. It often takes policymakers that long to develop a new policy, consult with stakeholders and implement the policy. Thus, policymakers need a structured, but concise framework in order to understand the issues and their various implications. At the same time, they also prefer policies that have stakeholder support. These considerations led the University of Twente in the Netherlands and the UK’s Trilateral Research to develop the scenario that follows. It is structured with several headings that policymakers need to consider in order to move toward a desired future and avoidance of an undesired future.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>e97796436a92a9c7</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Creative Composition Problem: A Knowledge Graph Logical-Based AI Construction and Optimization Solution - Applied in Cecilia: An Architecture of a Digital Companion Artificial Intelligence (AI) Agent System Composer of Dialogue Scripts for Well-Being and Mental Health</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Galindo, M.; Moreno, L.</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>pre_chatgpt</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Lecture notes in computer science</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Springer Science+Business Media</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>book-chapter</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-030-72308-8_4</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
+        <v>0</v>
+      </c>
+      <c r="P48" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>2020/e97796436a92a9c7.pdf</t>
+        </is>
+      </c>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>openalex,s2</t>
+        </is>
+      </c>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Contribution of this work is to Define the Creative Composition Problem (CCP) for Human Well-being Optimization by Construction of Knowledge Graph using Knowledge Representation and logic-based Artificial Intelligence reasoning-planning where the computation of the Optimal Solution is achieved by Dynamic Programming or Logic Programming. The Creative Composition Problem is embedded within Cecilia: an architecture of a digital companion artificial intelligence agent system composer of dialogue scripts for Well-being and Mental Health. Where Cecilia Framework is instantiated in Well-being and Mental Health domain for optimal well-being development of first year university students. We define the ‘The Problem of Creating a Dialogue Composition (PCDC)’ and we propose a feasible and optimal solution of it. CCP is instantiated in this applied domain to solve PCDC optimizing the Mental Health and Well-being of the student. CCP as PCDC is applied to optimize maximizing the mental health of the student but also maximizing the smoothness, coherence, enjoyment and engagement each time the dialogue session is composed. Cecilia helps students to manage stress/anxiety to attempt the prevention of depression. Students can interact through the digital companion making questions and answers. While the system “learns” from the user it allows the user to learn from herself. Once the student discovers elements that were unnoticed by her, she will find a better way to improve when discovering her points of improvement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>4f278c8b9ba9d758</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Teaching Programming for Mathematical Scientists</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Betteridge, J.; Chan, E.; Corless, R.; Davenport, J.; Grant, J.</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>pre_chatgpt</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Mathematics education in the digital era</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Springer Nature (Netherlands)</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>book-chapter</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-030-86909-0_12</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>4</v>
+      </c>
+      <c r="P49" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
           <t>2020/4f278c8b9ba9d758.pdf</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="R49" t="inlineStr">
         <is>
           <t>openalex,s2</t>
         </is>
       </c>
-      <c r="S45" s="2" t="inlineStr">
+      <c r="S49" s="2" t="inlineStr">
         <is>
           <t>Over the past thirty years or so the authors have been teaching various programming for mathematics courses at our respective Universities, as well as incorporating computer algebra and numerical computation into traditional mathematics courses. These activities are, in some important ways, natural precursors to the use of Artificial Intelligence in Mathematics Education. This paper reflects on some of our course designs and experiences and is therefore a mix of theory and practice. Underlying both is a clear recognition of the value of computer programming for mathematics education. We use this theory and practice to suggest good techniques for and to raise questions about the use of AI in Mathematics Education.</t>
         </is>
@@ -4628,6 +4986,14 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q44" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q45" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q46" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q47" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q48" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q49" r:id="rId96"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/rrl_matrix.xlsx
+++ b/output/rrl_matrix.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S49"/>
+  <dimension ref="A1:S77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1430,17 +1430,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>c6a4accaccaeb577</t>
+          <t>966facd8e5a135ea</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Capacity Building in Livestock Breeding and Genetic Improvement in Achieving UN Sustainable Development Goals for Africa</t>
+          <t>Accelerating Acoustics: A Learning Paradigm with Python and Prompt Engineering</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Tiambo, C.; Opoola, O.; Okpeku, M.; Houaga, I.; Touko, B.; Dessie, T.</t>
+          <t>Mari Ueda; Katsuhiro Kanamori; Katsumi Takahashi; Shogo Kiryu; Tetsuo Tanaka</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1453,22 +1453,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sustainable development goals series</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Springer International Publishing</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>book-chapter</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-031-92076-9_28</t>
+          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1478,7 +1463,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
@@ -1491,47 +1476,39 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>hybrid</t>
-        </is>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
       <c r="P12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2025/c6a4accaccaeb577.pdf</t>
+          <t>2025/966facd8e5a135ea.pdf</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>eric</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>Abstract To achieve the Sustainable Development Goals of the United Nations (UN-SDGs) in Africa, livestock breeding efficiency is a prerequisite. Human capital in the form of professional, managerial, and technical skills, improved policies and institutional operation are the key enablers of performance for the smallholder livestock sector. Capacity building is central to guarantee African livestock efficiency along the value chains and ultimately transformed livelihoods. Currently, animal breeding and genetic improvement in Africa are constrained by a serious human and institutional capacity gap. The Livestock Development Strategy for Africa (LiDESA) seeks to transform the livestock sector for accelerated and equitable growth and for enhanced contribution to socio-economic development. Sustainable livestock development in Africa could be better realized through the development of customized capacity building strategies targeting (1) relevant participatory breeding education, hands-on training, efficient technical assistance, and collaborations / partnerships aiming to address farmers’ present and future challenges, (2) enabling breeding systems for sustainable productivity, resilience of breeds, and animal seed stock management, and (3) market-led breeding solutions that are attractive for the younger and future generations. Challenges facing capacity building in livestock breeding in Africa vary between and within stakeholders of specific value chains, and farmers lack training and suitable support programmes for their breeding activities. Beyond the lack of skilled human resources, financial capacity to enforce legislation and policies in Animal Genetic Resources (AnGR) that may lead to the design and implementation of conservation and breeding programmes is a major limiting factor in most African countries. Currently, animal breeding programmes may not thrive, unless a new cohort of breeders, infrastructures, and policies are in place and backed by long-term investment plans. The main loopholes of the desired revolution reside in the current gaps and limitations of higher education and professional trainings, in terms of human resources, infrastructure, curricular content, research, and cooperation. The required capacity development could also be through people-centred community-based breeding programmes (CBBP), training of trainers, and continuous education with major inputs/roles by agricultural training institutions (e.g. Pan African University), the African Union InterAfrican Bureau for Animal Genetics Resources (AU-IBAR) and the African Animal Breeding Network (AABNet), in the form of collaborations for teaching, research, and outreach. Key capacity building intervention areas needing attention are: (1) Conservation and restoration of local animal genetic diversity, their improvement and dissemination of elite locally adapted and farmers-preferred genetics, and preservation of their natural habitat; (2) Demand-led capacity development in modern livestock breeding techniques; (3) Sustainable intensification of livestock farming practices; (4) Adaptation to extreme environmental conditions and livestock emergency guidelines and standards (LEGS); (5) Breeding for animal welfare, adaptability, and biosafety; (6) Big Data and artificial intelligence for smart farming and livestock breeding programmes; and (7) Infrastructural development and policies’ integration for technology uptake.</t>
+          <t>Generative Artificial Intelligence (GenAI) is catalyzing a paradigm shift in higher education, demanding new pedagogical approaches that integrate AI literacy as a core competency. This paper addresses the long-standing challenge of teaching acoustics, a field often perceived as abstract and mathematically intensive by undergraduate students. We propose a novel, 13-week exercise-based course designed for the Faculty of Information Science at the Kanagawa Institute of Technology. This course uniquely integrates Python programming with the systematic application of prompt engineering to facilitate the learning of fundamental acoustics concepts. The methodology involves leveraging GenAI as a personalized tutor, a code-generation assistant for visualization, and a tool for conceptual exploration. The expected outcomes include not only a deeper, more intuitive understanding of acoustics but also the cultivation of critical AI literacy and problem-solving skills essential for the next generation of engineers. This approach has the transformative potential to reshape engineering pedagogy, making complex subjects more accessible and engaging while preparing students for a future of human-AI collaboration. [For the complete proceedings, &amp;quot;Proceedings of the International Association for Development of the Information Society (IADIS) International Conference on Cognition and Exploratory Learning in the Digital Age (CELDA) (22nd, Porto, Portugal, November 1-3, 2025),&amp;quot; see ED677812.]</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>262fa18a25cef7c6</t>
+          <t>0d507483b5131d42</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Catastrophic Computation. On the Impossibility of Sustainable Artificial Intelligence</t>
+          <t>Adaptive Learning with Cognitive Awareness: An AI Model from the ELSEI Master&amp;apos;s Program</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Rehak, R.</t>
+          <t>Zakaria Tagdimi; Souhaib Aammou; Marina Sounoglou</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1544,22 +1521,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lecture notes in computer science</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Springer Science+Business Media</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>book-chapter</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-032-11108-1_8</t>
+          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1569,7 +1531,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1581,48 +1543,40 @@
         <is>
           <t>Yes</t>
         </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>hybrid</t>
-        </is>
-      </c>
-      <c r="O13" t="n">
-        <v>0</v>
       </c>
       <c r="P13" t="n">
         <v>2</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2025/262fa18a25cef7c6.pdf</t>
+          <t>2025/0d507483b5131d42.pdf</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>eric</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>Artificial intelligence (AI) is currently considered a sustainability “game-changer” within and outside of academia. I argue that while there are indeed many sustainability-related use cases for AI, they are likely to have more overall drawbacks than benefits. To substantiate this claim, I differentiate three ‘AI materialities’ of the AI supply chain: first the literal materiality (e.g. water, cobalt, lithium, energy consumption etc.), second, the informational materiality (e.g. lots of data and centralised control necessary), and third, the social materiality (e.g. exploitative data work, communities harm by waste and pollution). In all materialities, effects are especially devastating for the global south while benefiting the global north. A second strong claim regarding sustainable AI circles around so-called apolitical optimisation (e.g. regarding city traffic), however the optimisation criteria (e.g. cars, bikes, emissions, commute time, health) are purely political and have to be collectively negotiated before applying AI optimisation. Hence, sustainable AI, in principle, cannot break the glass ceiling of transformation and might even distract from necessary societal change. To address that I propose to stop ‘unformation gathering’ and to apply the ‘small is beautiful’ principle. This aims to contribute to an informed academic and collective negotiation on how to (not) integrate AI into the sustainability project while avoiding to reproduce the status quo by serving hegemonic interests between useful AI use cases, techno-utopian salvation narratives, technology-centred efficiency paradigms, the exploitative and extractivist character of AI and concepts of digital degrowth. In order to discuss sustainable AI, this article draws from insights by critical data and algorithm studies, STS, transformative sustainability science, critical computer science, and public interest theory.</t>
+          <t>Personalization is often perceived as a technical problem in the context of digital education. However, it is also a cognitive challenge, requiring an understanding of how learners process information. This study presents a cognitive-based recommendation model designed and tested within the Master's program in E-learning and Intelligent Educational Systems (ELSEI) at the École Normale Supérieure (ENS) of Abdelmalek Essaadi University in Morocco. This model is based on the principles of cognitive load theory and uses artificial intelligence to adapt learning experiences in real time. The model aims to align content presentation with each learner's cognitive profile. This alignment is achieved through clustering, load classification, and hybrid recommendation techniques. This model is tested for six weeks involving 47 graduate students and has shown encouraging results: an improvement in engagement and academic performance, as well as a reduction in learning disruptions related to overload. These results suggest a broader evolution of educational AI, towards systems that are not only adaptive, but also attentive to the cognitive demands of learning. [For the complete proceedings, &amp;quot;Proceedings of the International Association for Development of the Information Society (IADIS) International Conference on Cognition and Exploratory Learning in the Digital Age (CELDA) (22nd, Porto, Portugal, November 1-3, 2025),&amp;quot; see ED677812.]</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>ca3c5062dc813e4f</t>
+          <t>049208b9a6bac215</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Comparative Analysis of Generative AI Performance in University Programming Courses</t>
+          <t>Artificial Intelligence in ESP Education Transformations, Ethical Considerations and Future Directions</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Suomalainen, E.; Vanhala, E.; Ikonen, J.</t>
+          <t>Silvia Osman</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1635,22 +1589,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lecture notes in business information processing</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>Springer Science+Business Media</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>book-chapter</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-032-14518-5_16</t>
+          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1660,7 +1599,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1673,47 +1612,39 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>hybrid</t>
-        </is>
-      </c>
-      <c r="O14" t="n">
-        <v>0</v>
-      </c>
       <c r="P14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2025/ca3c5062dc813e4f.pdf</t>
+          <t>2025/049208b9a6bac215.pdf</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>openalex,s2</t>
+          <t>eric</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>Generative artificial intelligence (GenAI) has had an impact on university education and also to the software industry. This can be seen in many different courses where GenAIs can complete exercises, exams, and even whole courses by themselves. This study aims to find out how effectively different GenAI tools can complete exercises in programming courses. Our objective is to find how GenAI’s performance varies across courses and what differences there are in results between multiple GenAI tools. During the study, five programming courses were evaluated using five different GenAI tools. These tools were able to solve 43–90% of programming assignments and 80–100% of quizzes. In practice, the result is that any of the selected GenAIs could have been used to pass the majority of all the tested course parts. Results indicate that we have to rethink how courses’ tasks are designed and that courses need to have an element where learning is verified in a controlled environment to verify that we are educating software professionals for the industry.</t>
+          <t>In the rapidly evolving digital landscape, artificial intelligence (AI) is fundamentally redefining English for Specific Purposes (ESP) education across disciplines such as Political Studies, International Relations, Sociology, and Psychology. This paper explores how AI-powered tools enhance personalized, immersive, and authentic learning experiences, fostering core linguistic and intercultural skills. Drawing on my extensive experience as a visiting professor at the University of Naples &amp;quot;Federico II&amp;quot; and Vlora University, I analyze pedagogical strategies, ethical challenges--including GDPR compliance and the EU AI Act--and the influence of digital sovereignty. This comprehensive discussion aims to provide strategic pathways for responsible and effective AI integration into ESP curricula, emphasizing the importance of preparing students for the demands of an interconnected, multicultural professional environment. [For the complete proceedings, &amp;quot;Proceedings of the International Association for Development of the Information Society (IADIS) International Conference on Cognition and Exploratory Learning in the Digital Age (CELDA) (22nd, Porto, Portugal, November 1-3, 2025),&amp;quot; see ED677812.]</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>82ca847ef02116ef</t>
+          <t>f34f1bb5de578666</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Digital Twin for Datacenter: HPC4AI UniTO Case Study</t>
+          <t>Boosting English Language Listening Skills through Copilot AI (A Case of Georgian Higher Education Institutions)</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Vaccaro, V.; Birke, R.; Meschini, S.; Tagliabue, L.; Rabellino, S.; Legazpi, P.; Andinucci, M.</t>
+          <t>Eliza Kintsurashvili</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1726,22 +1657,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lecture notes in civil engineering</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Springer Nature</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>book-chapter</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-032-09040-9_9</t>
+          <t>International Society for Technology, Education, and Science. 944 Maysey Drive, San Antonio, TX 78227. Tel: 515-294-1075; Fax: 515-294-1003; email: istesoffice@gmail.com; Web site: http://www.istes.org</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1751,7 +1667,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1763,48 +1679,40 @@
         <is>
           <t>Yes</t>
         </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>hybrid</t>
-        </is>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>2</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2025/82ca847ef02116ef.pdf</t>
+          <t>2025/f34f1bb5de578666.pdf</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>eric</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>Abstract The HPC4AI (High-Performance Computing for Artificial Intelligence) datacenter at the University of Turin’s Computer Science Department was established to meet the rapidly growing computational demands of interdisciplinary AI research. HPC4AI innovates by redefining the traditional roles of Cloud and High-Performance Computing (HPC) systems, where the Cloud provides a modern interface for HPC, and HPC acts as an accelerator for Cloud applications. To date, it has supported over 40 research projects spanning diverse fields such as astronomy, medicine, and human sciences. Additionally, HPC4AI serves as a research and development platform for exploring, developing, and testing novel datacenter technologies. It features a variety of experimental computing platforms and the first prototype of a two-phase evaporative server cooling system. This work outlines the operational management of HPC4AI, highlighting challenges, lessons learned, and key opportunities related to digital twins for datacenters.</t>
+          <t>This study explores the impact of Copilot AI on enhancing English language listening skills among B1-level students through an experimental research design. The research involved two groups: an experimental group that used Copilot AI for listening practice and a control group that followed traditional listening activities. Over a set period, students in the experimental group engaged with AI-generated listening exercises, interactive transcripts, and real-time feedback, while the control group relied on conventional audio materials and teacher-led discussions. Pre- and post-tests were administered to measure improvements in listening comprehension. The results indicate that students showing to Copilot AI demonstrated greater progress in their ability to understand spoken English, recognize key details, and respond accurately. The study highlights the potential of AI-assisted learning in improving listening proficiency and suggests practical applications for integrating AI tools into English language instruction. [For the complete proceedings, see ED678959.]</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>b070f5d42bca7df6</t>
+          <t>c6a4accaccaeb577</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Generative AI in Simulation-Based Test Environments for Large-Scale Cyber-Physical Systems: An Industrial Study</t>
+          <t>Capacity Building in Livestock Breeding and Genetic Improvement in Achieving UN Sustainable Development Goals for Africa</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sadrnezhaad, M.; López, J.; Mårtensson, T.; Varró, D.</t>
+          <t>Tiambo, C.; Opoola, O.; Okpeku, M.; Houaga, I.; Touko, B.; Dessie, T.</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1817,12 +1725,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lecture notes in computer science</t>
+          <t>Sustainable development goals series</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Springer Science+Business Media</t>
+          <t>Springer International Publishing</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1832,7 +1740,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10.1007/978-3-032-12089-2_13</t>
+          <t>10.1007/978-3-031-92076-9_28</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1857,45 +1765,45 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="O16" t="n">
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2025/b070f5d42bca7df6.pdf</t>
+          <t>2025/c6a4accaccaeb577.pdf</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>openalex,s2</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>Quality assurance for large-scale cyber-physical systems relies on sophisticated test activities using complex test environments investigated with the help of numerous types of simulators. As these systems grow, extensive resources are required to develop and maintain simulation models of hardware and software components, as well as physical environments. Meanwhile, recent advances in generative AI have led to tools that can produce executable test cases for software systems, offering potential benefits such as reducing manual efforts or increasing test coverage. However, the application of generative AI techniques to simulation-based testing of large-scale cyber-physical systems remains underexplored. To better understand this gap, this study captures practitioners'perspectives on leveraging generative AI, based on a cross-company workshop with six organizations. Our contribution is twofold: (1) detailed, experience-based insights into challenges faced by engineers, and (2) a research agenda comprising three high-priority directions: (a) AI-generated scenarios and environment models, (b) simulators and AI in CI/CD pipelines, and (c) trustworthiness in generative AI for simulation. While participants acknowledged substantial potential, they also highlighted unresolved challenges. By detailing these issues, the paper aims to guide future academia-industry collaboration towards the responsible adoption of generative AI in simulation-based testing.</t>
+          <t>Abstract To achieve the Sustainable Development Goals of the United Nations (UN-SDGs) in Africa, livestock breeding efficiency is a prerequisite. Human capital in the form of professional, managerial, and technical skills, improved policies and institutional operation are the key enablers of performance for the smallholder livestock sector. Capacity building is central to guarantee African livestock efficiency along the value chains and ultimately transformed livelihoods. Currently, animal breeding and genetic improvement in Africa are constrained by a serious human and institutional capacity gap. The Livestock Development Strategy for Africa (LiDESA) seeks to transform the livestock sector for accelerated and equitable growth and for enhanced contribution to socio-economic development. Sustainable livestock development in Africa could be better realized through the development of customized capacity building strategies targeting (1) relevant participatory breeding education, hands-on training, efficient technical assistance, and collaborations / partnerships aiming to address farmers’ present and future challenges, (2) enabling breeding systems for sustainable productivity, resilience of breeds, and animal seed stock management, and (3) market-led breeding solutions that are attractive for the younger and future generations. Challenges facing capacity building in livestock breeding in Africa vary between and within stakeholders of specific value chains, and farmers lack training and suitable support programmes for their breeding activities. Beyond the lack of skilled human resources, financial capacity to enforce legislation and policies in Animal Genetic Resources (AnGR) that may lead to the design and implementation of conservation and breeding programmes is a major limiting factor in most African countries. Currently, animal breeding programmes may not thrive, unless a new cohort of breeders, infrastructures, and policies are in place and backed by long-term investment plans. The main loopholes of the desired revolution reside in the current gaps and limitations of higher education and professional trainings, in terms of human resources, infrastructure, curricular content, research, and cooperation. The required capacity development could also be through people-centred community-based breeding programmes (CBBP), training of trainers, and continuous education with major inputs/roles by agricultural training institutions (e.g. Pan African University), the African Union InterAfrican Bureau for Animal Genetics Resources (AU-IBAR) and the African Animal Breeding Network (AABNet), in the form of collaborations for teaching, research, and outreach. Key capacity building intervention areas needing attention are: (1) Conservation and restoration of local animal genetic diversity, their improvement and dissemination of elite locally adapted and farmers-preferred genetics, and preservation of their natural habitat; (2) Demand-led capacity development in modern livestock breeding techniques; (3) Sustainable intensification of livestock farming practices; (4) Adaptation to extreme environmental conditions and livestock emergency guidelines and standards (LEGS); (5) Breeding for animal welfare, adaptability, and biosafety; (6) Big Data and artificial intelligence for smart farming and livestock breeding programmes; and (7) Infrastructural development and policies’ integration for technology uptake.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>d9d8ca8edb1d6ec5</t>
+          <t>262fa18a25cef7c6</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Integrating Artificial Intelligence with Gamification Techniques to Enhance Student Motivation and Engagement</t>
+          <t>Catastrophic Computation. On the Impossibility of Sustainable Artificial Intelligence</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Choustoulakis, E.; Athanasopoulou, P.; Pollalis, Y.; Nikoloudakis, D.</t>
+          <t>Rehak, R.</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1908,12 +1816,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Springer proceedings in business and economics</t>
+          <t>Lecture notes in computer science</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Springer International Publishing</t>
+          <t>Springer Science+Business Media</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1923,7 +1831,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-81962-9_58</t>
+          <t>10.1007/978-3-032-11108-1_8</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1952,14 +1860,14 @@
         </is>
       </c>
       <c r="O17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
         <v>2</v>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2025/d9d8ca8edb1d6ec5.pdf</t>
+          <t>2025/262fa18a25cef7c6.pdf</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1969,24 +1877,24 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>Abstract This study investigated the integration of Artificial Intelligence (AI) with gamification techniques to enhance student motivation, engagement, and academic performance in management education. A non-probability sample of 200 undergraduate students from Greece was randomly assigned to one of two groups: an experimental group that experienced AI-driven gamification, or a control group that followed traditional instructional methods. Quantitative analysis revealed that students in the experimental group demonstrated a statistically significant increase in active participation and a statistically significant improvement in course completion rates compared to the control group. This was complemented by significant enhancements in academic performance, with final grades showing a notable difference. The AI-driven gamified environment, which included personalized challenges and real-time feedback, effectively boosted engagement and academic outcomes. Qualitative feedback from students indicated that the AI system’s ability to adapt to individual learning needs was particularly valued. Students appreciated the personalized support, which helped them stay on track and better understand complex concepts. The study highlights the potential of combining AI with gamification to create a more interactive and tailored educational experience, addressing diverse learning needs and preferences. These findings highlight the transformative impact of AI-driven gamification on management education and emphasize the critical role of courses in integrating these innovative methods. They also suggest avenues for future research to further optimize these approaches, enhancing both educational practices and student outcomes in management training.</t>
+          <t>Artificial intelligence (AI) is currently considered a sustainability “game-changer” within and outside of academia. I argue that while there are indeed many sustainability-related use cases for AI, they are likely to have more overall drawbacks than benefits. To substantiate this claim, I differentiate three ‘AI materialities’ of the AI supply chain: first the literal materiality (e.g. water, cobalt, lithium, energy consumption etc.), second, the informational materiality (e.g. lots of data and centralised control necessary), and third, the social materiality (e.g. exploitative data work, communities harm by waste and pollution). In all materialities, effects are especially devastating for the global south while benefiting the global north. A second strong claim regarding sustainable AI circles around so-called apolitical optimisation (e.g. regarding city traffic), however the optimisation criteria (e.g. cars, bikes, emissions, commute time, health) are purely political and have to be collectively negotiated before applying AI optimisation. Hence, sustainable AI, in principle, cannot break the glass ceiling of transformation and might even distract from necessary societal change. To address that I propose to stop ‘unformation gathering’ and to apply the ‘small is beautiful’ principle. This aims to contribute to an informed academic and collective negotiation on how to (not) integrate AI into the sustainability project while avoiding to reproduce the status quo by serving hegemonic interests between useful AI use cases, techno-utopian salvation narratives, technology-centred efficiency paradigms, the exploitative and extractivist character of AI and concepts of digital degrowth. In order to discuss sustainable AI, this article draws from insights by critical data and algorithm studies, STS, transformative sustainability science, critical computer science, and public interest theory.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>6adfc8932d140131</t>
+          <t>ca3c5062dc813e4f</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Micro-degree Artificial Intelligence and Society</t>
+          <t>Comparative Analysis of Generative AI Performance in University Programming Courses</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Lasser, J.; Pfiffner, M.</t>
+          <t>Suomalainen, E.; Vanhala, E.; Ikonen, J.</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1999,7 +1907,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lecture notes in computer science</t>
+          <t>Lecture notes in business information processing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2014,7 +1922,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>10.1007/978-3-032-11108-1_21</t>
+          <t>10.1007/978-3-032-14518-5_16</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -2046,38 +1954,38 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2025/6adfc8932d140131.pdf</t>
+          <t>2025/ca3c5062dc813e4f.pdf</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>openalex,s2</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>We introduce the micro-degree “Artificial Intelligence and Society” developed by the University of Graz, a novel interdisciplinary program designed to bridge the gap between technical AI knowledge and its broader societal implications. Recognising the rapid permeation of AI into all aspects of life and the limitations of traditional educational systems in addressing this transformation, the target audience of the micro-degree is both students enrolled in traditional university degrees as well as the existing workforce. The 16 ECTS curriculum, spanning two semesters, covers the technical foundations of AI systems alongside their ethical, legal, economic, and educational impacts. It features a modular structure with basic knowledge lectures, hands-on application courses – including a mandatory technical AI course and electives in ethics, law, economics, and education –, and practicals where students implement AI-based solutions to real-world problems. Here, we describe the structure and content of the micro-degree, including the learning objectives of the individual degree modules. We also provide Open Educational Resources used for teaching the (mandatory) lecture and hands-on course on the technical foundations of artificial intelligence. This micro-degree represents a crucial step towards fostering digital humanism by enabling individuals to confidently understand, apply, and shape AI’s role in society.</t>
+          <t>Generative artificial intelligence (GenAI) has had an impact on university education and also to the software industry. This can be seen in many different courses where GenAIs can complete exercises, exams, and even whole courses by themselves. This study aims to find out how effectively different GenAI tools can complete exercises in programming courses. Our objective is to find how GenAI’s performance varies across courses and what differences there are in results between multiple GenAI tools. During the study, five programming courses were evaluated using five different GenAI tools. These tools were able to solve 43–90% of programming assignments and 80–100% of quizzes. In practice, the result is that any of the selected GenAIs could have been used to pass the majority of all the tested course parts. Results indicate that we have to rethink how courses’ tasks are designed and that courses need to have an element where learning is verified in a controlled environment to verify that we are educating software professionals for the industry.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>03aa44aa607b0e73</t>
+          <t>2939cb4059ec9276</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Proposal of a framework to enhance the adoption of artificial intelligence in higher education considering sustainable development: a hybrid Lawshe-TOPSIS approach</t>
+          <t>Designing an Integrated Multi-Dimensional Assessment Framework for AI-Supported Academic Writing</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Fernandes, R.; Nagata, V.; Filho, W.; Rampasso, I.; Ávila, L.; Silva, J.; Anholon, R.; Martins, V.</t>
+          <t>Sabine Seufert; Niklas Eulitz</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2090,22 +1998,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>International Journal of Educational Management</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>Emerald Publishing Limited</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>article</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>10.1108/ijem-08-2024-0441</t>
+          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -2115,7 +2008,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
@@ -2128,42 +2021,39 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="O19" t="n">
-        <v>1</v>
-      </c>
       <c r="P19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2025/03aa44aa607b0e73.pdf</t>
+          <t>2025/2939cb4059ec9276.pdf</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
         <is>
-          <t>dean_provided,s2</t>
+          <t>eric</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>Purpose The main objective of this study was to propose a framework to enhance the adoption of artificial intelligence (AI) in higher education, considering sustainable development in the context of an emerging economy country. Design/methodology/approach The method adopted was a literature review and a survey conducted with higher education faculty members from Brazilian universities. Through an electronic questionnaire, 71 responses were collected. The data were analyzed using a hybrid Lawshe-TOPSIS approach. Findings As a result, the validated framework highlights six challenges related to the adoption of AI in higher education and nine ordered benefits of AI adoption, with the most significant for the analyzed context being the ability to process large amounts of data; sustainable solutions for industry, commerce and the economy; adaptive teaching strategies and greater scientific assistance for students and faculty. Research limitations/implications The article contributes to the literature by filling a research gap and provides insights for higher education institution managers regarding AI adoption in this mode of education. Originality/value The research underscores the importance of aligning technological initiatives with sustainable development goals, providing a structured guide.</t>
+          <t>The widespread adoption of generative AI is transforming academic writing in higher education, rendering traditional, product-focused assessment models obsolete. These methods fail to capture the iterative and tool-mediated nature of modern writing processes, creating an urgent need for new evaluation approaches. This paper addresses this gap by proposing an integrated, multi-dimensional assessment framework. Grounded in genre pedagogy, self-regulated learning, and writing analytics, our model conceptualizes assessment as a holistic process. It evaluates foundational skills for AI use (Computational Thinking and Genre-Knowledge), the quality of text revision, final writing performance, and long-term development. By aligning these dimensions with formative, summative, and diagnostic purposes, the framework fosters transparency, metacognitive engagement, and responsible AI use. We are preparing a design-based research project to pilot and iteratively refine key elements of the framework within a mastery learning programme for 1,800 first-year students. The goal is to explore how the model can be implemented in practice and refined through iterative cycles of design, enactment, and evaluation. [For the complete proceedings, &amp;quot;Proceedings of the International Association for Development of the Information Society (IADIS) International Conference on Cognition and Exploratory Learning in the Digital Age (CELDA) (22nd, Porto, Portugal, November 1-3, 2025),&amp;quot; see ED677812.]</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>36a4fda0d7a39cf4</t>
+          <t>82ca847ef02116ef</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Reconsidering Requirements Engineering: Human–AI Collaboration in AI-Native Software Development</t>
+          <t>Digital Twin for Datacenter: HPC4AI UniTO Case Study</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Abbasi, M.; Ihantola, P.; Mikkonen, T.; Mäkitalo, N.</t>
+          <t>Vaccaro, V.; Birke, R.; Meschini, S.; Tagliabue, L.; Rabellino, S.; Legazpi, P.; Andinucci, M.</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2176,12 +2066,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lecture notes in computer science</t>
+          <t>Lecture notes in civil engineering</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Springer Science+Business Media</t>
+          <t>Springer Nature</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2191,7 +2081,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10.1007/978-3-032-04190-6_11</t>
+          <t>10.1007/978-3-032-09040-9_9</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2216,45 +2106,45 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="O20" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
         <v>2</v>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2025/36a4fda0d7a39cf4.pdf</t>
+          <t>2025/82ca847ef02116ef.pdf</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>openalex,s2</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>Requirement Engineering (RE) is the foundation of successful software development. In RE, the goal is to ensure that implemented systems satisfy stakeholder needs through rigorous requirements elicitation, validation, and evaluation processes. Despite its critical role, RE continues to face persistent challenges, such as ambiguity, conflicting stakeholder needs, and the complexity of managing evolving requirements. A common view is that Artificial Intelligence (AI) has the potential to streamline the RE process, resulting in improved efficiency, accuracy, and management actions. However, using AI also introduces new concerns, such as ethical issues, biases, and lack of transparency. This paper explores how AI can enhance traditional RE practices by automating labor-intensive tasks, supporting requirement prioritization, and facilitating collaboration between stakeholders and AI systems. The paper also describes the opportunities and challenges that AI brings to RE. In particular, the vision calls for ethical practices in AI, along with a much-enhanced collaboration between academia and industry professionals. The focus should be on creating not only powerful but also trustworthy and practical AI solutions ready to adapt to the fast-paced world of software development.</t>
+          <t>Abstract The HPC4AI (High-Performance Computing for Artificial Intelligence) datacenter at the University of Turin’s Computer Science Department was established to meet the rapidly growing computational demands of interdisciplinary AI research. HPC4AI innovates by redefining the traditional roles of Cloud and High-Performance Computing (HPC) systems, where the Cloud provides a modern interface for HPC, and HPC acts as an accelerator for Cloud applications. To date, it has supported over 40 research projects spanning diverse fields such as astronomy, medicine, and human sciences. Additionally, HPC4AI serves as a research and development platform for exploring, developing, and testing novel datacenter technologies. It features a variety of experimental computing platforms and the first prototype of a two-phase evaporative server cooling system. This work outlines the operational management of HPC4AI, highlighting challenges, lessons learned, and key opportunities related to digital twins for datacenters.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>e8ba15cc7545622a</t>
+          <t>8421a3fd34fa7ee0</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Shape Computation Research at the University of Sydney</t>
+          <t>Exploring the Role of Artificial Intelligence in Shaping Students&amp;apos; Social Skills</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Gero, J.</t>
+          <t>Mariam Yasinskay; Irma Mesiridze</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2267,22 +2157,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Mathematics and the built environment</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Springer International Publishing</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>book-chapter</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-031-81623-9_15</t>
+          <t>International Society for Technology, Education, and Science. 944 Maysey Drive, San Antonio, TX 78227. Tel: 515-294-1075; Fax: 515-294-1003; email: istesoffice@gmail.com; Web site: http://www.istes.org</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2292,7 +2167,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2304,48 +2179,40 @@
         <is>
           <t>Yes</t>
         </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>hybrid</t>
-        </is>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
       </c>
       <c r="P21" t="n">
         <v>2</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2025/e8ba15cc7545622a.pdf</t>
+          <t>2025/8421a3fd34fa7ee0.pdf</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>eric</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>This chapter provides a brief overview of the shape computation research at the University of Sydney that was carried out over a 35-year period, between 1977 and 2012, referencing 17 Ph.D theses that discuss shape computation during that period. The chapter draws distinctions between shape computation using shape grammars and other approaches that parallel, supplement and diverge from shape grammars. It introduces a variety of methods for shape computation, including those based on infinite maximal lines, artificial intelligence, learning representations, learning generation rules, logic models, qualitative representation, qualitative reasoning, algebraic representation, shape semantics, situated learning, and shape interpretation.</t>
+          <t>Technological development and the emergence of artificial intelligence have rapidly reshaped the education sphere by transforming the ways students learn and master new knowledge. The learning process has become more adaptive since learners can effectively leverage artificial intelligence (AI) tools to complete multiple academic tasks without human assistance. However, researchers scrutinize the impact of artificial intelligence on learners' social skills since over-reliance on artificial intelligence assistance can potentially reduce the communication level with students and lecturers, resulting in deteriorated interaction skills. The study investigates the influence of artificial intelligence on students' social and interpersonal development in Georgian higher education institutions. By applying the mixed methodology, the extensive body of literature was analyzed, and the survey was conducted among 133 students from various academic programs and levels in 3 Georgian higher education institutions. The research findings revealed that even though AI-powered tools are valuable for academic processes, students demonstrate awareness of potential risks affecting their social and interpersonal skill development. Therefore, they try to maintain the balance between technological assistance and social interactions in their academic environment. The study concludes that the balanced application of AI in education can enhance students' academic performance without hindering the development of their social skills. [For the complete proceedings, see ED678959.]</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>fd9e23c6c69b4a0f</t>
+          <t>0902f81e01b244e8</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>The Future of Cybersecurity at Sea: Human vs Human or AI vs AI?</t>
+          <t>From Curriculum for All to Inclusive Practice: Insights from a Pilot Study on UDL-Based Pedagogical Transformation</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Alop, A.</t>
+          <t>Sara Cruz; Marisa Maia</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2358,22 +2225,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Signals and communication technology</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Springer Vienna</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>book-chapter</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-031-87290-7_1</t>
+          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2383,7 +2235,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2396,47 +2248,39 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>hybrid</t>
-        </is>
-      </c>
-      <c r="O22" t="n">
-        <v>0</v>
-      </c>
       <c r="P22" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2025/fd9e23c6c69b4a0f.pdf</t>
+          <t>2025/0902f81e01b244e8.pdf</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>eric</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>The digitalization of all areas of activity, including maritime, today is characterized, among other things, by two powerful influencing factors: on the one hand, artificial intelligence (AI) increasingly taking over the most important functions and develops very quickly, and on the other hand, threats and risks related to cybersecurity. The common belief, which is hard to argue against, is that the first factor is positive, because it contributes to developments, and the second is undoubtedly negative, because it hinders developments and can even inhibit them; from here, it is easy to conclude that in order to continue and accelerate progress, the positive aspects of the first factor must be contributed in every way and the fight against the effects of the second factor must be undertaken. But how realistic and consistently achievable are these two goals in interaction? True, in the light of the developments of the last years and even months, it seems that the AI “train” has started its impressive journey at high speed, and nothing can stop it. At the same time, continuing the allegory, there is still a “wagon” of cyber threats attached to this “train,” and getting rid of it or even defeating it to a sufficient extent seems problematic, at least now. The author of this chapter expresses an estimated opinion that as long as people fight against each other on both sides of the “cyber war” (“bad” guys against “good” ones), it is so to say war of attrition, where no glorious victory awaits either side. It seems to the author that it is possible to change the situation and achieve victory over the “bad” guys only if the AI itself takes over its own protection. Whether and to what extent this is possible is one of the main topics of this chapter. In the author’s opinion, there can be any truth behind this only if the AI acquires a large part of the characteristics unique to humans (values, moral principles, emotions, etc.), thanks to which it would be possible to be guided by the specific laws or rules of behavior of the AI. As a classic example, the so-called three laws of robotics, formulated by the American science fiction writer Isaac Asimov about 80 years ago, are based on the principle of avoiding harm to humans (Anderson, Asimov’s “Three Laws of Robotics” and machine metaethics, University of Connecticut, Dept. of Philosophy, Stamford, CT, https://cdn.aaai.org/Symposia/Fall/2005/FS-05-06/FS05-06-002.pdf ). In this chapter, we have analyzed whether such AI developments are possible at all and what threats and difficulties this entails in turn.</t>
+          <t>In the context of growing demands for inclusive and flexible pedagogical practices in higher education, this study explores how university lecturers can transform their teaching through the lens of Universal Design for Learning (UDL). Grounded in a pedagogical innovation initiative, this pilot study followed four higher education lecturers over the course of one semester as they engaged in a professional development process aimed at redesigning their teaching practices based on the principles of UDL. The objective was to understand the extent to which these lecturers appropriated and applied UDL principles in their pedagogical approaches. Employing a qualitative case study methodology, the research draws on document analysis of final reflective posters produced by each participant, which synthesise the evolution of their teaching practices. The findings reveal that all lecturers successfully integrated UDL principles into different aspects of their instruction, demonstrating increased awareness and practical application of strategies to enhance accessibility, flexibility, and learner engagement. Notably, there was a clear emerging trend towards the adoption of Artificial Intelligence tools as a means to support differentiated instruction and promote inclusive learning environments. This integration of AI technologies appears to complement UDL's emphasis on multiple means of representation, engagement, and expression. The study underscores the potential of structured, reflective, and context-sensitive professional development to foster meaningful pedagogical change in higher education, while also highlighting the evolving role of AI in supporting inclusive and adaptive teaching practices. These findings offer valuable insights for institutional strategies aiming to scale inclusive education through UDL and digital innovation. [For the complete proceedings, &amp;quot;Proceedings of the International Association for Development of the Information Society (IADIS) International Conference on Cognition and Exploratory Learning in the Digital Age (CELDA) (22nd, Porto, Portugal, November 1-3, 2025),&amp;quot; see ED677812.]</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>dd8a0e8d30483815</t>
+          <t>b070f5d42bca7df6</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>The Impact of AI Tools on Universities’ Educational Strategies and Student Success: Sultan Qaboos University and Qatar University as a Case Study</t>
+          <t>Generative AI in Simulation-Based Test Environments for Large-Scale Cyber-Physical Systems: An Industrial Study</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Al-Awadhi, T.; Al-Balushi, A.; Abdullah, M.; Abulibdeh, A.</t>
+          <t>Sadrnezhaad, M.; López, J.; Mårtensson, T.; Varró, D.</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2449,12 +2293,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Gulf Studies</t>
+          <t>Lecture notes in computer science</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Springer Nature</t>
+          <t>Springer Science+Business Media</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2464,7 +2308,7 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>10.1007/978-981-97-9667-0_9</t>
+          <t>10.1007/978-3-032-12089-2_13</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2489,45 +2333,45 @@
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>hybrid</t>
+          <t>green</t>
         </is>
       </c>
       <c r="O23" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2025/dd8a0e8d30483815.pdf</t>
+          <t>2025/b070f5d42bca7df6.pdf</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>openalex,s2</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>Abstract Sultan Qaboos University (SQU) and Qatar University (QU) are working to adopt short- and long-term plans to ensure leadership in teaching and learning, scientific research, and community service at regional and international levels. Modern technologies, especially artificial intelligence (AI), play an important role in our lives, providing realistic opportunities to accelerate business implementation and improve the final value of work. AI plays a crucial role in taking education and research to the next level, transforming the way these organisations work and make decisions. AI can improve the traditional work of educational institutions and transform the understanding of their complexity. However, challenges remain in various aspects, whether related to the nature of our work or to the AI technologies themselves. This is still a great opportunity for every HEI. Therefore, this paper aims to analyse the potential of AI to accelerate the implementation of the strategic plans of the two universities.</t>
+          <t>Quality assurance for large-scale cyber-physical systems relies on sophisticated test activities using complex test environments investigated with the help of numerous types of simulators. As these systems grow, extensive resources are required to develop and maintain simulation models of hardware and software components, as well as physical environments. Meanwhile, recent advances in generative AI have led to tools that can produce executable test cases for software systems, offering potential benefits such as reducing manual efforts or increasing test coverage. However, the application of generative AI techniques to simulation-based testing of large-scale cyber-physical systems remains underexplored. To better understand this gap, this study captures practitioners'perspectives on leveraging generative AI, based on a cross-company workshop with six organizations. Our contribution is twofold: (1) detailed, experience-based insights into challenges faced by engineers, and (2) a research agenda comprising three high-priority directions: (a) AI-generated scenarios and environment models, (b) simulators and AI in CI/CD pipelines, and (c) trustworthiness in generative AI for simulation. While participants acknowledged substantial potential, they also highlighted unresolved challenges. By detailing these issues, the paper aims to guide future academia-industry collaboration towards the responsible adoption of generative AI in simulation-based testing.</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ccacb2251f5b4e56</t>
+          <t>0663b0eda3890644</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Thinking Along the Lines Generated by GenAI? A Systematic Mapping Study on Academic Writing</t>
+          <t>Improving Generative AI Student Feedback: Direct Preference Optimization with Teachers in the Loop</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Kaczkó, É.; Ivanjek, L.; Norz, L.; Ammenwerth, E.</t>
+          <t>Juliette Woodrow; Sanmi Koyejo; Chris Piech</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -2540,22 +2384,7 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lecture notes in computer science</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Springer Science+Business Media</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>book-chapter</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-032-11108-1_35</t>
+          <t>International Educational Data Mining Society. e-mail: admin@educationaldatamining.org; Web site: https://educationaldatamining.org/conferences/</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2565,7 +2394,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2578,51 +2407,43 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>hybrid</t>
-        </is>
-      </c>
-      <c r="O24" t="n">
-        <v>0</v>
-      </c>
       <c r="P24" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2025/ccacb2251f5b4e56.pdf</t>
+          <t>2025/0663b0eda3890644.pdf</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>eric</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>The advent of generative AI (GenAI) tools in higher education challenges fundamental assumptions about academic authorship, students’ cognitive development and how writing cultivates critical thinking (CT). This systematic mapping study synthesized emerging research on how GenAI is reshaping the relationship between academic writing and CT in higher education. Drawing on 25 peer-reviewed studies published between 2023 and 2025, we analyzed conceptualizations of CT and academic writing, identified pedagogical approaches, and examined the use of GenAI tools across a range of disciplines, educational levels, and geographic contexts. Findings revealed that interest in the use of GenAI in academic writing is global and spans all disciplines and higher educational levels. However, only a minority of studies drew on robust theoretical frameworks. CT was conceptualized predominantly within a cognitive skills paradigm, while broader understandings linked to criticality and critical pedagogy were largely absent. Pedagogical models were rare and mostly untested, and educators’ perspectives were underrepresented. While GenAI was seen as supporting writing processes, its potential to foster or hinder CT remained contested. Future research should broaden conceptual foundations, include educator perspectives, and prioritize pedagogical design and evaluation. Rethinking academic writing as a transformative practice may require moving beyond the cognitive paradigm towards more participatory and ethically grounded approaches to CT.</t>
+          <t>High-quality feedback requires understanding of a student's work, insights into what concepts would help them improve, and language that matches the preferences of the specific teaching team. While Large Language Models (LLMs) can generate coherent feedback, adapting these responses to align with specific teacher preferences remains an open challenge. We present a method for aligning LLM-generated feedback with teacher preferences using Direct Preference Optimization (DPO). We integrate preference data collection into the grading process. This creates a self-improving pipeline keeping the teacher-in-the-loop to ensure feedback quality and maintain teacher autonomy. To evaluate effectiveness, we conducted a blind controlled study where expert evaluators compared feedback from multiple models on anonymized student submissions. Evaluators consistently preferred feedback from our DPO model over GPT-4o. We deployed the system in two offerings of a large university course, with nearly 300 students and over 10 teaching assistants per term, demonstrating its feasibility in real classroom settings. We share strategies for automated performance monitoring using critic models. We explore methods for examining fairness across protected demographics. [For the complete proceedings, see ED675583.]</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>bebfc35847a401fc</t>
+          <t>d9d8ca8edb1d6ec5</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Characteristics of Romanian Online Recruitment Websites and Students’ Use</t>
+          <t>Integrating Artificial Intelligence with Gamification Techniques to Enhance Student Motivation and Engagement</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Mardache, A.; Balasescu, M.</t>
+          <t>Choustoulakis, E.; Athanasopoulou, P.; Pollalis, Y.; Nikoloudakis, D.</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -2646,7 +2467,7 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-51038-0_76</t>
+          <t>10.1007/978-3-031-81962-9_58</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2675,14 +2496,14 @@
         </is>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P25" t="n">
         <v>2</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2024/bebfc35847a401fc.pdf</t>
+          <t>2025/d9d8ca8edb1d6ec5.pdf</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -2692,28 +2513,28 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>Abstract Technology has increasingly changed the way human resource (HR) function achieves its goals. Organizations seek agile employees who can cope with continuous changes in a complex and uncertain environment. Effective recruitment is closely related to talent management, as organizations are interested in attracting talented people who can give a competitive advantage for the organization. The use of technology and artificial intelligence in recruitment will increasingly enable the creation of profiles that help organizations attract the best candidates for vacancies. In this context, due to its multiple advantages both for organizations and candidates, online recruitment is increasingly being used. However, it is important to be aware of the various problems associated with online recruitment and to find solutions in solving them. In this study, we conducted a content analysis of ten of the most popular recruitment websites in Romania, according to a wide range of criteria concerning the jobs on offer, but also the features of the sites. Moreover, we also conducted an exploratory survey (with a sample of 200 students) in order to identify the perception and use of these recruitment websites by students and recent university graduates. Recruitment websites are more and more complex and offer diverse and useful tools for users. Some of them already use artificial intelligence to help users identify the most compatible job. Students and recent university graduates predominantly use such websites when they are looking for a job.</t>
+          <t>Abstract This study investigated the integration of Artificial Intelligence (AI) with gamification techniques to enhance student motivation, engagement, and academic performance in management education. A non-probability sample of 200 undergraduate students from Greece was randomly assigned to one of two groups: an experimental group that experienced AI-driven gamification, or a control group that followed traditional instructional methods. Quantitative analysis revealed that students in the experimental group demonstrated a statistically significant increase in active participation and a statistically significant improvement in course completion rates compared to the control group. This was complemented by significant enhancements in academic performance, with final grades showing a notable difference. The AI-driven gamified environment, which included personalized challenges and real-time feedback, effectively boosted engagement and academic outcomes. Qualitative feedback from students indicated that the AI system’s ability to adapt to individual learning needs was particularly valued. Students appreciated the personalized support, which helped them stay on track and better understand complex concepts. The study highlights the potential of combining AI with gamification to create a more interactive and tailored educational experience, addressing diverse learning needs and preferences. These findings highlight the transformative impact of AI-driven gamification on management education and emphasize the critical role of courses in integrating these innovative methods. They also suggest avenues for future research to further optimize these approaches, enhancing both educational practices and student outcomes in management training.</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>323ecbe01d1cd744</t>
+          <t>d27fcdfbec56edee</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Last Tendencies in Acquiring Text Competence in the Field of Tourism. The Case of Chatbots and AI</t>
+          <t>Integration of ChatGPT in the Problem-Based Learning Model</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Madueño, M.</t>
+          <t>Daniela Orozova; Nadezhda Angelova</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -2722,22 +2543,7 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Springer proceedings in business and economics</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Springer International Publishing</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>book-chapter</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-031-52607-7_17</t>
+          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2747,7 +2553,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2760,51 +2566,43 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>hybrid</t>
-        </is>
-      </c>
-      <c r="O26" t="n">
-        <v>1</v>
-      </c>
       <c r="P26" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2024/323ecbe01d1cd744.pdf</t>
+          <t>2025/d27fcdfbec56edee.pdf</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>eric</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>Abstract Our aim is to propose the usage of generative Artificial Intelligence, hereafter AI, while lecturing, as a complement to the traditional methodology, to ease technological skills acquisition in the related AI. Widely spread in all aspects of cultural life and professional praxis worldwide, it is of key importance in the training of our professional to be. In Malaga University’s Degree of Tourism, in subjects dealing with English for tourism management, we shall concentrate on chatbots aided by AI, in order to make a literary review to see the state of the question and to reflect on the needed changes to implement these tools. We shall try to outline the characteristics, possibilities, advantages and disadvantages, and the influence on both students and lecturers alike of the usage of AI in chatbots to deal with outcoming texts. Direct interaction with the tools will be highlighted. Of key importance is training lecturers in the productive use of “prompt engineering”. To conclude, handling specialised texts in the field of tourism by means of chatbots might help lecturers’ awareness and responsibility for right use to obtain semi-specialised and specialised texts in the field of tourism in order to understand, extract and evaluate its pertinence.</t>
+          <t>The development of modern technologies and the integration of AI into all aspects of life pose challenges for participants in the educational process. On the one hand, using chatbots and generative AI tools provides learners with unlimited opportunities to quickly and easily access a large amount of information and receive help with various homework assignments, making it difficult for teachers to assess their work. The article presents an experiment designed to motivate students and support teachers during training. The research was conducted during the education of bachelor students in the professional field of Informatics and Computer Sciences. The propositions presented in this report raise several questions and outline possible future research directions. An experiment is conducted with students in the second and third semesters of the Software Engineering bachelor's program. The goal is to integrate ChatGPT in the context of problem-based learning while mastering the fundamentals of programming languages such as C++, Java, and web programming. The idea is to train learners' critical thinking skills with systematically generated materials from ChatGPT, in dialogue with students, enriching them with additional knowledge and various resources. This study examines the potential of artificial intelligence technology, such as ChatGPT, to enhance core teaching materials through problem-based learning. Learners are encouraged to develop critical thinking on assigned tasks, and their progress is monitored by analyzing data collected during the learning process. This paper aims to demonstrate that generative AI technologies, such as ChatGPT, have the potential to enrich learning resources, adapt materials to individual learners' needs, and provide flexibility for both students and educators in the digital age. The main challenges associated with traditional teaching include the lecturer's limited time to present the learning material, a shortage of reference resources, and low student motivation. Integrating ChatGPT into a problem-solving learning model is hypothesized to personalize learning content, improve critical thinking, provide feedback, and increase learner motivation. [For the complete proceedings, &amp;quot;Proceedings of the International Association for Development of the Information Society (IADIS) International Conference on Cognition and Exploratory Learning in the Digital Age (CELDA) (22nd, Porto, Portugal, November 1-3, 2025),&amp;quot; see ED677812.]</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>e799f9736c02ac60</t>
+          <t>6adfc8932d140131</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Overcoming the Long Shadow of the Past: Defense AI in Japan</t>
+          <t>Micro-degree Artificial Intelligence and Society</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Tsuchiya, M.</t>
+          <t>Lasser, J.; Pfiffner, M.</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -2813,12 +2611,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Contributions to security and defence studies</t>
+          <t>Lecture notes in computer science</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Springer International Publishing</t>
+          <t>Springer Science+Business Media</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2828,7 +2626,7 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-58649-1_22</t>
+          <t>10.1007/978-3-032-11108-1_21</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2864,7 +2662,7 @@
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2024/e799f9736c02ac60.pdf</t>
+          <t>2025/6adfc8932d140131.pdf</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -2874,28 +2672,28 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>Abstract Since the end of World War II, Japan has not had a full-fledged military, but only Self-Defense Forces (SDF) for the sole purpose of “exclusively defensive defense.” Hesitancy exists in society, especially in academia, to research and develop technologies that could be diverted to military use. This has created a long shadow of the past in which public opinion, strategic culture, and the academic-industrial ecosystem mutually reinforce each other not to directly address defense technologies, though Japan is often recognized as one of the most technologically advanced countries. However, with the recent deterioration of the national security environment around Japan, such hesitance is weakening, and research and development of technologies that can be applied to defense purposes is now being conducted, also in cooperation with partners like the United States, the United Kingdom, and others. Discussions about artificial intelligence (AI) for defense purposes began in earnest around 2022, with descriptions found in government and defense documents, and budget appropriations beginning to be made. However, the budget size is miniscule and no special organization for defense AI exists. In addition, there is no plan to use defense AI in earnest in defense operations, and it is merely positioned as one of the technologies that are attracting widespread attention. The defense industry is working on AI across the board, but Japan’s defense industry has a large proportion of civilian demand, and there are aspects of the industry that are not necessarily for defense use. If necessary, they will be applied to defense applications, but they are not actively promoted as AI for defense. Attempts to deepen the knowledge of AI among SDF personnel have only just begun.</t>
+          <t>We introduce the micro-degree “Artificial Intelligence and Society” developed by the University of Graz, a novel interdisciplinary program designed to bridge the gap between technical AI knowledge and its broader societal implications. Recognising the rapid permeation of AI into all aspects of life and the limitations of traditional educational systems in addressing this transformation, the target audience of the micro-degree is both students enrolled in traditional university degrees as well as the existing workforce. The 16 ECTS curriculum, spanning two semesters, covers the technical foundations of AI systems alongside their ethical, legal, economic, and educational impacts. It features a modular structure with basic knowledge lectures, hands-on application courses – including a mandatory technical AI course and electives in ethics, law, economics, and education –, and practicals where students implement AI-based solutions to real-world problems. Here, we describe the structure and content of the micro-degree, including the learning objectives of the individual degree modules. We also provide Open Educational Resources used for teaching the (mandatory) lecture and hands-on course on the technical foundations of artificial intelligence. This micro-degree represents a crucial step towards fostering digital humanism by enabling individuals to confidently understand, apply, and shape AI’s role in society.</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>148d777c7af8aaae</t>
+          <t>9bebd7a1588a62f1</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Reimagining Extreme Event Scenarios: The Aesthetic Visualisation of Climate Uncertainty to Enhance Preparedness</t>
+          <t>Proceedings of the International Conference on Educational Data Mining (EDM) (18th, Palermo, Italy, July 20-23, 2025)</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Favero, D.; Thurow, S.; Pagnucco, M.; Frohne, U.</t>
+          <t>Caitlin Mills, E.; Giora Alexandron, E.; Davide Taibi, E.; Giosuè Lo Bosco, E.; Luc Paquette, E.</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -2904,22 +2702,7 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Arts, research, innovation and society</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Springer International Publishing</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>book-chapter</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-031-56114-6_2</t>
+          <t>International Educational Data Mining Society. e-mail: admin@educationaldatamining.org; Web site: https://educationaldatamining.org/conferences/</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2929,7 +2712,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2941,52 +2724,44 @@
         <is>
           <t>Yes</t>
         </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>hybrid</t>
-        </is>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
       </c>
       <c r="P28" t="n">
         <v>2</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2024/148d777c7af8aaae.pdf</t>
+          <t>2025/9bebd7a1588a62f1.pdf</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>eric</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>Abstract Responding to the rapidly escalating climate emergency, this chapter outlines transformative multidisciplinary research centred on the visualisation of unpredictable extreme event scenarios. It proposes a unique, scientifically grounded artistic approach to one of the world’s most immediate challenges—preparing communities for extreme climate events, such as firestorms and flash floods. As preparedness is a function of prior threat experience, it argues that visualising threat scenarios in advance can be a key to surviving and adapting in an era of increasing climate instability. This approach can enable communities to viscerally experience and rehearse threat perception, situational awareness, adaptive decision making and dynamic response to unexpected life-threatening extreme events. Using experimental case studies at The University of New South Wales’s iCinema Research Centre and international benchmarks, this chapter explores how advances in immersive visualisation and artificial intelligence aesthetics can be integrated to provide a framework that enables the virtual prototyping of unforeseen geolocated climate scenarios to facilitate readiness in the face of accelerating climate uncertainty.</t>
+          <t>The University of Palermo is proud to host the 18th International Conference on Educational Data Mining (EDM) in Palermo, Italy, from July 20 to July 23, 2025. EDM is the annual flagship conference of the International Educational Data Mining Society. This year's theme is &amp;quot;New Goals, New Measurements, New Incentives to Learn.&amp;quot; The theme highlights the shift toward an era dominated by artificial intelligence--where machines can surpass human performance in numerous cognitive tasks--and highlights the imperative for educational systems to evolve accordingly. The scientific program for EDM2025 includes: (1) two keynote talks by outstanding researchers in the field; (2) a plenary Prof. Ram Kumar Educational Data Mining Test of Time Award talk; (3) an invited Data Set Award talk; (4) five workshops and three tutorials; (5) eight presentation sessions with parallel (2 and 3) tracks; (6) a poster presentation session; (7) an industry track session; (8) a doctoral consortium session; and (9) a cross-conference panel. [Individual papers are indexed in ERIC.]</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>5beff436c4263cda</t>
+          <t>03aa44aa607b0e73</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Retrieval Augmented Large Language Model Chatbots in Higher Education: A Study on University Open Days</t>
+          <t>Proposal of a framework to enhance the adoption of artificial intelligence in higher education considering sustainable development: a hybrid Lawshe-TOPSIS approach</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Shanthakumar, A.; Fassihi-Tash, F.; Lotfi, A.; Bird, J.</t>
+          <t>Fernandes, R.; Nagata, V.; Filho, W.; Rampasso, I.; Ávila, L.; Silva, J.; Anholon, R.; Martins, V.</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2995,22 +2770,22 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Advances in intelligent systems and computing</t>
+          <t>International Journal of Educational Management</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Springer Nature</t>
+          <t>Emerald Publishing Limited</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>book-chapter</t>
+          <t>article</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-78857-4_3</t>
+          <t>10.1108/ijem-08-2024-0441</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -3031,49 +2806,48 @@
       <c r="M29" t="inlineStr">
         <is>
           <t>Yes</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>green</t>
         </is>
       </c>
       <c r="O29" t="n">
         <v>1</v>
       </c>
       <c r="P29" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2024/5beff436c4263cda.pdf</t>
+          <t>2025/03aa44aa607b0e73.pdf</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>openalex,s2</t>
-        </is>
-      </c>
-      <c r="S29" s="2" t="n"/>
+          <t>dean_provided,s2</t>
+        </is>
+      </c>
+      <c r="S29" s="2" t="inlineStr">
+        <is>
+          <t>Purpose The main objective of this study was to propose a framework to enhance the adoption of artificial intelligence (AI) in higher education, considering sustainable development in the context of an emerging economy country. Design/methodology/approach The method adopted was a literature review and a survey conducted with higher education faculty members from Brazilian universities. Through an electronic questionnaire, 71 responses were collected. The data were analyzed using a hybrid Lawshe-TOPSIS approach. Findings As a result, the validated framework highlights six challenges related to the adoption of AI in higher education and nine ordered benefits of AI adoption, with the most significant for the analyzed context being the ability to process large amounts of data; sustainable solutions for industry, commerce and the economy; adaptive teaching strategies and greater scientific assistance for students and faculty. Research limitations/implications The article contributes to the literature by filling a research gap and provides insights for higher education institution managers regarding AI adoption in this mode of education. Originality/value The research underscores the importance of aligning technological initiatives with sustainable development goals, providing a structured guide.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>a366da3974dd03f0</t>
+          <t>36a4fda0d7a39cf4</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ruffle&amp;amp;Riley: Insights from Designing and Evaluating a Large Language Model-Based Conversational Tutoring System</t>
+          <t>Reconsidering Requirements Engineering: Human–AI Collaboration in AI-Native Software Development</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Schmucker, R.; Xia, M.; Azaria, A.; Mitchell, T.</t>
+          <t>Abbasi, M.; Ihantola, P.; Mikkonen, T.; Mäkitalo, N.</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -3097,7 +2871,7 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-64302-6_6</t>
+          <t>10.1007/978-3-032-04190-6_11</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -3122,49 +2896,49 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>hybrid</t>
+          <t>green</t>
         </is>
       </c>
       <c r="O30" t="n">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="P30" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2024/a366da3974dd03f0.pdf</t>
+          <t>2025/36a4fda0d7a39cf4.pdf</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>openalex,s2</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>Abstract Conversational tutoring systems (CTSs) offer learning experiences through interactions based on natural language. They are recognized for promoting cognitive engagement and improving learning outcomes, especially in reasoning tasks. Nonetheless, the cost associated with authoring CTS content is a major obstacle to widespread adoption and to research on effective instructional design. In this paper, we discuss and evaluate a novel type of CTS that leverages recent advances in large language models (LLMs) in two ways: First, the system enables AI-assisted content authoring by inducing an easily editable tutoring script automatically from a lesson text. Second, the system automates the script orchestration in a learning-by-teaching format via two LLM-based agents (Ruffle&amp;amp;Riley) acting as a student and a professor. The system allows for free-form conversations that follow the ITS-typical inner and outer loop structure. We evaluate Ruffle&amp;amp;Riley’s ability to support biology lessons in two between-subject online user studies ( $$N = 200$$ &lt;mml:math xmlns:mml="http://www.w3.org/1998/Math/MathML"&gt; &lt;mml:mrow&gt; &lt;mml:mi&gt;N&lt;/mml:mi&gt; &lt;mml:mo&gt;=&lt;/mml:mo&gt; &lt;mml:mn&gt;200&lt;/mml:mn&gt; &lt;/mml:mrow&gt; &lt;/mml:math&gt; ) comparing the system to simpler QA chatbots and reading activity. Analyzing system usage patterns, pre/post-test scores and user experience surveys, we find that Ruffle&amp;amp;Riley users report high levels of engagement, understanding and perceive the offered support as helpful. Even though Ruffle&amp;amp;Riley users require more time to complete the activity, we did not find significant differences in short-term learning gains over the reading activity. Our system architecture and user study provide various insights for designers of future CTSs. We further open-source our system to support ongoing research on effective instructional design of LLM-based learning technologies.</t>
+          <t>Requirement Engineering (RE) is the foundation of successful software development. In RE, the goal is to ensure that implemented systems satisfy stakeholder needs through rigorous requirements elicitation, validation, and evaluation processes. Despite its critical role, RE continues to face persistent challenges, such as ambiguity, conflicting stakeholder needs, and the complexity of managing evolving requirements. A common view is that Artificial Intelligence (AI) has the potential to streamline the RE process, resulting in improved efficiency, accuracy, and management actions. However, using AI also introduces new concerns, such as ethical issues, biases, and lack of transparency. This paper explores how AI can enhance traditional RE practices by automating labor-intensive tasks, supporting requirement prioritization, and facilitating collaboration between stakeholders and AI systems. The paper also describes the opportunities and challenges that AI brings to RE. In particular, the vision calls for ethical practices in AI, along with a much-enhanced collaboration between academia and industry professionals. The focus should be on creating not only powerful but also trustworthy and practical AI solutions ready to adapt to the fast-paced world of software development.</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2c028fbe91e54d72</t>
+          <t>aca4033a09f8146c</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Survival of the Smartest? Defense AI in Ukraine</t>
+          <t>Reducing Speaking Anxiety among College ESL Students through Artificial Intelligence</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Goncharuk, V.</t>
+          <t>Promethi Das Deep; Nitu Ghosh; Andrey V. Koptelov</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -3173,22 +2947,7 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Contributions to security and defence studies</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Springer International Publishing</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>book-chapter</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-031-58649-1_17</t>
+          <t>International Society for Technology, Education, and Science. 944 Maysey Drive, San Antonio, TX 78227. Tel: 515-294-1075; Fax: 515-294-1003; email: istesoffice@gmail.com; Web site: http://www.istes.org</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -3198,7 +2957,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -3211,51 +2970,43 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>hybrid</t>
-        </is>
-      </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>4</v>
       </c>
-      <c r="P31" t="n">
-        <v>2</v>
-      </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2024/2c028fbe91e54d72.pdf</t>
+          <t>2025/aca4033a09f8146c.pdf</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>eric</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>Abstract Before Russia’s invasion in February 2022, Ukraine boasted a thriving ecosystem for producing artificial intelligence (AI) solutions, leading Eastern Europe in AI company numbers and hosting R&amp;amp;D offices of multinational giants like Amazon and Google. Despite this, Ukraine’s defense sector lagged in AI adoption due to a focus on traditional hardware. The conflict between Russia and Ukraine has transformed the situation, with both sides employing AI in geospatial intelligence, unmanned systems, military training, and cyber warfare, making this conflict the first to feature AI competition as a critical factor. Ukraine’s resilience during the war has relied on active use of awareness systems, volunteer initiatives, open-source platforms, and decentralized asset utilization. The government has begun systematically formulating defense AI policy initiatives and fostering a new ecosystem while civil IT companies shift focus towards dual-use products and talent acquisition in AI. Current defense AI development priorities include AI for unmanned systems, to combat disinformation and support cybersecurity and to advance logistics and mine detection. In parallel, the war has advanced closer cooperation between universities and the military sector, also in view of advancing training and developing AI-enhanced simulation-based training. Overall, the conflict serves as a testing ground for foreign AI developers, prompting reevaluation of regulatory assumptions and the need for war-proof defense AI solutions.</t>
+          <t>Speaking anxiety continues to challenge many college ESL students, affecting confidence, fluency, and classroom participation. With the growing integration of artificial intelligence (AI) and large language models (LLMs) in higher education, new opportunities have emerged to enhance oral language learning through adaptive and low-pressure environments. This review followed the SANRA guidelines to ensure clarity, rigor, and balance. Relevant peer-reviewed studies were identified from ERIC, EBSCOhost, JSTOR, IEEE Xplore, and Scopus using the keywords artificial intelligence, large language models, ESL, EFL, speaking anxiety, and communication confidence. Research focusing on higher education contexts was analyzed for methodological quality and pedagogical insights. Findings show that AI-based tools such as chatbots, speech recognition systems, and feedback applications improve learners' fluency, pronunciation, and vocabulary while enhancing grammatical accuracy and discourse coherence. These technologies also reduce anxiety, boost motivation, and promote autonomous learning by providing immediate, personalized feedback in supportive settings. However, limitations in emotional responsiveness, contextual adaptability, and the need for teacher mediation highlight the importance of balanced integration. Overall, AI serves as a valuable complement to traditional instruction, fostering both linguistic competence and emotional well-being among college ESL learners. [For the complete proceedings, see ED678731.]</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>ae87b25ad2e4631c</t>
+          <t>e8ba15cc7545622a</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Future of Learning and Education</t>
+          <t>Shape Computation Research at the University of Sydney</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Varghese, S.</t>
+          <t>Gero, J.</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -3264,7 +3015,7 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Future of business and finance</t>
+          <t>Mathematics and the built environment</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3279,7 +3030,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-36382-5_16</t>
+          <t>10.1007/978-3-031-81623-9_15</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3308,14 +3059,14 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P32" t="n">
         <v>2</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2023/ae87b25ad2e4631c.pdf</t>
+          <t>2025/e8ba15cc7545622a.pdf</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3325,28 +3076,28 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>Abstract According to “A Scorecard for Humanity,” a report from the Copenhagen Consensus Center, our world gains every time an individual is educated, and our world pays a price when people go illiterate. In the future, those regions and nations of the world that manage to educate its people would gain, whereas those that do not pay much attention to this crucial aspect would continue to suffer losses, hidden in plain sight. Hence, by 2050, we suggest that though the world would have made tremendous progress in basic education, illiteracy would persist with almost 500 million uneducated in the world. Illiteracy shall be most concentrated in the regions of Africa and South Asia, whereas most other nations would move toward a total eradication. However, there would also be a systemic change in the higher education sector across the globe, as the age cohort of 18 to 24 years in Europe would shrink, but in South Asia and Africa, this would continue to grow. There would also be a disruption of the current pedagogic and regimental learning systems toward flatter, flexible, and open systems based on research in learning sciences. Technology would also come by to play a larger role, where education would be driven by artificial intelligence (AI) and big data—resulting in complete personalization of curriculum and methodology focusing on each individual's minute needs.</t>
+          <t>This chapter provides a brief overview of the shape computation research at the University of Sydney that was carried out over a 35-year period, between 1977 and 2012, referencing 17 Ph.D theses that discuss shape computation during that period. The chapter draws distinctions between shape computation using shape grammars and other approaches that parallel, supplement and diverge from shape grammars. It introduces a variety of methods for shape computation, including those based on infinite maximal lines, artificial intelligence, learning representations, learning generation rules, logic models, qualitative representation, qualitative reasoning, algebraic representation, shape semantics, situated learning, and shape interpretation.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2ad51015436ad076</t>
+          <t>0256be53813d4df5</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Investigating the Role of ChatGPT in Supporting Text-Based Programming Education for Students and Teachers</t>
+          <t>Studies on Social and Education Sciences 2025</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Wieser, M.; Schöffmann, K.; Stefanics, D.; Bollin, A.; Pasterk, S.</t>
+          <t>Mustafa Koc, E.; Omer Tayfur Ozturk, E.</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -3355,22 +3106,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lecture notes in computer science</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Springer Science+Business Media</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>book-chapter</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-031-44900-0_4</t>
+          <t>International Society for Technology, Education, and Science. 944 Maysey Drive, San Antonio, TX 78227. Tel: 515-294-1075; Fax: 515-294-1003; email: istesoffice@gmail.com; Web site: http://www.istes.org</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3380,7 +3116,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3392,52 +3128,44 @@
         <is>
           <t>Yes</t>
         </is>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>hybrid</t>
-        </is>
-      </c>
-      <c r="O33" t="n">
-        <v>21</v>
       </c>
       <c r="P33" t="n">
         <v>2</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2023/2ad51015436ad076.pdf</t>
+          <t>2025/0256be53813d4df5.pdf</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>eric</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>Abstract Teaching text-based programming poses significant challenges in both school and university contexts. This study explores the potential of ChatGPT as a sustainable didactic tool to support students, freshmen, and teachers. By focusing on a beginner’s course with examples also relevant to vocational schools, we investigated three research questions. First, the extent to which ChatGPT assists students in solving and understanding initial examples; secondly, the feasibility of teachers utilizing the chatbot for grading student solutions; and finally, the additional support ChatGPT provides in terms of teaching. Our findings demonstrate that ChatGPT offers valuable guidance for teachers in terms of assessment and grading and aids students in understanding and optimizing their solutions.</t>
+          <t>Studies in the fields of education and social sciences have always been important in terms of their impacts on society. The studies in this book contribute to the fields of education and social sciences by different research methods, participants, and contexts and add a global perspective to these fields. The book involves seven chapters: (1) Attitudes and Practices of College Art Teachers towards Culturally Responsive Teaching in Art Creation Courses; (2) International Research on College Students' Perceptions regarding the Impact of the Lasallian Mission on Their Development; (3) The Unseen Revolution: Unlocking the Potential of Cross-Disciplinary Research; (4) The First Women Painters in Turkish Painting and Their Development; (5) Enhancing Research Methodology: The Role of Embedded Librarians in Supporting Academic Excellence; (6) The Role of Interdisciplinary Approaches in Addressing Global Challenges; and (7) The Uses of Artificial Intelligence to Improve Scientific Research to Confront the Problem of Extremism (A Field Study on Egypt).</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>135634b3c7c31d5d</t>
+          <t>5aa6b29d365d2193</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Judicial Decision-Making in the Age of Artificial Intelligence</t>
+          <t>Teaching Electricity and Magnetism in Higher Education through Virtual Reality and Artificial Intelligence</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Gravett, W.</t>
+          <t>Zhanara Malikova; Bayan Ualikhanova</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -3446,22 +3174,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Law, governance and technology series</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Springer International Publishing</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>book-chapter</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-031-41264-6_15</t>
+          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3471,7 +3184,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
@@ -3483,52 +3196,44 @@
         <is>
           <t>Yes</t>
         </is>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>hybrid</t>
-        </is>
-      </c>
-      <c r="O34" t="n">
-        <v>9</v>
       </c>
       <c r="P34" t="n">
         <v>2</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2023/135634b3c7c31d5d.pdf</t>
+          <t>2025/5aa6b29d365d2193.pdf</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>eric</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>Abstract Artificial intelligence (AI) has become a pervasive presence in almost every aspect of society and business: from assigning credit scores to people, to identifying the best candidates for an employment position, to ranking applicants for admission to university. One of the most striking innovations in the United States criminal justice system in the last three decades has been the introduction of risk-assessment software, powered by sophisticated algorithms, to predict whether individual offenders are likely to re-offend. The focus of this contribution is on the use of these risk-assessment tools in criminal sentencing. Apart from the broader social, ethical and legal considerations, to date, not much is known about how perceptions of technology influence cognition in decision-making, particularly in the legal context. What research does demonstrate is that humans are inclined to trust algorithms as objective, and, as such, as unobjectionable. This contribution examines two phenomena in this regard: (i) the “technology effect”—the human tendency towards excessive optimism when making decisions involving technology; and (ii) “automation bias”—the phenomenon whereby judges accept the recommendations of an automated decision-making system, and cease searching for confirmatory evidence, perhaps even transferring responsibility for decision-making onto the machine.</t>
+          <t>In recent years, virtual reality (VR) and artificial intelligence (AI) technologies have been widely adopted across various sectors of society, including education. We conducted a practical study to assess the effectiveness of immersive technologies in higher education institutions. The research was carried out over a period of ten weeks. Students were divided into control and experimental groups. Furthermore, the research work was based on the collection of quantitative data and monitoring students' academic performance. The study's results were analyzed using a paired t-test and descriptive statistics. The independent t-test results indicated significant differences in subsequent test scores between the experimental and control groups. Quantitative descriptive results were presented in the form of diagrams and evaluated across six pedagogical components. At the conclusion of the study, recommendations for future research were provided. [For the complete proceedings, &amp;quot;Proceedings of the International Association for Development of the Information Society (IADIS) International Conference on Cognition and Exploratory Learning in the Digital Age (CELDA) (22nd, Porto, Portugal, November 1-3, 2025),&amp;quot; see ED677812.]</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>7947ac0d82ac46e9</t>
+          <t>fd9e23c6c69b4a0f</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Metabolism in Crisis? A New Interplay Between Physiology and Ecology</t>
+          <t>The Future of Cybersecurity at Sea: Human vs Human or AI vs AI?</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Bognon-Küss, C.</t>
+          <t>Alop, A.</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -3537,12 +3242,12 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>History, philosophy and theory of the life sciences</t>
+          <t>Signals and communication technology</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Springer Nature (Netherlands)</t>
+          <t>Springer Vienna</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -3552,7 +3257,7 @@
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-12604-8_11</t>
+          <t>10.1007/978-3-031-87290-7_1</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3581,14 +3286,14 @@
         </is>
       </c>
       <c r="O35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="P35" t="n">
         <v>2</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2023/7947ac0d82ac46e9.pdf</t>
+          <t>2025/fd9e23c6c69b4a0f.pdf</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -3598,28 +3303,28 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>Abstract This chapter investigates the hybrid relationships between metabolism, broadly and a-historically understood as the set of processes through which alien matter is made homogeneous to that of the organism, and forms of vitalism from the eighteenth century on. While metabolic processes have long been modeled in a reductionist fashion as a straightforward function of repair and expansion of a given structure (either chemically, or mechanistically), a challenging vitalist view has characterized metabolism as a creative, organizing, vital faculty. I suggest that this tension was overcome in Claude Bernard’s works on “indirect nutrition”, in which nutrition, rightly conceived as a general vital phenomenon common to plants and animals, was both characterized as an instance of the general physico-chemical determinism of all phenomena and as the sign and condition of the “freedom and independence” of the organism with respect to the environment. I propose that Bernard’s theory of indirect nutrition was central in the elaboration of his general physiology and has, at the same time, underpinned a self-centered view of biological identity in which the organism creates itself continuously at the detriment of its external milieu . I further argue that this conception of biological individuality as metabolically constructed has since, and paradoxically, supported a view in which the organism appears as an autonomous and self-creating entity. I then contrast this classical view of the metabolic autonomy of the organism with the challenges raised by microbiome studies and suggest that these emerging fields contribute to sketch an ecological conception of the organism and its metabolism through the reconceptualization of its relationship with the environment. The recent focus on a “microbiota – host metabolism” axis contributes to shift the focus away from the classical concept of organism, somehow externalizing vitalism out of the autonomous individual in favor of an ecological, collaborative, and interactionist view of the living.</t>
+          <t>The digitalization of all areas of activity, including maritime, today is characterized, among other things, by two powerful influencing factors: on the one hand, artificial intelligence (AI) increasingly taking over the most important functions and develops very quickly, and on the other hand, threats and risks related to cybersecurity. The common belief, which is hard to argue against, is that the first factor is positive, because it contributes to developments, and the second is undoubtedly negative, because it hinders developments and can even inhibit them; from here, it is easy to conclude that in order to continue and accelerate progress, the positive aspects of the first factor must be contributed in every way and the fight against the effects of the second factor must be undertaken. But how realistic and consistently achievable are these two goals in interaction? True, in the light of the developments of the last years and even months, it seems that the AI “train” has started its impressive journey at high speed, and nothing can stop it. At the same time, continuing the allegory, there is still a “wagon” of cyber threats attached to this “train,” and getting rid of it or even defeating it to a sufficient extent seems problematic, at least now. The author of this chapter expresses an estimated opinion that as long as people fight against each other on both sides of the “cyber war” (“bad” guys against “good” ones), it is so to say war of attrition, where no glorious victory awaits either side. It seems to the author that it is possible to change the situation and achieve victory over the “bad” guys only if the AI itself takes over its own protection. Whether and to what extent this is possible is one of the main topics of this chapter. In the author’s opinion, there can be any truth behind this only if the AI acquires a large part of the characteristics unique to humans (values, moral principles, emotions, etc.), thanks to which it would be possible to be guided by the specific laws or rules of behavior of the AI. As a classic example, the so-called three laws of robotics, formulated by the American science fiction writer Isaac Asimov about 80 years ago, are based on the principle of avoiding harm to humans (Anderson, Asimov’s “Three Laws of Robotics” and machine metaethics, University of Connecticut, Dept. of Philosophy, Stamford, CT, https://cdn.aaai.org/Symposia/Fall/2005/FS-05-06/FS05-06-002.pdf ). In this chapter, we have analyzed whether such AI developments are possible at all and what threats and difficulties this entails in turn.</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>3827a11b5b949e39</t>
+          <t>dd8a0e8d30483815</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Rebuilding After War and Genocide: Learning with and from Refugees in the Transnational Digital Classroom</t>
+          <t>The Impact of AI Tools on Universities’ Educational Strategies and Student Success: Sultan Qaboos University and Qatar University as a Case Study</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Brill-Carlat, M.; Höhn, M.</t>
+          <t>Al-Awadhi, T.; Al-Balushi, A.; Abdullah, M.; Abulibdeh, A.</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -3628,12 +3333,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Political pedagogies</t>
+          <t>Gulf Studies</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Springer International Publishing</t>
+          <t>Springer Nature</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3643,7 +3348,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-12350-4_22</t>
+          <t>10.1007/978-981-97-9667-0_9</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3672,14 +3377,14 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P36" t="n">
         <v>3</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2023/3827a11b5b949e39.pdf</t>
+          <t>2025/dd8a0e8d30483815.pdf</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3689,28 +3394,28 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>Abstract The Covid-19 emergency spurred a flurry of teaching innovations as higher education institutions turned to online or blended learning models, and as international collaborations have moved nearly entirely online. These circumstances inspired us to revisit the digital transatlantic seminar, “Germany 1945: History and Memory in Germany after WWII,” taught by Höhn in Spring 2018 to a group of seven Vassar students (Brill-Carlat among them) and six advanced high-school students—between the ages of 17 and 22—who had come to Berlin as asylum seekers from Syria, Iraq, and Afghanistan. The course dealt with history and memory of World War II and the Holocaust in Germany. As such, it reflected a core commitment of the Consortium on Forced Migration, Displacement, and Education (CFMDE), founded by Höhn at Vassar and partners (Bard, Bennington, Sarah Lawrence, the New School, and the Council for European Studies): the importance of providing opportunities for our undergraduate students to learn with and from refugees and displaced individuals if they are to understand and tackle the global, multidimensional challenges of forced migration. As institutional resistance to digital teaching necessarily vanished with the Covid-19 pandemic in Spring 2020 and the direction of future online-learning policies is up for debate, we revisit the 2018 class to examine lessons learned and how this project points the way to another digital venture: digitally “hosting” displaced scholars at liberal arts campuses.</t>
+          <t>Abstract Sultan Qaboos University (SQU) and Qatar University (QU) are working to adopt short- and long-term plans to ensure leadership in teaching and learning, scientific research, and community service at regional and international levels. Modern technologies, especially artificial intelligence (AI), play an important role in our lives, providing realistic opportunities to accelerate business implementation and improve the final value of work. AI plays a crucial role in taking education and research to the next level, transforming the way these organisations work and make decisions. AI can improve the traditional work of educational institutions and transform the understanding of their complexity. However, challenges remain in various aspects, whether related to the nature of our work or to the AI technologies themselves. This is still a great opportunity for every HEI. Therefore, this paper aims to analyse the potential of AI to accelerate the implementation of the strategic plans of the two universities.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>c81bf633e42c7f19</t>
+          <t>ccacb2251f5b4e56</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Survey of AI Tool Usage in Programming Course: Early Observations</t>
+          <t>Thinking Along the Lines Generated by GenAI? A Systematic Mapping Study on Academic Writing</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Saari, M.; Rantanen, P.; Nurminen, M.; Kilamo, T.; Systä, K.; Abrahamsson, P.</t>
+          <t>Kaczkó, É.; Ivanjek, L.; Norz, L.; Ammenwerth, E.</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -3719,7 +3424,7 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lecture notes in business information processing</t>
+          <t>Lecture notes in computer science</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -3734,7 +3439,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-48550-3_18</t>
+          <t>10.1007/978-3-032-11108-1_35</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3763,14 +3468,14 @@
         </is>
       </c>
       <c r="O37" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P37" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2023/c81bf633e42c7f19.pdf</t>
+          <t>2025/ccacb2251f5b4e56.pdf</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3780,28 +3485,28 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>Abstract This study explores the role of artificial intelligence (AI) in university teaching, with a focus on the teaching of programming. Despite the growing use of AI in education, both students and teachers often struggle to understand its role and implications. To address this gap, we conducted a survey of a wide group of students (n = 200) to assess their experiences and perspectives on the use of AI in programming education. The survey results suggest that AI is becoming increasingly involved in university teaching, particularly in the teaching of programming. However, students require guidance from teachers in order to use AI tools effectively in their studies. The study concludes that the goal of teaching programming should be to guide students in the responsible use of AI. Overall, the study highlights the need for greater awareness and understanding of AI in university teaching and the fact that teachers have an important role to play in providing guidance to students on the responsible use of AI tools.</t>
+          <t>The advent of generative AI (GenAI) tools in higher education challenges fundamental assumptions about academic authorship, students’ cognitive development and how writing cultivates critical thinking (CT). This systematic mapping study synthesized emerging research on how GenAI is reshaping the relationship between academic writing and CT in higher education. Drawing on 25 peer-reviewed studies published between 2023 and 2025, we analyzed conceptualizations of CT and academic writing, identified pedagogical approaches, and examined the use of GenAI tools across a range of disciplines, educational levels, and geographic contexts. Findings revealed that interest in the use of GenAI in academic writing is global and spans all disciplines and higher educational levels. However, only a minority of studies drew on robust theoretical frameworks. CT was conceptualized predominantly within a cognitive skills paradigm, while broader understandings linked to criticality and critical pedagogy were largely absent. Pedagogical models were rare and mostly untested, and educators’ perspectives were underrepresented. While GenAI was seen as supporting writing processes, its potential to foster or hinder CT remained contested. Future research should broaden conceptual foundations, include educator perspectives, and prioritize pedagogical design and evaluation. Rethinking academic writing as a transformative practice may require moving beyond the cognitive paradigm towards more participatory and ethically grounded approaches to CT.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>96a698008602b3d7</t>
+          <t>8a4a82dd2792d328</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>The Role of Educational Interventions in Facing Social Media Threats: Overarching Principles of the COURAGE Project</t>
+          <t>University Students&amp;apos; Perceptions of the Use of Productive Artificial Intelligence: The Effects of ChatGPT on Assignment Processes</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Taibi, D.; Börsting, J.; Hoppe, U.; Ognibene, D.; Hernández-Leo, D.; Eimler, S.; Kruschwitz, U.</t>
+          <t>Halil Güvel; Muhammet Demirbilek; Seyfullah Gökoglu</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2023</v>
+        <v>2025</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -3810,22 +3515,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Communications in computer and information science</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Springer Science+Business Media</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>book-chapter</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-031-29800-4_25</t>
+          <t>International Society for Technology, Education, and Science. 944 Maysey Drive, San Antonio, TX 78227. Tel: 515-294-1075; Fax: 515-294-1003; email: istesoffice@gmail.com; Web site: http://www.istes.org</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3835,7 +3525,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3848,75 +3538,52 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>hybrid</t>
-        </is>
-      </c>
-      <c r="O38" t="n">
-        <v>6</v>
-      </c>
       <c r="P38" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2023/96a698008602b3d7.pdf</t>
+          <t>2025/8a4a82dd2792d328.pdf</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>eric</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>Abstract Social media are offering new opportunities for communication and interaction way beyond what was possible only a few years ago. However, social media are also virtual spaces where young people are exposed to a variety of threats. Digital addiction, discrimination, hate speech, misinformation, polarization as well as manipulative influences of algorithms, body stereotyping, and cyberbullying are examples of challenges that find fertile ground on social media. Educators and students are not adequately prepared to face these challenges. To this aim, the COURAGE project, presented in this paper, introduces new tools and learning methodologies that can be adopted within higher education learning paths to train educators to deal with social media threats. The overarching principles of the COURAGE project leverage the most recent advances in the fields of artificial intelligence and in the educational domain paired with social and media psychological insights to support the development of the COURAGE ecosystem. The results of the experiments currently implemented with teachers and students of secondary schools as well as the impact of the COURAGE project on societal changes and ethical questions are presented and discussed.</t>
+          <t>This study examines the perceptions of university students towards the use of generative artificial intelligence (GAI) in educational processes, especially in assignments. The main features of URM are human-like language abilities and the capacity to generate predictive content. In the study, descriptive research method, which is a quantitative method, was used to measure the views of university students towards the use of URM. The data collected from the participants in online format were analyzed through descriptive analysis. The findings of the study show that the majority of the students find it useful to use UIC tools such as ChatGPT in their assignments. While 63% of the students thought that using ChatGPT in assignments was useful, 21% were undecided and 16% expressed negative opinions. There was a high level of positive feedback that ChatGPT increased success in the assignment process, speeded up work and supported productivity. However, some students reported concerns about the impact of this technology on academic ethics issues and possible negative aspects on critical thinking skills. It was observed that students found the process of learning and using ChatGPT easy but needed integration and guidance support. In addition, the incentives from their social environment were found to have an impact on students' tendency to use the IWB. The study recommends developing guidance and training programs on the use of URMs, raising awareness about the accuracy of information, and encouraging ethical use. [For the complete proceedings, see ED678757.]</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>e3b815e1a83132e6</t>
+          <t>2a772f767ed3fd8e</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>About the Editor</t>
+          <t>Beyond the Books: A Study on AI Augmentation in Civil Engineering Pedagogy for Pavement Design</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MBA, S.</t>
+          <t>Javier Vásquez-Monteros; Yasmany García-Ramírez</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>pre_chatgpt</t>
+          <t>post_chatgpt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Digital Health</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>SAGE Publishing</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>book-chapter</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>10.36255/exon-publications-digital-health.editor</t>
+          <t>International Society for Technology, Education, and Science. 944 Maysey Drive, San Antonio, TX 78227. Tel: 515-294-1075; Fax: 515-294-1003; email: istesoffice@gmail.com; Web site: http://www.istes.org</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3926,7 +3593,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3939,65 +3606,57 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>gold</t>
-        </is>
-      </c>
-      <c r="O39" t="n">
-        <v>0</v>
-      </c>
       <c r="P39" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2022/e3b815e1a83132e6.pdf</t>
+          <t>2024/2a772f767ed3fd8e.pdf</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>eric</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>Professor Simon Lin Linwood, MD, MBA, is the Chief Medical Information Officer at the UCR Health and UCR School of Medicine, Riverside, CA, USA. He obtained his executive education in Artificial Intelligence Strategy and Implementation from Harvard University. He was named Innovator of the Year by CHIME in 2018. He is a national thought leader on digital transformation and acknowledged for providing vision and leadership in information technology to drive business growth in large, complex, and highly distributed environments. He has supervised and mentored many PhD students on data-driven innovation in healthcare, such as deep learning for risk prediction in population health to control costs, and methods to reduce physician documentation burden. He received Mentor of the Year Award in 2016. His areas of expertise include digital transformation, data-driven innovation, data science, data lake, artificial intelligence, and natural language processing, among others. He has extensively published on digital health, artificial intelligence/machine learning, data science, clinical informatics, genome informatics.</t>
+          <t>This study investigates the integration of AI tools, ChatGPT 3.5 and Bard (now Gemini), in the education of civil engineering students specializing in pavement design. Two groups, totaling sixty-eight undergraduate students (Group A=28, Group B=40), enrolled in the Pavement Design course at UTPL from October 2023 to February 2024, participated. They were tasked with generating prompts covering various pavement design topics. These included Traffic, Subgrade Characteristics, Asphalt Materials, AASHTO-Flexible Design, AASHTO-Rigid Design, Interlocking Concrete Pavements Design, International Roughness Index (IRI), and Construction Systems on Pavements. Students then assessed AI-generated responses using a predefined grading scale. The results revealed Bard achieved a higher approval rate of 71.1% compared to ChatGPT's 48.5%. ChatGPT 3.5 would not meet the passing threshold for certain topics, such as AASHTO-Flexible Design, AASHTO-Rigid Design, and IRI. In contrast, Bard consistently achieved higher approval rates across all assessed topics. Students acknowledged the AI tools' significant contribution to a deeper understanding of the course material. This integration positively influenced civil engineering students' learning outcomes, highlighting the evolving role of AI in education and encouraging further exploration in academia. [For the complete proceedings, see ED672804.]</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>246ac766bd6d1c42</t>
+          <t>bebfc35847a401fc</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>List of Contributors</t>
+          <t>Characteristics of Romanian Online Recruitment Websites and Students’ Use</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Contributors, L.</t>
+          <t>Mardache, A.; Balasescu, M.</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>2022</v>
+        <v>2024</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>pre_chatgpt</t>
+          <t>post_chatgpt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Digital Health</t>
+          <t>Springer proceedings in business and economics</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>SAGE Publishing</t>
+          <t>Springer International Publishing</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -4007,7 +3666,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>10.36255/exon-publications-digital-health.contributors</t>
+          <t>10.1007/978-3-031-51038-0_76</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -4017,7 +3676,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
@@ -4032,18 +3691,18 @@
       </c>
       <c r="N40" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2022/246ac766bd6d1c42.pdf</t>
+          <t>2024/bebfc35847a401fc.pdf</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -4053,37 +3712,37 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>ABRAR-AHMAD ZULFIQAR, MDService de Médecine Interne, Diabète et Maladies métaboliques de la Clinique Médicale B, Hôpitaux Universitaires de Strasbourg et Equipe EA 3072 “Mitochondrie, Stress oxydant et Protection musculaire”, Faculté de Médecine-Université de Strasbourg, Strasbourg, France AIKO OSAWA, MD, PHDNational Center for Geriatrics and Gerontology, Aichi, Japan AMIR HAJJAM, PHDLaboratoire IRTES-SeT, Université de Technologie de Belfort-Montbéliard (UTBM), Belfort-Montbéliard, Belfort, France BRYONY MCGARRY, PHDPRECISE4Q, Predictive Modelling in Stroke, Technological University Dublin, Dublin, Ireland CEES TH. SMIT SIBINGA, MD, PHD, FRCP, FRCPATHIQM Consulting and University of Groningen, De Gast 46, 9801AE Zuidhorn, The Netherlands CLÁUDIA S. SOUSA, MDPulmonology Department, Central Hospital of Funchal, Portugal EMMANUEL ANDRÈS, MD, PHDLaboratoire IRTES-SeT, Université de Technologie de Belfort-Montbéliard (UTBM), Belfort-Montbéliard, Belfort, France EN-JU LIN, PHD, MPHResearch Information Solutions and Innovation, The Research Institute at Nationwide Children’s Hospital, Columbus, OH, USA ESRA ZIHNI, MSCPRECISE4Q, Predictive Modelling in Stroke, Technological University Dublin, Dublin, Ireland HIDENORI ARAI, MD, PHDNational Center for Geriatrics and Gerontology, Aichi, Japan IRVING D. KAPLAN, MDDepartment of Radiation Oncology, Beth Israel Deaconess Medical Center, Boston, MA, USA JENAY YUEN, BSKeck School of Medicine, University of Southern California, California, USA JESSAMINE P. WINER-JONES, PHDTriNetX, LLC, Cambridge, MA, USA JOHN KELLEHER, PHDPRECISE4Q, Predictive Modelling in Stroke, Technological University Dublin, Dublin, Ireland KATHARINE LAWRENCE, MD MPHNYU Grossman School of Medicine, Department of Population Health; NY, USA LIMOR APPELBAUM, MDDepartment of Radiation Oncology, Beth Israel Deaconess Medical Center, Boston, MA, USA MADELEINE SCHROEDER, MSResearch Information Solutions and Innovation, The Research Institute at Nationwide Children’s Hospital, Columbus, OH, USA MÁRIO MORAIS-ALMEIDA, MDAllergy Centre, CUF Descobertas Hospital, Lisboa, Portugal MARTIN RINARD, PHDComputer Science and Artificial Intelligence Laboratory, Massachusetts Institute of Technology, Cambridge, MA, USA MATVEY B. PALCHUK, MD, MSTriNetX, LLC, Cambridge, MA, USA MAURICE MARS, MBCHB, MDDepartment of TeleHealth, University of KwaZulu-Natal, Durban, South Africa MIGUEL T. BARBOSA, MDAllergy Centre, CUF Descobertas Hospital, Lisboa, Portugal MOHAMED HAJJAM, MDPredimed Technology, Schiltigheim, France RICHARD E. SCOTT, PHDDepartment of Community Health Sciences, University of Calgary, Calgary, Alberta, Canada SARAH PIKE, BAKeck School of Medicine, University of Southern California, California, USA SHINICHIRO MAESHIMA, MD, PHDKinjo University, Ishikawa, Japan SIMON LIN LINWOOD, MD, MBASchool of Medicine, University of California, Riverside, CA, USA STEVE KHACHIKYANDornsife College of Letters, Arts &amp;amp; Sciences, University of Southern California, California, USA STEVEN KUNDROT, BS, MBA&amp;nbsp;TriNetX, LLC, Cambridge, MA, USA SUDHA NALLASAMY, MDThe Vision Center at Children’s Hospital Los Angeles, California, USA; USC Roski Eye Institute, University of Southern California, California, USA YUNGUI HUANG, PHD, MBAResearch Information Solutions and Innovation, The Research Institute at Nationwide Children’s Hospital, Columbus, OH, USA</t>
+          <t>Abstract Technology has increasingly changed the way human resource (HR) function achieves its goals. Organizations seek agile employees who can cope with continuous changes in a complex and uncertain environment. Effective recruitment is closely related to talent management, as organizations are interested in attracting talented people who can give a competitive advantage for the organization. The use of technology and artificial intelligence in recruitment will increasingly enable the creation of profiles that help organizations attract the best candidates for vacancies. In this context, due to its multiple advantages both for organizations and candidates, online recruitment is increasingly being used. However, it is important to be aware of the various problems associated with online recruitment and to find solutions in solving them. In this study, we conducted a content analysis of ten of the most popular recruitment websites in Romania, according to a wide range of criteria concerning the jobs on offer, but also the features of the sites. Moreover, we also conducted an exploratory survey (with a sample of 200 students) in order to identify the perception and use of these recruitment websites by students and recent university graduates. Recruitment websites are more and more complex and offer diverse and useful tools for users. Some of them already use artificial intelligence to help users identify the most compatible job. Students and recent university graduates predominantly use such websites when they are looking for a job.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>05cd11abf81f4c96</t>
+          <t>323ecbe01d1cd744</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Artificial Intelligence and Machine Learning: An Instructor’s Exoskeleton in the Future of Education</t>
+          <t>Last Tendencies in Acquiring Text Competence in the Field of Tourism. The Case of Chatbots and AI</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>August, S.; Tsaima, A.</t>
+          <t>Madueño, M.</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>pre_chatgpt</t>
+          <t>post_chatgpt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>SpringerBriefs in statistics</t>
+          <t>Springer proceedings in business and economics</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -4098,7 +3757,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>10.1007/978-3-030-58948-6_5</t>
+          <t>10.1007/978-3-031-52607-7_17</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -4127,69 +3786,54 @@
         </is>
       </c>
       <c r="O41" t="n">
-        <v>26</v>
+        <v>1</v>
       </c>
       <c r="P41" t="n">
         <v>2</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2021/05cd11abf81f4c96.pdf</t>
+          <t>2024/323ecbe01d1cd744.pdf</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>openalex,s2</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>Abstract The role of artificial intelligence in US education is expanding. As education moves toward providing customized learning paths, the use of artificial intelligence (AI) and machine learning (ML) algorithms in learning systems increases. This can be viewed as growing metaphorical exoskeletons for instructors, enabling them to provide a higher level of guidance, feedback, and autonomy to learners. In turn, the instructor gains time to sense student needs and support authentic learning experiences that go beyond what AI and ML can provide. Applications of AI-based education technology support learning through automated tutoring, personalizing learning, assessing student knowledge, and automating tasks normally performed by the instructor. This technology raises questions about how it is best used, what data provides evidence of the impact of AI and ML on learning, and future directions in interactive learning systems. Exploration of the use of AI and ML for both co-curricular and independent learnings in content presentation and instruction; interactions, communications, and discussions; learner activities; assessment and evaluation; and co-curricular opportunities provide guidance for future research.</t>
+          <t>Abstract Our aim is to propose the usage of generative Artificial Intelligence, hereafter AI, while lecturing, as a complement to the traditional methodology, to ease technological skills acquisition in the related AI. Widely spread in all aspects of cultural life and professional praxis worldwide, it is of key importance in the training of our professional to be. In Malaga University’s Degree of Tourism, in subjects dealing with English for tourism management, we shall concentrate on chatbots aided by AI, in order to make a literary review to see the state of the question and to reflect on the needed changes to implement these tools. We shall try to outline the characteristics, possibilities, advantages and disadvantages, and the influence on both students and lecturers alike of the usage of AI in chatbots to deal with outcoming texts. Direct interaction with the tools will be highlighted. Of key importance is training lecturers in the productive use of “prompt engineering”. To conclude, handling specialised texts in the field of tourism by means of chatbots might help lecturers’ awareness and responsibility for right use to obtain semi-specialised and specialised texts in the field of tourism in order to understand, extract and evaluate its pertinence.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>e4785c336fe78ec7</t>
+          <t>4ef9c0fd48d39cc4</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Personalized and Adaptive Learning</t>
+          <t>Leveraging ChatGPT for Automated Knowledge Concept Generation</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Taylor, D.; Yeung, M.; Bashet, A.</t>
+          <t>Tianyuan Yang; Baofeng Ren; Chenghao Gu; Boxuan Ma; Shin 'ichi Konomi</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>pre_chatgpt</t>
+          <t>post_chatgpt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>SpringerBriefs in statistics</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Springer International Publishing</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>book-chapter</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-030-58948-6_2</t>
+          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -4199,7 +3843,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -4212,65 +3856,57 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="N42" t="inlineStr">
-        <is>
-          <t>hybrid</t>
-        </is>
-      </c>
-      <c r="O42" t="n">
-        <v>136</v>
-      </c>
       <c r="P42" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2021/e4785c336fe78ec7.pdf</t>
+          <t>2024/4ef9c0fd48d39cc4.pdf</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>openalex,s2</t>
+          <t>eric</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>Abstract Personalized and adaptive learning has been touted to be one of the most promising emerging tools for increasing student learning and student success. Yet, the terms are neither precise nor clearly defined at this time, thus making it difficult for institutions of higher education to adopt and implement a learning approach using technology that is in its infancy and not clearly understood by those who will be utilizing it. One goal of this chapter is to define adaptive and personalized learning as it is used at this time in the hopes that as the technology evolves the promise of increased student learning can come to fruition. Adaptive learning personalizes learning by continuously evaluating each student’s performance in real time and creating an ever-changing individualized learning pathway as directed by artificial intelligence and machine learning, thus increasing learning and student satisfaction.</t>
+          <t>As education increasingly shifts towards a technology-driven model, artificial intelligence systems like ChatGPT are gaining recognition for their potential to enhance educational support. In university education and MOOC environments, students often select courses that align with their specific needs. During this process, access to information about the knowledge concepts covered in a course can help students make more informed decisions. However, manually constructing this knowledge concept information is a labor-intensive and time-consuming task. In this paper, we explore the capability of ChatGPT in generating relevant knowledge concepts from course syllabi and evaluate the accuracy and consistency of these AI-generated concepts against course content using four assessment techniques at both the concept level and course level. We investigate the feasibility of using ChatGPT-generated concepts as a direct educational resource, as well as their potential integration into broader educational technologies, such as interpretable course recommendation systems. [For the full proceedings, see ED665357.]</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>085fa965ce157d51</t>
+          <t>e799f9736c02ac60</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Robots as My Future Colleagues: Changing Attitudes Toward Collaborative Robots by Means of Experience-Based Workshops</t>
+          <t>Overcoming the Long Shadow of the Past: Defense AI in Japan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Leoste, J.; Viik, T.; López, J.; Kangur, M.; Vunder, V.; Mollard, Y.; Õun, T.; Tammo, H.; Paekivi, K.</t>
+          <t>Tsuchiya, M.</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>pre_chatgpt</t>
+          <t>post_chatgpt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Smart innovation, systems and technologies</t>
+          <t>Contributions to security and defence studies</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Springer Nature</t>
+          <t>Springer International Publishing</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -4280,7 +3916,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>10.1007/978-981-16-3930-2_13</t>
+          <t>10.1007/978-3-031-58649-1_22</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -4309,14 +3945,14 @@
         </is>
       </c>
       <c r="O43" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P43" t="n">
         <v>2</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2021/085fa965ce157d51.pdf</t>
+          <t>2024/e799f9736c02ac60.pdf</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4326,42 +3962,42 @@
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>Abstract Artificial intelligence-driven robots are increasingly being introduced in various workplaces. Research implies that people’s negative attitudes toward intelligent and collaborative robots might hinder their willingness to use them. We propose that interactive educational activities such as specialized workshops help people to overcome such negative attitudes. We designed a two-day workshop that introduced two quasi-industrial robots (Poppy Ergo Jr and ClearBot) to 16 university students. Students’ attitudes were qualitatively measured before and after the workshop. The results imply that the workshop helped students to increase their understanding of the nature of the intelligent collaborative robots. More precisely, robots became to be seen as empowering tools, rather than friends or enemies. Interestingly, there were significant gender differences, as the female participants had a greater tendency to view robots as animated objects. We concluded that specialized workshops effectively lead participants to become aware of various promising opportunities for their robotic co-workers in the possible future.</t>
+          <t>Abstract Since the end of World War II, Japan has not had a full-fledged military, but only Self-Defense Forces (SDF) for the sole purpose of “exclusively defensive defense.” Hesitancy exists in society, especially in academia, to research and develop technologies that could be diverted to military use. This has created a long shadow of the past in which public opinion, strategic culture, and the academic-industrial ecosystem mutually reinforce each other not to directly address defense technologies, though Japan is often recognized as one of the most technologically advanced countries. However, with the recent deterioration of the national security environment around Japan, such hesitance is weakening, and research and development of technologies that can be applied to defense purposes is now being conducted, also in cooperation with partners like the United States, the United Kingdom, and others. Discussions about artificial intelligence (AI) for defense purposes began in earnest around 2022, with descriptions found in government and defense documents, and budget appropriations beginning to be made. However, the budget size is miniscule and no special organization for defense AI exists. In addition, there is no plan to use defense AI in earnest in defense operations, and it is merely positioned as one of the technologies that are attracting widespread attention. The defense industry is working on AI across the board, but Japan’s defense industry has a large proportion of civilian demand, and there are aspects of the industry that are not necessarily for defense use. If necessary, they will be applied to defense applications, but they are not actively promoted as AI for defense. Attempts to deepen the knowledge of AI among SDF personnel have only just begun.</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0141788f9ac5d7cb</t>
+          <t>148d777c7af8aaae</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>University Student Surveys Using Chatbots: Artificial Intelligence Conversational Agents</t>
+          <t>Reimagining Extreme Event Scenarios: The Aesthetic Visualisation of Climate Uncertainty to Enhance Preparedness</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Abbas, N.; Pickard, T.; Atwell, E.; Walker, A.</t>
+          <t>Favero, D.; Thurow, S.; Pagnucco, M.; Frohne, U.</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>2021</v>
+        <v>2024</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>pre_chatgpt</t>
+          <t>post_chatgpt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lecture notes in computer science</t>
+          <t>Arts, research, innovation and society</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Springer Science+Business Media</t>
+          <t>Springer International Publishing</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -4371,7 +4007,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>10.1007/978-3-030-77943-6_10</t>
+          <t>10.1007/978-3-031-56114-6_2</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4396,59 +4032,63 @@
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="O44" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="P44" t="n">
         <v>2</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2021/0141788f9ac5d7cb.pdf</t>
+          <t>2024/148d777c7af8aaae.pdf</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
         <is>
-          <t>openalex,s2</t>
-        </is>
-      </c>
-      <c r="S44" s="2" t="n"/>
+          <t>openalex</t>
+        </is>
+      </c>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Responding to the rapidly escalating climate emergency, this chapter outlines transformative multidisciplinary research centred on the visualisation of unpredictable extreme event scenarios. It proposes a unique, scientifically grounded artistic approach to one of the world’s most immediate challenges—preparing communities for extreme climate events, such as firestorms and flash floods. As preparedness is a function of prior threat experience, it argues that visualising threat scenarios in advance can be a key to surviving and adapting in an era of increasing climate instability. This approach can enable communities to viscerally experience and rehearse threat perception, situational awareness, adaptive decision making and dynamic response to unexpected life-threatening extreme events. Using experimental case studies at The University of New South Wales’s iCinema Research Centre and international benchmarks, this chapter explores how advances in immersive visualisation and artificial intelligence aesthetics can be integrated to provide a framework that enables the virtual prototyping of unforeseen geolocated climate scenarios to facilitate readiness in the face of accelerating climate uncertainty.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>d0f022dbfc25bf9e</t>
+          <t>5beff436c4263cda</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>About the Book</t>
+          <t>Retrieval Augmented Large Language Model Chatbots in Higher Education: A Study on University Open Days</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Bartneck, C.; Lütge, C.; Wagner, A.; Welsh, S.</t>
+          <t>Shanthakumar, A.; Fassihi-Tash, F.; Lotfi, A.; Bird, J.</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>pre_chatgpt</t>
+          <t>post_chatgpt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>SpringerBriefs in ethics</t>
+          <t>Advances in intelligent systems and computing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Springer International Publishing</t>
+          <t>Springer Nature</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4458,7 +4098,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>10.1007/978-3-030-51110-4_1</t>
+          <t>10.1007/978-3-031-78857-4_3</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4483,63 +4123,59 @@
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>hybrid</t>
+          <t>green</t>
         </is>
       </c>
       <c r="O45" t="n">
         <v>1</v>
       </c>
       <c r="P45" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2020/d0f022dbfc25bf9e.pdf</t>
+          <t>2024/5beff436c4263cda.pdf</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>openalex</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="inlineStr">
-        <is>
-          <t>This book provides an introduction into the ethics of robots and artificial intelligence. The book was written with university students, policy makers, and professionals in mind but should be accessible for most adults. The book is meant to provide balanced and, at times, conflicting viewpoints as to the benefits and deficits of AI through the lens of ethics. As discussed in the chapters that follow, ethical questions are often not cut and dry. Nations, communities, and individuals may have unique and important perspectives on these topics that should be heard and considered. While the voices that compose this book are our own, we have attempted to represent the views of the broader AI, robotics, and ethics communities.</t>
-        </is>
-      </c>
+          <t>openalex,s2</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>68c8ca7f7b8e293f</t>
+          <t>a366da3974dd03f0</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Collaborative Innovation Between Shenzhen Municipal Government and Tsinghua University</t>
+          <t>Ruffle&amp;amp;Riley: Insights from Designing and Evaluating a Large Language Model-Based Conversational Tutoring System</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Kang, F.</t>
+          <t>Schmucker, R.; Xia, M.; Azaria, A.; Mitchell, T.</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>pre_chatgpt</t>
+          <t>post_chatgpt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Education in the Asia-Pacific region</t>
+          <t>Lecture notes in computer science</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Springer Nature</t>
+          <t>Springer Science+Business Media</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -4549,7 +4185,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>10.1007/978-981-15-7018-6_20</t>
+          <t>10.1007/978-3-031-64302-6_6</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4578,69 +4214,54 @@
         </is>
       </c>
       <c r="O46" t="n">
+        <v>32</v>
+      </c>
+      <c r="P46" t="n">
         <v>4</v>
       </c>
-      <c r="P46" t="n">
-        <v>3</v>
-      </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2020/68c8ca7f7b8e293f.pdf</t>
+          <t>2024/a366da3974dd03f0.pdf</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>openalex,s2</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>Global megatrendsGlobal megatrends—the rise of frontier technologies, the dramatic growth of information, sociopolitical landscape changes, and demographic changes—call for the need for ecosystem orchestration that requires collaboration. The People’s Republic of China has been heavily investing on Artificial Intelligence (AI) and Research and Development (R&amp;D) to become an innovation leader globally and to further leverage its position as a manufacturing powerhouse. The Chinese innovation ecosystemInnovation ecosystem has grown steadily in recent years as they tapped higher education and research institutes. University-research-industry linkagesUniversity-research-industry linkages have proven to be successful in achieving PRC’s innovation-driven endeavors as evidenced by the large number of firms and start-ups from such linkages have grown into large businesses and key technological leaders.</t>
+          <t>Abstract Conversational tutoring systems (CTSs) offer learning experiences through interactions based on natural language. They are recognized for promoting cognitive engagement and improving learning outcomes, especially in reasoning tasks. Nonetheless, the cost associated with authoring CTS content is a major obstacle to widespread adoption and to research on effective instructional design. In this paper, we discuss and evaluate a novel type of CTS that leverages recent advances in large language models (LLMs) in two ways: First, the system enables AI-assisted content authoring by inducing an easily editable tutoring script automatically from a lesson text. Second, the system automates the script orchestration in a learning-by-teaching format via two LLM-based agents (Ruffle&amp;amp;Riley) acting as a student and a professor. The system allows for free-form conversations that follow the ITS-typical inner and outer loop structure. We evaluate Ruffle&amp;amp;Riley’s ability to support biology lessons in two between-subject online user studies ( $$N = 200$$ &lt;mml:math xmlns:mml="http://www.w3.org/1998/Math/MathML"&gt; &lt;mml:mrow&gt; &lt;mml:mi&gt;N&lt;/mml:mi&gt; &lt;mml:mo&gt;=&lt;/mml:mo&gt; &lt;mml:mn&gt;200&lt;/mml:mn&gt; &lt;/mml:mrow&gt; &lt;/mml:math&gt; ) comparing the system to simpler QA chatbots and reading activity. Analyzing system usage patterns, pre/post-test scores and user experience surveys, we find that Ruffle&amp;amp;Riley users report high levels of engagement, understanding and perceive the offered support as helpful. Even though Ruffle&amp;amp;Riley users require more time to complete the activity, we did not find significant differences in short-term learning gains over the reading activity. Our system architecture and user study provide various insights for designers of future CTSs. We further open-source our system to support ongoing research on effective instructional design of LLM-based learning technologies.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>ccad16bc20847787</t>
+          <t>9184c19bd9973246</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Correction to: Predictive Policing in 2025: A Scenario</t>
+          <t>Success through Error: Using Error Analysis of ChatGPT Output in English as a Foreign Language Learner Writing Instruction</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Macnish, K.; Wright, D.; Jiya, T.</t>
+          <t>Arifi Waked; Muhammad W. Ashraf; Hanadi AbdelSalam; Khadija El Alaoui; Maura Pilotti</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>pre_chatgpt</t>
+          <t>post_chatgpt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Advanced sciences and technologies for security applications</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Springer International Publishing</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>book-chapter</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-030-50613-1_9</t>
+          <t>International Society for Technology, Education, and Science. 944 Maysey Drive, San Antonio, TX 78227. Tel: 515-294-1075; Fax: 515-294-1003; email: istesoffice@gmail.com; Web site: http://www.istes.org</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4650,7 +4271,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4662,66 +4283,58 @@
         <is>
           <t>Yes</t>
         </is>
-      </c>
-      <c r="N47" t="inlineStr">
-        <is>
-          <t>hybrid</t>
-        </is>
-      </c>
-      <c r="O47" t="n">
-        <v>10</v>
       </c>
       <c r="P47" t="n">
         <v>2</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2020/ccad16bc20847787.pdf</t>
+          <t>2024/9184c19bd9973246.pdf</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
         <is>
-          <t>openalex,s2</t>
+          <t>eric</t>
         </is>
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>Abstract Law enforcement authorities (LEAs) have begun using artificial intelligence and predictive policing applications that are likely to raise ethical, data protection, social, political and economic issues. This paper describes application of a new scenario methodology for identifying issues that emerging technologies are likely to raise in a future six or seven years hence, but that deserve policymakers’ attention now. It often takes policymakers that long to develop a new policy, consult with stakeholders and implement the policy. Thus, policymakers need a structured, but concise framework in order to understand the issues and their various implications. At the same time, they also prefer policies that have stakeholder support. These considerations led the University of Twente in the Netherlands and the UK’s Trilateral Research to develop the scenario that follows. It is structured with several headings that policymakers need to consider in order to move toward a desired future and avoidance of an undesired future.</t>
+          <t>Questions exist as to whether AI tools, such as ChatGPT, can aid learning. This study examined whether in-class exercises involving error detection in text generated by ChatGPT can aid students' foreign language writing. Participants were Arabic-English speakers who were classified as ranging from modest to competent English users according to IELTS standards. There were two conditions, each involving four sections of an English communication course, distributed across consecutive semesters and taught by the same instructor. In the treatment condition (n = 101), students performed error detection exercises using text generated by ChatGPT. In the control condition (n = 112), students performed the same exercises without ChatGPT. Then, they wrote a descriptive essay. It was hypothesized that if ChatGPT exercises enhanced students' confidence as writers, they would write longer essays. If ChatGPT exercises enhanced attention to detail, the exercises would increase writing quality (e.g., greater use of low-frequency and abstract words, and greater reliance on complex syntactic structures). In this study, students exposed to ChatGPT exercises used more low-frequency words and wrote more sentences but of shorter length than control condition students. The number of words did not differ, suggesting that ChatGPT exercises enhanced writers' attention to the shorter sentence length of the English language and its vast vocabulary. The results of this study suggest that ChatGPT exercises yield minor benefits for improving the writing of second-language speakers. Yet, extensive and broader exercises may yield more substantial benefits. [For the complete proceedings, see ED672804.]</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>e97796436a92a9c7</t>
+          <t>2c028fbe91e54d72</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Creative Composition Problem: A Knowledge Graph Logical-Based AI Construction and Optimization Solution - Applied in Cecilia: An Architecture of a Digital Companion Artificial Intelligence (AI) Agent System Composer of Dialogue Scripts for Well-Being and Mental Health</t>
+          <t>Survival of the Smartest? Defense AI in Ukraine</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Galindo, M.; Moreno, L.</t>
+          <t>Goncharuk, V.</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2020</v>
+        <v>2024</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>pre_chatgpt</t>
+          <t>post_chatgpt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lecture notes in computer science</t>
+          <t>Contributions to security and defence studies</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Springer Science+Business Media</t>
+          <t>Springer International Publishing</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
@@ -4731,7 +4344,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>10.1007/978-3-030-72308-8_4</t>
+          <t>10.1007/978-3-031-58649-1_17</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4760,113 +4373,2389 @@
         </is>
       </c>
       <c r="O48" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P48" t="n">
         <v>2</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2020/e97796436a92a9c7.pdf</t>
+          <t>2024/2c028fbe91e54d72.pdf</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>openalex,s2</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>Abstract Contribution of this work is to Define the Creative Composition Problem (CCP) for Human Well-being Optimization by Construction of Knowledge Graph using Knowledge Representation and logic-based Artificial Intelligence reasoning-planning where the computation of the Optimal Solution is achieved by Dynamic Programming or Logic Programming. The Creative Composition Problem is embedded within Cecilia: an architecture of a digital companion artificial intelligence agent system composer of dialogue scripts for Well-being and Mental Health. Where Cecilia Framework is instantiated in Well-being and Mental Health domain for optimal well-being development of first year university students. We define the ‘The Problem of Creating a Dialogue Composition (PCDC)’ and we propose a feasible and optimal solution of it. CCP is instantiated in this applied domain to solve PCDC optimizing the Mental Health and Well-being of the student. CCP as PCDC is applied to optimize maximizing the mental health of the student but also maximizing the smoothness, coherence, enjoyment and engagement each time the dialogue session is composed. Cecilia helps students to manage stress/anxiety to attempt the prevention of depression. Students can interact through the digital companion making questions and answers. While the system “learns” from the user it allows the user to learn from herself. Once the student discovers elements that were unnoticed by her, she will find a better way to improve when discovering her points of improvement.</t>
+          <t>Abstract Before Russia’s invasion in February 2022, Ukraine boasted a thriving ecosystem for producing artificial intelligence (AI) solutions, leading Eastern Europe in AI company numbers and hosting R&amp;amp;D offices of multinational giants like Amazon and Google. Despite this, Ukraine’s defense sector lagged in AI adoption due to a focus on traditional hardware. The conflict between Russia and Ukraine has transformed the situation, with both sides employing AI in geospatial intelligence, unmanned systems, military training, and cyber warfare, making this conflict the first to feature AI competition as a critical factor. Ukraine’s resilience during the war has relied on active use of awareness systems, volunteer initiatives, open-source platforms, and decentralized asset utilization. The government has begun systematically formulating defense AI policy initiatives and fostering a new ecosystem while civil IT companies shift focus towards dual-use products and talent acquisition in AI. Current defense AI development priorities include AI for unmanned systems, to combat disinformation and support cybersecurity and to advance logistics and mine detection. In parallel, the war has advanced closer cooperation between universities and the military sector, also in view of advancing training and developing AI-enhanced simulation-based training. Overall, the conflict serves as a testing ground for foreign AI developers, prompting reevaluation of regulatory assumptions and the need for war-proof defense AI solutions.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
+          <t>d7adc1344b2359ef</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>The Convergent Validity of Mobile Learning Apps&amp;apos; Usability Evaluation by Popular Generative Artificial Intelligence (AI) Robots</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Victor K. Y. Chan</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>post_chatgpt</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P49" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>2024/d7adc1344b2359ef.pdf</t>
+        </is>
+      </c>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>eric</t>
+        </is>
+      </c>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>This article seeks to explore the convergent validity of (and thus the consistency between) a few popular generative artificial intelligence (AI) robots in evaluating popular mobile learning apps' usability. The three robots adopted in the study were Microsoft Copilot, Google PaLM, and Meta Llama, which were individually instructed to accord rating scores to the eight major usability dimensions, namely, (1) content/course quality, (2) pedagogical design, (3) learner support, (4) technology infrastructure, (5) social interaction, (6) learner engagement, (7) instructor support, and (8) cost-effectiveness of 17 currently most popular mobile learning apps. For each of the three robots, the minimum, the maximum, the range, and the standard deviation of the rating scores for each of the eight dimensions were computed across all the mobile learning apps. The rating score difference for each of the eight dimensions between any pair of the above three robots was calculated for each app. The mean of the absolute value, the minimum, the maximum, the range, and the standard deviation of the differences for each dimensions between each pair of robots were calculated across all the apps. A paired sample t-test was then applied to each dimension for the rating score difference between each robot pair over all the apps. Finally, Cronbach's coefficient alpha of the rating scores was computed for each of the eight dimensions between all the three robots across all the apps. The computational results were to reveal whether the three robots awarded discrimination in evaluating each dimension across the apps, whether each robot, with respect to any other robot, erratically and/or systematically overrate or underrate any dimension over the apps, and whether there was high convergent validity of (and thus consistency between) the three robots in evaluating each dimension across the apps. Among other auxiliary results, it was revealed that the convergent validity of (and the consistency between) the three robots was marginally acceptable only in evaluating mobile learning apps' dimension of (1) content/course quality but not at all in the dimensions (2) pedagogical design, (3) learner support, (4) technology infrastructure, (5) social interaction, (6) learner engagement, (7) instructor support, and (8) cost-effectiveness. [For the full proceedings, see ED659933.]</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>b8a9ff54254ee8ef</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>The Impact of Falsely Detecting AI-Generated Text on Academic Assessment</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Arifi N. Waked; Hanadi Abdelsalem; Muhammad Waqar Ashraf; Maura Pilotti; Khadija El Alaoui</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>post_chatgpt</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>International Society for Technology, Education, and Science. 944 Maysey Drive, San Antonio, TX 78227. Tel: 515-294-1075; Fax: 515-294-1003; email: istesoffice@gmail.com; Web site: http://www.istes.org</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P50" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>2024/b8a9ff54254ee8ef.pdf</t>
+        </is>
+      </c>
+      <c r="R50" t="inlineStr">
+        <is>
+          <t>eric</t>
+        </is>
+      </c>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>Large Language Model (LLM) Functionalities, such as Chat Generative Pre-Trained Transformer (ChatGPT), are a form of artificial intelligence (AI) that have the ability to produce human-like writing in response to a wide array of input. As this technology has become a staple of everyday life, many educators find themselves rapidly redefining best assessment practices regarding this new area of potential plagiarism. As it becomes increasingly difficult to discern between well-written assignments produced by students and those that have been generated by AI, educators may turn to AI-detection programs to determine whether work submitted by students is in fact their own. However, these programs notoriously return a high rate of false detection of AI-generated text. This phenomenon leads to the increased likelihood that students will be unfairly academically penalized. In this study, hand-written examinations for a university-level introductory academic writing class were submitted to different AI-detection programs. Results indicate an association between higher exam grades and greater false detection of AI-generated writing. These results suggest that educators must carefully consider the benefits of such programs when assessing students' work. [For the complete proceedings, see ED672804.]</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>85ea8f1340dce200</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Anchoring Concepts Influence Essay Conceptual Structure and Test Performance</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Roy B. Clariana; Ryan Solnosky</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>post_chatgpt</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P51" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>2023/85ea8f1340dce200.pdf</t>
+        </is>
+      </c>
+      <c r="R51" t="inlineStr">
+        <is>
+          <t>eric</t>
+        </is>
+      </c>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>This quasi-experimental study seeks to improve the conceptual quality of summary essays by comparing two conditions, essay prompts with or without a list of 13 broad concepts, the concepts were selected across a continuum of the 100 most frequent words in the lesson materials. It is anticipated that only the most central concepts will be used as &amp;quot;anchors&amp;quot; when writing. Participants (n = 90) in an Architectural Engineering undergraduate course read the assigned lesson textbook chapter and attended lectures and labs, then in a final lab session were asked to write a 300-word summary of the lesson content. Data consists of the essays converted to networks and the end-of-unit multiple choice test. Compared to the expert network benchmark, the essay networks of those receiving the broad concepts in the writing prompt were not significantly different from those who did not receive these concepts. However those receiving the broad concepts were significantly more like peer essay networks (mental model convergence) and like the networks of the two PowerPoint lectures but neither were like the textbook chapter. Further, those receiving the broad concepts performed significantly better on the end-of-unit test than those not receiving the concepts. Term frequency analysis of the essays indicates as expected that the most network-central concepts had a greater frequency in essays, the other terms frequencies were remarkably the same for both the terms and no terms groups, suggesting a similar underlying conceptual mental model of this lesson content. To further explore the influence of anchoring concepts in summary writing prompts, essays were generated with the same two summary writing prompts using OpenAI (ChatGPT) and Google Bard, plus a new prompt that used the 13 most central concepts from the expert's network. The quality of the essay networks for both AI systems were equivalent to the students' essay networks for the broad concepts and for the no concept treatments. However, the AI essays derived with the 13 most central concepts were significantly better (more like the expert network) than the students and AI essays derived with broad concepts or no concepts treatments. In addition, Bard and OpenAI used several of the same concepts at a higher frequency than the students suggesting that the two AI systems have more similar knowledge graphs of this content. In sum, adding 13 broad conceptual terms to a summary writing prompt improved both structural and declarative knowledge outcomes, but adding 13 most central concepts may be even better. More research is needed to understand how including concepts and other terms in a writing prompt influences students' essay conceptual structure and subsequent test performance. [For the full proceedings, see ED636095.]</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>b142a08020007c56</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Education to Prevent Human Mechanisation in a Faculty of Informatics: Developing Learning Materials to Improve Students&amp;apos; Verbal Communication Skills</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Mari Ueda; Isoharu Nishiguchi; Hiroshi Tanaka; Kazunori Matsumoto; Tetsuo Tanaka</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>post_chatgpt</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P52" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>2023/b142a08020007c56.pdf</t>
+        </is>
+      </c>
+      <c r="R52" t="inlineStr">
+        <is>
+          <t>eric</t>
+        </is>
+      </c>
+      <c r="S52" s="2" t="inlineStr">
+        <is>
+          <t>Although information technology (ICT) education is being strengthened based on the national context, there are reports suggesting a decline in young people's communication skills. This phenomenon can be attributed to the rapid development of informatisation, which includes the diversification and spread of information tools, as well as the prevalence of nonverbal communication, such as pictograms in social networking services. In addition, the COVID-19 pandemic has drastically reduced face-to-face communication opportunities, making interactive communication in on-demand classes challenging. Even in assignments and short tests completed during class, many instances of content being copied and pasted from the web or written in a disorganized manner have been observed. For instance, students entering ICT-related careers, particularly those graduating from the faculty of informatics, must possess the ability to communicate with engineers and clients while implementing ICT advancements. Alongside programming skills, strong communication abilities are essential. Moreover, the emergence of generative artificial intelligence (AI) tools, such as ChatGPT and Bing AI, has considerably diminished the opportunities for independent thinking. In the current era of enhanced ICT education, AI, and IoT, the Faculty of Informatics at the Kanagawa Institute of Technology has been engaged in discussions regarding learning materials that aim to strengthen students' ability to think and communicate in their own words, preventing the mechanisation of individuals. This paper presents the development and implementation of learning materials designed to enhance students' verbal communication skills through the description and re-production of mathematical graphs. [For the full proceedings, see ED636095.]</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>aa42fa1562d18625</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Evaluating Popular MOOC Platforms by Generative Artificial Intelligence (AI) Robots: How Consistent Are the Robots?</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Victor K. Y. Chan</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>post_chatgpt</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P53" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2023/aa42fa1562d18625.pdf</t>
+        </is>
+      </c>
+      <c r="R53" t="inlineStr">
+        <is>
+          <t>eric</t>
+        </is>
+      </c>
+      <c r="S53" s="2" t="inlineStr">
+        <is>
+          <t>This article intends to investigate the consistency between a few popular generative AI robots in the evaluation of massive open online course (MOOC) platforms. The four robots experimented with in the study were Claude+, GPT-4, Sage, and Dragonfly, which were tasked with awarding rating scores to the eight major dimensions, namely (1) content/course quality, (2) pedagogical design, (3) learner support, (4) technology infrastructure, (5) social interaction, (6) learner engagement, (7) instructor support, and (8) cost-effectiveness, of the 31 currently very popular MOOC platforms. Only Claude+'s and Dragonfly's rating scores turned out to be amenable to statistical analysis. For each of the two robots, the minimum, the maximum, the range, and the standard deviation of the rating scores for each of the eight dimensions were computed across all the 31 MOOC platforms. The rating score difference for each of the eight dimensions between the two robots was calculated for each platform. The mean of the absolute value, the minimum, the maximum, the range, and the standard deviation of the differences for each dimension between the two robots were calculated across all platforms. A paired sample t-test was then applied to each dimension for the rating score difference between the two robots over all the platforms. Finally, a correlation coefficient of the rating scores was computed for each of the eight dimensions between the two robots across all the MOOC platforms. The computational results were to reveal whether the two robots awarded discrimination in evaluating each dimension across the platforms, whether any of the two robots systematically underrated or overrated any dimension with respect to the other robot, and whether there was consistency between the two robots in evaluating each dimension across the platforms. It was found that discrimination was prominent in the evaluation of all dimensions save Dragonfly's rating of the dimensions learner support, technology infrastructure, and instructor support, Claude+ systematically underrated all dimensions (p &amp;lt; 0.000 &amp;lt; 0.05) compared with Dragonfly except for the dimension cost-effectiveness, which Claude+ systematically overrated (p = 0.003 &amp;lt; 0.05), and the evaluation by the two robots was consistent only for the dimensions content/course quality, pedagogical design, and learner engagement with the correlation coefficients ranging from 0.445 to 0.632 (p from 0.000 to 0.012 &amp;lt; 0.05). Consistency implies at least the partial trustworthiness of the evaluation of these MOOC platforms by either of these two popular generative AI robots based on the analogous concept of convergent validity for an operationalized instrument to measure an abstract construct. [For the full proceedings, see ED636095.]</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>192252b29da5b302</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Fostering Problem Solving and Critical Thinking in Mathematics through Generative Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Barana, A.; Marchisio, M.; Roman, F.</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>post_chatgpt</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P54" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>2023/192252b29da5b302.pdf</t>
+        </is>
+      </c>
+      <c r="R54" t="inlineStr">
+        <is>
+          <t>eric</t>
+        </is>
+      </c>
+      <c r="S54" s="2" t="inlineStr">
+        <is>
+          <t>The spread of Artificial Intelligence (AI) has been recently generating worries among teachers and educators about the validity of assessment when students make use of AI tools to solve tasks. To tackle this issue, we propose mathematical problem solving activities to be carried out with the aid of ChatGPT, showing how problem solving and critical thinking continue to be pivotal in solving mathematical problems, even if this is performed with the aid of AI. After discussing theoretical frameworks on strategies of problem solving and phases of the critical thinking process, we present six problems of combinatorics that we submitted to ChatGPT. We also asked 40 university students to solve the six problems in group with the aid of ChatGPT during an international module on Problem Solving and Critical Thinking and collected the tutors' observations about the activities. Analyzing ChatGPT solutions and tutors' reflections, we show that the proposed activity requires problem solving and critical thinking to be accomplished. The results corroborate the idea that, instead of limiting the use of AI in education, it is possible to integrate it within learning and assessment to achieve the learning goals. [For the full proceedings, see ED636095.]</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>ae87b25ad2e4631c</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Future of Learning and Education</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Varghese, S.</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>post_chatgpt</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Future of business and finance</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Springer International Publishing</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>book-chapter</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-031-36382-5_16</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="O55" t="n">
+        <v>1</v>
+      </c>
+      <c r="P55" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>2023/ae87b25ad2e4631c.pdf</t>
+        </is>
+      </c>
+      <c r="R55" t="inlineStr">
+        <is>
+          <t>openalex</t>
+        </is>
+      </c>
+      <c r="S55" s="2" t="inlineStr">
+        <is>
+          <t>Abstract According to “A Scorecard for Humanity,” a report from the Copenhagen Consensus Center, our world gains every time an individual is educated, and our world pays a price when people go illiterate. In the future, those regions and nations of the world that manage to educate its people would gain, whereas those that do not pay much attention to this crucial aspect would continue to suffer losses, hidden in plain sight. Hence, by 2050, we suggest that though the world would have made tremendous progress in basic education, illiteracy would persist with almost 500 million uneducated in the world. Illiteracy shall be most concentrated in the regions of Africa and South Asia, whereas most other nations would move toward a total eradication. However, there would also be a systemic change in the higher education sector across the globe, as the age cohort of 18 to 24 years in Europe would shrink, but in South Asia and Africa, this would continue to grow. There would also be a disruption of the current pedagogic and regimental learning systems toward flatter, flexible, and open systems based on research in learning sciences. Technology would also come by to play a larger role, where education would be driven by artificial intelligence (AI) and big data—resulting in complete personalization of curriculum and methodology focusing on each individual's minute needs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>c1cdc5cf92b29adf</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Generating Multiple Choice Questions from a Textbook: LLMs Match Human Performance on Most Metrics</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Andrew M. Olney</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>post_chatgpt</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P56" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q56" t="inlineStr">
+        <is>
+          <t>2023/c1cdc5cf92b29adf.pdf</t>
+        </is>
+      </c>
+      <c r="R56" t="inlineStr">
+        <is>
+          <t>eric</t>
+        </is>
+      </c>
+      <c r="S56" s="2" t="inlineStr">
+        <is>
+          <t>Multiple choice questions are traditionally expensive to produce. Recent advances in large language models (LLMs) have led to fine-tuned LLMs that generate questions competitive with human-authored questions. However, the relative capabilities of ChatGPT-family models have not yet been established for this task. We present a carefully-controlled human evaluation of three conditions: a fine-tuned, augmented version of Macaw, instruction-tuned Bing Chat with zero-shot prompting, and human-authored questions from a college science textbook. Our results indicate that on six of seven measures tested, both LLM's performance was not significantly different from human performance. Analysis of LLM errors further suggests that Macaw and Bing Chat have different failure modes for this task: Macaw tends to repeat answer options whereas Bing Chat tends to not include the specified answer in the answer options. For Macaw, removing error items from analysis results in performance on par with humans for all metrics; for Bing Chat, removing error items improves performance but does not reach human-level performance. [This paper was published in the &amp;quot;CEUR Workshop Proceedings,&amp;quot; 2023.]</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>bf419dfa66e76b7f</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>How to Deal with AI-Powered Writing Tools in Academic Writing: A Stakeholder Analysis</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Michael Burkhard</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>post_chatgpt</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P57" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q57" t="inlineStr">
+        <is>
+          <t>2023/bf419dfa66e76b7f.pdf</t>
+        </is>
+      </c>
+      <c r="R57" t="inlineStr">
+        <is>
+          <t>eric</t>
+        </is>
+      </c>
+      <c r="S57" s="2" t="inlineStr">
+        <is>
+          <t>Due to the advances of artificial intelligence (AI) and natural language processing, new AI-powered writing tools have emerged. They can be used by students among other things for text translation, to improve spelling or to generate new texts. In academic writing, AI-powered writing tools are posing challenges but also opportunities for teaching and learning. It is an open question in which way to sensibly deal with these tools. To address the issue, this paper investigates, what interests different stakeholders (students, lecturers, university administration) pursue in relation to AI-powered writing tools. Building on this, tensions between different stakeholders are identified and (teaching) strategies proposed to deal with these tensions. To discuss the findings in light of recent developments around ChatGPT, semi-structured expert interviews were conducted in April 2023 with five academic writing lecturers at the University of St. Gallen. The results suggest that as writing tools become more and more powerful, the need for strategies to ensure their reasonable and transparent use also increases. [For the full proceedings, see ED636095.]</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2ad51015436ad076</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Investigating the Role of ChatGPT in Supporting Text-Based Programming Education for Students and Teachers</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Wieser, M.; Schöffmann, K.; Stefanics, D.; Bollin, A.; Pasterk, S.</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>post_chatgpt</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Lecture notes in computer science</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Springer Science+Business Media</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>book-chapter</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-031-44900-0_4</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="O58" t="n">
+        <v>21</v>
+      </c>
+      <c r="P58" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q58" t="inlineStr">
+        <is>
+          <t>2023/2ad51015436ad076.pdf</t>
+        </is>
+      </c>
+      <c r="R58" t="inlineStr">
+        <is>
+          <t>openalex</t>
+        </is>
+      </c>
+      <c r="S58" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Teaching text-based programming poses significant challenges in both school and university contexts. This study explores the potential of ChatGPT as a sustainable didactic tool to support students, freshmen, and teachers. By focusing on a beginner’s course with examples also relevant to vocational schools, we investigated three research questions. First, the extent to which ChatGPT assists students in solving and understanding initial examples; secondly, the feasibility of teachers utilizing the chatbot for grading student solutions; and finally, the additional support ChatGPT provides in terms of teaching. Our findings demonstrate that ChatGPT offers valuable guidance for teachers in terms of assessment and grading and aids students in understanding and optimizing their solutions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>135634b3c7c31d5d</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Judicial Decision-Making in the Age of Artificial Intelligence</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Gravett, W.</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>post_chatgpt</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Law, governance and technology series</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Springer International Publishing</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>book-chapter</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-031-41264-6_15</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="O59" t="n">
+        <v>9</v>
+      </c>
+      <c r="P59" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q59" t="inlineStr">
+        <is>
+          <t>2023/135634b3c7c31d5d.pdf</t>
+        </is>
+      </c>
+      <c r="R59" t="inlineStr">
+        <is>
+          <t>openalex</t>
+        </is>
+      </c>
+      <c r="S59" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Artificial intelligence (AI) has become a pervasive presence in almost every aspect of society and business: from assigning credit scores to people, to identifying the best candidates for an employment position, to ranking applicants for admission to university. One of the most striking innovations in the United States criminal justice system in the last three decades has been the introduction of risk-assessment software, powered by sophisticated algorithms, to predict whether individual offenders are likely to re-offend. The focus of this contribution is on the use of these risk-assessment tools in criminal sentencing. Apart from the broader social, ethical and legal considerations, to date, not much is known about how perceptions of technology influence cognition in decision-making, particularly in the legal context. What research does demonstrate is that humans are inclined to trust algorithms as objective, and, as such, as unobjectionable. This contribution examines two phenomena in this regard: (i) the “technology effect”—the human tendency towards excessive optimism when making decisions involving technology; and (ii) “automation bias”—the phenomenon whereby judges accept the recommendations of an automated decision-making system, and cease searching for confirmatory evidence, perhaps even transferring responsibility for decision-making onto the machine.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>7947ac0d82ac46e9</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Metabolism in Crisis? A New Interplay Between Physiology and Ecology</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Bognon-Küss, C.</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>post_chatgpt</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>History, philosophy and theory of the life sciences</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Springer Nature (Netherlands)</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>book-chapter</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-031-12604-8_11</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="O60" t="n">
+        <v>2</v>
+      </c>
+      <c r="P60" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q60" t="inlineStr">
+        <is>
+          <t>2023/7947ac0d82ac46e9.pdf</t>
+        </is>
+      </c>
+      <c r="R60" t="inlineStr">
+        <is>
+          <t>openalex</t>
+        </is>
+      </c>
+      <c r="S60" s="2" t="inlineStr">
+        <is>
+          <t>Abstract This chapter investigates the hybrid relationships between metabolism, broadly and a-historically understood as the set of processes through which alien matter is made homogeneous to that of the organism, and forms of vitalism from the eighteenth century on. While metabolic processes have long been modeled in a reductionist fashion as a straightforward function of repair and expansion of a given structure (either chemically, or mechanistically), a challenging vitalist view has characterized metabolism as a creative, organizing, vital faculty. I suggest that this tension was overcome in Claude Bernard’s works on “indirect nutrition”, in which nutrition, rightly conceived as a general vital phenomenon common to plants and animals, was both characterized as an instance of the general physico-chemical determinism of all phenomena and as the sign and condition of the “freedom and independence” of the organism with respect to the environment. I propose that Bernard’s theory of indirect nutrition was central in the elaboration of his general physiology and has, at the same time, underpinned a self-centered view of biological identity in which the organism creates itself continuously at the detriment of its external milieu . I further argue that this conception of biological individuality as metabolically constructed has since, and paradoxically, supported a view in which the organism appears as an autonomous and self-creating entity. I then contrast this classical view of the metabolic autonomy of the organism with the challenges raised by microbiome studies and suggest that these emerging fields contribute to sketch an ecological conception of the organism and its metabolism through the reconceptualization of its relationship with the environment. The recent focus on a “microbiota – host metabolism” axis contributes to shift the focus away from the classical concept of organism, somehow externalizing vitalism out of the autonomous individual in favor of an ecological, collaborative, and interactionist view of the living.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>3827a11b5b949e39</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Rebuilding After War and Genocide: Learning with and from Refugees in the Transnational Digital Classroom</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Brill-Carlat, M.; Höhn, M.</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>post_chatgpt</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Political pedagogies</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Springer International Publishing</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>book-chapter</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-031-12350-4_22</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="O61" t="n">
+        <v>0</v>
+      </c>
+      <c r="P61" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q61" t="inlineStr">
+        <is>
+          <t>2023/3827a11b5b949e39.pdf</t>
+        </is>
+      </c>
+      <c r="R61" t="inlineStr">
+        <is>
+          <t>openalex</t>
+        </is>
+      </c>
+      <c r="S61" s="2" t="inlineStr">
+        <is>
+          <t>Abstract The Covid-19 emergency spurred a flurry of teaching innovations as higher education institutions turned to online or blended learning models, and as international collaborations have moved nearly entirely online. These circumstances inspired us to revisit the digital transatlantic seminar, “Germany 1945: History and Memory in Germany after WWII,” taught by Höhn in Spring 2018 to a group of seven Vassar students (Brill-Carlat among them) and six advanced high-school students—between the ages of 17 and 22—who had come to Berlin as asylum seekers from Syria, Iraq, and Afghanistan. The course dealt with history and memory of World War II and the Holocaust in Germany. As such, it reflected a core commitment of the Consortium on Forced Migration, Displacement, and Education (CFMDE), founded by Höhn at Vassar and partners (Bard, Bennington, Sarah Lawrence, the New School, and the Council for European Studies): the importance of providing opportunities for our undergraduate students to learn with and from refugees and displaced individuals if they are to understand and tackle the global, multidimensional challenges of forced migration. As institutional resistance to digital teaching necessarily vanished with the Covid-19 pandemic in Spring 2020 and the direction of future online-learning policies is up for debate, we revisit the 2018 class to examine lessons learned and how this project points the way to another digital venture: digitally “hosting” displaced scholars at liberal arts campuses.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>c81bf633e42c7f19</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Survey of AI Tool Usage in Programming Course: Early Observations</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Saari, M.; Rantanen, P.; Nurminen, M.; Kilamo, T.; Systä, K.; Abrahamsson, P.</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>post_chatgpt</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Lecture notes in business information processing</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Springer Science+Business Media</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>book-chapter</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-031-48550-3_18</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="O62" t="n">
+        <v>4</v>
+      </c>
+      <c r="P62" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q62" t="inlineStr">
+        <is>
+          <t>2023/c81bf633e42c7f19.pdf</t>
+        </is>
+      </c>
+      <c r="R62" t="inlineStr">
+        <is>
+          <t>openalex</t>
+        </is>
+      </c>
+      <c r="S62" s="2" t="inlineStr">
+        <is>
+          <t>Abstract This study explores the role of artificial intelligence (AI) in university teaching, with a focus on the teaching of programming. Despite the growing use of AI in education, both students and teachers often struggle to understand its role and implications. To address this gap, we conducted a survey of a wide group of students (n = 200) to assess their experiences and perspectives on the use of AI in programming education. The survey results suggest that AI is becoming increasingly involved in university teaching, particularly in the teaching of programming. However, students require guidance from teachers in order to use AI tools effectively in their studies. The study concludes that the goal of teaching programming should be to guide students in the responsible use of AI. Overall, the study highlights the need for greater awareness and understanding of AI in university teaching and the fact that teachers have an important role to play in providing guidance to students on the responsible use of AI tools.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>96a698008602b3d7</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>The Role of Educational Interventions in Facing Social Media Threats: Overarching Principles of the COURAGE Project</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Taibi, D.; Börsting, J.; Hoppe, U.; Ognibene, D.; Hernández-Leo, D.; Eimler, S.; Kruschwitz, U.</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>post_chatgpt</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Communications in computer and information science</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Springer Science+Business Media</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>book-chapter</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-031-29800-4_25</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="O63" t="n">
+        <v>6</v>
+      </c>
+      <c r="P63" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q63" t="inlineStr">
+        <is>
+          <t>2023/96a698008602b3d7.pdf</t>
+        </is>
+      </c>
+      <c r="R63" t="inlineStr">
+        <is>
+          <t>openalex</t>
+        </is>
+      </c>
+      <c r="S63" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Social media are offering new opportunities for communication and interaction way beyond what was possible only a few years ago. However, social media are also virtual spaces where young people are exposed to a variety of threats. Digital addiction, discrimination, hate speech, misinformation, polarization as well as manipulative influences of algorithms, body stereotyping, and cyberbullying are examples of challenges that find fertile ground on social media. Educators and students are not adequately prepared to face these challenges. To this aim, the COURAGE project, presented in this paper, introduces new tools and learning methodologies that can be adopted within higher education learning paths to train educators to deal with social media threats. The overarching principles of the COURAGE project leverage the most recent advances in the fields of artificial intelligence and in the educational domain paired with social and media psychological insights to support the development of the COURAGE ecosystem. The results of the experiments currently implemented with teachers and students of secondary schools as well as the impact of the COURAGE project on societal changes and ethical questions are presented and discussed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>8f81d56c326a06d3</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Transformer Language Model-Based Mobile Learning Solution for Higher Education</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Silvia García-Méndez; Francisco de Arriba-Pérez; Francisco J. González-Castaño</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>post_chatgpt</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P64" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q64" t="inlineStr">
+        <is>
+          <t>2023/8f81d56c326a06d3.pdf</t>
+        </is>
+      </c>
+      <c r="R64" t="inlineStr">
+        <is>
+          <t>eric</t>
+        </is>
+      </c>
+      <c r="S64" s="2" t="inlineStr">
+        <is>
+          <t>Mobile learning or mLearning has become an essential tool in many fields in this digital era, among the ones educational training deserves special attention, that is, applied to both basic and higher education towards active, flexible, effective high-quality and continuous learning. However, despite the advances in Natural Language Processing techniques, mLearning still does not take full advantage of the great potential of the latter techniques. It is the case of the transformer language models distributed in chatbot form. Accordingly, this work presents a mLearning application based on OpenAI GPT-3 model, which enables user-friendly interactions. The proposed system was tested in two evaluation scenarios, and the experimental results endorse its appropriateness toward learning experience enhancement. [For the full proceedings, see ED639391.]</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>e3b815e1a83132e6</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>About the Editor</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>MBA, S.</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>pre_chatgpt</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Digital Health</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>SAGE Publishing</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>book-chapter</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>10.36255/exon-publications-digital-health.editor</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="O65" t="n">
+        <v>0</v>
+      </c>
+      <c r="P65" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q65" t="inlineStr">
+        <is>
+          <t>2022/e3b815e1a83132e6.pdf</t>
+        </is>
+      </c>
+      <c r="R65" t="inlineStr">
+        <is>
+          <t>openalex</t>
+        </is>
+      </c>
+      <c r="S65" s="2" t="inlineStr">
+        <is>
+          <t>Professor Simon Lin Linwood, MD, MBA, is the Chief Medical Information Officer at the UCR Health and UCR School of Medicine, Riverside, CA, USA. He obtained his executive education in Artificial Intelligence Strategy and Implementation from Harvard University. He was named Innovator of the Year by CHIME in 2018. He is a national thought leader on digital transformation and acknowledged for providing vision and leadership in information technology to drive business growth in large, complex, and highly distributed environments. He has supervised and mentored many PhD students on data-driven innovation in healthcare, such as deep learning for risk prediction in population health to control costs, and methods to reduce physician documentation burden. He received Mentor of the Year Award in 2016. His areas of expertise include digital transformation, data-driven innovation, data science, data lake, artificial intelligence, and natural language processing, among others. He has extensively published on digital health, artificial intelligence/machine learning, data science, clinical informatics, genome informatics.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>246ac766bd6d1c42</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>List of Contributors</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Contributors, L.</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>2022</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>pre_chatgpt</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Digital Health</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>SAGE Publishing</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>book-chapter</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>10.36255/exon-publications-digital-health.contributors</t>
+        </is>
+      </c>
+      <c r="J66" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="K66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N66" t="inlineStr">
+        <is>
+          <t>gold</t>
+        </is>
+      </c>
+      <c r="O66" t="n">
+        <v>0</v>
+      </c>
+      <c r="P66" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q66" t="inlineStr">
+        <is>
+          <t>2022/246ac766bd6d1c42.pdf</t>
+        </is>
+      </c>
+      <c r="R66" t="inlineStr">
+        <is>
+          <t>openalex</t>
+        </is>
+      </c>
+      <c r="S66" s="2" t="inlineStr">
+        <is>
+          <t>ABRAR-AHMAD ZULFIQAR, MDService de Médecine Interne, Diabète et Maladies métaboliques de la Clinique Médicale B, Hôpitaux Universitaires de Strasbourg et Equipe EA 3072 “Mitochondrie, Stress oxydant et Protection musculaire”, Faculté de Médecine-Université de Strasbourg, Strasbourg, France AIKO OSAWA, MD, PHDNational Center for Geriatrics and Gerontology, Aichi, Japan AMIR HAJJAM, PHDLaboratoire IRTES-SeT, Université de Technologie de Belfort-Montbéliard (UTBM), Belfort-Montbéliard, Belfort, France BRYONY MCGARRY, PHDPRECISE4Q, Predictive Modelling in Stroke, Technological University Dublin, Dublin, Ireland CEES TH. SMIT SIBINGA, MD, PHD, FRCP, FRCPATHIQM Consulting and University of Groningen, De Gast 46, 9801AE Zuidhorn, The Netherlands CLÁUDIA S. SOUSA, MDPulmonology Department, Central Hospital of Funchal, Portugal EMMANUEL ANDRÈS, MD, PHDLaboratoire IRTES-SeT, Université de Technologie de Belfort-Montbéliard (UTBM), Belfort-Montbéliard, Belfort, France EN-JU LIN, PHD, MPHResearch Information Solutions and Innovation, The Research Institute at Nationwide Children’s Hospital, Columbus, OH, USA ESRA ZIHNI, MSCPRECISE4Q, Predictive Modelling in Stroke, Technological University Dublin, Dublin, Ireland HIDENORI ARAI, MD, PHDNational Center for Geriatrics and Gerontology, Aichi, Japan IRVING D. KAPLAN, MDDepartment of Radiation Oncology, Beth Israel Deaconess Medical Center, Boston, MA, USA JENAY YUEN, BSKeck School of Medicine, University of Southern California, California, USA JESSAMINE P. WINER-JONES, PHDTriNetX, LLC, Cambridge, MA, USA JOHN KELLEHER, PHDPRECISE4Q, Predictive Modelling in Stroke, Technological University Dublin, Dublin, Ireland KATHARINE LAWRENCE, MD MPHNYU Grossman School of Medicine, Department of Population Health; NY, USA LIMOR APPELBAUM, MDDepartment of Radiation Oncology, Beth Israel Deaconess Medical Center, Boston, MA, USA MADELEINE SCHROEDER, MSResearch Information Solutions and Innovation, The Research Institute at Nationwide Children’s Hospital, Columbus, OH, USA MÁRIO MORAIS-ALMEIDA, MDAllergy Centre, CUF Descobertas Hospital, Lisboa, Portugal MARTIN RINARD, PHDComputer Science and Artificial Intelligence Laboratory, Massachusetts Institute of Technology, Cambridge, MA, USA MATVEY B. PALCHUK, MD, MSTriNetX, LLC, Cambridge, MA, USA MAURICE MARS, MBCHB, MDDepartment of TeleHealth, University of KwaZulu-Natal, Durban, South Africa MIGUEL T. BARBOSA, MDAllergy Centre, CUF Descobertas Hospital, Lisboa, Portugal MOHAMED HAJJAM, MDPredimed Technology, Schiltigheim, France RICHARD E. SCOTT, PHDDepartment of Community Health Sciences, University of Calgary, Calgary, Alberta, Canada SARAH PIKE, BAKeck School of Medicine, University of Southern California, California, USA SHINICHIRO MAESHIMA, MD, PHDKinjo University, Ishikawa, Japan SIMON LIN LINWOOD, MD, MBASchool of Medicine, University of California, Riverside, CA, USA STEVE KHACHIKYANDornsife College of Letters, Arts &amp;amp; Sciences, University of Southern California, California, USA STEVEN KUNDROT, BS, MBA&amp;nbsp;TriNetX, LLC, Cambridge, MA, USA SUDHA NALLASAMY, MDThe Vision Center at Children’s Hospital Los Angeles, California, USA; USC Roski Eye Institute, University of Southern California, California, USA YUNGUI HUANG, PHD, MBAResearch Information Solutions and Innovation, The Research Institute at Nationwide Children’s Hospital, Columbus, OH, USA</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>05cd11abf81f4c96</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Artificial Intelligence and Machine Learning: An Instructor’s Exoskeleton in the Future of Education</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>August, S.; Tsaima, A.</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>pre_chatgpt</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>SpringerBriefs in statistics</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Springer International Publishing</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>book-chapter</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-030-58948-6_5</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="K67" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="O67" t="n">
+        <v>26</v>
+      </c>
+      <c r="P67" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q67" t="inlineStr">
+        <is>
+          <t>2021/05cd11abf81f4c96.pdf</t>
+        </is>
+      </c>
+      <c r="R67" t="inlineStr">
+        <is>
+          <t>openalex,s2</t>
+        </is>
+      </c>
+      <c r="S67" s="2" t="inlineStr">
+        <is>
+          <t>Abstract The role of artificial intelligence in US education is expanding. As education moves toward providing customized learning paths, the use of artificial intelligence (AI) and machine learning (ML) algorithms in learning systems increases. This can be viewed as growing metaphorical exoskeletons for instructors, enabling them to provide a higher level of guidance, feedback, and autonomy to learners. In turn, the instructor gains time to sense student needs and support authentic learning experiences that go beyond what AI and ML can provide. Applications of AI-based education technology support learning through automated tutoring, personalizing learning, assessing student knowledge, and automating tasks normally performed by the instructor. This technology raises questions about how it is best used, what data provides evidence of the impact of AI and ML on learning, and future directions in interactive learning systems. Exploration of the use of AI and ML for both co-curricular and independent learnings in content presentation and instruction; interactions, communications, and discussions; learner activities; assessment and evaluation; and co-curricular opportunities provide guidance for future research.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>6f715e2962c0cd6d</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Jobs at Risk of Automation in the USA: Implications for Community College</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Yamashita, T.; Cummins, P.</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>pre_chatgpt</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="K68" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P68" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q68" t="inlineStr">
+        <is>
+          <t>2021/6f715e2962c0cd6d.pdf</t>
+        </is>
+      </c>
+      <c r="R68" t="inlineStr">
+        <is>
+          <t>eric</t>
+        </is>
+      </c>
+      <c r="S68" s="2" t="inlineStr">
+        <is>
+          <t>Advancing technology such as artificial intelligence and robots is steadily replacing jobs in the USA. Continuous skill-upgrading and re-skilling are critical for workers to remain employable throughout their careers. In these social and economic contexts, community colleges play significant roles to provide workforce education and training because of their open admission, lower tuition, and shorter and more specific occupational programs compared to four-year universities. However, the detailed data of jobs at risk of automation are currently unavailable. This study used the national occupation and risk-of-automation data (Frey &amp;amp; Osborne, 2017) to estimate specific numbers of jobs at risk by industries and age groups. Results showed that approximately 48% of the jobs could be replaced within two decades. Four industries (1) service; (2) sales and office; (3) natural resources, construction and maintenance; and (4) production, transportation, and material moving were at a particularly higher risk (up to 75%). At the same time, computer, engineering, and health care occupations had a lower risk (up to 12%). The estimated numbers of jobs at risk informs community colleges' strategic planning. [This is the advance online version of an article published in &amp;quot;Community College Journal of Research and Practice.&amp;quot;]</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>e4785c336fe78ec7</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Personalized and Adaptive Learning</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Taylor, D.; Yeung, M.; Bashet, A.</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>pre_chatgpt</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>SpringerBriefs in statistics</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Springer International Publishing</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>book-chapter</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-030-58948-6_2</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="K69" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N69" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="O69" t="n">
+        <v>136</v>
+      </c>
+      <c r="P69" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>2021/e4785c336fe78ec7.pdf</t>
+        </is>
+      </c>
+      <c r="R69" t="inlineStr">
+        <is>
+          <t>openalex,s2</t>
+        </is>
+      </c>
+      <c r="S69" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Personalized and adaptive learning has been touted to be one of the most promising emerging tools for increasing student learning and student success. Yet, the terms are neither precise nor clearly defined at this time, thus making it difficult for institutions of higher education to adopt and implement a learning approach using technology that is in its infancy and not clearly understood by those who will be utilizing it. One goal of this chapter is to define adaptive and personalized learning as it is used at this time in the hopes that as the technology evolves the promise of increased student learning can come to fruition. Adaptive learning personalizes learning by continuously evaluating each student’s performance in real time and creating an ever-changing individualized learning pathway as directed by artificial intelligence and machine learning, thus increasing learning and student satisfaction.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>085fa965ce157d51</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Robots as My Future Colleagues: Changing Attitudes Toward Collaborative Robots by Means of Experience-Based Workshops</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Leoste, J.; Viik, T.; López, J.; Kangur, M.; Vunder, V.; Mollard, Y.; Õun, T.; Tammo, H.; Paekivi, K.</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>pre_chatgpt</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Smart innovation, systems and technologies</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Springer Nature</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>book-chapter</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>10.1007/978-981-16-3930-2_13</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="K70" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="O70" t="n">
+        <v>4</v>
+      </c>
+      <c r="P70" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q70" t="inlineStr">
+        <is>
+          <t>2021/085fa965ce157d51.pdf</t>
+        </is>
+      </c>
+      <c r="R70" t="inlineStr">
+        <is>
+          <t>openalex</t>
+        </is>
+      </c>
+      <c r="S70" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Artificial intelligence-driven robots are increasingly being introduced in various workplaces. Research implies that people’s negative attitudes toward intelligent and collaborative robots might hinder their willingness to use them. We propose that interactive educational activities such as specialized workshops help people to overcome such negative attitudes. We designed a two-day workshop that introduced two quasi-industrial robots (Poppy Ergo Jr and ClearBot) to 16 university students. Students’ attitudes were qualitatively measured before and after the workshop. The results imply that the workshop helped students to increase their understanding of the nature of the intelligent collaborative robots. More precisely, robots became to be seen as empowering tools, rather than friends or enemies. Interestingly, there were significant gender differences, as the female participants had a greater tendency to view robots as animated objects. We concluded that specialized workshops effectively lead participants to become aware of various promising opportunities for their robotic co-workers in the possible future.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>0141788f9ac5d7cb</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>University Student Surveys Using Chatbots: Artificial Intelligence Conversational Agents</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Abbas, N.; Pickard, T.; Atwell, E.; Walker, A.</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>pre_chatgpt</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Lecture notes in computer science</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Springer Science+Business Media</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>book-chapter</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-030-77943-6_10</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="K71" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N71" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O71" t="n">
+        <v>14</v>
+      </c>
+      <c r="P71" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q71" t="inlineStr">
+        <is>
+          <t>2021/0141788f9ac5d7cb.pdf</t>
+        </is>
+      </c>
+      <c r="R71" t="inlineStr">
+        <is>
+          <t>openalex,s2</t>
+        </is>
+      </c>
+      <c r="S71" s="2" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>d0f022dbfc25bf9e</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>About the Book</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Bartneck, C.; Lütge, C.; Wagner, A.; Welsh, S.</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>pre_chatgpt</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>SpringerBriefs in ethics</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Springer International Publishing</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>book-chapter</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-030-51110-4_1</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="K72" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N72" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="O72" t="n">
+        <v>1</v>
+      </c>
+      <c r="P72" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>2020/d0f022dbfc25bf9e.pdf</t>
+        </is>
+      </c>
+      <c r="R72" t="inlineStr">
+        <is>
+          <t>openalex</t>
+        </is>
+      </c>
+      <c r="S72" s="2" t="inlineStr">
+        <is>
+          <t>This book provides an introduction into the ethics of robots and artificial intelligence. The book was written with university students, policy makers, and professionals in mind but should be accessible for most adults. The book is meant to provide balanced and, at times, conflicting viewpoints as to the benefits and deficits of AI through the lens of ethics. As discussed in the chapters that follow, ethical questions are often not cut and dry. Nations, communities, and individuals may have unique and important perspectives on these topics that should be heard and considered. While the voices that compose this book are our own, we have attempted to represent the views of the broader AI, robotics, and ethics communities.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>68c8ca7f7b8e293f</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Collaborative Innovation Between Shenzhen Municipal Government and Tsinghua University</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Kang, F.</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>pre_chatgpt</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Education in the Asia-Pacific region</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Springer Nature</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>book-chapter</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>10.1007/978-981-15-7018-6_20</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L73" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N73" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="O73" t="n">
+        <v>4</v>
+      </c>
+      <c r="P73" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q73" t="inlineStr">
+        <is>
+          <t>2020/68c8ca7f7b8e293f.pdf</t>
+        </is>
+      </c>
+      <c r="R73" t="inlineStr">
+        <is>
+          <t>openalex,s2</t>
+        </is>
+      </c>
+      <c r="S73" s="2" t="inlineStr">
+        <is>
+          <t>Global megatrendsGlobal megatrends—the rise of frontier technologies, the dramatic growth of information, sociopolitical landscape changes, and demographic changes—call for the need for ecosystem orchestration that requires collaboration. The People’s Republic of China has been heavily investing on Artificial Intelligence (AI) and Research and Development (R&amp;D) to become an innovation leader globally and to further leverage its position as a manufacturing powerhouse. The Chinese innovation ecosystemInnovation ecosystem has grown steadily in recent years as they tapped higher education and research institutes. University-research-industry linkagesUniversity-research-industry linkages have proven to be successful in achieving PRC’s innovation-driven endeavors as evidenced by the large number of firms and start-ups from such linkages have grown into large businesses and key technological leaders.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>ccad16bc20847787</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Correction to: Predictive Policing in 2025: A Scenario</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Macnish, K.; Wright, D.; Jiya, T.</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>pre_chatgpt</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Advanced sciences and technologies for security applications</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Springer International Publishing</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>book-chapter</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-030-50613-1_9</t>
+        </is>
+      </c>
+      <c r="J74" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="K74" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N74" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="O74" t="n">
+        <v>10</v>
+      </c>
+      <c r="P74" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q74" t="inlineStr">
+        <is>
+          <t>2020/ccad16bc20847787.pdf</t>
+        </is>
+      </c>
+      <c r="R74" t="inlineStr">
+        <is>
+          <t>openalex,s2</t>
+        </is>
+      </c>
+      <c r="S74" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Law enforcement authorities (LEAs) have begun using artificial intelligence and predictive policing applications that are likely to raise ethical, data protection, social, political and economic issues. This paper describes application of a new scenario methodology for identifying issues that emerging technologies are likely to raise in a future six or seven years hence, but that deserve policymakers’ attention now. It often takes policymakers that long to develop a new policy, consult with stakeholders and implement the policy. Thus, policymakers need a structured, but concise framework in order to understand the issues and their various implications. At the same time, they also prefer policies that have stakeholder support. These considerations led the University of Twente in the Netherlands and the UK’s Trilateral Research to develop the scenario that follows. It is structured with several headings that policymakers need to consider in order to move toward a desired future and avoidance of an undesired future.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>e97796436a92a9c7</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Creative Composition Problem: A Knowledge Graph Logical-Based AI Construction and Optimization Solution - Applied in Cecilia: An Architecture of a Digital Companion Artificial Intelligence (AI) Agent System Composer of Dialogue Scripts for Well-Being and Mental Health</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Galindo, M.; Moreno, L.</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>pre_chatgpt</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Lecture notes in computer science</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Springer Science+Business Media</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>book-chapter</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-030-72308-8_4</t>
+        </is>
+      </c>
+      <c r="J75" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="L75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q75" t="inlineStr">
+        <is>
+          <t>2020/e97796436a92a9c7.pdf</t>
+        </is>
+      </c>
+      <c r="R75" t="inlineStr">
+        <is>
+          <t>openalex,s2</t>
+        </is>
+      </c>
+      <c r="S75" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Contribution of this work is to Define the Creative Composition Problem (CCP) for Human Well-being Optimization by Construction of Knowledge Graph using Knowledge Representation and logic-based Artificial Intelligence reasoning-planning where the computation of the Optimal Solution is achieved by Dynamic Programming or Logic Programming. The Creative Composition Problem is embedded within Cecilia: an architecture of a digital companion artificial intelligence agent system composer of dialogue scripts for Well-being and Mental Health. Where Cecilia Framework is instantiated in Well-being and Mental Health domain for optimal well-being development of first year university students. We define the ‘The Problem of Creating a Dialogue Composition (PCDC)’ and we propose a feasible and optimal solution of it. CCP is instantiated in this applied domain to solve PCDC optimizing the Mental Health and Well-being of the student. CCP as PCDC is applied to optimize maximizing the mental health of the student but also maximizing the smoothness, coherence, enjoyment and engagement each time the dialogue session is composed. Cecilia helps students to manage stress/anxiety to attempt the prevention of depression. Students can interact through the digital companion making questions and answers. While the system “learns” from the user it allows the user to learn from herself. Once the student discovers elements that were unnoticed by her, she will find a better way to improve when discovering her points of improvement.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>8ed280224b419888</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Psychological Applications and Trends 2020</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Pracana, C.; Wang, M.</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>2020</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>pre_chatgpt</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="K76" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L76" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P76" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q76" t="inlineStr">
+        <is>
+          <t>2020/8ed280224b419888.pdf</t>
+        </is>
+      </c>
+      <c r="R76" t="inlineStr">
+        <is>
+          <t>eric</t>
+        </is>
+      </c>
+      <c r="S76" s="2" t="inlineStr">
+        <is>
+          <t>This book contains a compilation of papers presented at the International Psychological Applications Conference and Trends (InPACT) 2020, organized by the World Institute for Advanced Research and Science (W.I.A.R.S.), that this year had to be transformed into a fully Virtual Conference as a result of the Coronavirus (COVID 19) pandemic. Modern psychology offers a large range of scientific fields where it can be applied. The goal of understanding individuals and groups (mental functions and behavioral standpoints), from this academic and practical scientific discipline, aims ultimately to benefit society. The International Conference seeks to provide some answers and explore the several areas within the Psychology field, new developments in studies and proposals for future scientific projects. The goal is to offer a worldwide connection between psychologists, researchers and lecturers, from a wide range of academic fields, interested in exploring and giving their contribution in psychological issues. We take pride in having been able to connect and bring together academics, scholars, practitioners and others interested in a field that is fertile in new perspectives, ideas and knowledge. We counted on an extensive variety of contributors and presenters, which can supplement the view of the human essence and behavior, showing the impact of their different personal, academic and cultural experiences. This is, certainly, one of the reasons there are nationalities and cultures represented, inspiring multi-disciplinary collaborative links, fomenting intellectual encounter and development. InPACT 2020 received 240 submissions, from more than 45 different countries from all over the world, reviewed by a double-blind process. Submissions were prepared to take form of Virtual Presentations and Posters. 75 submissions (overall, 31% acceptance rate) were accepted for presentation in the conference. The conference also included: - One keynote presentation by Prof. Dr. Michael Wang (Emeritus Professor of Clinical Psychology, University of Leicester; Chair, Association of Clinical Psychologists, United Kingdom). - One Special Talk by Prof. Dr. Matthias Ammann (PhD, Department of Social Sciences, Uminho; Psychotherapist and psychoanalyst at Equilibrium Oporto; Climate activist, Portugal). We would like to express our gratitude to our invitees. The Conference addresses different categories inside Applied Psychology area and papers fit broadly into one of the named themes and sub-themes. The conference program includes six main broad-ranging categories that cover diversified interest areas: (1) Clinical Psychology: Emotions and related psychological processes; Assessment; Psychotherapy and counseling; Addictive behaviors; Eating disorders; Personality disorders; Quality of life and mental health; Communication within relationships; Services of mental health; and Psychopathology. (2) Educational Psychology: Language and cognitive processes; School environment and childhood disorders; Parenting and parenting related processes; Learning and technology; Psychology in schools; Intelligence and creativity; Motivation in classroom; Perspectives on teaching; Assessment and evaluation; and Individual differences in learning. (3) Social Psychology: Cross-cultural dimensions of mental disorders; Employment issues and training; Organizational psychology; Psychology in politics and international issues; Social factors in adolescence and its development; Social anxiety and self-esteem; Immigration and social policy; Self-efficacy and identity development; Parenting and social support; Addiction and stigmatization; and Psychological and social impact of virtual networks. (4) Legal Psychology: Violence and trauma; Mass-media and aggression; Intra-familial violence; Juvenile delinquency; Aggressive behavior in childhood; Internet offending; Working with crime perpetrators; Forensic psychology; Violent risk assessment; and Law enforcement and stress. (5) Cognitive and Experimental Psychology: Perception, memory and attention; Decision making and problem-solving; Concept formation, reasoning and judgment; Language processing; Learning skills and education; Cognitive Neuroscience; Computer analogies and information processing (Artificial Intelligence and computer simulations); Social and cultural factors in the cognitive approach; Experimental methods, research and statistics; and Biopsychology. (6) Psychoanalysis and Psychoanalytical Psychotherapy: Psychoanalysis and psychology; The unconscious; The Oedipus complex; Psychoanalysis of children; Pathological mourning; Addictive personalities; Borderline organizations; Narcissistic personalities; Anxiety and phobias; Psychosis; Neuropsychoanalysis. This book contains the results of the different researches conducted by authors who focused on what they are passionate about: to study and develop research in areas related to Psychology and its applications. It includes an extensive variety of contributors and presenters that are hereby sharing with us their different personal, academic and cultural experiences. We would like to thank all the authors and participants, the members of the academic scientific committee, and of course, to the organizing and administration team for making and putting this conference together. [This document contains the proceedings of the virtual International Psychological Applications Conference and Trends (InPACT) 2020. The proceedings were published by InScience Press. Abstract modified to meet ERIC guidelines. For the 2019 proceedings, see ED604954.]</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
           <t>4f278c8b9ba9d758</t>
         </is>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B77" t="inlineStr">
         <is>
           <t>Teaching Programming for Mathematical Scientists</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
+      <c r="C77" t="inlineStr">
         <is>
           <t>Betteridge, J.; Chan, E.; Corless, R.; Davenport, J.; Grant, J.</t>
         </is>
       </c>
-      <c r="D49" t="n">
+      <c r="D77" t="n">
         <v>2020</v>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="E77" t="inlineStr">
         <is>
           <t>pre_chatgpt</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="F77" t="inlineStr">
         <is>
           <t>Mathematics education in the digital era</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="G77" t="inlineStr">
         <is>
           <t>Springer Nature (Netherlands)</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>book-chapter</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>book-chapter</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
         <is>
           <t>10.1007/978-3-030-86909-0_12</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>en</t>
+        </is>
+      </c>
+      <c r="K77" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="N77" t="inlineStr">
         <is>
           <t>green</t>
         </is>
       </c>
-      <c r="O49" t="n">
+      <c r="O77" t="n">
         <v>4</v>
       </c>
-      <c r="P49" t="n">
+      <c r="P77" t="n">
         <v>2</v>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="Q77" t="inlineStr">
         <is>
           <t>2020/4f278c8b9ba9d758.pdf</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="R77" t="inlineStr">
         <is>
           <t>openalex,s2</t>
         </is>
       </c>
-      <c r="S49" s="2" t="inlineStr">
+      <c r="S77" s="2" t="inlineStr">
         <is>
           <t>Over the past thirty years or so the authors have been teaching various programming for mathematics courses at our respective Universities, as well as incorporating computer algebra and numerical computation into traditional mathematics courses. These activities are, in some important ways, natural precursors to the use of Artificial Intelligence in Mathematics Education. This paper reflects on some of our course designs and experiences and is therefore a mix of theory and practice. Underlying both is a clear recognition of the value of computer programming for mathematics education. We use this theory and practice to suggest good techniques for and to raise questions about the use of AI in Mathematics Education.</t>
         </is>
@@ -4894,82 +6783,110 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId19"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I19" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I21" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q24" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q25" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q26" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q27" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q28" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q29" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q30" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q31" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q32" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q33" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I34" r:id="rId65"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q34" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q35" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q36" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q37" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I38" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q38" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q39" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q40" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q41" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q42" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q43" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q44" r:id="rId86"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId87"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q45" r:id="rId88"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId89"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q46" r:id="rId90"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I47" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q47" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q48" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I49" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q49" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q24" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q25" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q26" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q27" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q28" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q29" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q30" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q31" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q32" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q33" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q34" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q35" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q36" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q37" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q38" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q39" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q40" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q41" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q42" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q43" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q44" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q45" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q46" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q47" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q48" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q49" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q50" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q51" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q52" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q53" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q54" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q55" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q56" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q57" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q58" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q59" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q60" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q61" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q62" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q63" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q64" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q65" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q66" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q67" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q68" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q69" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I70" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q70" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q71" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q72" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q73" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q74" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q75" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q76" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q77" r:id="rId124"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/rrl_matrix.xlsx
+++ b/output/rrl_matrix.xlsx
@@ -441,7 +441,7 @@
     <col width="16" customWidth="1" min="15" max="15"/>
     <col width="19" customWidth="1" min="16" max="16"/>
     <col width="27" customWidth="1" min="17" max="17"/>
-    <col width="18" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
     <col width="60" customWidth="1" min="19" max="19"/>
   </cols>
   <sheetData>
@@ -705,7 +705,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>dean_provided,s2</t>
+          <t>s2</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
@@ -786,7 +786,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>dean_provided,s2</t>
+          <t>s2</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>dean_provided,s2</t>
+          <t>s2</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
@@ -2821,7 +2821,7 @@
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>dean_provided,s2</t>
+          <t>s2</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">

--- a/output/rrl_matrix.xlsx
+++ b/output/rrl_matrix.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="high_confidence" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="review_needed" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="high_confidence" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="review_needed" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S77"/>
+  <dimension ref="A1:S73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -636,17 +636,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>786b0581c04bbb7a</t>
+          <t>af7fc167eb9a6103</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Artificial intelligence in higher education: a bibliometric analysis of research trends (2015–2024)</t>
+          <t>Business Simulation in the Context of Emerging Technologies the SPEE Case Study</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Mittal, N.; Batra, G.; Sijariya, R.</t>
+          <t>Sequeira, G.; Pereira, R.; Cossa, G.; Pinto, A.; Roque, L.</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -659,17 +659,22 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>International Conference on Artificial Intelligence in Education</t>
+          <t>Lecture notes in computer science</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Springer Science+Business Media</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>book-chapter</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10.1108/aiie-04-2025-0076</t>
+          <t>10.1007/978-3-032-20129-4_24</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -679,7 +684,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -692,42 +697,47 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026/786b0581c04bbb7a.pdf</t>
+          <t>2026/af7fc167eb9a6103.pdf</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>s2</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
-          <t>Purpose Previous research on Artificial Intelligence in Education (AIEd) has predominantly focused on specific tools and outcomes. Few studies provide data-driven insights into its evolution, particularly in the period after the launch of ChatGPT. This study addresses this gap through a bibliometric analysis of publications on Artificial Intelligence in Higher Education from 2015 to 2024, mapping research output, collaboration patterns, and citation trends. Design/methodology/approach A total of 1,671 peer-reviewed journal articles indexed in Scopus were analyzed based on the PRISMA framework. Using performance analysis and scientific mapping, the study examined the AIEd research landscape to offer document, author, country, institution, and keyword-level insights. Findings The publications depict a 67% annual growth rate, especially after 2022, with output tripling from 353 in 2023 to 927 in 2024, coinciding with the release of ChatGPT. Most highly cited articles focus on generative AI, signifying a thematic shift towards AI-driven academic concerns like academic integrity, assessment challenges, and AI ethics. Practical implications The findings can guide universities in implementing AI literacy initiatives, embedding ethical safeguards, and shaping evidence-based institutional and policy frameworks for responsible AI integration. Originality/value This study captures the trajectory of AI in higher education over the past decade. It highlights a significant thematic shift in research following the emergence of ChatGPT, which has not yet been comprehensively assessed. The findings of the study are poised to shape the direction of future research in the field.</t>
+          <t>This study analyzed the factors to consider for updating business simulation systems within the context of digital transformation driven by emerging technologies. To achieve this, a qualitative research approach was adopted, focusing on the Business Practices and Entrepreneurship System (SPEE), the leading business simulator in Mozambique, to identify critical factors for its modernization. The investigation, conducted as a single case study, incorporated a literature review, document analysis, and interviews, which revealed five key dimensions: realism, multidisciplinary approach, communication and interaction, ease of use and support, and accessibility and scalability. The research concluded that the most significant factors include the complexity of the local market, automation and operational efficiency, the level of digital literacy and technological infrastructure, the anticipation of future scenarios, and the enhancement of user experience. These findings suggest that integrating emerging technologies such as Artificial Intelligence (AI), Blockchain, and Virtual Reality (VR) could enhance realism, adaptability, and user engagement. Additionally, hybrid solutions combining online and offline accessibility were recommended to address technological infrastructure limitations in developing countries. The study provides practical guidelines for aligning SPEE with contemporary educational and market demands, reinforcing its relevance in higher education.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>281df417f101e592</t>
+          <t>5237174bb1448508</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Artificial intelligence in higher education: faculty empowerment or future workplace stress</t>
+          <t>Deploying Generative-AI-Powered Multimodal Intelligence for Bespoke English Language Instruction: A Cross-Disciplinary Case Study in 21st-Century Higher Education</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Soomro, S.; Fan, M.; Soomro, S.; Sohu, J.; Shaikh, S.; Kherazi, F.</t>
+          <t>Raj, D.; Anuradha, G.; Kavitha, V.; Shalini, K.; Steffi, R.; Mathew, D.</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -740,17 +750,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Learning Futures and Emerging Technologies</t>
+          <t>Communications in computer and information science</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Springer Science+Business Media</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>book-chapter</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>10.1108/lfet-06-2025-0077</t>
+          <t>10.1007/978-3-032-17300-3_14</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -773,42 +788,47 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026/281df417f101e592.pdf</t>
+          <t>2026/5237174bb1448508.pdf</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>s2</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>Purpose This research paper aims to investigate the impact of artificial intelligence adoption (AIA) on workplace well-being (WWB) in Pakistani higher education institutions (HEIs) with a focus on the mediating roles of job autonomy (JA) and work–life balance (WLB) and the moderating effect of training (T). Design/methodology/approach Applying cross-sectional survey research, the data were gathered from 462 Faculty members within Pakistani HEIs. Constructs were measured using validated scales. The analysis used structural equation modeling (SEM) to test direct, mediating and moderating relationships among variables. Findings AI adoption was found to affect faculty workplace well-being significantly. Although AI increases efficiency and flexibility, it entails risks of work intensification and decreased job control. Job autonomy and work–life balance partially mediate the AIA–WWB relation. Moreover, training significantly moderates the relationship between AI adoption and job autonomy. Originality/value To the best of the authors’ knowledge, this analysis provides one of the first empirical considerations of AI’s implications on faculty well-being. It extends SDT by integrating it into AI adoption research and highlights how psychological needs interact with digital transformation in academic environments.</t>
+          <t>Abstract This study examines the use of generative artificial intelligence and multimodal analytics to create a more personalised experience of English language instruction for the pertinent diverse learners in higher education institutions. Using a large major research university as the site of an extensive case study, and with a sizeable contingent of disciplinary English as a Second Language (ESL) instructors, who worked at the behest of the principal investigator, unquestioningly, for 12 months, the discipline-agnostic experimental classroom was populated with upward of 200 ESL students, each of whom was subject to varying degrees and types of private AI supervision. The study makes a substantial contribution to research on educational technologies by establishing a robust framework for integrating multimodal AI into education. It is clear that the comfortable pedagogical fit of AI in language education is the result of: (1) fostering instructor agency through careful and inclusive planning; (2) placing personnel training at the center of implementation efforts; (3) enacting strong support throughout all levels of the institution; and (4) keeping the ethics of AI use at the forefront of decision-making.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>8ab99685bf611427</t>
+          <t>26c869f88b616e34</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Artificial intelligence in higher education: stakeholder perceptions and policy implications</t>
+          <t>Efficacy of Selected Generative AI Systems in Assessing Discourse Coherence, Pragmatic Competence, Collocational Competence, and Figurative Language</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lawrence, S.</t>
+          <t>Prajapati, A.; Teraiya, A.; Vaghela, K.</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -821,22 +841,22 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Journal of Applied Research in Higher Education</t>
+          <t>Communications in computer and information science</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Babeș-Bolyai University</t>
+          <t>Springer Science+Business Media</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>article</t>
+          <t>book-chapter</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>10.1108/jarhe-10-2025-0872</t>
+          <t>10.1007/978-3-032-17300-3_10</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -857,44 +877,49 @@
       <c r="M5" t="inlineStr">
         <is>
           <t>Yes</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="O5" t="n">
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>2026/8ab99685bf611427.pdf</t>
+          <t>2026/26c869f88b616e34.pdf</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>s2</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>Purpose This study aims to examine stakeholder perceptions of artificial intelligence (AI) at a small regional comprehensive university in the southern United States to inform the development of ethical, transparent and inclusive institutional policies. Guided by an integrated conceptual framework, the study explored how stakeholder role and age influence perceptions of AI and identified perceived training and policy gaps related to responsible AI use. Design/methodology/approach Guided by the technology acceptance model, diffusion of innovations theory, the ethical decision-making framework and social constructivism, the study employed an exploratory survey design (n = 248) combining Likert-scale items and open-ended responses. Quantitative data were analyzed using descriptive and nonparametric statistics, and qualitative data were examined through thematic analysis to capture both patterns and contextual insights. Findings Results revealed significant differences in AI perceptions by role and age. Students were highly accepting of AI for learning and efficiency, whereas faculty and administrators expressed greater concern about academic integrity, privacy and ethical use. Staff responses were mixed, emphasizing workflow efficiency alongside ethical and governance-related risks. Across groups, participants highlighted the need for clearer guidelines and structured training to support responsible AI adoption. Research limitations/implications The single-institution, cross-sectional design may limit transferability. Future research could extend these findings through multi-institutional, longitudinal or qualitative studies that further examine evolving AI governance and practice. Practical implications Findings provide actionable guidance for developing AI policies, professional learning and governance structures that promote transparency, accountability, and equitable access while respecting institutional context. Originality/value This study contributes a multi-stakeholder empirical analysis of AI perceptions within a single institutional context, guided by an integrated conceptual framework to inform ethical policy, governance and practice in higher education.</t>
+          <t>Abstract Artificial Intelligence (AI) is rapidly transforming language education, functioning not merely as an automation tool but as a catalyst for understanding, accuracy, and individualized learning. Nonetheless, despite the extensive integration of AI in education, comprehension of its efficacy in assessing language proficiency, particularly these four parameters, discourse coherence, pragmatic competence, collocational competence, and figurative language, remains largely underexplored from the perspective of integrating AI. Consequently, capacity to embed AI driven formative assessments for enhanced feedback can be insightful. The present study assesses the efficacy of five leading generative AI systems namely GPT-4, Gemini, DeepSeek, Copilot, and Claude Sonnet 4, through standardised dialogues that encompass four linguistic criteria, discourse coherence, pragmatic competence, collocational competence, and figurative language. language. The dialogues constructed by students as a part of a classroom activity are assessed through each AI tool will through CEFR based 5-point rubrics. The study of this evaluation, aims to explore how effectively and precisely these AI tools process the specific language inputs deliver the feedback that aids learners in improving expression, increasing their clarity, and enriching their contextual comprehension. The findings of this study will benefit teachers, curriculum developers and language learners by offering evidence-based insights into which generative AI systems can be utilised for the improvement, accuracy and learner autonomy in higher education and EFL domains.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>af7fc167eb9a6103</t>
+          <t>2e7b056c99eebd67</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Business Simulation in the Context of Emerging Technologies the SPEE Case Study</t>
+          <t>Enhancing Agile Workflows with AI-Driven, Sustainability-Aware Requirements Engineering: A Design Science Approach</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Sequeira, G.; Pereira, R.; Cossa, G.; Pinto, A.; Roque, L.</t>
+          <t>Weerakoon, O.; Oyedeji, S.; Samad, M.; Abubakar, A.; Ishan, A.; Shayan, M.; Mäkilä, T.; Kaila, E.</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -907,7 +932,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lecture notes in computer science</t>
+          <t>Lecture notes in business information processing</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -922,7 +947,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>10.1007/978-3-032-20129-4_24</t>
+          <t>10.1007/978-3-032-14518-5_17</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -958,7 +983,7 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026/af7fc167eb9a6103.pdf</t>
+          <t>2026/2e7b056c99eebd67.pdf</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -968,24 +993,24 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>This study analyzed the factors to consider for updating business simulation systems within the context of digital transformation driven by emerging technologies. To achieve this, a qualitative research approach was adopted, focusing on the Business Practices and Entrepreneurship System (SPEE), the leading business simulator in Mozambique, to identify critical factors for its modernization. The investigation, conducted as a single case study, incorporated a literature review, document analysis, and interviews, which revealed five key dimensions: realism, multidisciplinary approach, communication and interaction, ease of use and support, and accessibility and scalability. The research concluded that the most significant factors include the complexity of the local market, automation and operational efficiency, the level of digital literacy and technological infrastructure, the anticipation of future scenarios, and the enhancement of user experience. These findings suggest that integrating emerging technologies such as Artificial Intelligence (AI), Blockchain, and Virtual Reality (VR) could enhance realism, adaptability, and user engagement. Additionally, hybrid solutions combining online and offline accessibility were recommended to address technological infrastructure limitations in developing countries. The study provides practical guidelines for aligning SPEE with contemporary educational and market demands, reinforcing its relevance in higher education.</t>
+          <t>Generative AI presents growing opportunities across various fields, including Requirements Engineering (RE). RE, which is the backbone of software projects, drives the entire product development toward respective business goals. However, sustainability is not considered a primary need during the requirement elicitation, and as a result, software engineers are usually unable to envision the sustainability impacts of the products they build. To explore this gap, we introduce Reqwire, an AI-driven, sustainability-aware multi-agent system that (i) generates user stories from software requirement documents, (ii) enriches them with sustainability attributes, and (iii) integrates with common agile project management tools, like Jira. The system consists of specialized agents, namely as root, distributor, user story generator, and Jira. We followed a Design Science Research (DSR) approach under seven iterative cycles, incorporating feedback from an industry partner and academia to design and evaluate the Reqwire workflow. Our results indicate that Reqwire reduces manual effort by generating structured user stories, estimating story points, and assigning sustainability tags across five sustainability dimensions: environmental, economic, social, individual, and technical. The multi-agent-based framework enables integration with third-party tools, supporting consistent, systematic project tracking. Reqwire shows promise for enhancing agile workflows and promoting sustainable software practices from initial test rounds with the client.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5237174bb1448508</t>
+          <t>19da11449909222f</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Deploying Generative-AI-Powered Multimodal Intelligence for Bespoke English Language Instruction: A Cross-Disciplinary Case Study in 21st-Century Higher Education</t>
+          <t>Narrative AI Strategies for Media, Ethics and Higher Education Impulse Perspectives from Practice Based Media Education</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Raj, D.; Anuradha, G.; Kavitha, V.; Shalini, K.; Steffi, R.; Mathew, D.</t>
+          <t>Simon, M.; Khafif, D.</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -998,7 +1023,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Communications in computer and information science</t>
+          <t>Lecture notes in business information processing</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1013,7 +1038,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>10.1007/978-3-032-17300-3_14</t>
+          <t>10.1007/978-3-032-14518-5_18</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1045,11 +1070,11 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>2026/5237174bb1448508.pdf</t>
+          <t>2026/19da11449909222f.pdf</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -1059,24 +1084,24 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>Abstract This study examines the use of generative artificial intelligence and multimodal analytics to create a more personalised experience of English language instruction for the pertinent diverse learners in higher education institutions. Using a large major research university as the site of an extensive case study, and with a sizeable contingent of disciplinary English as a Second Language (ESL) instructors, who worked at the behest of the principal investigator, unquestioningly, for 12 months, the discipline-agnostic experimental classroom was populated with upward of 200 ESL students, each of whom was subject to varying degrees and types of private AI supervision. The study makes a substantial contribution to research on educational technologies by establishing a robust framework for integrating multimodal AI into education. It is clear that the comfortable pedagogical fit of AI in language education is the result of: (1) fostering instructor agency through careful and inclusive planning; (2) placing personnel training at the center of implementation efforts; (3) enacting strong support throughout all levels of the institution; and (4) keeping the ethics of AI use at the forefront of decision-making.</t>
+          <t>The transformation of narrative creation, authorship, and authenticity in the age of Generative AI is not merely a technological shift, but a cultural, epistemic, and ethical realignment. This paper argues that this transformation requires a threefold competence profile—technical proficiency, narrative design capability, and ethical reflexivity—cultivated in both higher education and corporate practice. This motive connects interdisciplinary teaching with strategic implications for communication, marketing, and oragnisational governance, bridging theory and real-world applications.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>26c869f88b616e34</t>
+          <t>bde689abecf48b32</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Efficacy of Selected Generative AI Systems in Assessing Discourse Coherence, Pragmatic Competence, Collocational Competence, and Figurative Language</t>
+          <t>Practical Adoption of Green Coding: A Comparative Study Across Organizations in Finland and Globally</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Prajapati, A.; Teraiya, A.; Vaghela, K.</t>
+          <t>Moktan, I.; Khan, M.; Oyedeji, S.; Puonti, M.; Adisa, M.; Porras, J.</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -1089,7 +1114,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Communications in computer and information science</t>
+          <t>Lecture notes in business information processing</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1104,7 +1129,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>10.1007/978-3-032-17300-3_10</t>
+          <t>10.1007/978-3-032-14518-5_28</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1136,11 +1161,11 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>2026/26c869f88b616e34.pdf</t>
+          <t>2026/bde689abecf48b32.pdf</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -1150,28 +1175,28 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>Abstract Artificial Intelligence (AI) is rapidly transforming language education, functioning not merely as an automation tool but as a catalyst for understanding, accuracy, and individualized learning. Nonetheless, despite the extensive integration of AI in education, comprehension of its efficacy in assessing language proficiency, particularly these four parameters, discourse coherence, pragmatic competence, collocational competence, and figurative language, remains largely underexplored from the perspective of integrating AI. Consequently, capacity to embed AI driven formative assessments for enhanced feedback can be insightful. The present study assesses the efficacy of five leading generative AI systems namely GPT-4, Gemini, DeepSeek, Copilot, and Claude Sonnet 4, through standardised dialogues that encompass four linguistic criteria, discourse coherence, pragmatic competence, collocational competence, and figurative language. language. The dialogues constructed by students as a part of a classroom activity are assessed through each AI tool will through CEFR based 5-point rubrics. The study of this evaluation, aims to explore how effectively and precisely these AI tools process the specific language inputs deliver the feedback that aids learners in improving expression, increasing their clarity, and enriching their contextual comprehension. The findings of this study will benefit teachers, curriculum developers and language learners by offering evidence-based insights into which generative AI systems can be utilised for the improvement, accuracy and learner autonomy in higher education and EFL domains.</t>
+          <t>As the environmental impact of digital technologies gains increasing attention, green coding has emerged as a critical aspect of green software engineering. This study investigates the practical adoption of green coding practices in organizations in Finland and globally to understand how they approach green coding in their software-development workflow. This study adopts a qualitative research methodology, combining a systematic literature review and semi-structured interviews. Key findings indicate that while organizations adhere to academic-recommended coding practices such as caching, lazy loading, asynchronous processing, microservices, and content/UI optimization, industry prioritization often depends on business needs, with less emphasis on energy-efficient programming languages or priority in green coding, especially in organizations outside the EU. Interestingly, in larger organizations, such as banks, green coding initiatives are mostly driven from the bottom up and led by software engineers. This reflects a positive change. However, innovative academic proposals, such as large language model (LLM)-based assistants for recommending green libraries, remain prototypes without industrial adoption. While LLM-based assistants show potential in recommending greener libraries, their current energy demand raises questions about net sustainability. Future research should evaluate their carbon trade-offs to ensure these tools contribute positively to sustainability goals. This study underscores the need for closer collaboration between academia and industry to promote the practical adoption of effective tools, along with standardized guidelines and sustainability-oriented education, to enable the wider adoption of green coding practices.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2e7b056c99eebd67</t>
+          <t>966facd8e5a135ea</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Enhancing Agile Workflows with AI-Driven, Sustainability-Aware Requirements Engineering: A Design Science Approach</t>
+          <t>Accelerating Acoustics: A Learning Paradigm with Python and Prompt Engineering</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Weerakoon, O.; Oyedeji, S.; Samad, M.; Abubakar, A.; Ishan, A.; Shayan, M.; Mäkilä, T.; Kaila, E.</t>
+          <t>Mari Ueda; Katsuhiro Kanamori; Katsumi Takahashi; Shogo Kiryu; Tetsuo Tanaka</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -1180,22 +1205,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lecture notes in business information processing</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Springer Science+Business Media</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>book-chapter</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-032-14518-5_17</t>
+          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1205,7 +1215,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
@@ -1218,51 +1228,43 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>hybrid</t>
-        </is>
-      </c>
-      <c r="O9" t="n">
-        <v>0</v>
-      </c>
       <c r="P9" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>2026/2e7b056c99eebd67.pdf</t>
+          <t>2025/966facd8e5a135ea.pdf</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>eric</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>Generative AI presents growing opportunities across various fields, including Requirements Engineering (RE). RE, which is the backbone of software projects, drives the entire product development toward respective business goals. However, sustainability is not considered a primary need during the requirement elicitation, and as a result, software engineers are usually unable to envision the sustainability impacts of the products they build. To explore this gap, we introduce Reqwire, an AI-driven, sustainability-aware multi-agent system that (i) generates user stories from software requirement documents, (ii) enriches them with sustainability attributes, and (iii) integrates with common agile project management tools, like Jira. The system consists of specialized agents, namely as root, distributor, user story generator, and Jira. We followed a Design Science Research (DSR) approach under seven iterative cycles, incorporating feedback from an industry partner and academia to design and evaluate the Reqwire workflow. Our results indicate that Reqwire reduces manual effort by generating structured user stories, estimating story points, and assigning sustainability tags across five sustainability dimensions: environmental, economic, social, individual, and technical. The multi-agent-based framework enables integration with third-party tools, supporting consistent, systematic project tracking. Reqwire shows promise for enhancing agile workflows and promoting sustainable software practices from initial test rounds with the client.</t>
+          <t>Generative Artificial Intelligence (GenAI) is catalyzing a paradigm shift in higher education, demanding new pedagogical approaches that integrate AI literacy as a core competency. This paper addresses the long-standing challenge of teaching acoustics, a field often perceived as abstract and mathematically intensive by undergraduate students. We propose a novel, 13-week exercise-based course designed for the Faculty of Information Science at the Kanagawa Institute of Technology. This course uniquely integrates Python programming with the systematic application of prompt engineering to facilitate the learning of fundamental acoustics concepts. The methodology involves leveraging GenAI as a personalized tutor, a code-generation assistant for visualization, and a tool for conceptual exploration. The expected outcomes include not only a deeper, more intuitive understanding of acoustics but also the cultivation of critical AI literacy and problem-solving skills essential for the next generation of engineers. This approach has the transformative potential to reshape engineering pedagogy, making complex subjects more accessible and engaging while preparing students for a future of human-AI collaboration. [For the complete proceedings, &amp;quot;Proceedings of the International Association for Development of the Information Society (IADIS) International Conference on Cognition and Exploratory Learning in the Digital Age (CELDA) (22nd, Porto, Portugal, November 1-3, 2025),&amp;quot; see ED677812.]</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>19da11449909222f</t>
+          <t>0d507483b5131d42</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Narrative AI Strategies for Media, Ethics and Higher Education Impulse Perspectives from Practice Based Media Education</t>
+          <t>Adaptive Learning with Cognitive Awareness: An AI Model from the ELSEI Master&amp;apos;s Program</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Simon, M.; Khafif, D.</t>
+          <t>Zakaria Tagdimi; Souhaib Aammou; Marina Sounoglou</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -1271,22 +1273,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lecture notes in business information processing</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Springer Science+Business Media</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>book-chapter</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-032-14518-5_18</t>
+          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1296,7 +1283,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
@@ -1308,52 +1295,44 @@
         <is>
           <t>Yes</t>
         </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>hybrid</t>
-        </is>
-      </c>
-      <c r="O10" t="n">
-        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>2</v>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>2026/19da11449909222f.pdf</t>
+          <t>2025/0d507483b5131d42.pdf</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>eric</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>The transformation of narrative creation, authorship, and authenticity in the age of Generative AI is not merely a technological shift, but a cultural, epistemic, and ethical realignment. This paper argues that this transformation requires a threefold competence profile—technical proficiency, narrative design capability, and ethical reflexivity—cultivated in both higher education and corporate practice. This motive connects interdisciplinary teaching with strategic implications for communication, marketing, and oragnisational governance, bridging theory and real-world applications.</t>
+          <t>Personalization is often perceived as a technical problem in the context of digital education. However, it is also a cognitive challenge, requiring an understanding of how learners process information. This study presents a cognitive-based recommendation model designed and tested within the Master's program in E-learning and Intelligent Educational Systems (ELSEI) at the École Normale Supérieure (ENS) of Abdelmalek Essaadi University in Morocco. This model is based on the principles of cognitive load theory and uses artificial intelligence to adapt learning experiences in real time. The model aims to align content presentation with each learner's cognitive profile. This alignment is achieved through clustering, load classification, and hybrid recommendation techniques. This model is tested for six weeks involving 47 graduate students and has shown encouraging results: an improvement in engagement and academic performance, as well as a reduction in learning disruptions related to overload. These results suggest a broader evolution of educational AI, towards systems that are not only adaptive, but also attentive to the cognitive demands of learning. [For the complete proceedings, &amp;quot;Proceedings of the International Association for Development of the Information Society (IADIS) International Conference on Cognition and Exploratory Learning in the Digital Age (CELDA) (22nd, Porto, Portugal, November 1-3, 2025),&amp;quot; see ED677812.]</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>bde689abecf48b32</t>
+          <t>049208b9a6bac215</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Practical Adoption of Green Coding: A Comparative Study Across Organizations in Finland and Globally</t>
+          <t>Artificial Intelligence in ESP Education Transformations, Ethical Considerations and Future Directions</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Moktan, I.; Khan, M.; Oyedeji, S.; Puonti, M.; Adisa, M.; Porras, J.</t>
+          <t>Silvia Osman</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>2026</v>
+        <v>2025</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -1362,22 +1341,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lecture notes in business information processing</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Springer Science+Business Media</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>book-chapter</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-032-14518-5_28</t>
+          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1387,7 +1351,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
@@ -1399,48 +1363,40 @@
         <is>
           <t>Yes</t>
         </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>hybrid</t>
-        </is>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
       </c>
       <c r="P11" t="n">
         <v>3</v>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>2026/bde689abecf48b32.pdf</t>
+          <t>2025/049208b9a6bac215.pdf</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>eric</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>As the environmental impact of digital technologies gains increasing attention, green coding has emerged as a critical aspect of green software engineering. This study investigates the practical adoption of green coding practices in organizations in Finland and globally to understand how they approach green coding in their software-development workflow. This study adopts a qualitative research methodology, combining a systematic literature review and semi-structured interviews. Key findings indicate that while organizations adhere to academic-recommended coding practices such as caching, lazy loading, asynchronous processing, microservices, and content/UI optimization, industry prioritization often depends on business needs, with less emphasis on energy-efficient programming languages or priority in green coding, especially in organizations outside the EU. Interestingly, in larger organizations, such as banks, green coding initiatives are mostly driven from the bottom up and led by software engineers. This reflects a positive change. However, innovative academic proposals, such as large language model (LLM)-based assistants for recommending green libraries, remain prototypes without industrial adoption. While LLM-based assistants show potential in recommending greener libraries, their current energy demand raises questions about net sustainability. Future research should evaluate their carbon trade-offs to ensure these tools contribute positively to sustainability goals. This study underscores the need for closer collaboration between academia and industry to promote the practical adoption of effective tools, along with standardized guidelines and sustainability-oriented education, to enable the wider adoption of green coding practices.</t>
+          <t>In the rapidly evolving digital landscape, artificial intelligence (AI) is fundamentally redefining English for Specific Purposes (ESP) education across disciplines such as Political Studies, International Relations, Sociology, and Psychology. This paper explores how AI-powered tools enhance personalized, immersive, and authentic learning experiences, fostering core linguistic and intercultural skills. Drawing on my extensive experience as a visiting professor at the University of Naples &amp;quot;Federico II&amp;quot; and Vlora University, I analyze pedagogical strategies, ethical challenges--including GDPR compliance and the EU AI Act--and the influence of digital sovereignty. This comprehensive discussion aims to provide strategic pathways for responsible and effective AI integration into ESP curricula, emphasizing the importance of preparing students for the demands of an interconnected, multicultural professional environment. [For the complete proceedings, &amp;quot;Proceedings of the International Association for Development of the Information Society (IADIS) International Conference on Cognition and Exploratory Learning in the Digital Age (CELDA) (22nd, Porto, Portugal, November 1-3, 2025),&amp;quot; see ED677812.]</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>966facd8e5a135ea</t>
+          <t>f34f1bb5de578666</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Accelerating Acoustics: A Learning Paradigm with Python and Prompt Engineering</t>
+          <t>Boosting English Language Listening Skills through Copilot AI (A Case of Georgian Higher Education Institutions)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Mari Ueda; Katsuhiro Kanamori; Katsumi Takahashi; Shogo Kiryu; Tetsuo Tanaka</t>
+          <t>Eliza Kintsurashvili</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -1453,7 +1409,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
+          <t>International Society for Technology, Education, and Science. 944 Maysey Drive, San Antonio, TX 78227. Tel: 515-294-1075; Fax: 515-294-1003; email: istesoffice@gmail.com; Web site: http://www.istes.org</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1477,11 +1433,11 @@
         </is>
       </c>
       <c r="P12" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>2025/966facd8e5a135ea.pdf</t>
+          <t>2025/f34f1bb5de578666.pdf</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -1491,24 +1447,24 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>Generative Artificial Intelligence (GenAI) is catalyzing a paradigm shift in higher education, demanding new pedagogical approaches that integrate AI literacy as a core competency. This paper addresses the long-standing challenge of teaching acoustics, a field often perceived as abstract and mathematically intensive by undergraduate students. We propose a novel, 13-week exercise-based course designed for the Faculty of Information Science at the Kanagawa Institute of Technology. This course uniquely integrates Python programming with the systematic application of prompt engineering to facilitate the learning of fundamental acoustics concepts. The methodology involves leveraging GenAI as a personalized tutor, a code-generation assistant for visualization, and a tool for conceptual exploration. The expected outcomes include not only a deeper, more intuitive understanding of acoustics but also the cultivation of critical AI literacy and problem-solving skills essential for the next generation of engineers. This approach has the transformative potential to reshape engineering pedagogy, making complex subjects more accessible and engaging while preparing students for a future of human-AI collaboration. [For the complete proceedings, &amp;quot;Proceedings of the International Association for Development of the Information Society (IADIS) International Conference on Cognition and Exploratory Learning in the Digital Age (CELDA) (22nd, Porto, Portugal, November 1-3, 2025),&amp;quot; see ED677812.]</t>
+          <t>This study explores the impact of Copilot AI on enhancing English language listening skills among B1-level students through an experimental research design. The research involved two groups: an experimental group that used Copilot AI for listening practice and a control group that followed traditional listening activities. Over a set period, students in the experimental group engaged with AI-generated listening exercises, interactive transcripts, and real-time feedback, while the control group relied on conventional audio materials and teacher-led discussions. Pre- and post-tests were administered to measure improvements in listening comprehension. The results indicate that students showing to Copilot AI demonstrated greater progress in their ability to understand spoken English, recognize key details, and respond accurately. The study highlights the potential of AI-assisted learning in improving listening proficiency and suggests practical applications for integrating AI tools into English language instruction. [For the complete proceedings, see ED678959.]</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0d507483b5131d42</t>
+          <t>c6a4accaccaeb577</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Adaptive Learning with Cognitive Awareness: An AI Model from the ELSEI Master&amp;apos;s Program</t>
+          <t>Capacity Building in Livestock Breeding and Genetic Improvement in Achieving UN Sustainable Development Goals for Africa</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Zakaria Tagdimi; Souhaib Aammou; Marina Sounoglou</t>
+          <t>Tiambo, C.; Opoola, O.; Okpeku, M.; Houaga, I.; Touko, B.; Dessie, T.</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -1521,7 +1477,22 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
+          <t>Sustainable development goals series</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Springer International Publishing</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>book-chapter</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-031-92076-9_28</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1531,7 +1502,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1544,39 +1515,47 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
       <c r="P13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>2025/0d507483b5131d42.pdf</t>
+          <t>2025/c6a4accaccaeb577.pdf</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>eric</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>Personalization is often perceived as a technical problem in the context of digital education. However, it is also a cognitive challenge, requiring an understanding of how learners process information. This study presents a cognitive-based recommendation model designed and tested within the Master's program in E-learning and Intelligent Educational Systems (ELSEI) at the École Normale Supérieure (ENS) of Abdelmalek Essaadi University in Morocco. This model is based on the principles of cognitive load theory and uses artificial intelligence to adapt learning experiences in real time. The model aims to align content presentation with each learner's cognitive profile. This alignment is achieved through clustering, load classification, and hybrid recommendation techniques. This model is tested for six weeks involving 47 graduate students and has shown encouraging results: an improvement in engagement and academic performance, as well as a reduction in learning disruptions related to overload. These results suggest a broader evolution of educational AI, towards systems that are not only adaptive, but also attentive to the cognitive demands of learning. [For the complete proceedings, &amp;quot;Proceedings of the International Association for Development of the Information Society (IADIS) International Conference on Cognition and Exploratory Learning in the Digital Age (CELDA) (22nd, Porto, Portugal, November 1-3, 2025),&amp;quot; see ED677812.]</t>
+          <t>Abstract To achieve the Sustainable Development Goals of the United Nations (UN-SDGs) in Africa, livestock breeding efficiency is a prerequisite. Human capital in the form of professional, managerial, and technical skills, improved policies and institutional operation are the key enablers of performance for the smallholder livestock sector. Capacity building is central to guarantee African livestock efficiency along the value chains and ultimately transformed livelihoods. Currently, animal breeding and genetic improvement in Africa are constrained by a serious human and institutional capacity gap. The Livestock Development Strategy for Africa (LiDESA) seeks to transform the livestock sector for accelerated and equitable growth and for enhanced contribution to socio-economic development. Sustainable livestock development in Africa could be better realized through the development of customized capacity building strategies targeting (1) relevant participatory breeding education, hands-on training, efficient technical assistance, and collaborations / partnerships aiming to address farmers’ present and future challenges, (2) enabling breeding systems for sustainable productivity, resilience of breeds, and animal seed stock management, and (3) market-led breeding solutions that are attractive for the younger and future generations. Challenges facing capacity building in livestock breeding in Africa vary between and within stakeholders of specific value chains, and farmers lack training and suitable support programmes for their breeding activities. Beyond the lack of skilled human resources, financial capacity to enforce legislation and policies in Animal Genetic Resources (AnGR) that may lead to the design and implementation of conservation and breeding programmes is a major limiting factor in most African countries. Currently, animal breeding programmes may not thrive, unless a new cohort of breeders, infrastructures, and policies are in place and backed by long-term investment plans. The main loopholes of the desired revolution reside in the current gaps and limitations of higher education and professional trainings, in terms of human resources, infrastructure, curricular content, research, and cooperation. The required capacity development could also be through people-centred community-based breeding programmes (CBBP), training of trainers, and continuous education with major inputs/roles by agricultural training institutions (e.g. Pan African University), the African Union InterAfrican Bureau for Animal Genetics Resources (AU-IBAR) and the African Animal Breeding Network (AABNet), in the form of collaborations for teaching, research, and outreach. Key capacity building intervention areas needing attention are: (1) Conservation and restoration of local animal genetic diversity, their improvement and dissemination of elite locally adapted and farmers-preferred genetics, and preservation of their natural habitat; (2) Demand-led capacity development in modern livestock breeding techniques; (3) Sustainable intensification of livestock farming practices; (4) Adaptation to extreme environmental conditions and livestock emergency guidelines and standards (LEGS); (5) Breeding for animal welfare, adaptability, and biosafety; (6) Big Data and artificial intelligence for smart farming and livestock breeding programmes; and (7) Infrastructural development and policies’ integration for technology uptake.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>049208b9a6bac215</t>
+          <t>262fa18a25cef7c6</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Artificial Intelligence in ESP Education Transformations, Ethical Considerations and Future Directions</t>
+          <t>Catastrophic Computation. On the Impossibility of Sustainable Artificial Intelligence</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Silvia Osman</t>
+          <t>Rehak, R.</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -1589,7 +1568,22 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
+          <t>Lecture notes in computer science</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Springer Science+Business Media</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>book-chapter</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-032-11108-1_8</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1599,7 +1593,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
@@ -1612,39 +1606,47 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
       <c r="P14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>2025/049208b9a6bac215.pdf</t>
+          <t>2025/262fa18a25cef7c6.pdf</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>eric</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>In the rapidly evolving digital landscape, artificial intelligence (AI) is fundamentally redefining English for Specific Purposes (ESP) education across disciplines such as Political Studies, International Relations, Sociology, and Psychology. This paper explores how AI-powered tools enhance personalized, immersive, and authentic learning experiences, fostering core linguistic and intercultural skills. Drawing on my extensive experience as a visiting professor at the University of Naples &amp;quot;Federico II&amp;quot; and Vlora University, I analyze pedagogical strategies, ethical challenges--including GDPR compliance and the EU AI Act--and the influence of digital sovereignty. This comprehensive discussion aims to provide strategic pathways for responsible and effective AI integration into ESP curricula, emphasizing the importance of preparing students for the demands of an interconnected, multicultural professional environment. [For the complete proceedings, &amp;quot;Proceedings of the International Association for Development of the Information Society (IADIS) International Conference on Cognition and Exploratory Learning in the Digital Age (CELDA) (22nd, Porto, Portugal, November 1-3, 2025),&amp;quot; see ED677812.]</t>
+          <t>Artificial intelligence (AI) is currently considered a sustainability “game-changer” within and outside of academia. I argue that while there are indeed many sustainability-related use cases for AI, they are likely to have more overall drawbacks than benefits. To substantiate this claim, I differentiate three ‘AI materialities’ of the AI supply chain: first the literal materiality (e.g. water, cobalt, lithium, energy consumption etc.), second, the informational materiality (e.g. lots of data and centralised control necessary), and third, the social materiality (e.g. exploitative data work, communities harm by waste and pollution). In all materialities, effects are especially devastating for the global south while benefiting the global north. A second strong claim regarding sustainable AI circles around so-called apolitical optimisation (e.g. regarding city traffic), however the optimisation criteria (e.g. cars, bikes, emissions, commute time, health) are purely political and have to be collectively negotiated before applying AI optimisation. Hence, sustainable AI, in principle, cannot break the glass ceiling of transformation and might even distract from necessary societal change. To address that I propose to stop ‘unformation gathering’ and to apply the ‘small is beautiful’ principle. This aims to contribute to an informed academic and collective negotiation on how to (not) integrate AI into the sustainability project while avoiding to reproduce the status quo by serving hegemonic interests between useful AI use cases, techno-utopian salvation narratives, technology-centred efficiency paradigms, the exploitative and extractivist character of AI and concepts of digital degrowth. In order to discuss sustainable AI, this article draws from insights by critical data and algorithm studies, STS, transformative sustainability science, critical computer science, and public interest theory.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>f34f1bb5de578666</t>
+          <t>ca3c5062dc813e4f</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Boosting English Language Listening Skills through Copilot AI (A Case of Georgian Higher Education Institutions)</t>
+          <t>Comparative Analysis of Generative AI Performance in University Programming Courses</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Eliza Kintsurashvili</t>
+          <t>Suomalainen, E.; Vanhala, E.; Ikonen, J.</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -1657,7 +1659,22 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>International Society for Technology, Education, and Science. 944 Maysey Drive, San Antonio, TX 78227. Tel: 515-294-1075; Fax: 515-294-1003; email: istesoffice@gmail.com; Web site: http://www.istes.org</t>
+          <t>Lecture notes in business information processing</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Springer Science+Business Media</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>book-chapter</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-032-14518-5_16</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1667,7 +1684,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
@@ -1680,39 +1697,47 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
       <c r="P15" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>2025/f34f1bb5de578666.pdf</t>
+          <t>2025/ca3c5062dc813e4f.pdf</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
         <is>
-          <t>eric</t>
+          <t>openalex,s2</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>This study explores the impact of Copilot AI on enhancing English language listening skills among B1-level students through an experimental research design. The research involved two groups: an experimental group that used Copilot AI for listening practice and a control group that followed traditional listening activities. Over a set period, students in the experimental group engaged with AI-generated listening exercises, interactive transcripts, and real-time feedback, while the control group relied on conventional audio materials and teacher-led discussions. Pre- and post-tests were administered to measure improvements in listening comprehension. The results indicate that students showing to Copilot AI demonstrated greater progress in their ability to understand spoken English, recognize key details, and respond accurately. The study highlights the potential of AI-assisted learning in improving listening proficiency and suggests practical applications for integrating AI tools into English language instruction. [For the complete proceedings, see ED678959.]</t>
+          <t>Generative artificial intelligence (GenAI) has had an impact on university education and also to the software industry. This can be seen in many different courses where GenAIs can complete exercises, exams, and even whole courses by themselves. This study aims to find out how effectively different GenAI tools can complete exercises in programming courses. Our objective is to find how GenAI’s performance varies across courses and what differences there are in results between multiple GenAI tools. During the study, five programming courses were evaluated using five different GenAI tools. These tools were able to solve 43–90% of programming assignments and 80–100% of quizzes. In practice, the result is that any of the selected GenAIs could have been used to pass the majority of all the tested course parts. Results indicate that we have to rethink how courses’ tasks are designed and that courses need to have an element where learning is verified in a controlled environment to verify that we are educating software professionals for the industry.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>c6a4accaccaeb577</t>
+          <t>2939cb4059ec9276</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Capacity Building in Livestock Breeding and Genetic Improvement in Achieving UN Sustainable Development Goals for Africa</t>
+          <t>Designing an Integrated Multi-Dimensional Assessment Framework for AI-Supported Academic Writing</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Tiambo, C.; Opoola, O.; Okpeku, M.; Houaga, I.; Touko, B.; Dessie, T.</t>
+          <t>Sabine Seufert; Niklas Eulitz</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -1725,22 +1750,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Sustainable development goals series</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Springer International Publishing</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>book-chapter</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-031-92076-9_28</t>
+          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1750,7 +1760,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
@@ -1763,47 +1773,39 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>hybrid</t>
-        </is>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
       <c r="P16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>2025/c6a4accaccaeb577.pdf</t>
+          <t>2025/2939cb4059ec9276.pdf</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>eric</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>Abstract To achieve the Sustainable Development Goals of the United Nations (UN-SDGs) in Africa, livestock breeding efficiency is a prerequisite. Human capital in the form of professional, managerial, and technical skills, improved policies and institutional operation are the key enablers of performance for the smallholder livestock sector. Capacity building is central to guarantee African livestock efficiency along the value chains and ultimately transformed livelihoods. Currently, animal breeding and genetic improvement in Africa are constrained by a serious human and institutional capacity gap. The Livestock Development Strategy for Africa (LiDESA) seeks to transform the livestock sector for accelerated and equitable growth and for enhanced contribution to socio-economic development. Sustainable livestock development in Africa could be better realized through the development of customized capacity building strategies targeting (1) relevant participatory breeding education, hands-on training, efficient technical assistance, and collaborations / partnerships aiming to address farmers’ present and future challenges, (2) enabling breeding systems for sustainable productivity, resilience of breeds, and animal seed stock management, and (3) market-led breeding solutions that are attractive for the younger and future generations. Challenges facing capacity building in livestock breeding in Africa vary between and within stakeholders of specific value chains, and farmers lack training and suitable support programmes for their breeding activities. Beyond the lack of skilled human resources, financial capacity to enforce legislation and policies in Animal Genetic Resources (AnGR) that may lead to the design and implementation of conservation and breeding programmes is a major limiting factor in most African countries. Currently, animal breeding programmes may not thrive, unless a new cohort of breeders, infrastructures, and policies are in place and backed by long-term investment plans. The main loopholes of the desired revolution reside in the current gaps and limitations of higher education and professional trainings, in terms of human resources, infrastructure, curricular content, research, and cooperation. The required capacity development could also be through people-centred community-based breeding programmes (CBBP), training of trainers, and continuous education with major inputs/roles by agricultural training institutions (e.g. Pan African University), the African Union InterAfrican Bureau for Animal Genetics Resources (AU-IBAR) and the African Animal Breeding Network (AABNet), in the form of collaborations for teaching, research, and outreach. Key capacity building intervention areas needing attention are: (1) Conservation and restoration of local animal genetic diversity, their improvement and dissemination of elite locally adapted and farmers-preferred genetics, and preservation of their natural habitat; (2) Demand-led capacity development in modern livestock breeding techniques; (3) Sustainable intensification of livestock farming practices; (4) Adaptation to extreme environmental conditions and livestock emergency guidelines and standards (LEGS); (5) Breeding for animal welfare, adaptability, and biosafety; (6) Big Data and artificial intelligence for smart farming and livestock breeding programmes; and (7) Infrastructural development and policies’ integration for technology uptake.</t>
+          <t>The widespread adoption of generative AI is transforming academic writing in higher education, rendering traditional, product-focused assessment models obsolete. These methods fail to capture the iterative and tool-mediated nature of modern writing processes, creating an urgent need for new evaluation approaches. This paper addresses this gap by proposing an integrated, multi-dimensional assessment framework. Grounded in genre pedagogy, self-regulated learning, and writing analytics, our model conceptualizes assessment as a holistic process. It evaluates foundational skills for AI use (Computational Thinking and Genre-Knowledge), the quality of text revision, final writing performance, and long-term development. By aligning these dimensions with formative, summative, and diagnostic purposes, the framework fosters transparency, metacognitive engagement, and responsible AI use. We are preparing a design-based research project to pilot and iteratively refine key elements of the framework within a mastery learning programme for 1,800 first-year students. The goal is to explore how the model can be implemented in practice and refined through iterative cycles of design, enactment, and evaluation. [For the complete proceedings, &amp;quot;Proceedings of the International Association for Development of the Information Society (IADIS) International Conference on Cognition and Exploratory Learning in the Digital Age (CELDA) (22nd, Porto, Portugal, November 1-3, 2025),&amp;quot; see ED677812.]</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>262fa18a25cef7c6</t>
+          <t>82ca847ef02116ef</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Catastrophic Computation. On the Impossibility of Sustainable Artificial Intelligence</t>
+          <t>Digital Twin for Datacenter: HPC4AI UniTO Case Study</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Rehak, R.</t>
+          <t>Vaccaro, V.; Birke, R.; Meschini, S.; Tagliabue, L.; Rabellino, S.; Legazpi, P.; Andinucci, M.</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1816,12 +1818,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lecture notes in computer science</t>
+          <t>Lecture notes in civil engineering</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Springer Science+Business Media</t>
+          <t>Springer Nature</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1831,7 +1833,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10.1007/978-3-032-11108-1_8</t>
+          <t>10.1007/978-3-032-09040-9_9</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1867,7 +1869,7 @@
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>2025/262fa18a25cef7c6.pdf</t>
+          <t>2025/82ca847ef02116ef.pdf</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -1877,24 +1879,24 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>Artificial intelligence (AI) is currently considered a sustainability “game-changer” within and outside of academia. I argue that while there are indeed many sustainability-related use cases for AI, they are likely to have more overall drawbacks than benefits. To substantiate this claim, I differentiate three ‘AI materialities’ of the AI supply chain: first the literal materiality (e.g. water, cobalt, lithium, energy consumption etc.), second, the informational materiality (e.g. lots of data and centralised control necessary), and third, the social materiality (e.g. exploitative data work, communities harm by waste and pollution). In all materialities, effects are especially devastating for the global south while benefiting the global north. A second strong claim regarding sustainable AI circles around so-called apolitical optimisation (e.g. regarding city traffic), however the optimisation criteria (e.g. cars, bikes, emissions, commute time, health) are purely political and have to be collectively negotiated before applying AI optimisation. Hence, sustainable AI, in principle, cannot break the glass ceiling of transformation and might even distract from necessary societal change. To address that I propose to stop ‘unformation gathering’ and to apply the ‘small is beautiful’ principle. This aims to contribute to an informed academic and collective negotiation on how to (not) integrate AI into the sustainability project while avoiding to reproduce the status quo by serving hegemonic interests between useful AI use cases, techno-utopian salvation narratives, technology-centred efficiency paradigms, the exploitative and extractivist character of AI and concepts of digital degrowth. In order to discuss sustainable AI, this article draws from insights by critical data and algorithm studies, STS, transformative sustainability science, critical computer science, and public interest theory.</t>
+          <t>Abstract The HPC4AI (High-Performance Computing for Artificial Intelligence) datacenter at the University of Turin’s Computer Science Department was established to meet the rapidly growing computational demands of interdisciplinary AI research. HPC4AI innovates by redefining the traditional roles of Cloud and High-Performance Computing (HPC) systems, where the Cloud provides a modern interface for HPC, and HPC acts as an accelerator for Cloud applications. To date, it has supported over 40 research projects spanning diverse fields such as astronomy, medicine, and human sciences. Additionally, HPC4AI serves as a research and development platform for exploring, developing, and testing novel datacenter technologies. It features a variety of experimental computing platforms and the first prototype of a two-phase evaporative server cooling system. This work outlines the operational management of HPC4AI, highlighting challenges, lessons learned, and key opportunities related to digital twins for datacenters.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>ca3c5062dc813e4f</t>
+          <t>8421a3fd34fa7ee0</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Comparative Analysis of Generative AI Performance in University Programming Courses</t>
+          <t>Exploring the Role of Artificial Intelligence in Shaping Students&amp;apos; Social Skills</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Suomalainen, E.; Vanhala, E.; Ikonen, J.</t>
+          <t>Mariam Yasinskay; Irma Mesiridze</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1907,22 +1909,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lecture notes in business information processing</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Springer Science+Business Media</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>book-chapter</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-032-14518-5_16</t>
+          <t>International Society for Technology, Education, and Science. 944 Maysey Drive, San Antonio, TX 78227. Tel: 515-294-1075; Fax: 515-294-1003; email: istesoffice@gmail.com; Web site: http://www.istes.org</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1932,7 +1919,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
@@ -1945,47 +1932,39 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>hybrid</t>
-        </is>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
       <c r="P18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>2025/ca3c5062dc813e4f.pdf</t>
+          <t>2025/8421a3fd34fa7ee0.pdf</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>openalex,s2</t>
+          <t>eric</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>Generative artificial intelligence (GenAI) has had an impact on university education and also to the software industry. This can be seen in many different courses where GenAIs can complete exercises, exams, and even whole courses by themselves. This study aims to find out how effectively different GenAI tools can complete exercises in programming courses. Our objective is to find how GenAI’s performance varies across courses and what differences there are in results between multiple GenAI tools. During the study, five programming courses were evaluated using five different GenAI tools. These tools were able to solve 43–90% of programming assignments and 80–100% of quizzes. In practice, the result is that any of the selected GenAIs could have been used to pass the majority of all the tested course parts. Results indicate that we have to rethink how courses’ tasks are designed and that courses need to have an element where learning is verified in a controlled environment to verify that we are educating software professionals for the industry.</t>
+          <t>Technological development and the emergence of artificial intelligence have rapidly reshaped the education sphere by transforming the ways students learn and master new knowledge. The learning process has become more adaptive since learners can effectively leverage artificial intelligence (AI) tools to complete multiple academic tasks without human assistance. However, researchers scrutinize the impact of artificial intelligence on learners' social skills since over-reliance on artificial intelligence assistance can potentially reduce the communication level with students and lecturers, resulting in deteriorated interaction skills. The study investigates the influence of artificial intelligence on students' social and interpersonal development in Georgian higher education institutions. By applying the mixed methodology, the extensive body of literature was analyzed, and the survey was conducted among 133 students from various academic programs and levels in 3 Georgian higher education institutions. The research findings revealed that even though AI-powered tools are valuable for academic processes, students demonstrate awareness of potential risks affecting their social and interpersonal skill development. Therefore, they try to maintain the balance between technological assistance and social interactions in their academic environment. The study concludes that the balanced application of AI in education can enhance students' academic performance without hindering the development of their social skills. [For the complete proceedings, see ED678959.]</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2939cb4059ec9276</t>
+          <t>0902f81e01b244e8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Designing an Integrated Multi-Dimensional Assessment Framework for AI-Supported Academic Writing</t>
+          <t>From Curriculum for All to Inclusive Practice: Insights from a Pilot Study on UDL-Based Pedagogical Transformation</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Sabine Seufert; Niklas Eulitz</t>
+          <t>Sara Cruz; Marisa Maia</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -2022,11 +2001,11 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>2025/2939cb4059ec9276.pdf</t>
+          <t>2025/0902f81e01b244e8.pdf</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -2036,24 +2015,24 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>The widespread adoption of generative AI is transforming academic writing in higher education, rendering traditional, product-focused assessment models obsolete. These methods fail to capture the iterative and tool-mediated nature of modern writing processes, creating an urgent need for new evaluation approaches. This paper addresses this gap by proposing an integrated, multi-dimensional assessment framework. Grounded in genre pedagogy, self-regulated learning, and writing analytics, our model conceptualizes assessment as a holistic process. It evaluates foundational skills for AI use (Computational Thinking and Genre-Knowledge), the quality of text revision, final writing performance, and long-term development. By aligning these dimensions with formative, summative, and diagnostic purposes, the framework fosters transparency, metacognitive engagement, and responsible AI use. We are preparing a design-based research project to pilot and iteratively refine key elements of the framework within a mastery learning programme for 1,800 first-year students. The goal is to explore how the model can be implemented in practice and refined through iterative cycles of design, enactment, and evaluation. [For the complete proceedings, &amp;quot;Proceedings of the International Association for Development of the Information Society (IADIS) International Conference on Cognition and Exploratory Learning in the Digital Age (CELDA) (22nd, Porto, Portugal, November 1-3, 2025),&amp;quot; see ED677812.]</t>
+          <t>In the context of growing demands for inclusive and flexible pedagogical practices in higher education, this study explores how university lecturers can transform their teaching through the lens of Universal Design for Learning (UDL). Grounded in a pedagogical innovation initiative, this pilot study followed four higher education lecturers over the course of one semester as they engaged in a professional development process aimed at redesigning their teaching practices based on the principles of UDL. The objective was to understand the extent to which these lecturers appropriated and applied UDL principles in their pedagogical approaches. Employing a qualitative case study methodology, the research draws on document analysis of final reflective posters produced by each participant, which synthesise the evolution of their teaching practices. The findings reveal that all lecturers successfully integrated UDL principles into different aspects of their instruction, demonstrating increased awareness and practical application of strategies to enhance accessibility, flexibility, and learner engagement. Notably, there was a clear emerging trend towards the adoption of Artificial Intelligence tools as a means to support differentiated instruction and promote inclusive learning environments. This integration of AI technologies appears to complement UDL's emphasis on multiple means of representation, engagement, and expression. The study underscores the potential of structured, reflective, and context-sensitive professional development to foster meaningful pedagogical change in higher education, while also highlighting the evolving role of AI in supporting inclusive and adaptive teaching practices. These findings offer valuable insights for institutional strategies aiming to scale inclusive education through UDL and digital innovation. [For the complete proceedings, &amp;quot;Proceedings of the International Association for Development of the Information Society (IADIS) International Conference on Cognition and Exploratory Learning in the Digital Age (CELDA) (22nd, Porto, Portugal, November 1-3, 2025),&amp;quot; see ED677812.]</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>82ca847ef02116ef</t>
+          <t>b070f5d42bca7df6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Digital Twin for Datacenter: HPC4AI UniTO Case Study</t>
+          <t>Generative AI in Simulation-Based Test Environments for Large-Scale Cyber-Physical Systems: An Industrial Study</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Vaccaro, V.; Birke, R.; Meschini, S.; Tagliabue, L.; Rabellino, S.; Legazpi, P.; Andinucci, M.</t>
+          <t>Sadrnezhaad, M.; López, J.; Mårtensson, T.; Varró, D.</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -2066,12 +2045,12 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lecture notes in civil engineering</t>
+          <t>Lecture notes in computer science</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Springer Nature</t>
+          <t>Springer Science+Business Media</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -2081,7 +2060,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>10.1007/978-3-032-09040-9_9</t>
+          <t>10.1007/978-3-032-12089-2_13</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2106,7 +2085,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>hybrid</t>
+          <t>green</t>
         </is>
       </c>
       <c r="O20" t="n">
@@ -2117,34 +2096,34 @@
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>2025/82ca847ef02116ef.pdf</t>
+          <t>2025/b070f5d42bca7df6.pdf</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>openalex,s2</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>Abstract The HPC4AI (High-Performance Computing for Artificial Intelligence) datacenter at the University of Turin’s Computer Science Department was established to meet the rapidly growing computational demands of interdisciplinary AI research. HPC4AI innovates by redefining the traditional roles of Cloud and High-Performance Computing (HPC) systems, where the Cloud provides a modern interface for HPC, and HPC acts as an accelerator for Cloud applications. To date, it has supported over 40 research projects spanning diverse fields such as astronomy, medicine, and human sciences. Additionally, HPC4AI serves as a research and development platform for exploring, developing, and testing novel datacenter technologies. It features a variety of experimental computing platforms and the first prototype of a two-phase evaporative server cooling system. This work outlines the operational management of HPC4AI, highlighting challenges, lessons learned, and key opportunities related to digital twins for datacenters.</t>
+          <t>Quality assurance for large-scale cyber-physical systems relies on sophisticated test activities using complex test environments investigated with the help of numerous types of simulators. As these systems grow, extensive resources are required to develop and maintain simulation models of hardware and software components, as well as physical environments. Meanwhile, recent advances in generative AI have led to tools that can produce executable test cases for software systems, offering potential benefits such as reducing manual efforts or increasing test coverage. However, the application of generative AI techniques to simulation-based testing of large-scale cyber-physical systems remains underexplored. To better understand this gap, this study captures practitioners'perspectives on leveraging generative AI, based on a cross-company workshop with six organizations. Our contribution is twofold: (1) detailed, experience-based insights into challenges faced by engineers, and (2) a research agenda comprising three high-priority directions: (a) AI-generated scenarios and environment models, (b) simulators and AI in CI/CD pipelines, and (c) trustworthiness in generative AI for simulation. While participants acknowledged substantial potential, they also highlighted unresolved challenges. By detailing these issues, the paper aims to guide future academia-industry collaboration towards the responsible adoption of generative AI in simulation-based testing.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>8421a3fd34fa7ee0</t>
+          <t>0663b0eda3890644</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Exploring the Role of Artificial Intelligence in Shaping Students&amp;apos; Social Skills</t>
+          <t>Improving Generative AI Student Feedback: Direct Preference Optimization with Teachers in the Loop</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Mariam Yasinskay; Irma Mesiridze</t>
+          <t>Juliette Woodrow; Sanmi Koyejo; Chris Piech</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -2157,7 +2136,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>International Society for Technology, Education, and Science. 944 Maysey Drive, San Antonio, TX 78227. Tel: 515-294-1075; Fax: 515-294-1003; email: istesoffice@gmail.com; Web site: http://www.istes.org</t>
+          <t>International Educational Data Mining Society. e-mail: admin@educationaldatamining.org; Web site: https://educationaldatamining.org/conferences/</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2181,11 +2160,11 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>2025/8421a3fd34fa7ee0.pdf</t>
+          <t>2025/0663b0eda3890644.pdf</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -2195,24 +2174,24 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>Technological development and the emergence of artificial intelligence have rapidly reshaped the education sphere by transforming the ways students learn and master new knowledge. The learning process has become more adaptive since learners can effectively leverage artificial intelligence (AI) tools to complete multiple academic tasks without human assistance. However, researchers scrutinize the impact of artificial intelligence on learners' social skills since over-reliance on artificial intelligence assistance can potentially reduce the communication level with students and lecturers, resulting in deteriorated interaction skills. The study investigates the influence of artificial intelligence on students' social and interpersonal development in Georgian higher education institutions. By applying the mixed methodology, the extensive body of literature was analyzed, and the survey was conducted among 133 students from various academic programs and levels in 3 Georgian higher education institutions. The research findings revealed that even though AI-powered tools are valuable for academic processes, students demonstrate awareness of potential risks affecting their social and interpersonal skill development. Therefore, they try to maintain the balance between technological assistance and social interactions in their academic environment. The study concludes that the balanced application of AI in education can enhance students' academic performance without hindering the development of their social skills. [For the complete proceedings, see ED678959.]</t>
+          <t>High-quality feedback requires understanding of a student's work, insights into what concepts would help them improve, and language that matches the preferences of the specific teaching team. While Large Language Models (LLMs) can generate coherent feedback, adapting these responses to align with specific teacher preferences remains an open challenge. We present a method for aligning LLM-generated feedback with teacher preferences using Direct Preference Optimization (DPO). We integrate preference data collection into the grading process. This creates a self-improving pipeline keeping the teacher-in-the-loop to ensure feedback quality and maintain teacher autonomy. To evaluate effectiveness, we conducted a blind controlled study where expert evaluators compared feedback from multiple models on anonymized student submissions. Evaluators consistently preferred feedback from our DPO model over GPT-4o. We deployed the system in two offerings of a large university course, with nearly 300 students and over 10 teaching assistants per term, demonstrating its feasibility in real classroom settings. We share strategies for automated performance monitoring using critic models. We explore methods for examining fairness across protected demographics. [For the complete proceedings, see ED675583.]</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0902f81e01b244e8</t>
+          <t>d9d8ca8edb1d6ec5</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>From Curriculum for All to Inclusive Practice: Insights from a Pilot Study on UDL-Based Pedagogical Transformation</t>
+          <t>Integrating Artificial Intelligence with Gamification Techniques to Enhance Student Motivation and Engagement</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Sara Cruz; Marisa Maia</t>
+          <t>Choustoulakis, E.; Athanasopoulou, P.; Pollalis, Y.; Nikoloudakis, D.</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -2225,7 +2204,22 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
+          <t>Springer proceedings in business and economics</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Springer International Publishing</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>book-chapter</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-031-81962-9_58</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2235,7 +2229,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2248,39 +2242,47 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="O22" t="n">
+        <v>1</v>
+      </c>
       <c r="P22" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>2025/0902f81e01b244e8.pdf</t>
+          <t>2025/d9d8ca8edb1d6ec5.pdf</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
         <is>
-          <t>eric</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>In the context of growing demands for inclusive and flexible pedagogical practices in higher education, this study explores how university lecturers can transform their teaching through the lens of Universal Design for Learning (UDL). Grounded in a pedagogical innovation initiative, this pilot study followed four higher education lecturers over the course of one semester as they engaged in a professional development process aimed at redesigning their teaching practices based on the principles of UDL. The objective was to understand the extent to which these lecturers appropriated and applied UDL principles in their pedagogical approaches. Employing a qualitative case study methodology, the research draws on document analysis of final reflective posters produced by each participant, which synthesise the evolution of their teaching practices. The findings reveal that all lecturers successfully integrated UDL principles into different aspects of their instruction, demonstrating increased awareness and practical application of strategies to enhance accessibility, flexibility, and learner engagement. Notably, there was a clear emerging trend towards the adoption of Artificial Intelligence tools as a means to support differentiated instruction and promote inclusive learning environments. This integration of AI technologies appears to complement UDL's emphasis on multiple means of representation, engagement, and expression. The study underscores the potential of structured, reflective, and context-sensitive professional development to foster meaningful pedagogical change in higher education, while also highlighting the evolving role of AI in supporting inclusive and adaptive teaching practices. These findings offer valuable insights for institutional strategies aiming to scale inclusive education through UDL and digital innovation. [For the complete proceedings, &amp;quot;Proceedings of the International Association for Development of the Information Society (IADIS) International Conference on Cognition and Exploratory Learning in the Digital Age (CELDA) (22nd, Porto, Portugal, November 1-3, 2025),&amp;quot; see ED677812.]</t>
+          <t>Abstract This study investigated the integration of Artificial Intelligence (AI) with gamification techniques to enhance student motivation, engagement, and academic performance in management education. A non-probability sample of 200 undergraduate students from Greece was randomly assigned to one of two groups: an experimental group that experienced AI-driven gamification, or a control group that followed traditional instructional methods. Quantitative analysis revealed that students in the experimental group demonstrated a statistically significant increase in active participation and a statistically significant improvement in course completion rates compared to the control group. This was complemented by significant enhancements in academic performance, with final grades showing a notable difference. The AI-driven gamified environment, which included personalized challenges and real-time feedback, effectively boosted engagement and academic outcomes. Qualitative feedback from students indicated that the AI system’s ability to adapt to individual learning needs was particularly valued. Students appreciated the personalized support, which helped them stay on track and better understand complex concepts. The study highlights the potential of combining AI with gamification to create a more interactive and tailored educational experience, addressing diverse learning needs and preferences. These findings highlight the transformative impact of AI-driven gamification on management education and emphasize the critical role of courses in integrating these innovative methods. They also suggest avenues for future research to further optimize these approaches, enhancing both educational practices and student outcomes in management training.</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>b070f5d42bca7df6</t>
+          <t>d27fcdfbec56edee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Generative AI in Simulation-Based Test Environments for Large-Scale Cyber-Physical Systems: An Industrial Study</t>
+          <t>Integration of ChatGPT in the Problem-Based Learning Model</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Sadrnezhaad, M.; López, J.; Mårtensson, T.; Varró, D.</t>
+          <t>Daniela Orozova; Nadezhda Angelova</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -2293,22 +2295,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lecture notes in computer science</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Springer Science+Business Media</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>book-chapter</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-032-12089-2_13</t>
+          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
@@ -2318,7 +2305,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2331,47 +2318,39 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="O23" t="n">
-        <v>0</v>
-      </c>
       <c r="P23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>2025/b070f5d42bca7df6.pdf</t>
+          <t>2025/d27fcdfbec56edee.pdf</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
         <is>
-          <t>openalex,s2</t>
+          <t>eric</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>Quality assurance for large-scale cyber-physical systems relies on sophisticated test activities using complex test environments investigated with the help of numerous types of simulators. As these systems grow, extensive resources are required to develop and maintain simulation models of hardware and software components, as well as physical environments. Meanwhile, recent advances in generative AI have led to tools that can produce executable test cases for software systems, offering potential benefits such as reducing manual efforts or increasing test coverage. However, the application of generative AI techniques to simulation-based testing of large-scale cyber-physical systems remains underexplored. To better understand this gap, this study captures practitioners'perspectives on leveraging generative AI, based on a cross-company workshop with six organizations. Our contribution is twofold: (1) detailed, experience-based insights into challenges faced by engineers, and (2) a research agenda comprising three high-priority directions: (a) AI-generated scenarios and environment models, (b) simulators and AI in CI/CD pipelines, and (c) trustworthiness in generative AI for simulation. While participants acknowledged substantial potential, they also highlighted unresolved challenges. By detailing these issues, the paper aims to guide future academia-industry collaboration towards the responsible adoption of generative AI in simulation-based testing.</t>
+          <t>The development of modern technologies and the integration of AI into all aspects of life pose challenges for participants in the educational process. On the one hand, using chatbots and generative AI tools provides learners with unlimited opportunities to quickly and easily access a large amount of information and receive help with various homework assignments, making it difficult for teachers to assess their work. The article presents an experiment designed to motivate students and support teachers during training. The research was conducted during the education of bachelor students in the professional field of Informatics and Computer Sciences. The propositions presented in this report raise several questions and outline possible future research directions. An experiment is conducted with students in the second and third semesters of the Software Engineering bachelor's program. The goal is to integrate ChatGPT in the context of problem-based learning while mastering the fundamentals of programming languages such as C++, Java, and web programming. The idea is to train learners' critical thinking skills with systematically generated materials from ChatGPT, in dialogue with students, enriching them with additional knowledge and various resources. This study examines the potential of artificial intelligence technology, such as ChatGPT, to enhance core teaching materials through problem-based learning. Learners are encouraged to develop critical thinking on assigned tasks, and their progress is monitored by analyzing data collected during the learning process. This paper aims to demonstrate that generative AI technologies, such as ChatGPT, have the potential to enrich learning resources, adapt materials to individual learners' needs, and provide flexibility for both students and educators in the digital age. The main challenges associated with traditional teaching include the lecturer's limited time to present the learning material, a shortage of reference resources, and low student motivation. Integrating ChatGPT into a problem-solving learning model is hypothesized to personalize learning content, improve critical thinking, provide feedback, and increase learner motivation. [For the complete proceedings, &amp;quot;Proceedings of the International Association for Development of the Information Society (IADIS) International Conference on Cognition and Exploratory Learning in the Digital Age (CELDA) (22nd, Porto, Portugal, November 1-3, 2025),&amp;quot; see ED677812.]</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0663b0eda3890644</t>
+          <t>6adfc8932d140131</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Improving Generative AI Student Feedback: Direct Preference Optimization with Teachers in the Loop</t>
+          <t>Micro-degree Artificial Intelligence and Society</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Juliette Woodrow; Sanmi Koyejo; Chris Piech</t>
+          <t>Lasser, J.; Pfiffner, M.</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -2384,7 +2363,22 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>International Educational Data Mining Society. e-mail: admin@educationaldatamining.org; Web site: https://educationaldatamining.org/conferences/</t>
+          <t>Lecture notes in computer science</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Springer Science+Business Media</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>book-chapter</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-032-11108-1_21</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2394,7 +2388,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2407,39 +2401,47 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
       <c r="P24" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2025/0663b0eda3890644.pdf</t>
+          <t>2025/6adfc8932d140131.pdf</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
         <is>
-          <t>eric</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>High-quality feedback requires understanding of a student's work, insights into what concepts would help them improve, and language that matches the preferences of the specific teaching team. While Large Language Models (LLMs) can generate coherent feedback, adapting these responses to align with specific teacher preferences remains an open challenge. We present a method for aligning LLM-generated feedback with teacher preferences using Direct Preference Optimization (DPO). We integrate preference data collection into the grading process. This creates a self-improving pipeline keeping the teacher-in-the-loop to ensure feedback quality and maintain teacher autonomy. To evaluate effectiveness, we conducted a blind controlled study where expert evaluators compared feedback from multiple models on anonymized student submissions. Evaluators consistently preferred feedback from our DPO model over GPT-4o. We deployed the system in two offerings of a large university course, with nearly 300 students and over 10 teaching assistants per term, demonstrating its feasibility in real classroom settings. We share strategies for automated performance monitoring using critic models. We explore methods for examining fairness across protected demographics. [For the complete proceedings, see ED675583.]</t>
+          <t>We introduce the micro-degree “Artificial Intelligence and Society” developed by the University of Graz, a novel interdisciplinary program designed to bridge the gap between technical AI knowledge and its broader societal implications. Recognising the rapid permeation of AI into all aspects of life and the limitations of traditional educational systems in addressing this transformation, the target audience of the micro-degree is both students enrolled in traditional university degrees as well as the existing workforce. The 16 ECTS curriculum, spanning two semesters, covers the technical foundations of AI systems alongside their ethical, legal, economic, and educational impacts. It features a modular structure with basic knowledge lectures, hands-on application courses – including a mandatory technical AI course and electives in ethics, law, economics, and education –, and practicals where students implement AI-based solutions to real-world problems. Here, we describe the structure and content of the micro-degree, including the learning objectives of the individual degree modules. We also provide Open Educational Resources used for teaching the (mandatory) lecture and hands-on course on the technical foundations of artificial intelligence. This micro-degree represents a crucial step towards fostering digital humanism by enabling individuals to confidently understand, apply, and shape AI’s role in society.</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>d9d8ca8edb1d6ec5</t>
+          <t>9bebd7a1588a62f1</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Integrating Artificial Intelligence with Gamification Techniques to Enhance Student Motivation and Engagement</t>
+          <t>Proceedings of the International Conference on Educational Data Mining (EDM) (18th, Palermo, Italy, July 20-23, 2025)</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Choustoulakis, E.; Athanasopoulou, P.; Pollalis, Y.; Nikoloudakis, D.</t>
+          <t>Caitlin Mills, E.; Giora Alexandron, E.; Davide Taibi, E.; Giosuè Lo Bosco, E.; Luc Paquette, E.</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -2452,22 +2454,7 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Springer proceedings in business and economics</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Springer International Publishing</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>book-chapter</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-031-81962-9_58</t>
+          <t>International Educational Data Mining Society. e-mail: admin@educationaldatamining.org; Web site: https://educationaldatamining.org/conferences/</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
@@ -2477,7 +2464,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
@@ -2489,48 +2476,40 @@
         <is>
           <t>Yes</t>
         </is>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>hybrid</t>
-        </is>
-      </c>
-      <c r="O25" t="n">
-        <v>1</v>
       </c>
       <c r="P25" t="n">
         <v>2</v>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>2025/d9d8ca8edb1d6ec5.pdf</t>
+          <t>2025/9bebd7a1588a62f1.pdf</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>eric</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>Abstract This study investigated the integration of Artificial Intelligence (AI) with gamification techniques to enhance student motivation, engagement, and academic performance in management education. A non-probability sample of 200 undergraduate students from Greece was randomly assigned to one of two groups: an experimental group that experienced AI-driven gamification, or a control group that followed traditional instructional methods. Quantitative analysis revealed that students in the experimental group demonstrated a statistically significant increase in active participation and a statistically significant improvement in course completion rates compared to the control group. This was complemented by significant enhancements in academic performance, with final grades showing a notable difference. The AI-driven gamified environment, which included personalized challenges and real-time feedback, effectively boosted engagement and academic outcomes. Qualitative feedback from students indicated that the AI system’s ability to adapt to individual learning needs was particularly valued. Students appreciated the personalized support, which helped them stay on track and better understand complex concepts. The study highlights the potential of combining AI with gamification to create a more interactive and tailored educational experience, addressing diverse learning needs and preferences. These findings highlight the transformative impact of AI-driven gamification on management education and emphasize the critical role of courses in integrating these innovative methods. They also suggest avenues for future research to further optimize these approaches, enhancing both educational practices and student outcomes in management training.</t>
+          <t>The University of Palermo is proud to host the 18th International Conference on Educational Data Mining (EDM) in Palermo, Italy, from July 20 to July 23, 2025. EDM is the annual flagship conference of the International Educational Data Mining Society. This year's theme is &amp;quot;New Goals, New Measurements, New Incentives to Learn.&amp;quot; The theme highlights the shift toward an era dominated by artificial intelligence--where machines can surpass human performance in numerous cognitive tasks--and highlights the imperative for educational systems to evolve accordingly. The scientific program for EDM2025 includes: (1) two keynote talks by outstanding researchers in the field; (2) a plenary Prof. Ram Kumar Educational Data Mining Test of Time Award talk; (3) an invited Data Set Award talk; (4) five workshops and three tutorials; (5) eight presentation sessions with parallel (2 and 3) tracks; (6) a poster presentation session; (7) an industry track session; (8) a doctoral consortium session; and (9) a cross-conference panel. [Individual papers are indexed in ERIC.]</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>d27fcdfbec56edee</t>
+          <t>36a4fda0d7a39cf4</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Integration of ChatGPT in the Problem-Based Learning Model</t>
+          <t>Reconsidering Requirements Engineering: Human–AI Collaboration in AI-Native Software Development</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Daniela Orozova; Nadezhda Angelova</t>
+          <t>Abbasi, M.; Ihantola, P.; Mikkonen, T.; Mäkitalo, N.</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -2543,7 +2522,22 @@
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
+          <t>Lecture notes in computer science</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Springer Science+Business Media</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>book-chapter</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-032-04190-6_11</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2553,7 +2547,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
@@ -2566,39 +2560,47 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>green</t>
+        </is>
+      </c>
+      <c r="O26" t="n">
+        <v>1</v>
+      </c>
       <c r="P26" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>2025/d27fcdfbec56edee.pdf</t>
+          <t>2025/36a4fda0d7a39cf4.pdf</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
         <is>
-          <t>eric</t>
+          <t>openalex,s2</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>The development of modern technologies and the integration of AI into all aspects of life pose challenges for participants in the educational process. On the one hand, using chatbots and generative AI tools provides learners with unlimited opportunities to quickly and easily access a large amount of information and receive help with various homework assignments, making it difficult for teachers to assess their work. The article presents an experiment designed to motivate students and support teachers during training. The research was conducted during the education of bachelor students in the professional field of Informatics and Computer Sciences. The propositions presented in this report raise several questions and outline possible future research directions. An experiment is conducted with students in the second and third semesters of the Software Engineering bachelor's program. The goal is to integrate ChatGPT in the context of problem-based learning while mastering the fundamentals of programming languages such as C++, Java, and web programming. The idea is to train learners' critical thinking skills with systematically generated materials from ChatGPT, in dialogue with students, enriching them with additional knowledge and various resources. This study examines the potential of artificial intelligence technology, such as ChatGPT, to enhance core teaching materials through problem-based learning. Learners are encouraged to develop critical thinking on assigned tasks, and their progress is monitored by analyzing data collected during the learning process. This paper aims to demonstrate that generative AI technologies, such as ChatGPT, have the potential to enrich learning resources, adapt materials to individual learners' needs, and provide flexibility for both students and educators in the digital age. The main challenges associated with traditional teaching include the lecturer's limited time to present the learning material, a shortage of reference resources, and low student motivation. Integrating ChatGPT into a problem-solving learning model is hypothesized to personalize learning content, improve critical thinking, provide feedback, and increase learner motivation. [For the complete proceedings, &amp;quot;Proceedings of the International Association for Development of the Information Society (IADIS) International Conference on Cognition and Exploratory Learning in the Digital Age (CELDA) (22nd, Porto, Portugal, November 1-3, 2025),&amp;quot; see ED677812.]</t>
+          <t>Requirement Engineering (RE) is the foundation of successful software development. In RE, the goal is to ensure that implemented systems satisfy stakeholder needs through rigorous requirements elicitation, validation, and evaluation processes. Despite its critical role, RE continues to face persistent challenges, such as ambiguity, conflicting stakeholder needs, and the complexity of managing evolving requirements. A common view is that Artificial Intelligence (AI) has the potential to streamline the RE process, resulting in improved efficiency, accuracy, and management actions. However, using AI also introduces new concerns, such as ethical issues, biases, and lack of transparency. This paper explores how AI can enhance traditional RE practices by automating labor-intensive tasks, supporting requirement prioritization, and facilitating collaboration between stakeholders and AI systems. The paper also describes the opportunities and challenges that AI brings to RE. In particular, the vision calls for ethical practices in AI, along with a much-enhanced collaboration between academia and industry professionals. The focus should be on creating not only powerful but also trustworthy and practical AI solutions ready to adapt to the fast-paced world of software development.</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>6adfc8932d140131</t>
+          <t>aca4033a09f8146c</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Micro-degree Artificial Intelligence and Society</t>
+          <t>Reducing Speaking Anxiety among College ESL Students through Artificial Intelligence</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Lasser, J.; Pfiffner, M.</t>
+          <t>Promethi Das Deep; Nitu Ghosh; Andrey V. Koptelov</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -2611,22 +2613,7 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lecture notes in computer science</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Springer Science+Business Media</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>book-chapter</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-032-11108-1_21</t>
+          <t>International Society for Technology, Education, and Science. 944 Maysey Drive, San Antonio, TX 78227. Tel: 515-294-1075; Fax: 515-294-1003; email: istesoffice@gmail.com; Web site: http://www.istes.org</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2636,7 +2623,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2649,47 +2636,39 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>hybrid</t>
-        </is>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
       <c r="P27" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>2025/6adfc8932d140131.pdf</t>
+          <t>2025/aca4033a09f8146c.pdf</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>eric</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>We introduce the micro-degree “Artificial Intelligence and Society” developed by the University of Graz, a novel interdisciplinary program designed to bridge the gap between technical AI knowledge and its broader societal implications. Recognising the rapid permeation of AI into all aspects of life and the limitations of traditional educational systems in addressing this transformation, the target audience of the micro-degree is both students enrolled in traditional university degrees as well as the existing workforce. The 16 ECTS curriculum, spanning two semesters, covers the technical foundations of AI systems alongside their ethical, legal, economic, and educational impacts. It features a modular structure with basic knowledge lectures, hands-on application courses – including a mandatory technical AI course and electives in ethics, law, economics, and education –, and practicals where students implement AI-based solutions to real-world problems. Here, we describe the structure and content of the micro-degree, including the learning objectives of the individual degree modules. We also provide Open Educational Resources used for teaching the (mandatory) lecture and hands-on course on the technical foundations of artificial intelligence. This micro-degree represents a crucial step towards fostering digital humanism by enabling individuals to confidently understand, apply, and shape AI’s role in society.</t>
+          <t>Speaking anxiety continues to challenge many college ESL students, affecting confidence, fluency, and classroom participation. With the growing integration of artificial intelligence (AI) and large language models (LLMs) in higher education, new opportunities have emerged to enhance oral language learning through adaptive and low-pressure environments. This review followed the SANRA guidelines to ensure clarity, rigor, and balance. Relevant peer-reviewed studies were identified from ERIC, EBSCOhost, JSTOR, IEEE Xplore, and Scopus using the keywords artificial intelligence, large language models, ESL, EFL, speaking anxiety, and communication confidence. Research focusing on higher education contexts was analyzed for methodological quality and pedagogical insights. Findings show that AI-based tools such as chatbots, speech recognition systems, and feedback applications improve learners' fluency, pronunciation, and vocabulary while enhancing grammatical accuracy and discourse coherence. These technologies also reduce anxiety, boost motivation, and promote autonomous learning by providing immediate, personalized feedback in supportive settings. However, limitations in emotional responsiveness, contextual adaptability, and the need for teacher mediation highlight the importance of balanced integration. Overall, AI serves as a valuable complement to traditional instruction, fostering both linguistic competence and emotional well-being among college ESL learners. [For the complete proceedings, see ED678731.]</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>9bebd7a1588a62f1</t>
+          <t>e8ba15cc7545622a</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Proceedings of the International Conference on Educational Data Mining (EDM) (18th, Palermo, Italy, July 20-23, 2025)</t>
+          <t>Shape Computation Research at the University of Sydney</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Caitlin Mills, E.; Giora Alexandron, E.; Davide Taibi, E.; Giosuè Lo Bosco, E.; Luc Paquette, E.</t>
+          <t>Gero, J.</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -2702,7 +2681,22 @@
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>International Educational Data Mining Society. e-mail: admin@educationaldatamining.org; Web site: https://educationaldatamining.org/conferences/</t>
+          <t>Mathematics and the built environment</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Springer International Publishing</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>book-chapter</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-031-81623-9_15</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
@@ -2712,7 +2706,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2724,40 +2718,48 @@
         <is>
           <t>Yes</t>
         </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
       </c>
       <c r="P28" t="n">
         <v>2</v>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>2025/9bebd7a1588a62f1.pdf</t>
+          <t>2025/e8ba15cc7545622a.pdf</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
         <is>
-          <t>eric</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>The University of Palermo is proud to host the 18th International Conference on Educational Data Mining (EDM) in Palermo, Italy, from July 20 to July 23, 2025. EDM is the annual flagship conference of the International Educational Data Mining Society. This year's theme is &amp;quot;New Goals, New Measurements, New Incentives to Learn.&amp;quot; The theme highlights the shift toward an era dominated by artificial intelligence--where machines can surpass human performance in numerous cognitive tasks--and highlights the imperative for educational systems to evolve accordingly. The scientific program for EDM2025 includes: (1) two keynote talks by outstanding researchers in the field; (2) a plenary Prof. Ram Kumar Educational Data Mining Test of Time Award talk; (3) an invited Data Set Award talk; (4) five workshops and three tutorials; (5) eight presentation sessions with parallel (2 and 3) tracks; (6) a poster presentation session; (7) an industry track session; (8) a doctoral consortium session; and (9) a cross-conference panel. [Individual papers are indexed in ERIC.]</t>
+          <t>This chapter provides a brief overview of the shape computation research at the University of Sydney that was carried out over a 35-year period, between 1977 and 2012, referencing 17 Ph.D theses that discuss shape computation during that period. The chapter draws distinctions between shape computation using shape grammars and other approaches that parallel, supplement and diverge from shape grammars. It introduces a variety of methods for shape computation, including those based on infinite maximal lines, artificial intelligence, learning representations, learning generation rules, logic models, qualitative representation, qualitative reasoning, algebraic representation, shape semantics, situated learning, and shape interpretation.</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>03aa44aa607b0e73</t>
+          <t>0256be53813d4df5</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Proposal of a framework to enhance the adoption of artificial intelligence in higher education considering sustainable development: a hybrid Lawshe-TOPSIS approach</t>
+          <t>Studies on Social and Education Sciences 2025</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Fernandes, R.; Nagata, V.; Filho, W.; Rampasso, I.; Ávila, L.; Silva, J.; Anholon, R.; Martins, V.</t>
+          <t>Mustafa Koc, E.; Omer Tayfur Ozturk, E.</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -2770,22 +2772,7 @@
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>International Journal of Educational Management</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Emerald Publishing Limited</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>article</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>10.1108/ijem-08-2024-0441</t>
+          <t>International Society for Technology, Education, and Science. 944 Maysey Drive, San Antonio, TX 78227. Tel: 515-294-1075; Fax: 515-294-1003; email: istesoffice@gmail.com; Web site: http://www.istes.org</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2795,7 +2782,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
@@ -2808,42 +2795,39 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="O29" t="n">
-        <v>1</v>
-      </c>
       <c r="P29" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>2025/03aa44aa607b0e73.pdf</t>
+          <t>2025/0256be53813d4df5.pdf</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
         <is>
-          <t>s2</t>
+          <t>eric</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>Purpose The main objective of this study was to propose a framework to enhance the adoption of artificial intelligence (AI) in higher education, considering sustainable development in the context of an emerging economy country. Design/methodology/approach The method adopted was a literature review and a survey conducted with higher education faculty members from Brazilian universities. Through an electronic questionnaire, 71 responses were collected. The data were analyzed using a hybrid Lawshe-TOPSIS approach. Findings As a result, the validated framework highlights six challenges related to the adoption of AI in higher education and nine ordered benefits of AI adoption, with the most significant for the analyzed context being the ability to process large amounts of data; sustainable solutions for industry, commerce and the economy; adaptive teaching strategies and greater scientific assistance for students and faculty. Research limitations/implications The article contributes to the literature by filling a research gap and provides insights for higher education institution managers regarding AI adoption in this mode of education. Originality/value The research underscores the importance of aligning technological initiatives with sustainable development goals, providing a structured guide.</t>
+          <t>Studies in the fields of education and social sciences have always been important in terms of their impacts on society. The studies in this book contribute to the fields of education and social sciences by different research methods, participants, and contexts and add a global perspective to these fields. The book involves seven chapters: (1) Attitudes and Practices of College Art Teachers towards Culturally Responsive Teaching in Art Creation Courses; (2) International Research on College Students' Perceptions regarding the Impact of the Lasallian Mission on Their Development; (3) The Unseen Revolution: Unlocking the Potential of Cross-Disciplinary Research; (4) The First Women Painters in Turkish Painting and Their Development; (5) Enhancing Research Methodology: The Role of Embedded Librarians in Supporting Academic Excellence; (6) The Role of Interdisciplinary Approaches in Addressing Global Challenges; and (7) The Uses of Artificial Intelligence to Improve Scientific Research to Confront the Problem of Extremism (A Field Study on Egypt).</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>36a4fda0d7a39cf4</t>
+          <t>5aa6b29d365d2193</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Reconsidering Requirements Engineering: Human–AI Collaboration in AI-Native Software Development</t>
+          <t>Teaching Electricity and Magnetism in Higher Education through Virtual Reality and Artificial Intelligence</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Abbasi, M.; Ihantola, P.; Mikkonen, T.; Mäkitalo, N.</t>
+          <t>Zhanara Malikova; Bayan Ualikhanova</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -2856,22 +2840,7 @@
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lecture notes in computer science</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Springer Science+Business Media</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>book-chapter</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-032-04190-6_11</t>
+          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2881,7 +2850,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2893,48 +2862,40 @@
         <is>
           <t>Yes</t>
         </is>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="O30" t="n">
-        <v>1</v>
       </c>
       <c r="P30" t="n">
         <v>2</v>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>2025/36a4fda0d7a39cf4.pdf</t>
+          <t>2025/5aa6b29d365d2193.pdf</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
         <is>
-          <t>openalex,s2</t>
+          <t>eric</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>Requirement Engineering (RE) is the foundation of successful software development. In RE, the goal is to ensure that implemented systems satisfy stakeholder needs through rigorous requirements elicitation, validation, and evaluation processes. Despite its critical role, RE continues to face persistent challenges, such as ambiguity, conflicting stakeholder needs, and the complexity of managing evolving requirements. A common view is that Artificial Intelligence (AI) has the potential to streamline the RE process, resulting in improved efficiency, accuracy, and management actions. However, using AI also introduces new concerns, such as ethical issues, biases, and lack of transparency. This paper explores how AI can enhance traditional RE practices by automating labor-intensive tasks, supporting requirement prioritization, and facilitating collaboration between stakeholders and AI systems. The paper also describes the opportunities and challenges that AI brings to RE. In particular, the vision calls for ethical practices in AI, along with a much-enhanced collaboration between academia and industry professionals. The focus should be on creating not only powerful but also trustworthy and practical AI solutions ready to adapt to the fast-paced world of software development.</t>
+          <t>In recent years, virtual reality (VR) and artificial intelligence (AI) technologies have been widely adopted across various sectors of society, including education. We conducted a practical study to assess the effectiveness of immersive technologies in higher education institutions. The research was carried out over a period of ten weeks. Students were divided into control and experimental groups. Furthermore, the research work was based on the collection of quantitative data and monitoring students' academic performance. The study's results were analyzed using a paired t-test and descriptive statistics. The independent t-test results indicated significant differences in subsequent test scores between the experimental and control groups. Quantitative descriptive results were presented in the form of diagrams and evaluated across six pedagogical components. At the conclusion of the study, recommendations for future research were provided. [For the complete proceedings, &amp;quot;Proceedings of the International Association for Development of the Information Society (IADIS) International Conference on Cognition and Exploratory Learning in the Digital Age (CELDA) (22nd, Porto, Portugal, November 1-3, 2025),&amp;quot; see ED677812.]</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>aca4033a09f8146c</t>
+          <t>fd9e23c6c69b4a0f</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Reducing Speaking Anxiety among College ESL Students through Artificial Intelligence</t>
+          <t>The Future of Cybersecurity at Sea: Human vs Human or AI vs AI?</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Promethi Das Deep; Nitu Ghosh; Andrey V. Koptelov</t>
+          <t>Alop, A.</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -2947,7 +2908,22 @@
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>International Society for Technology, Education, and Science. 944 Maysey Drive, San Antonio, TX 78227. Tel: 515-294-1075; Fax: 515-294-1003; email: istesoffice@gmail.com; Web site: http://www.istes.org</t>
+          <t>Signals and communication technology</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Springer Vienna</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>book-chapter</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-031-87290-7_1</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2957,7 +2933,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2970,39 +2946,47 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="O31" t="n">
+        <v>0</v>
+      </c>
       <c r="P31" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>2025/aca4033a09f8146c.pdf</t>
+          <t>2025/fd9e23c6c69b4a0f.pdf</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
         <is>
-          <t>eric</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>Speaking anxiety continues to challenge many college ESL students, affecting confidence, fluency, and classroom participation. With the growing integration of artificial intelligence (AI) and large language models (LLMs) in higher education, new opportunities have emerged to enhance oral language learning through adaptive and low-pressure environments. This review followed the SANRA guidelines to ensure clarity, rigor, and balance. Relevant peer-reviewed studies were identified from ERIC, EBSCOhost, JSTOR, IEEE Xplore, and Scopus using the keywords artificial intelligence, large language models, ESL, EFL, speaking anxiety, and communication confidence. Research focusing on higher education contexts was analyzed for methodological quality and pedagogical insights. Findings show that AI-based tools such as chatbots, speech recognition systems, and feedback applications improve learners' fluency, pronunciation, and vocabulary while enhancing grammatical accuracy and discourse coherence. These technologies also reduce anxiety, boost motivation, and promote autonomous learning by providing immediate, personalized feedback in supportive settings. However, limitations in emotional responsiveness, contextual adaptability, and the need for teacher mediation highlight the importance of balanced integration. Overall, AI serves as a valuable complement to traditional instruction, fostering both linguistic competence and emotional well-being among college ESL learners. [For the complete proceedings, see ED678731.]</t>
+          <t>The digitalization of all areas of activity, including maritime, today is characterized, among other things, by two powerful influencing factors: on the one hand, artificial intelligence (AI) increasingly taking over the most important functions and develops very quickly, and on the other hand, threats and risks related to cybersecurity. The common belief, which is hard to argue against, is that the first factor is positive, because it contributes to developments, and the second is undoubtedly negative, because it hinders developments and can even inhibit them; from here, it is easy to conclude that in order to continue and accelerate progress, the positive aspects of the first factor must be contributed in every way and the fight against the effects of the second factor must be undertaken. But how realistic and consistently achievable are these two goals in interaction? True, in the light of the developments of the last years and even months, it seems that the AI “train” has started its impressive journey at high speed, and nothing can stop it. At the same time, continuing the allegory, there is still a “wagon” of cyber threats attached to this “train,” and getting rid of it or even defeating it to a sufficient extent seems problematic, at least now. The author of this chapter expresses an estimated opinion that as long as people fight against each other on both sides of the “cyber war” (“bad” guys against “good” ones), it is so to say war of attrition, where no glorious victory awaits either side. It seems to the author that it is possible to change the situation and achieve victory over the “bad” guys only if the AI itself takes over its own protection. Whether and to what extent this is possible is one of the main topics of this chapter. In the author’s opinion, there can be any truth behind this only if the AI acquires a large part of the characteristics unique to humans (values, moral principles, emotions, etc.), thanks to which it would be possible to be guided by the specific laws or rules of behavior of the AI. As a classic example, the so-called three laws of robotics, formulated by the American science fiction writer Isaac Asimov about 80 years ago, are based on the principle of avoiding harm to humans (Anderson, Asimov’s “Three Laws of Robotics” and machine metaethics, University of Connecticut, Dept. of Philosophy, Stamford, CT, https://cdn.aaai.org/Symposia/Fall/2005/FS-05-06/FS05-06-002.pdf ). In this chapter, we have analyzed whether such AI developments are possible at all and what threats and difficulties this entails in turn.</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>e8ba15cc7545622a</t>
+          <t>dd8a0e8d30483815</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Shape Computation Research at the University of Sydney</t>
+          <t>The Impact of AI Tools on Universities’ Educational Strategies and Student Success: Sultan Qaboos University and Qatar University as a Case Study</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Gero, J.</t>
+          <t>Al-Awadhi, T.; Al-Balushi, A.; Abdullah, M.; Abulibdeh, A.</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -3015,12 +2999,12 @@
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mathematics and the built environment</t>
+          <t>Gulf Studies</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Springer International Publishing</t>
+          <t>Springer Nature</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -3030,7 +3014,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-81623-9_15</t>
+          <t>10.1007/978-981-97-9667-0_9</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -3059,14 +3043,14 @@
         </is>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P32" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2025/e8ba15cc7545622a.pdf</t>
+          <t>2025/dd8a0e8d30483815.pdf</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -3076,24 +3060,24 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>This chapter provides a brief overview of the shape computation research at the University of Sydney that was carried out over a 35-year period, between 1977 and 2012, referencing 17 Ph.D theses that discuss shape computation during that period. The chapter draws distinctions between shape computation using shape grammars and other approaches that parallel, supplement and diverge from shape grammars. It introduces a variety of methods for shape computation, including those based on infinite maximal lines, artificial intelligence, learning representations, learning generation rules, logic models, qualitative representation, qualitative reasoning, algebraic representation, shape semantics, situated learning, and shape interpretation.</t>
+          <t>Abstract Sultan Qaboos University (SQU) and Qatar University (QU) are working to adopt short- and long-term plans to ensure leadership in teaching and learning, scientific research, and community service at regional and international levels. Modern technologies, especially artificial intelligence (AI), play an important role in our lives, providing realistic opportunities to accelerate business implementation and improve the final value of work. AI plays a crucial role in taking education and research to the next level, transforming the way these organisations work and make decisions. AI can improve the traditional work of educational institutions and transform the understanding of their complexity. However, challenges remain in various aspects, whether related to the nature of our work or to the AI technologies themselves. This is still a great opportunity for every HEI. Therefore, this paper aims to analyse the potential of AI to accelerate the implementation of the strategic plans of the two universities.</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0256be53813d4df5</t>
+          <t>ccacb2251f5b4e56</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Studies on Social and Education Sciences 2025</t>
+          <t>Thinking Along the Lines Generated by GenAI? A Systematic Mapping Study on Academic Writing</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Mustafa Koc, E.; Omer Tayfur Ozturk, E.</t>
+          <t>Kaczkó, É.; Ivanjek, L.; Norz, L.; Ammenwerth, E.</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -3106,7 +3090,22 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>International Society for Technology, Education, and Science. 944 Maysey Drive, San Antonio, TX 78227. Tel: 515-294-1075; Fax: 515-294-1003; email: istesoffice@gmail.com; Web site: http://www.istes.org</t>
+          <t>Lecture notes in computer science</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Springer Science+Business Media</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>book-chapter</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-032-11108-1_35</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3116,7 +3115,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
@@ -3129,39 +3128,47 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
       <c r="P33" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>2025/0256be53813d4df5.pdf</t>
+          <t>2025/ccacb2251f5b4e56.pdf</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
         <is>
-          <t>eric</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>Studies in the fields of education and social sciences have always been important in terms of their impacts on society. The studies in this book contribute to the fields of education and social sciences by different research methods, participants, and contexts and add a global perspective to these fields. The book involves seven chapters: (1) Attitudes and Practices of College Art Teachers towards Culturally Responsive Teaching in Art Creation Courses; (2) International Research on College Students' Perceptions regarding the Impact of the Lasallian Mission on Their Development; (3) The Unseen Revolution: Unlocking the Potential of Cross-Disciplinary Research; (4) The First Women Painters in Turkish Painting and Their Development; (5) Enhancing Research Methodology: The Role of Embedded Librarians in Supporting Academic Excellence; (6) The Role of Interdisciplinary Approaches in Addressing Global Challenges; and (7) The Uses of Artificial Intelligence to Improve Scientific Research to Confront the Problem of Extremism (A Field Study on Egypt).</t>
+          <t>The advent of generative AI (GenAI) tools in higher education challenges fundamental assumptions about academic authorship, students’ cognitive development and how writing cultivates critical thinking (CT). This systematic mapping study synthesized emerging research on how GenAI is reshaping the relationship between academic writing and CT in higher education. Drawing on 25 peer-reviewed studies published between 2023 and 2025, we analyzed conceptualizations of CT and academic writing, identified pedagogical approaches, and examined the use of GenAI tools across a range of disciplines, educational levels, and geographic contexts. Findings revealed that interest in the use of GenAI in academic writing is global and spans all disciplines and higher educational levels. However, only a minority of studies drew on robust theoretical frameworks. CT was conceptualized predominantly within a cognitive skills paradigm, while broader understandings linked to criticality and critical pedagogy were largely absent. Pedagogical models were rare and mostly untested, and educators’ perspectives were underrepresented. While GenAI was seen as supporting writing processes, its potential to foster or hinder CT remained contested. Future research should broaden conceptual foundations, include educator perspectives, and prioritize pedagogical design and evaluation. Rethinking academic writing as a transformative practice may require moving beyond the cognitive paradigm towards more participatory and ethically grounded approaches to CT.</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>5aa6b29d365d2193</t>
+          <t>8a4a82dd2792d328</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Teaching Electricity and Magnetism in Higher Education through Virtual Reality and Artificial Intelligence</t>
+          <t>University Students&amp;apos; Perceptions of the Use of Productive Artificial Intelligence: The Effects of ChatGPT on Assignment Processes</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Zhanara Malikova; Bayan Ualikhanova</t>
+          <t>Halil Güvel; Muhammet Demirbilek; Seyfullah Gökoglu</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -3174,7 +3181,7 @@
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
+          <t>International Society for Technology, Education, and Science. 944 Maysey Drive, San Antonio, TX 78227. Tel: 515-294-1075; Fax: 515-294-1003; email: istesoffice@gmail.com; Web site: http://www.istes.org</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3198,11 +3205,11 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>2025/5aa6b29d365d2193.pdf</t>
+          <t>2025/8a4a82dd2792d328.pdf</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -3212,28 +3219,28 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>In recent years, virtual reality (VR) and artificial intelligence (AI) technologies have been widely adopted across various sectors of society, including education. We conducted a practical study to assess the effectiveness of immersive technologies in higher education institutions. The research was carried out over a period of ten weeks. Students were divided into control and experimental groups. Furthermore, the research work was based on the collection of quantitative data and monitoring students' academic performance. The study's results were analyzed using a paired t-test and descriptive statistics. The independent t-test results indicated significant differences in subsequent test scores between the experimental and control groups. Quantitative descriptive results were presented in the form of diagrams and evaluated across six pedagogical components. At the conclusion of the study, recommendations for future research were provided. [For the complete proceedings, &amp;quot;Proceedings of the International Association for Development of the Information Society (IADIS) International Conference on Cognition and Exploratory Learning in the Digital Age (CELDA) (22nd, Porto, Portugal, November 1-3, 2025),&amp;quot; see ED677812.]</t>
+          <t>This study examines the perceptions of university students towards the use of generative artificial intelligence (GAI) in educational processes, especially in assignments. The main features of URM are human-like language abilities and the capacity to generate predictive content. In the study, descriptive research method, which is a quantitative method, was used to measure the views of university students towards the use of URM. The data collected from the participants in online format were analyzed through descriptive analysis. The findings of the study show that the majority of the students find it useful to use UIC tools such as ChatGPT in their assignments. While 63% of the students thought that using ChatGPT in assignments was useful, 21% were undecided and 16% expressed negative opinions. There was a high level of positive feedback that ChatGPT increased success in the assignment process, speeded up work and supported productivity. However, some students reported concerns about the impact of this technology on academic ethics issues and possible negative aspects on critical thinking skills. It was observed that students found the process of learning and using ChatGPT easy but needed integration and guidance support. In addition, the incentives from their social environment were found to have an impact on students' tendency to use the IWB. The study recommends developing guidance and training programs on the use of URMs, raising awareness about the accuracy of information, and encouraging ethical use. [For the complete proceedings, see ED678757.]</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>fd9e23c6c69b4a0f</t>
+          <t>2a772f767ed3fd8e</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>The Future of Cybersecurity at Sea: Human vs Human or AI vs AI?</t>
+          <t>Beyond the Books: A Study on AI Augmentation in Civil Engineering Pedagogy for Pavement Design</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Alop, A.</t>
+          <t>Javier Vásquez-Monteros; Yasmany García-Ramírez</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -3242,22 +3249,7 @@
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Signals and communication technology</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Springer Vienna</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>book-chapter</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-031-87290-7_1</t>
+          <t>International Society for Technology, Education, and Science. 944 Maysey Drive, San Antonio, TX 78227. Tel: 515-294-1075; Fax: 515-294-1003; email: istesoffice@gmail.com; Web site: http://www.istes.org</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3267,7 +3259,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
@@ -3280,51 +3272,43 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>hybrid</t>
-        </is>
-      </c>
-      <c r="O35" t="n">
-        <v>0</v>
-      </c>
       <c r="P35" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>2025/fd9e23c6c69b4a0f.pdf</t>
+          <t>2024/2a772f767ed3fd8e.pdf</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>eric</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>The digitalization of all areas of activity, including maritime, today is characterized, among other things, by two powerful influencing factors: on the one hand, artificial intelligence (AI) increasingly taking over the most important functions and develops very quickly, and on the other hand, threats and risks related to cybersecurity. The common belief, which is hard to argue against, is that the first factor is positive, because it contributes to developments, and the second is undoubtedly negative, because it hinders developments and can even inhibit them; from here, it is easy to conclude that in order to continue and accelerate progress, the positive aspects of the first factor must be contributed in every way and the fight against the effects of the second factor must be undertaken. But how realistic and consistently achievable are these two goals in interaction? True, in the light of the developments of the last years and even months, it seems that the AI “train” has started its impressive journey at high speed, and nothing can stop it. At the same time, continuing the allegory, there is still a “wagon” of cyber threats attached to this “train,” and getting rid of it or even defeating it to a sufficient extent seems problematic, at least now. The author of this chapter expresses an estimated opinion that as long as people fight against each other on both sides of the “cyber war” (“bad” guys against “good” ones), it is so to say war of attrition, where no glorious victory awaits either side. It seems to the author that it is possible to change the situation and achieve victory over the “bad” guys only if the AI itself takes over its own protection. Whether and to what extent this is possible is one of the main topics of this chapter. In the author’s opinion, there can be any truth behind this only if the AI acquires a large part of the characteristics unique to humans (values, moral principles, emotions, etc.), thanks to which it would be possible to be guided by the specific laws or rules of behavior of the AI. As a classic example, the so-called three laws of robotics, formulated by the American science fiction writer Isaac Asimov about 80 years ago, are based on the principle of avoiding harm to humans (Anderson, Asimov’s “Three Laws of Robotics” and machine metaethics, University of Connecticut, Dept. of Philosophy, Stamford, CT, https://cdn.aaai.org/Symposia/Fall/2005/FS-05-06/FS05-06-002.pdf ). In this chapter, we have analyzed whether such AI developments are possible at all and what threats and difficulties this entails in turn.</t>
+          <t>This study investigates the integration of AI tools, ChatGPT 3.5 and Bard (now Gemini), in the education of civil engineering students specializing in pavement design. Two groups, totaling sixty-eight undergraduate students (Group A=28, Group B=40), enrolled in the Pavement Design course at UTPL from October 2023 to February 2024, participated. They were tasked with generating prompts covering various pavement design topics. These included Traffic, Subgrade Characteristics, Asphalt Materials, AASHTO-Flexible Design, AASHTO-Rigid Design, Interlocking Concrete Pavements Design, International Roughness Index (IRI), and Construction Systems on Pavements. Students then assessed AI-generated responses using a predefined grading scale. The results revealed Bard achieved a higher approval rate of 71.1% compared to ChatGPT's 48.5%. ChatGPT 3.5 would not meet the passing threshold for certain topics, such as AASHTO-Flexible Design, AASHTO-Rigid Design, and IRI. In contrast, Bard consistently achieved higher approval rates across all assessed topics. Students acknowledged the AI tools' significant contribution to a deeper understanding of the course material. This integration positively influenced civil engineering students' learning outcomes, highlighting the evolving role of AI in education and encouraging further exploration in academia. [For the complete proceedings, see ED672804.]</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>dd8a0e8d30483815</t>
+          <t>bebfc35847a401fc</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>The Impact of AI Tools on Universities’ Educational Strategies and Student Success: Sultan Qaboos University and Qatar University as a Case Study</t>
+          <t>Characteristics of Romanian Online Recruitment Websites and Students’ Use</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Al-Awadhi, T.; Al-Balushi, A.; Abdullah, M.; Abulibdeh, A.</t>
+          <t>Mardache, A.; Balasescu, M.</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -3333,12 +3317,12 @@
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Gulf Studies</t>
+          <t>Springer proceedings in business and economics</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Springer Nature</t>
+          <t>Springer International Publishing</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -3348,7 +3332,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>10.1007/978-981-97-9667-0_9</t>
+          <t>10.1007/978-3-031-51038-0_76</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3377,14 +3361,14 @@
         </is>
       </c>
       <c r="O36" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P36" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>2025/dd8a0e8d30483815.pdf</t>
+          <t>2024/bebfc35847a401fc.pdf</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -3394,28 +3378,28 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>Abstract Sultan Qaboos University (SQU) and Qatar University (QU) are working to adopt short- and long-term plans to ensure leadership in teaching and learning, scientific research, and community service at regional and international levels. Modern technologies, especially artificial intelligence (AI), play an important role in our lives, providing realistic opportunities to accelerate business implementation and improve the final value of work. AI plays a crucial role in taking education and research to the next level, transforming the way these organisations work and make decisions. AI can improve the traditional work of educational institutions and transform the understanding of their complexity. However, challenges remain in various aspects, whether related to the nature of our work or to the AI technologies themselves. This is still a great opportunity for every HEI. Therefore, this paper aims to analyse the potential of AI to accelerate the implementation of the strategic plans of the two universities.</t>
+          <t>Abstract Technology has increasingly changed the way human resource (HR) function achieves its goals. Organizations seek agile employees who can cope with continuous changes in a complex and uncertain environment. Effective recruitment is closely related to talent management, as organizations are interested in attracting talented people who can give a competitive advantage for the organization. The use of technology and artificial intelligence in recruitment will increasingly enable the creation of profiles that help organizations attract the best candidates for vacancies. In this context, due to its multiple advantages both for organizations and candidates, online recruitment is increasingly being used. However, it is important to be aware of the various problems associated with online recruitment and to find solutions in solving them. In this study, we conducted a content analysis of ten of the most popular recruitment websites in Romania, according to a wide range of criteria concerning the jobs on offer, but also the features of the sites. Moreover, we also conducted an exploratory survey (with a sample of 200 students) in order to identify the perception and use of these recruitment websites by students and recent university graduates. Recruitment websites are more and more complex and offer diverse and useful tools for users. Some of them already use artificial intelligence to help users identify the most compatible job. Students and recent university graduates predominantly use such websites when they are looking for a job.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ccacb2251f5b4e56</t>
+          <t>323ecbe01d1cd744</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Thinking Along the Lines Generated by GenAI? A Systematic Mapping Study on Academic Writing</t>
+          <t>Last Tendencies in Acquiring Text Competence in the Field of Tourism. The Case of Chatbots and AI</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Kaczkó, É.; Ivanjek, L.; Norz, L.; Ammenwerth, E.</t>
+          <t>Madueño, M.</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -3424,12 +3408,12 @@
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lecture notes in computer science</t>
+          <t>Springer proceedings in business and economics</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Springer Science+Business Media</t>
+          <t>Springer International Publishing</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3439,7 +3423,7 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10.1007/978-3-032-11108-1_35</t>
+          <t>10.1007/978-3-031-52607-7_17</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3468,14 +3452,14 @@
         </is>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P37" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>2025/ccacb2251f5b4e56.pdf</t>
+          <t>2024/323ecbe01d1cd744.pdf</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -3485,28 +3469,28 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>The advent of generative AI (GenAI) tools in higher education challenges fundamental assumptions about academic authorship, students’ cognitive development and how writing cultivates critical thinking (CT). This systematic mapping study synthesized emerging research on how GenAI is reshaping the relationship between academic writing and CT in higher education. Drawing on 25 peer-reviewed studies published between 2023 and 2025, we analyzed conceptualizations of CT and academic writing, identified pedagogical approaches, and examined the use of GenAI tools across a range of disciplines, educational levels, and geographic contexts. Findings revealed that interest in the use of GenAI in academic writing is global and spans all disciplines and higher educational levels. However, only a minority of studies drew on robust theoretical frameworks. CT was conceptualized predominantly within a cognitive skills paradigm, while broader understandings linked to criticality and critical pedagogy were largely absent. Pedagogical models were rare and mostly untested, and educators’ perspectives were underrepresented. While GenAI was seen as supporting writing processes, its potential to foster or hinder CT remained contested. Future research should broaden conceptual foundations, include educator perspectives, and prioritize pedagogical design and evaluation. Rethinking academic writing as a transformative practice may require moving beyond the cognitive paradigm towards more participatory and ethically grounded approaches to CT.</t>
+          <t>Abstract Our aim is to propose the usage of generative Artificial Intelligence, hereafter AI, while lecturing, as a complement to the traditional methodology, to ease technological skills acquisition in the related AI. Widely spread in all aspects of cultural life and professional praxis worldwide, it is of key importance in the training of our professional to be. In Malaga University’s Degree of Tourism, in subjects dealing with English for tourism management, we shall concentrate on chatbots aided by AI, in order to make a literary review to see the state of the question and to reflect on the needed changes to implement these tools. We shall try to outline the characteristics, possibilities, advantages and disadvantages, and the influence on both students and lecturers alike of the usage of AI in chatbots to deal with outcoming texts. Direct interaction with the tools will be highlighted. Of key importance is training lecturers in the productive use of “prompt engineering”. To conclude, handling specialised texts in the field of tourism by means of chatbots might help lecturers’ awareness and responsibility for right use to obtain semi-specialised and specialised texts in the field of tourism in order to understand, extract and evaluate its pertinence.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>8a4a82dd2792d328</t>
+          <t>4ef9c0fd48d39cc4</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>University Students&amp;apos; Perceptions of the Use of Productive Artificial Intelligence: The Effects of ChatGPT on Assignment Processes</t>
+          <t>Leveraging ChatGPT for Automated Knowledge Concept Generation</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Halil Güvel; Muhammet Demirbilek; Seyfullah Gökoglu</t>
+          <t>Tianyuan Yang; Baofeng Ren; Chenghao Gu; Boxuan Ma; Shin 'ichi Konomi</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -3515,7 +3499,7 @@
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>International Society for Technology, Education, and Science. 944 Maysey Drive, San Antonio, TX 78227. Tel: 515-294-1075; Fax: 515-294-1003; email: istesoffice@gmail.com; Web site: http://www.istes.org</t>
+          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3539,11 +3523,11 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q38" t="inlineStr">
         <is>
-          <t>2025/8a4a82dd2792d328.pdf</t>
+          <t>2024/4ef9c0fd48d39cc4.pdf</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -3553,24 +3537,24 @@
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>This study examines the perceptions of university students towards the use of generative artificial intelligence (GAI) in educational processes, especially in assignments. The main features of URM are human-like language abilities and the capacity to generate predictive content. In the study, descriptive research method, which is a quantitative method, was used to measure the views of university students towards the use of URM. The data collected from the participants in online format were analyzed through descriptive analysis. The findings of the study show that the majority of the students find it useful to use UIC tools such as ChatGPT in their assignments. While 63% of the students thought that using ChatGPT in assignments was useful, 21% were undecided and 16% expressed negative opinions. There was a high level of positive feedback that ChatGPT increased success in the assignment process, speeded up work and supported productivity. However, some students reported concerns about the impact of this technology on academic ethics issues and possible negative aspects on critical thinking skills. It was observed that students found the process of learning and using ChatGPT easy but needed integration and guidance support. In addition, the incentives from their social environment were found to have an impact on students' tendency to use the IWB. The study recommends developing guidance and training programs on the use of URMs, raising awareness about the accuracy of information, and encouraging ethical use. [For the complete proceedings, see ED678757.]</t>
+          <t>As education increasingly shifts towards a technology-driven model, artificial intelligence systems like ChatGPT are gaining recognition for their potential to enhance educational support. In university education and MOOC environments, students often select courses that align with their specific needs. During this process, access to information about the knowledge concepts covered in a course can help students make more informed decisions. However, manually constructing this knowledge concept information is a labor-intensive and time-consuming task. In this paper, we explore the capability of ChatGPT in generating relevant knowledge concepts from course syllabi and evaluate the accuracy and consistency of these AI-generated concepts against course content using four assessment techniques at both the concept level and course level. We investigate the feasibility of using ChatGPT-generated concepts as a direct educational resource, as well as their potential integration into broader educational technologies, such as interpretable course recommendation systems. [For the full proceedings, see ED665357.]</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2a772f767ed3fd8e</t>
+          <t>e799f9736c02ac60</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Beyond the Books: A Study on AI Augmentation in Civil Engineering Pedagogy for Pavement Design</t>
+          <t>Overcoming the Long Shadow of the Past: Defense AI in Japan</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Javier Vásquez-Monteros; Yasmany García-Ramírez</t>
+          <t>Tsuchiya, M.</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -3583,7 +3567,22 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>International Society for Technology, Education, and Science. 944 Maysey Drive, San Antonio, TX 78227. Tel: 515-294-1075; Fax: 515-294-1003; email: istesoffice@gmail.com; Web site: http://www.istes.org</t>
+          <t>Contributions to security and defence studies</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Springer International Publishing</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>book-chapter</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-031-58649-1_22</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -3593,7 +3592,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L39" t="inlineStr">
@@ -3606,39 +3605,47 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>0</v>
+      </c>
       <c r="P39" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Q39" t="inlineStr">
         <is>
-          <t>2024/2a772f767ed3fd8e.pdf</t>
+          <t>2024/e799f9736c02ac60.pdf</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
         <is>
-          <t>eric</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>This study investigates the integration of AI tools, ChatGPT 3.5 and Bard (now Gemini), in the education of civil engineering students specializing in pavement design. Two groups, totaling sixty-eight undergraduate students (Group A=28, Group B=40), enrolled in the Pavement Design course at UTPL from October 2023 to February 2024, participated. They were tasked with generating prompts covering various pavement design topics. These included Traffic, Subgrade Characteristics, Asphalt Materials, AASHTO-Flexible Design, AASHTO-Rigid Design, Interlocking Concrete Pavements Design, International Roughness Index (IRI), and Construction Systems on Pavements. Students then assessed AI-generated responses using a predefined grading scale. The results revealed Bard achieved a higher approval rate of 71.1% compared to ChatGPT's 48.5%. ChatGPT 3.5 would not meet the passing threshold for certain topics, such as AASHTO-Flexible Design, AASHTO-Rigid Design, and IRI. In contrast, Bard consistently achieved higher approval rates across all assessed topics. Students acknowledged the AI tools' significant contribution to a deeper understanding of the course material. This integration positively influenced civil engineering students' learning outcomes, highlighting the evolving role of AI in education and encouraging further exploration in academia. [For the complete proceedings, see ED672804.]</t>
+          <t>Abstract Since the end of World War II, Japan has not had a full-fledged military, but only Self-Defense Forces (SDF) for the sole purpose of “exclusively defensive defense.” Hesitancy exists in society, especially in academia, to research and develop technologies that could be diverted to military use. This has created a long shadow of the past in which public opinion, strategic culture, and the academic-industrial ecosystem mutually reinforce each other not to directly address defense technologies, though Japan is often recognized as one of the most technologically advanced countries. However, with the recent deterioration of the national security environment around Japan, such hesitance is weakening, and research and development of technologies that can be applied to defense purposes is now being conducted, also in cooperation with partners like the United States, the United Kingdom, and others. Discussions about artificial intelligence (AI) for defense purposes began in earnest around 2022, with descriptions found in government and defense documents, and budget appropriations beginning to be made. However, the budget size is miniscule and no special organization for defense AI exists. In addition, there is no plan to use defense AI in earnest in defense operations, and it is merely positioned as one of the technologies that are attracting widespread attention. The defense industry is working on AI across the board, but Japan’s defense industry has a large proportion of civilian demand, and there are aspects of the industry that are not necessarily for defense use. If necessary, they will be applied to defense applications, but they are not actively promoted as AI for defense. Attempts to deepen the knowledge of AI among SDF personnel have only just begun.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>bebfc35847a401fc</t>
+          <t>148d777c7af8aaae</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Characteristics of Romanian Online Recruitment Websites and Students’ Use</t>
+          <t>Reimagining Extreme Event Scenarios: The Aesthetic Visualisation of Climate Uncertainty to Enhance Preparedness</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Mardache, A.; Balasescu, M.</t>
+          <t>Favero, D.; Thurow, S.; Pagnucco, M.; Frohne, U.</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -3651,7 +3658,7 @@
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Springer proceedings in business and economics</t>
+          <t>Arts, research, innovation and society</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3666,7 +3673,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-51038-0_76</t>
+          <t>10.1007/978-3-031-56114-6_2</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3702,7 +3709,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>2024/bebfc35847a401fc.pdf</t>
+          <t>2024/148d777c7af8aaae.pdf</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -3712,24 +3719,24 @@
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>Abstract Technology has increasingly changed the way human resource (HR) function achieves its goals. Organizations seek agile employees who can cope with continuous changes in a complex and uncertain environment. Effective recruitment is closely related to talent management, as organizations are interested in attracting talented people who can give a competitive advantage for the organization. The use of technology and artificial intelligence in recruitment will increasingly enable the creation of profiles that help organizations attract the best candidates for vacancies. In this context, due to its multiple advantages both for organizations and candidates, online recruitment is increasingly being used. However, it is important to be aware of the various problems associated with online recruitment and to find solutions in solving them. In this study, we conducted a content analysis of ten of the most popular recruitment websites in Romania, according to a wide range of criteria concerning the jobs on offer, but also the features of the sites. Moreover, we also conducted an exploratory survey (with a sample of 200 students) in order to identify the perception and use of these recruitment websites by students and recent university graduates. Recruitment websites are more and more complex and offer diverse and useful tools for users. Some of them already use artificial intelligence to help users identify the most compatible job. Students and recent university graduates predominantly use such websites when they are looking for a job.</t>
+          <t>Abstract Responding to the rapidly escalating climate emergency, this chapter outlines transformative multidisciplinary research centred on the visualisation of unpredictable extreme event scenarios. It proposes a unique, scientifically grounded artistic approach to one of the world’s most immediate challenges—preparing communities for extreme climate events, such as firestorms and flash floods. As preparedness is a function of prior threat experience, it argues that visualising threat scenarios in advance can be a key to surviving and adapting in an era of increasing climate instability. This approach can enable communities to viscerally experience and rehearse threat perception, situational awareness, adaptive decision making and dynamic response to unexpected life-threatening extreme events. Using experimental case studies at The University of New South Wales’s iCinema Research Centre and international benchmarks, this chapter explores how advances in immersive visualisation and artificial intelligence aesthetics can be integrated to provide a framework that enables the virtual prototyping of unforeseen geolocated climate scenarios to facilitate readiness in the face of accelerating climate uncertainty.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>323ecbe01d1cd744</t>
+          <t>5beff436c4263cda</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Last Tendencies in Acquiring Text Competence in the Field of Tourism. The Case of Chatbots and AI</t>
+          <t>Retrieval Augmented Large Language Model Chatbots in Higher Education: A Study on University Open Days</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Madueño, M.</t>
+          <t>Shanthakumar, A.; Fassihi-Tash, F.; Lotfi, A.; Bird, J.</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -3742,12 +3749,12 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Springer proceedings in business and economics</t>
+          <t>Advances in intelligent systems and computing</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Springer International Publishing</t>
+          <t>Springer Nature</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -3757,7 +3764,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-52607-7_17</t>
+          <t>10.1007/978-3-031-78857-4_3</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3782,45 +3789,41 @@
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>hybrid</t>
+          <t>green</t>
         </is>
       </c>
       <c r="O41" t="n">
         <v>1</v>
       </c>
       <c r="P41" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q41" t="inlineStr">
         <is>
-          <t>2024/323ecbe01d1cd744.pdf</t>
+          <t>2024/5beff436c4263cda.pdf</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
         <is>
-          <t>openalex</t>
-        </is>
-      </c>
-      <c r="S41" s="2" t="inlineStr">
-        <is>
-          <t>Abstract Our aim is to propose the usage of generative Artificial Intelligence, hereafter AI, while lecturing, as a complement to the traditional methodology, to ease technological skills acquisition in the related AI. Widely spread in all aspects of cultural life and professional praxis worldwide, it is of key importance in the training of our professional to be. In Malaga University’s Degree of Tourism, in subjects dealing with English for tourism management, we shall concentrate on chatbots aided by AI, in order to make a literary review to see the state of the question and to reflect on the needed changes to implement these tools. We shall try to outline the characteristics, possibilities, advantages and disadvantages, and the influence on both students and lecturers alike of the usage of AI in chatbots to deal with outcoming texts. Direct interaction with the tools will be highlighted. Of key importance is training lecturers in the productive use of “prompt engineering”. To conclude, handling specialised texts in the field of tourism by means of chatbots might help lecturers’ awareness and responsibility for right use to obtain semi-specialised and specialised texts in the field of tourism in order to understand, extract and evaluate its pertinence.</t>
-        </is>
-      </c>
+          <t>openalex,s2</t>
+        </is>
+      </c>
+      <c r="S41" s="2" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>4ef9c0fd48d39cc4</t>
+          <t>a366da3974dd03f0</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Leveraging ChatGPT for Automated Knowledge Concept Generation</t>
+          <t>Ruffle&amp;amp;Riley: Insights from Designing and Evaluating a Large Language Model-Based Conversational Tutoring System</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Tianyuan Yang; Baofeng Ren; Chenghao Gu; Boxuan Ma; Shin 'ichi Konomi</t>
+          <t>Schmucker, R.; Xia, M.; Azaria, A.; Mitchell, T.</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -3833,7 +3836,22 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
+          <t>Lecture notes in computer science</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Springer Science+Business Media</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>book-chapter</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-031-64302-6_6</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3843,7 +3861,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3856,39 +3874,47 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>32</v>
+      </c>
       <c r="P42" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q42" t="inlineStr">
         <is>
-          <t>2024/4ef9c0fd48d39cc4.pdf</t>
+          <t>2024/a366da3974dd03f0.pdf</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
         <is>
-          <t>eric</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>As education increasingly shifts towards a technology-driven model, artificial intelligence systems like ChatGPT are gaining recognition for their potential to enhance educational support. In university education and MOOC environments, students often select courses that align with their specific needs. During this process, access to information about the knowledge concepts covered in a course can help students make more informed decisions. However, manually constructing this knowledge concept information is a labor-intensive and time-consuming task. In this paper, we explore the capability of ChatGPT in generating relevant knowledge concepts from course syllabi and evaluate the accuracy and consistency of these AI-generated concepts against course content using four assessment techniques at both the concept level and course level. We investigate the feasibility of using ChatGPT-generated concepts as a direct educational resource, as well as their potential integration into broader educational technologies, such as interpretable course recommendation systems. [For the full proceedings, see ED665357.]</t>
+          <t>Abstract Conversational tutoring systems (CTSs) offer learning experiences through interactions based on natural language. They are recognized for promoting cognitive engagement and improving learning outcomes, especially in reasoning tasks. Nonetheless, the cost associated with authoring CTS content is a major obstacle to widespread adoption and to research on effective instructional design. In this paper, we discuss and evaluate a novel type of CTS that leverages recent advances in large language models (LLMs) in two ways: First, the system enables AI-assisted content authoring by inducing an easily editable tutoring script automatically from a lesson text. Second, the system automates the script orchestration in a learning-by-teaching format via two LLM-based agents (Ruffle&amp;amp;Riley) acting as a student and a professor. The system allows for free-form conversations that follow the ITS-typical inner and outer loop structure. We evaluate Ruffle&amp;amp;Riley’s ability to support biology lessons in two between-subject online user studies ( $$N = 200$$ &lt;mml:math xmlns:mml="http://www.w3.org/1998/Math/MathML"&gt; &lt;mml:mrow&gt; &lt;mml:mi&gt;N&lt;/mml:mi&gt; &lt;mml:mo&gt;=&lt;/mml:mo&gt; &lt;mml:mn&gt;200&lt;/mml:mn&gt; &lt;/mml:mrow&gt; &lt;/mml:math&gt; ) comparing the system to simpler QA chatbots and reading activity. Analyzing system usage patterns, pre/post-test scores and user experience surveys, we find that Ruffle&amp;amp;Riley users report high levels of engagement, understanding and perceive the offered support as helpful. Even though Ruffle&amp;amp;Riley users require more time to complete the activity, we did not find significant differences in short-term learning gains over the reading activity. Our system architecture and user study provide various insights for designers of future CTSs. We further open-source our system to support ongoing research on effective instructional design of LLM-based learning technologies.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>e799f9736c02ac60</t>
+          <t>9184c19bd9973246</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Overcoming the Long Shadow of the Past: Defense AI in Japan</t>
+          <t>Success through Error: Using Error Analysis of ChatGPT Output in English as a Foreign Language Learner Writing Instruction</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Tsuchiya, M.</t>
+          <t>Arifi Waked; Muhammad W. Ashraf; Hanadi AbdelSalam; Khadija El Alaoui; Maura Pilotti</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -3901,22 +3927,7 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Contributions to security and defence studies</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Springer International Publishing</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>book-chapter</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-031-58649-1_22</t>
+          <t>International Society for Technology, Education, and Science. 944 Maysey Drive, San Antonio, TX 78227. Tel: 515-294-1075; Fax: 515-294-1003; email: istesoffice@gmail.com; Web site: http://www.istes.org</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3926,7 +3937,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
@@ -3938,48 +3949,40 @@
         <is>
           <t>Yes</t>
         </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>hybrid</t>
-        </is>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
       </c>
       <c r="P43" t="n">
         <v>2</v>
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>2024/e799f9736c02ac60.pdf</t>
+          <t>2024/9184c19bd9973246.pdf</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>eric</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>Abstract Since the end of World War II, Japan has not had a full-fledged military, but only Self-Defense Forces (SDF) for the sole purpose of “exclusively defensive defense.” Hesitancy exists in society, especially in academia, to research and develop technologies that could be diverted to military use. This has created a long shadow of the past in which public opinion, strategic culture, and the academic-industrial ecosystem mutually reinforce each other not to directly address defense technologies, though Japan is often recognized as one of the most technologically advanced countries. However, with the recent deterioration of the national security environment around Japan, such hesitance is weakening, and research and development of technologies that can be applied to defense purposes is now being conducted, also in cooperation with partners like the United States, the United Kingdom, and others. Discussions about artificial intelligence (AI) for defense purposes began in earnest around 2022, with descriptions found in government and defense documents, and budget appropriations beginning to be made. However, the budget size is miniscule and no special organization for defense AI exists. In addition, there is no plan to use defense AI in earnest in defense operations, and it is merely positioned as one of the technologies that are attracting widespread attention. The defense industry is working on AI across the board, but Japan’s defense industry has a large proportion of civilian demand, and there are aspects of the industry that are not necessarily for defense use. If necessary, they will be applied to defense applications, but they are not actively promoted as AI for defense. Attempts to deepen the knowledge of AI among SDF personnel have only just begun.</t>
+          <t>Questions exist as to whether AI tools, such as ChatGPT, can aid learning. This study examined whether in-class exercises involving error detection in text generated by ChatGPT can aid students' foreign language writing. Participants were Arabic-English speakers who were classified as ranging from modest to competent English users according to IELTS standards. There were two conditions, each involving four sections of an English communication course, distributed across consecutive semesters and taught by the same instructor. In the treatment condition (n = 101), students performed error detection exercises using text generated by ChatGPT. In the control condition (n = 112), students performed the same exercises without ChatGPT. Then, they wrote a descriptive essay. It was hypothesized that if ChatGPT exercises enhanced students' confidence as writers, they would write longer essays. If ChatGPT exercises enhanced attention to detail, the exercises would increase writing quality (e.g., greater use of low-frequency and abstract words, and greater reliance on complex syntactic structures). In this study, students exposed to ChatGPT exercises used more low-frequency words and wrote more sentences but of shorter length than control condition students. The number of words did not differ, suggesting that ChatGPT exercises enhanced writers' attention to the shorter sentence length of the English language and its vast vocabulary. The results of this study suggest that ChatGPT exercises yield minor benefits for improving the writing of second-language speakers. Yet, extensive and broader exercises may yield more substantial benefits. [For the complete proceedings, see ED672804.]</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>148d777c7af8aaae</t>
+          <t>2c028fbe91e54d72</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Reimagining Extreme Event Scenarios: The Aesthetic Visualisation of Climate Uncertainty to Enhance Preparedness</t>
+          <t>Survival of the Smartest? Defense AI in Ukraine</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Favero, D.; Thurow, S.; Pagnucco, M.; Frohne, U.</t>
+          <t>Goncharuk, V.</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -3992,7 +3995,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Arts, research, innovation and society</t>
+          <t>Contributions to security and defence studies</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4007,7 +4010,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-56114-6_2</t>
+          <t>10.1007/978-3-031-58649-1_17</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
@@ -4036,14 +4039,14 @@
         </is>
       </c>
       <c r="O44" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P44" t="n">
         <v>2</v>
       </c>
       <c r="Q44" t="inlineStr">
         <is>
-          <t>2024/148d777c7af8aaae.pdf</t>
+          <t>2024/2c028fbe91e54d72.pdf</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4053,24 +4056,24 @@
       </c>
       <c r="S44" s="2" t="inlineStr">
         <is>
-          <t>Abstract Responding to the rapidly escalating climate emergency, this chapter outlines transformative multidisciplinary research centred on the visualisation of unpredictable extreme event scenarios. It proposes a unique, scientifically grounded artistic approach to one of the world’s most immediate challenges—preparing communities for extreme climate events, such as firestorms and flash floods. As preparedness is a function of prior threat experience, it argues that visualising threat scenarios in advance can be a key to surviving and adapting in an era of increasing climate instability. This approach can enable communities to viscerally experience and rehearse threat perception, situational awareness, adaptive decision making and dynamic response to unexpected life-threatening extreme events. Using experimental case studies at The University of New South Wales’s iCinema Research Centre and international benchmarks, this chapter explores how advances in immersive visualisation and artificial intelligence aesthetics can be integrated to provide a framework that enables the virtual prototyping of unforeseen geolocated climate scenarios to facilitate readiness in the face of accelerating climate uncertainty.</t>
+          <t>Abstract Before Russia’s invasion in February 2022, Ukraine boasted a thriving ecosystem for producing artificial intelligence (AI) solutions, leading Eastern Europe in AI company numbers and hosting R&amp;amp;D offices of multinational giants like Amazon and Google. Despite this, Ukraine’s defense sector lagged in AI adoption due to a focus on traditional hardware. The conflict between Russia and Ukraine has transformed the situation, with both sides employing AI in geospatial intelligence, unmanned systems, military training, and cyber warfare, making this conflict the first to feature AI competition as a critical factor. Ukraine’s resilience during the war has relied on active use of awareness systems, volunteer initiatives, open-source platforms, and decentralized asset utilization. The government has begun systematically formulating defense AI policy initiatives and fostering a new ecosystem while civil IT companies shift focus towards dual-use products and talent acquisition in AI. Current defense AI development priorities include AI for unmanned systems, to combat disinformation and support cybersecurity and to advance logistics and mine detection. In parallel, the war has advanced closer cooperation between universities and the military sector, also in view of advancing training and developing AI-enhanced simulation-based training. Overall, the conflict serves as a testing ground for foreign AI developers, prompting reevaluation of regulatory assumptions and the need for war-proof defense AI solutions.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>5beff436c4263cda</t>
+          <t>d7adc1344b2359ef</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Retrieval Augmented Large Language Model Chatbots in Higher Education: A Study on University Open Days</t>
+          <t>The Convergent Validity of Mobile Learning Apps&amp;apos; Usability Evaluation by Popular Generative Artificial Intelligence (AI) Robots</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Shanthakumar, A.; Fassihi-Tash, F.; Lotfi, A.; Bird, J.</t>
+          <t>Victor K. Y. Chan</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -4083,22 +4086,7 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Advances in intelligent systems and computing</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Springer Nature</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>book-chapter</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-031-78857-4_3</t>
+          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
@@ -4108,7 +4096,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4120,44 +4108,40 @@
         <is>
           <t>Yes</t>
         </is>
-      </c>
-      <c r="N45" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="O45" t="n">
-        <v>1</v>
       </c>
       <c r="P45" t="n">
         <v>3</v>
       </c>
       <c r="Q45" t="inlineStr">
         <is>
-          <t>2024/5beff436c4263cda.pdf</t>
+          <t>2024/d7adc1344b2359ef.pdf</t>
         </is>
       </c>
       <c r="R45" t="inlineStr">
         <is>
-          <t>openalex,s2</t>
-        </is>
-      </c>
-      <c r="S45" s="2" t="n"/>
+          <t>eric</t>
+        </is>
+      </c>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>This article seeks to explore the convergent validity of (and thus the consistency between) a few popular generative artificial intelligence (AI) robots in evaluating popular mobile learning apps' usability. The three robots adopted in the study were Microsoft Copilot, Google PaLM, and Meta Llama, which were individually instructed to accord rating scores to the eight major usability dimensions, namely, (1) content/course quality, (2) pedagogical design, (3) learner support, (4) technology infrastructure, (5) social interaction, (6) learner engagement, (7) instructor support, and (8) cost-effectiveness of 17 currently most popular mobile learning apps. For each of the three robots, the minimum, the maximum, the range, and the standard deviation of the rating scores for each of the eight dimensions were computed across all the mobile learning apps. The rating score difference for each of the eight dimensions between any pair of the above three robots was calculated for each app. The mean of the absolute value, the minimum, the maximum, the range, and the standard deviation of the differences for each dimensions between each pair of robots were calculated across all the apps. A paired sample t-test was then applied to each dimension for the rating score difference between each robot pair over all the apps. Finally, Cronbach's coefficient alpha of the rating scores was computed for each of the eight dimensions between all the three robots across all the apps. The computational results were to reveal whether the three robots awarded discrimination in evaluating each dimension across the apps, whether each robot, with respect to any other robot, erratically and/or systematically overrate or underrate any dimension over the apps, and whether there was high convergent validity of (and thus consistency between) the three robots in evaluating each dimension across the apps. Among other auxiliary results, it was revealed that the convergent validity of (and the consistency between) the three robots was marginally acceptable only in evaluating mobile learning apps' dimension of (1) content/course quality but not at all in the dimensions (2) pedagogical design, (3) learner support, (4) technology infrastructure, (5) social interaction, (6) learner engagement, (7) instructor support, and (8) cost-effectiveness. [For the full proceedings, see ED659933.]</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>a366da3974dd03f0</t>
+          <t>b8a9ff54254ee8ef</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Ruffle&amp;amp;Riley: Insights from Designing and Evaluating a Large Language Model-Based Conversational Tutoring System</t>
+          <t>The Impact of Falsely Detecting AI-Generated Text on Academic Assessment</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Schmucker, R.; Xia, M.; Azaria, A.; Mitchell, T.</t>
+          <t>Arifi N. Waked; Hanadi Abdelsalem; Muhammad Waqar Ashraf; Maura Pilotti; Khadija El Alaoui</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -4170,22 +4154,7 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lecture notes in computer science</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Springer Science+Business Media</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>book-chapter</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-031-64302-6_6</t>
+          <t>International Society for Technology, Education, and Science. 944 Maysey Drive, San Antonio, TX 78227. Tel: 515-294-1075; Fax: 515-294-1003; email: istesoffice@gmail.com; Web site: http://www.istes.org</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
@@ -4195,7 +4164,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4208,51 +4177,43 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>hybrid</t>
-        </is>
-      </c>
-      <c r="O46" t="n">
-        <v>32</v>
-      </c>
       <c r="P46" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q46" t="inlineStr">
         <is>
-          <t>2024/a366da3974dd03f0.pdf</t>
+          <t>2024/b8a9ff54254ee8ef.pdf</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>eric</t>
         </is>
       </c>
       <c r="S46" s="2" t="inlineStr">
         <is>
-          <t>Abstract Conversational tutoring systems (CTSs) offer learning experiences through interactions based on natural language. They are recognized for promoting cognitive engagement and improving learning outcomes, especially in reasoning tasks. Nonetheless, the cost associated with authoring CTS content is a major obstacle to widespread adoption and to research on effective instructional design. In this paper, we discuss and evaluate a novel type of CTS that leverages recent advances in large language models (LLMs) in two ways: First, the system enables AI-assisted content authoring by inducing an easily editable tutoring script automatically from a lesson text. Second, the system automates the script orchestration in a learning-by-teaching format via two LLM-based agents (Ruffle&amp;amp;Riley) acting as a student and a professor. The system allows for free-form conversations that follow the ITS-typical inner and outer loop structure. We evaluate Ruffle&amp;amp;Riley’s ability to support biology lessons in two between-subject online user studies ( $$N = 200$$ &lt;mml:math xmlns:mml="http://www.w3.org/1998/Math/MathML"&gt; &lt;mml:mrow&gt; &lt;mml:mi&gt;N&lt;/mml:mi&gt; &lt;mml:mo&gt;=&lt;/mml:mo&gt; &lt;mml:mn&gt;200&lt;/mml:mn&gt; &lt;/mml:mrow&gt; &lt;/mml:math&gt; ) comparing the system to simpler QA chatbots and reading activity. Analyzing system usage patterns, pre/post-test scores and user experience surveys, we find that Ruffle&amp;amp;Riley users report high levels of engagement, understanding and perceive the offered support as helpful. Even though Ruffle&amp;amp;Riley users require more time to complete the activity, we did not find significant differences in short-term learning gains over the reading activity. Our system architecture and user study provide various insights for designers of future CTSs. We further open-source our system to support ongoing research on effective instructional design of LLM-based learning technologies.</t>
+          <t>Large Language Model (LLM) Functionalities, such as Chat Generative Pre-Trained Transformer (ChatGPT), are a form of artificial intelligence (AI) that have the ability to produce human-like writing in response to a wide array of input. As this technology has become a staple of everyday life, many educators find themselves rapidly redefining best assessment practices regarding this new area of potential plagiarism. As it becomes increasingly difficult to discern between well-written assignments produced by students and those that have been generated by AI, educators may turn to AI-detection programs to determine whether work submitted by students is in fact their own. However, these programs notoriously return a high rate of false detection of AI-generated text. This phenomenon leads to the increased likelihood that students will be unfairly academically penalized. In this study, hand-written examinations for a university-level introductory academic writing class were submitted to different AI-detection programs. Results indicate an association between higher exam grades and greater false detection of AI-generated writing. These results suggest that educators must carefully consider the benefits of such programs when assessing students' work. [For the complete proceedings, see ED672804.]</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>9184c19bd9973246</t>
+          <t>85ea8f1340dce200</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Success through Error: Using Error Analysis of ChatGPT Output in English as a Foreign Language Learner Writing Instruction</t>
+          <t>Anchoring Concepts Influence Essay Conceptual Structure and Test Performance</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Arifi Waked; Muhammad W. Ashraf; Hanadi AbdelSalam; Khadija El Alaoui; Maura Pilotti</t>
+          <t>Roy B. Clariana; Ryan Solnosky</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -4261,7 +4222,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>International Society for Technology, Education, and Science. 944 Maysey Drive, San Antonio, TX 78227. Tel: 515-294-1075; Fax: 515-294-1003; email: istesoffice@gmail.com; Web site: http://www.istes.org</t>
+          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4285,11 +4246,11 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q47" t="inlineStr">
         <is>
-          <t>2024/9184c19bd9973246.pdf</t>
+          <t>2023/85ea8f1340dce200.pdf</t>
         </is>
       </c>
       <c r="R47" t="inlineStr">
@@ -4299,28 +4260,28 @@
       </c>
       <c r="S47" s="2" t="inlineStr">
         <is>
-          <t>Questions exist as to whether AI tools, such as ChatGPT, can aid learning. This study examined whether in-class exercises involving error detection in text generated by ChatGPT can aid students' foreign language writing. Participants were Arabic-English speakers who were classified as ranging from modest to competent English users according to IELTS standards. There were two conditions, each involving four sections of an English communication course, distributed across consecutive semesters and taught by the same instructor. In the treatment condition (n = 101), students performed error detection exercises using text generated by ChatGPT. In the control condition (n = 112), students performed the same exercises without ChatGPT. Then, they wrote a descriptive essay. It was hypothesized that if ChatGPT exercises enhanced students' confidence as writers, they would write longer essays. If ChatGPT exercises enhanced attention to detail, the exercises would increase writing quality (e.g., greater use of low-frequency and abstract words, and greater reliance on complex syntactic structures). In this study, students exposed to ChatGPT exercises used more low-frequency words and wrote more sentences but of shorter length than control condition students. The number of words did not differ, suggesting that ChatGPT exercises enhanced writers' attention to the shorter sentence length of the English language and its vast vocabulary. The results of this study suggest that ChatGPT exercises yield minor benefits for improving the writing of second-language speakers. Yet, extensive and broader exercises may yield more substantial benefits. [For the complete proceedings, see ED672804.]</t>
+          <t>This quasi-experimental study seeks to improve the conceptual quality of summary essays by comparing two conditions, essay prompts with or without a list of 13 broad concepts, the concepts were selected across a continuum of the 100 most frequent words in the lesson materials. It is anticipated that only the most central concepts will be used as &amp;quot;anchors&amp;quot; when writing. Participants (n = 90) in an Architectural Engineering undergraduate course read the assigned lesson textbook chapter and attended lectures and labs, then in a final lab session were asked to write a 300-word summary of the lesson content. Data consists of the essays converted to networks and the end-of-unit multiple choice test. Compared to the expert network benchmark, the essay networks of those receiving the broad concepts in the writing prompt were not significantly different from those who did not receive these concepts. However those receiving the broad concepts were significantly more like peer essay networks (mental model convergence) and like the networks of the two PowerPoint lectures but neither were like the textbook chapter. Further, those receiving the broad concepts performed significantly better on the end-of-unit test than those not receiving the concepts. Term frequency analysis of the essays indicates as expected that the most network-central concepts had a greater frequency in essays, the other terms frequencies were remarkably the same for both the terms and no terms groups, suggesting a similar underlying conceptual mental model of this lesson content. To further explore the influence of anchoring concepts in summary writing prompts, essays were generated with the same two summary writing prompts using OpenAI (ChatGPT) and Google Bard, plus a new prompt that used the 13 most central concepts from the expert's network. The quality of the essay networks for both AI systems were equivalent to the students' essay networks for the broad concepts and for the no concept treatments. However, the AI essays derived with the 13 most central concepts were significantly better (more like the expert network) than the students and AI essays derived with broad concepts or no concepts treatments. In addition, Bard and OpenAI used several of the same concepts at a higher frequency than the students suggesting that the two AI systems have more similar knowledge graphs of this content. In sum, adding 13 broad conceptual terms to a summary writing prompt improved both structural and declarative knowledge outcomes, but adding 13 most central concepts may be even better. More research is needed to understand how including concepts and other terms in a writing prompt influences students' essay conceptual structure and subsequent test performance. [For the full proceedings, see ED636095.]</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2c028fbe91e54d72</t>
+          <t>b142a08020007c56</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Survival of the Smartest? Defense AI in Ukraine</t>
+          <t>Education to Prevent Human Mechanisation in a Faculty of Informatics: Developing Learning Materials to Improve Students&amp;apos; Verbal Communication Skills</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Goncharuk, V.</t>
+          <t>Mari Ueda; Isoharu Nishiguchi; Hiroshi Tanaka; Kazunori Matsumoto; Tetsuo Tanaka</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -4329,22 +4290,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Contributions to security and defence studies</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Springer International Publishing</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>book-chapter</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-031-58649-1_17</t>
+          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4354,7 +4300,7 @@
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
@@ -4367,42 +4313,34 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="N48" t="inlineStr">
-        <is>
-          <t>hybrid</t>
-        </is>
-      </c>
-      <c r="O48" t="n">
-        <v>4</v>
-      </c>
       <c r="P48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q48" t="inlineStr">
         <is>
-          <t>2024/2c028fbe91e54d72.pdf</t>
+          <t>2023/b142a08020007c56.pdf</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>eric</t>
         </is>
       </c>
       <c r="S48" s="2" t="inlineStr">
         <is>
-          <t>Abstract Before Russia’s invasion in February 2022, Ukraine boasted a thriving ecosystem for producing artificial intelligence (AI) solutions, leading Eastern Europe in AI company numbers and hosting R&amp;amp;D offices of multinational giants like Amazon and Google. Despite this, Ukraine’s defense sector lagged in AI adoption due to a focus on traditional hardware. The conflict between Russia and Ukraine has transformed the situation, with both sides employing AI in geospatial intelligence, unmanned systems, military training, and cyber warfare, making this conflict the first to feature AI competition as a critical factor. Ukraine’s resilience during the war has relied on active use of awareness systems, volunteer initiatives, open-source platforms, and decentralized asset utilization. The government has begun systematically formulating defense AI policy initiatives and fostering a new ecosystem while civil IT companies shift focus towards dual-use products and talent acquisition in AI. Current defense AI development priorities include AI for unmanned systems, to combat disinformation and support cybersecurity and to advance logistics and mine detection. In parallel, the war has advanced closer cooperation between universities and the military sector, also in view of advancing training and developing AI-enhanced simulation-based training. Overall, the conflict serves as a testing ground for foreign AI developers, prompting reevaluation of regulatory assumptions and the need for war-proof defense AI solutions.</t>
+          <t>Although information technology (ICT) education is being strengthened based on the national context, there are reports suggesting a decline in young people's communication skills. This phenomenon can be attributed to the rapid development of informatisation, which includes the diversification and spread of information tools, as well as the prevalence of nonverbal communication, such as pictograms in social networking services. In addition, the COVID-19 pandemic has drastically reduced face-to-face communication opportunities, making interactive communication in on-demand classes challenging. Even in assignments and short tests completed during class, many instances of content being copied and pasted from the web or written in a disorganized manner have been observed. For instance, students entering ICT-related careers, particularly those graduating from the faculty of informatics, must possess the ability to communicate with engineers and clients while implementing ICT advancements. Alongside programming skills, strong communication abilities are essential. Moreover, the emergence of generative artificial intelligence (AI) tools, such as ChatGPT and Bing AI, has considerably diminished the opportunities for independent thinking. In the current era of enhanced ICT education, AI, and IoT, the Faculty of Informatics at the Kanagawa Institute of Technology has been engaged in discussions regarding learning materials that aim to strengthen students' ability to think and communicate in their own words, preventing the mechanisation of individuals. This paper presents the development and implementation of learning materials designed to enhance students' verbal communication skills through the description and re-production of mathematical graphs. [For the full proceedings, see ED636095.]</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>d7adc1344b2359ef</t>
+          <t>aa42fa1562d18625</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>The Convergent Validity of Mobile Learning Apps&amp;apos; Usability Evaluation by Popular Generative Artificial Intelligence (AI) Robots</t>
+          <t>Evaluating Popular MOOC Platforms by Generative Artificial Intelligence (AI) Robots: How Consistent Are the Robots?</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4411,7 +4349,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -4444,11 +4382,11 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="Q49" t="inlineStr">
         <is>
-          <t>2024/d7adc1344b2359ef.pdf</t>
+          <t>2023/aa42fa1562d18625.pdf</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4458,28 +4396,28 @@
       </c>
       <c r="S49" s="2" t="inlineStr">
         <is>
-          <t>This article seeks to explore the convergent validity of (and thus the consistency between) a few popular generative artificial intelligence (AI) robots in evaluating popular mobile learning apps' usability. The three robots adopted in the study were Microsoft Copilot, Google PaLM, and Meta Llama, which were individually instructed to accord rating scores to the eight major usability dimensions, namely, (1) content/course quality, (2) pedagogical design, (3) learner support, (4) technology infrastructure, (5) social interaction, (6) learner engagement, (7) instructor support, and (8) cost-effectiveness of 17 currently most popular mobile learning apps. For each of the three robots, the minimum, the maximum, the range, and the standard deviation of the rating scores for each of the eight dimensions were computed across all the mobile learning apps. The rating score difference for each of the eight dimensions between any pair of the above three robots was calculated for each app. The mean of the absolute value, the minimum, the maximum, the range, and the standard deviation of the differences for each dimensions between each pair of robots were calculated across all the apps. A paired sample t-test was then applied to each dimension for the rating score difference between each robot pair over all the apps. Finally, Cronbach's coefficient alpha of the rating scores was computed for each of the eight dimensions between all the three robots across all the apps. The computational results were to reveal whether the three robots awarded discrimination in evaluating each dimension across the apps, whether each robot, with respect to any other robot, erratically and/or systematically overrate or underrate any dimension over the apps, and whether there was high convergent validity of (and thus consistency between) the three robots in evaluating each dimension across the apps. Among other auxiliary results, it was revealed that the convergent validity of (and the consistency between) the three robots was marginally acceptable only in evaluating mobile learning apps' dimension of (1) content/course quality but not at all in the dimensions (2) pedagogical design, (3) learner support, (4) technology infrastructure, (5) social interaction, (6) learner engagement, (7) instructor support, and (8) cost-effectiveness. [For the full proceedings, see ED659933.]</t>
+          <t>This article intends to investigate the consistency between a few popular generative AI robots in the evaluation of massive open online course (MOOC) platforms. The four robots experimented with in the study were Claude+, GPT-4, Sage, and Dragonfly, which were tasked with awarding rating scores to the eight major dimensions, namely (1) content/course quality, (2) pedagogical design, (3) learner support, (4) technology infrastructure, (5) social interaction, (6) learner engagement, (7) instructor support, and (8) cost-effectiveness, of the 31 currently very popular MOOC platforms. Only Claude+'s and Dragonfly's rating scores turned out to be amenable to statistical analysis. For each of the two robots, the minimum, the maximum, the range, and the standard deviation of the rating scores for each of the eight dimensions were computed across all the 31 MOOC platforms. The rating score difference for each of the eight dimensions between the two robots was calculated for each platform. The mean of the absolute value, the minimum, the maximum, the range, and the standard deviation of the differences for each dimension between the two robots were calculated across all platforms. A paired sample t-test was then applied to each dimension for the rating score difference between the two robots over all the platforms. Finally, a correlation coefficient of the rating scores was computed for each of the eight dimensions between the two robots across all the MOOC platforms. The computational results were to reveal whether the two robots awarded discrimination in evaluating each dimension across the platforms, whether any of the two robots systematically underrated or overrated any dimension with respect to the other robot, and whether there was consistency between the two robots in evaluating each dimension across the platforms. It was found that discrimination was prominent in the evaluation of all dimensions save Dragonfly's rating of the dimensions learner support, technology infrastructure, and instructor support, Claude+ systematically underrated all dimensions (p &amp;lt; 0.000 &amp;lt; 0.05) compared with Dragonfly except for the dimension cost-effectiveness, which Claude+ systematically overrated (p = 0.003 &amp;lt; 0.05), and the evaluation by the two robots was consistent only for the dimensions content/course quality, pedagogical design, and learner engagement with the correlation coefficients ranging from 0.445 to 0.632 (p from 0.000 to 0.012 &amp;lt; 0.05). Consistency implies at least the partial trustworthiness of the evaluation of these MOOC platforms by either of these two popular generative AI robots based on the analogous concept of convergent validity for an operationalized instrument to measure an abstract construct. [For the full proceedings, see ED636095.]</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>b8a9ff54254ee8ef</t>
+          <t>192252b29da5b302</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>The Impact of Falsely Detecting AI-Generated Text on Academic Assessment</t>
+          <t>Fostering Problem Solving and Critical Thinking in Mathematics through Generative Artificial Intelligence</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Arifi N. Waked; Hanadi Abdelsalem; Muhammad Waqar Ashraf; Maura Pilotti; Khadija El Alaoui</t>
+          <t>Barana, A.; Marchisio, M.; Roman, F.</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>2024</v>
+        <v>2023</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -4488,7 +4426,7 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>International Society for Technology, Education, and Science. 944 Maysey Drive, San Antonio, TX 78227. Tel: 515-294-1075; Fax: 515-294-1003; email: istesoffice@gmail.com; Web site: http://www.istes.org</t>
+          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4512,11 +4450,11 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q50" t="inlineStr">
         <is>
-          <t>2024/b8a9ff54254ee8ef.pdf</t>
+          <t>2023/192252b29da5b302.pdf</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4526,24 +4464,24 @@
       </c>
       <c r="S50" s="2" t="inlineStr">
         <is>
-          <t>Large Language Model (LLM) Functionalities, such as Chat Generative Pre-Trained Transformer (ChatGPT), are a form of artificial intelligence (AI) that have the ability to produce human-like writing in response to a wide array of input. As this technology has become a staple of everyday life, many educators find themselves rapidly redefining best assessment practices regarding this new area of potential plagiarism. As it becomes increasingly difficult to discern between well-written assignments produced by students and those that have been generated by AI, educators may turn to AI-detection programs to determine whether work submitted by students is in fact their own. However, these programs notoriously return a high rate of false detection of AI-generated text. This phenomenon leads to the increased likelihood that students will be unfairly academically penalized. In this study, hand-written examinations for a university-level introductory academic writing class were submitted to different AI-detection programs. Results indicate an association between higher exam grades and greater false detection of AI-generated writing. These results suggest that educators must carefully consider the benefits of such programs when assessing students' work. [For the complete proceedings, see ED672804.]</t>
+          <t>The spread of Artificial Intelligence (AI) has been recently generating worries among teachers and educators about the validity of assessment when students make use of AI tools to solve tasks. To tackle this issue, we propose mathematical problem solving activities to be carried out with the aid of ChatGPT, showing how problem solving and critical thinking continue to be pivotal in solving mathematical problems, even if this is performed with the aid of AI. After discussing theoretical frameworks on strategies of problem solving and phases of the critical thinking process, we present six problems of combinatorics that we submitted to ChatGPT. We also asked 40 university students to solve the six problems in group with the aid of ChatGPT during an international module on Problem Solving and Critical Thinking and collected the tutors' observations about the activities. Analyzing ChatGPT solutions and tutors' reflections, we show that the proposed activity requires problem solving and critical thinking to be accomplished. The results corroborate the idea that, instead of limiting the use of AI in education, it is possible to integrate it within learning and assessment to achieve the learning goals. [For the full proceedings, see ED636095.]</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>85ea8f1340dce200</t>
+          <t>ae87b25ad2e4631c</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Anchoring Concepts Influence Essay Conceptual Structure and Test Performance</t>
+          <t>Future of Learning and Education</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Roy B. Clariana; Ryan Solnosky</t>
+          <t>Varghese, S.</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -4556,7 +4494,22 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
+          <t>Future of business and finance</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Springer International Publishing</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>book-chapter</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-031-36382-5_16</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4566,7 +4519,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
@@ -4579,39 +4532,47 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="O51" t="n">
+        <v>1</v>
+      </c>
       <c r="P51" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q51" t="inlineStr">
         <is>
-          <t>2023/85ea8f1340dce200.pdf</t>
+          <t>2023/ae87b25ad2e4631c.pdf</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
         <is>
-          <t>eric</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="S51" s="2" t="inlineStr">
         <is>
-          <t>This quasi-experimental study seeks to improve the conceptual quality of summary essays by comparing two conditions, essay prompts with or without a list of 13 broad concepts, the concepts were selected across a continuum of the 100 most frequent words in the lesson materials. It is anticipated that only the most central concepts will be used as &amp;quot;anchors&amp;quot; when writing. Participants (n = 90) in an Architectural Engineering undergraduate course read the assigned lesson textbook chapter and attended lectures and labs, then in a final lab session were asked to write a 300-word summary of the lesson content. Data consists of the essays converted to networks and the end-of-unit multiple choice test. Compared to the expert network benchmark, the essay networks of those receiving the broad concepts in the writing prompt were not significantly different from those who did not receive these concepts. However those receiving the broad concepts were significantly more like peer essay networks (mental model convergence) and like the networks of the two PowerPoint lectures but neither were like the textbook chapter. Further, those receiving the broad concepts performed significantly better on the end-of-unit test than those not receiving the concepts. Term frequency analysis of the essays indicates as expected that the most network-central concepts had a greater frequency in essays, the other terms frequencies were remarkably the same for both the terms and no terms groups, suggesting a similar underlying conceptual mental model of this lesson content. To further explore the influence of anchoring concepts in summary writing prompts, essays were generated with the same two summary writing prompts using OpenAI (ChatGPT) and Google Bard, plus a new prompt that used the 13 most central concepts from the expert's network. The quality of the essay networks for both AI systems were equivalent to the students' essay networks for the broad concepts and for the no concept treatments. However, the AI essays derived with the 13 most central concepts were significantly better (more like the expert network) than the students and AI essays derived with broad concepts or no concepts treatments. In addition, Bard and OpenAI used several of the same concepts at a higher frequency than the students suggesting that the two AI systems have more similar knowledge graphs of this content. In sum, adding 13 broad conceptual terms to a summary writing prompt improved both structural and declarative knowledge outcomes, but adding 13 most central concepts may be even better. More research is needed to understand how including concepts and other terms in a writing prompt influences students' essay conceptual structure and subsequent test performance. [For the full proceedings, see ED636095.]</t>
+          <t>Abstract According to “A Scorecard for Humanity,” a report from the Copenhagen Consensus Center, our world gains every time an individual is educated, and our world pays a price when people go illiterate. In the future, those regions and nations of the world that manage to educate its people would gain, whereas those that do not pay much attention to this crucial aspect would continue to suffer losses, hidden in plain sight. Hence, by 2050, we suggest that though the world would have made tremendous progress in basic education, illiteracy would persist with almost 500 million uneducated in the world. Illiteracy shall be most concentrated in the regions of Africa and South Asia, whereas most other nations would move toward a total eradication. However, there would also be a systemic change in the higher education sector across the globe, as the age cohort of 18 to 24 years in Europe would shrink, but in South Asia and Africa, this would continue to grow. There would also be a disruption of the current pedagogic and regimental learning systems toward flatter, flexible, and open systems based on research in learning sciences. Technology would also come by to play a larger role, where education would be driven by artificial intelligence (AI) and big data—resulting in complete personalization of curriculum and methodology focusing on each individual's minute needs.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>b142a08020007c56</t>
+          <t>c1cdc5cf92b29adf</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Education to Prevent Human Mechanisation in a Faculty of Informatics: Developing Learning Materials to Improve Students&amp;apos; Verbal Communication Skills</t>
+          <t>Generating Multiple Choice Questions from a Textbook: LLMs Match Human Performance on Most Metrics</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Mari Ueda; Isoharu Nishiguchi; Hiroshi Tanaka; Kazunori Matsumoto; Tetsuo Tanaka</t>
+          <t>Andrew M. Olney</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -4622,11 +4583,6 @@
           <t>post_chatgpt</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
-        </is>
-      </c>
       <c r="J52" t="inlineStr">
         <is>
           <t>en</t>
@@ -4648,11 +4604,11 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q52" t="inlineStr">
         <is>
-          <t>2023/b142a08020007c56.pdf</t>
+          <t>2023/c1cdc5cf92b29adf.pdf</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4662,24 +4618,24 @@
       </c>
       <c r="S52" s="2" t="inlineStr">
         <is>
-          <t>Although information technology (ICT) education is being strengthened based on the national context, there are reports suggesting a decline in young people's communication skills. This phenomenon can be attributed to the rapid development of informatisation, which includes the diversification and spread of information tools, as well as the prevalence of nonverbal communication, such as pictograms in social networking services. In addition, the COVID-19 pandemic has drastically reduced face-to-face communication opportunities, making interactive communication in on-demand classes challenging. Even in assignments and short tests completed during class, many instances of content being copied and pasted from the web or written in a disorganized manner have been observed. For instance, students entering ICT-related careers, particularly those graduating from the faculty of informatics, must possess the ability to communicate with engineers and clients while implementing ICT advancements. Alongside programming skills, strong communication abilities are essential. Moreover, the emergence of generative artificial intelligence (AI) tools, such as ChatGPT and Bing AI, has considerably diminished the opportunities for independent thinking. In the current era of enhanced ICT education, AI, and IoT, the Faculty of Informatics at the Kanagawa Institute of Technology has been engaged in discussions regarding learning materials that aim to strengthen students' ability to think and communicate in their own words, preventing the mechanisation of individuals. This paper presents the development and implementation of learning materials designed to enhance students' verbal communication skills through the description and re-production of mathematical graphs. [For the full proceedings, see ED636095.]</t>
+          <t>Multiple choice questions are traditionally expensive to produce. Recent advances in large language models (LLMs) have led to fine-tuned LLMs that generate questions competitive with human-authored questions. However, the relative capabilities of ChatGPT-family models have not yet been established for this task. We present a carefully-controlled human evaluation of three conditions: a fine-tuned, augmented version of Macaw, instruction-tuned Bing Chat with zero-shot prompting, and human-authored questions from a college science textbook. Our results indicate that on six of seven measures tested, both LLM's performance was not significantly different from human performance. Analysis of LLM errors further suggests that Macaw and Bing Chat have different failure modes for this task: Macaw tends to repeat answer options whereas Bing Chat tends to not include the specified answer in the answer options. For Macaw, removing error items from analysis results in performance on par with humans for all metrics; for Bing Chat, removing error items improves performance but does not reach human-level performance. [This paper was published in the &amp;quot;CEUR Workshop Proceedings,&amp;quot; 2023.]</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>aa42fa1562d18625</t>
+          <t>bf419dfa66e76b7f</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Evaluating Popular MOOC Platforms by Generative Artificial Intelligence (AI) Robots: How Consistent Are the Robots?</t>
+          <t>How to Deal with AI-Powered Writing Tools in Academic Writing: A Stakeholder Analysis</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Victor K. Y. Chan</t>
+          <t>Michael Burkhard</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -4716,11 +4672,11 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="Q53" t="inlineStr">
         <is>
-          <t>2023/aa42fa1562d18625.pdf</t>
+          <t>2023/bf419dfa66e76b7f.pdf</t>
         </is>
       </c>
       <c r="R53" t="inlineStr">
@@ -4730,24 +4686,24 @@
       </c>
       <c r="S53" s="2" t="inlineStr">
         <is>
-          <t>This article intends to investigate the consistency between a few popular generative AI robots in the evaluation of massive open online course (MOOC) platforms. The four robots experimented with in the study were Claude+, GPT-4, Sage, and Dragonfly, which were tasked with awarding rating scores to the eight major dimensions, namely (1) content/course quality, (2) pedagogical design, (3) learner support, (4) technology infrastructure, (5) social interaction, (6) learner engagement, (7) instructor support, and (8) cost-effectiveness, of the 31 currently very popular MOOC platforms. Only Claude+'s and Dragonfly's rating scores turned out to be amenable to statistical analysis. For each of the two robots, the minimum, the maximum, the range, and the standard deviation of the rating scores for each of the eight dimensions were computed across all the 31 MOOC platforms. The rating score difference for each of the eight dimensions between the two robots was calculated for each platform. The mean of the absolute value, the minimum, the maximum, the range, and the standard deviation of the differences for each dimension between the two robots were calculated across all platforms. A paired sample t-test was then applied to each dimension for the rating score difference between the two robots over all the platforms. Finally, a correlation coefficient of the rating scores was computed for each of the eight dimensions between the two robots across all the MOOC platforms. The computational results were to reveal whether the two robots awarded discrimination in evaluating each dimension across the platforms, whether any of the two robots systematically underrated or overrated any dimension with respect to the other robot, and whether there was consistency between the two robots in evaluating each dimension across the platforms. It was found that discrimination was prominent in the evaluation of all dimensions save Dragonfly's rating of the dimensions learner support, technology infrastructure, and instructor support, Claude+ systematically underrated all dimensions (p &amp;lt; 0.000 &amp;lt; 0.05) compared with Dragonfly except for the dimension cost-effectiveness, which Claude+ systematically overrated (p = 0.003 &amp;lt; 0.05), and the evaluation by the two robots was consistent only for the dimensions content/course quality, pedagogical design, and learner engagement with the correlation coefficients ranging from 0.445 to 0.632 (p from 0.000 to 0.012 &amp;lt; 0.05). Consistency implies at least the partial trustworthiness of the evaluation of these MOOC platforms by either of these two popular generative AI robots based on the analogous concept of convergent validity for an operationalized instrument to measure an abstract construct. [For the full proceedings, see ED636095.]</t>
+          <t>Due to the advances of artificial intelligence (AI) and natural language processing, new AI-powered writing tools have emerged. They can be used by students among other things for text translation, to improve spelling or to generate new texts. In academic writing, AI-powered writing tools are posing challenges but also opportunities for teaching and learning. It is an open question in which way to sensibly deal with these tools. To address the issue, this paper investigates, what interests different stakeholders (students, lecturers, university administration) pursue in relation to AI-powered writing tools. Building on this, tensions between different stakeholders are identified and (teaching) strategies proposed to deal with these tensions. To discuss the findings in light of recent developments around ChatGPT, semi-structured expert interviews were conducted in April 2023 with five academic writing lecturers at the University of St. Gallen. The results suggest that as writing tools become more and more powerful, the need for strategies to ensure their reasonable and transparent use also increases. [For the full proceedings, see ED636095.]</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>192252b29da5b302</t>
+          <t>2ad51015436ad076</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Fostering Problem Solving and Critical Thinking in Mathematics through Generative Artificial Intelligence</t>
+          <t>Investigating the Role of ChatGPT in Supporting Text-Based Programming Education for Students and Teachers</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Barana, A.; Marchisio, M.; Roman, F.</t>
+          <t>Wieser, M.; Schöffmann, K.; Stefanics, D.; Bollin, A.; Pasterk, S.</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -4760,7 +4716,22 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
+          <t>Lecture notes in computer science</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Springer Science+Business Media</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>book-chapter</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-031-44900-0_4</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -4770,7 +4741,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4783,39 +4754,47 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="O54" t="n">
+        <v>21</v>
+      </c>
       <c r="P54" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q54" t="inlineStr">
         <is>
-          <t>2023/192252b29da5b302.pdf</t>
+          <t>2023/2ad51015436ad076.pdf</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
         <is>
-          <t>eric</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="S54" s="2" t="inlineStr">
         <is>
-          <t>The spread of Artificial Intelligence (AI) has been recently generating worries among teachers and educators about the validity of assessment when students make use of AI tools to solve tasks. To tackle this issue, we propose mathematical problem solving activities to be carried out with the aid of ChatGPT, showing how problem solving and critical thinking continue to be pivotal in solving mathematical problems, even if this is performed with the aid of AI. After discussing theoretical frameworks on strategies of problem solving and phases of the critical thinking process, we present six problems of combinatorics that we submitted to ChatGPT. We also asked 40 university students to solve the six problems in group with the aid of ChatGPT during an international module on Problem Solving and Critical Thinking and collected the tutors' observations about the activities. Analyzing ChatGPT solutions and tutors' reflections, we show that the proposed activity requires problem solving and critical thinking to be accomplished. The results corroborate the idea that, instead of limiting the use of AI in education, it is possible to integrate it within learning and assessment to achieve the learning goals. [For the full proceedings, see ED636095.]</t>
+          <t>Abstract Teaching text-based programming poses significant challenges in both school and university contexts. This study explores the potential of ChatGPT as a sustainable didactic tool to support students, freshmen, and teachers. By focusing on a beginner’s course with examples also relevant to vocational schools, we investigated three research questions. First, the extent to which ChatGPT assists students in solving and understanding initial examples; secondly, the feasibility of teachers utilizing the chatbot for grading student solutions; and finally, the additional support ChatGPT provides in terms of teaching. Our findings demonstrate that ChatGPT offers valuable guidance for teachers in terms of assessment and grading and aids students in understanding and optimizing their solutions.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ae87b25ad2e4631c</t>
+          <t>135634b3c7c31d5d</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Future of Learning and Education</t>
+          <t>Judicial Decision-Making in the Age of Artificial Intelligence</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Varghese, S.</t>
+          <t>Gravett, W.</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -4828,7 +4807,7 @@
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Future of business and finance</t>
+          <t>Law, governance and technology series</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -4843,7 +4822,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-36382-5_16</t>
+          <t>10.1007/978-3-031-41264-6_15</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4872,14 +4851,14 @@
         </is>
       </c>
       <c r="O55" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="P55" t="n">
         <v>2</v>
       </c>
       <c r="Q55" t="inlineStr">
         <is>
-          <t>2023/ae87b25ad2e4631c.pdf</t>
+          <t>2023/135634b3c7c31d5d.pdf</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -4889,24 +4868,24 @@
       </c>
       <c r="S55" s="2" t="inlineStr">
         <is>
-          <t>Abstract According to “A Scorecard for Humanity,” a report from the Copenhagen Consensus Center, our world gains every time an individual is educated, and our world pays a price when people go illiterate. In the future, those regions and nations of the world that manage to educate its people would gain, whereas those that do not pay much attention to this crucial aspect would continue to suffer losses, hidden in plain sight. Hence, by 2050, we suggest that though the world would have made tremendous progress in basic education, illiteracy would persist with almost 500 million uneducated in the world. Illiteracy shall be most concentrated in the regions of Africa and South Asia, whereas most other nations would move toward a total eradication. However, there would also be a systemic change in the higher education sector across the globe, as the age cohort of 18 to 24 years in Europe would shrink, but in South Asia and Africa, this would continue to grow. There would also be a disruption of the current pedagogic and regimental learning systems toward flatter, flexible, and open systems based on research in learning sciences. Technology would also come by to play a larger role, where education would be driven by artificial intelligence (AI) and big data—resulting in complete personalization of curriculum and methodology focusing on each individual's minute needs.</t>
+          <t>Abstract Artificial intelligence (AI) has become a pervasive presence in almost every aspect of society and business: from assigning credit scores to people, to identifying the best candidates for an employment position, to ranking applicants for admission to university. One of the most striking innovations in the United States criminal justice system in the last three decades has been the introduction of risk-assessment software, powered by sophisticated algorithms, to predict whether individual offenders are likely to re-offend. The focus of this contribution is on the use of these risk-assessment tools in criminal sentencing. Apart from the broader social, ethical and legal considerations, to date, not much is known about how perceptions of technology influence cognition in decision-making, particularly in the legal context. What research does demonstrate is that humans are inclined to trust algorithms as objective, and, as such, as unobjectionable. This contribution examines two phenomena in this regard: (i) the “technology effect”—the human tendency towards excessive optimism when making decisions involving technology; and (ii) “automation bias”—the phenomenon whereby judges accept the recommendations of an automated decision-making system, and cease searching for confirmatory evidence, perhaps even transferring responsibility for decision-making onto the machine.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>c1cdc5cf92b29adf</t>
+          <t>7947ac0d82ac46e9</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Generating Multiple Choice Questions from a Textbook: LLMs Match Human Performance on Most Metrics</t>
+          <t>Metabolism in Crisis? A New Interplay Between Physiology and Ecology</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Andrew M. Olney</t>
+          <t>Bognon-Küss, C.</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -4917,6 +4896,26 @@
           <t>post_chatgpt</t>
         </is>
       </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>History, philosophy and theory of the life sciences</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Springer Nature (Netherlands)</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>book-chapter</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-031-12604-8_11</t>
+        </is>
+      </c>
       <c r="J56" t="inlineStr">
         <is>
           <t>en</t>
@@ -4924,7 +4923,7 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4937,39 +4936,47 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="N56" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="O56" t="n">
+        <v>2</v>
+      </c>
       <c r="P56" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q56" t="inlineStr">
         <is>
-          <t>2023/c1cdc5cf92b29adf.pdf</t>
+          <t>2023/7947ac0d82ac46e9.pdf</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
         <is>
-          <t>eric</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="S56" s="2" t="inlineStr">
         <is>
-          <t>Multiple choice questions are traditionally expensive to produce. Recent advances in large language models (LLMs) have led to fine-tuned LLMs that generate questions competitive with human-authored questions. However, the relative capabilities of ChatGPT-family models have not yet been established for this task. We present a carefully-controlled human evaluation of three conditions: a fine-tuned, augmented version of Macaw, instruction-tuned Bing Chat with zero-shot prompting, and human-authored questions from a college science textbook. Our results indicate that on six of seven measures tested, both LLM's performance was not significantly different from human performance. Analysis of LLM errors further suggests that Macaw and Bing Chat have different failure modes for this task: Macaw tends to repeat answer options whereas Bing Chat tends to not include the specified answer in the answer options. For Macaw, removing error items from analysis results in performance on par with humans for all metrics; for Bing Chat, removing error items improves performance but does not reach human-level performance. [This paper was published in the &amp;quot;CEUR Workshop Proceedings,&amp;quot; 2023.]</t>
+          <t>Abstract This chapter investigates the hybrid relationships between metabolism, broadly and a-historically understood as the set of processes through which alien matter is made homogeneous to that of the organism, and forms of vitalism from the eighteenth century on. While metabolic processes have long been modeled in a reductionist fashion as a straightforward function of repair and expansion of a given structure (either chemically, or mechanistically), a challenging vitalist view has characterized metabolism as a creative, organizing, vital faculty. I suggest that this tension was overcome in Claude Bernard’s works on “indirect nutrition”, in which nutrition, rightly conceived as a general vital phenomenon common to plants and animals, was both characterized as an instance of the general physico-chemical determinism of all phenomena and as the sign and condition of the “freedom and independence” of the organism with respect to the environment. I propose that Bernard’s theory of indirect nutrition was central in the elaboration of his general physiology and has, at the same time, underpinned a self-centered view of biological identity in which the organism creates itself continuously at the detriment of its external milieu . I further argue that this conception of biological individuality as metabolically constructed has since, and paradoxically, supported a view in which the organism appears as an autonomous and self-creating entity. I then contrast this classical view of the metabolic autonomy of the organism with the challenges raised by microbiome studies and suggest that these emerging fields contribute to sketch an ecological conception of the organism and its metabolism through the reconceptualization of its relationship with the environment. The recent focus on a “microbiota – host metabolism” axis contributes to shift the focus away from the classical concept of organism, somehow externalizing vitalism out of the autonomous individual in favor of an ecological, collaborative, and interactionist view of the living.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>bf419dfa66e76b7f</t>
+          <t>3827a11b5b949e39</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>How to Deal with AI-Powered Writing Tools in Academic Writing: A Stakeholder Analysis</t>
+          <t>Rebuilding After War and Genocide: Learning with and from Refugees in the Transnational Digital Classroom</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Michael Burkhard</t>
+          <t>Brill-Carlat, M.; Höhn, M.</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -4982,7 +4989,22 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
+          <t>Political pedagogies</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Springer International Publishing</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>book-chapter</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-031-12350-4_22</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4992,7 +5014,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -5004,40 +5026,48 @@
         <is>
           <t>Yes</t>
         </is>
+      </c>
+      <c r="N57" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="O57" t="n">
+        <v>0</v>
       </c>
       <c r="P57" t="n">
         <v>3</v>
       </c>
       <c r="Q57" t="inlineStr">
         <is>
-          <t>2023/bf419dfa66e76b7f.pdf</t>
+          <t>2023/3827a11b5b949e39.pdf</t>
         </is>
       </c>
       <c r="R57" t="inlineStr">
         <is>
-          <t>eric</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="S57" s="2" t="inlineStr">
         <is>
-          <t>Due to the advances of artificial intelligence (AI) and natural language processing, new AI-powered writing tools have emerged. They can be used by students among other things for text translation, to improve spelling or to generate new texts. In academic writing, AI-powered writing tools are posing challenges but also opportunities for teaching and learning. It is an open question in which way to sensibly deal with these tools. To address the issue, this paper investigates, what interests different stakeholders (students, lecturers, university administration) pursue in relation to AI-powered writing tools. Building on this, tensions between different stakeholders are identified and (teaching) strategies proposed to deal with these tensions. To discuss the findings in light of recent developments around ChatGPT, semi-structured expert interviews were conducted in April 2023 with five academic writing lecturers at the University of St. Gallen. The results suggest that as writing tools become more and more powerful, the need for strategies to ensure their reasonable and transparent use also increases. [For the full proceedings, see ED636095.]</t>
+          <t>Abstract The Covid-19 emergency spurred a flurry of teaching innovations as higher education institutions turned to online or blended learning models, and as international collaborations have moved nearly entirely online. These circumstances inspired us to revisit the digital transatlantic seminar, “Germany 1945: History and Memory in Germany after WWII,” taught by Höhn in Spring 2018 to a group of seven Vassar students (Brill-Carlat among them) and six advanced high-school students—between the ages of 17 and 22—who had come to Berlin as asylum seekers from Syria, Iraq, and Afghanistan. The course dealt with history and memory of World War II and the Holocaust in Germany. As such, it reflected a core commitment of the Consortium on Forced Migration, Displacement, and Education (CFMDE), founded by Höhn at Vassar and partners (Bard, Bennington, Sarah Lawrence, the New School, and the Council for European Studies): the importance of providing opportunities for our undergraduate students to learn with and from refugees and displaced individuals if they are to understand and tackle the global, multidimensional challenges of forced migration. As institutional resistance to digital teaching necessarily vanished with the Covid-19 pandemic in Spring 2020 and the direction of future online-learning policies is up for debate, we revisit the 2018 class to examine lessons learned and how this project points the way to another digital venture: digitally “hosting” displaced scholars at liberal arts campuses.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2ad51015436ad076</t>
+          <t>c81bf633e42c7f19</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Investigating the Role of ChatGPT in Supporting Text-Based Programming Education for Students and Teachers</t>
+          <t>Survey of AI Tool Usage in Programming Course: Early Observations</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Wieser, M.; Schöffmann, K.; Stefanics, D.; Bollin, A.; Pasterk, S.</t>
+          <t>Saari, M.; Rantanen, P.; Nurminen, M.; Kilamo, T.; Systä, K.; Abrahamsson, P.</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -5050,7 +5080,7 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lecture notes in computer science</t>
+          <t>Lecture notes in business information processing</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5065,7 +5095,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-44900-0_4</t>
+          <t>10.1007/978-3-031-48550-3_18</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5094,14 +5124,14 @@
         </is>
       </c>
       <c r="O58" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="P58" t="n">
         <v>2</v>
       </c>
       <c r="Q58" t="inlineStr">
         <is>
-          <t>2023/2ad51015436ad076.pdf</t>
+          <t>2023/c81bf633e42c7f19.pdf</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -5111,24 +5141,24 @@
       </c>
       <c r="S58" s="2" t="inlineStr">
         <is>
-          <t>Abstract Teaching text-based programming poses significant challenges in both school and university contexts. This study explores the potential of ChatGPT as a sustainable didactic tool to support students, freshmen, and teachers. By focusing on a beginner’s course with examples also relevant to vocational schools, we investigated three research questions. First, the extent to which ChatGPT assists students in solving and understanding initial examples; secondly, the feasibility of teachers utilizing the chatbot for grading student solutions; and finally, the additional support ChatGPT provides in terms of teaching. Our findings demonstrate that ChatGPT offers valuable guidance for teachers in terms of assessment and grading and aids students in understanding and optimizing their solutions.</t>
+          <t>Abstract This study explores the role of artificial intelligence (AI) in university teaching, with a focus on the teaching of programming. Despite the growing use of AI in education, both students and teachers often struggle to understand its role and implications. To address this gap, we conducted a survey of a wide group of students (n = 200) to assess their experiences and perspectives on the use of AI in programming education. The survey results suggest that AI is becoming increasingly involved in university teaching, particularly in the teaching of programming. However, students require guidance from teachers in order to use AI tools effectively in their studies. The study concludes that the goal of teaching programming should be to guide students in the responsible use of AI. Overall, the study highlights the need for greater awareness and understanding of AI in university teaching and the fact that teachers have an important role to play in providing guidance to students on the responsible use of AI tools.</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>135634b3c7c31d5d</t>
+          <t>96a698008602b3d7</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Judicial Decision-Making in the Age of Artificial Intelligence</t>
+          <t>The Role of Educational Interventions in Facing Social Media Threats: Overarching Principles of the COURAGE Project</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Gravett, W.</t>
+          <t>Taibi, D.; Börsting, J.; Hoppe, U.; Ognibene, D.; Hernández-Leo, D.; Eimler, S.; Kruschwitz, U.</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -5141,12 +5171,12 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Law, governance and technology series</t>
+          <t>Communications in computer and information science</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Springer International Publishing</t>
+          <t>Springer Science+Business Media</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
@@ -5156,7 +5186,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-41264-6_15</t>
+          <t>10.1007/978-3-031-29800-4_25</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5185,14 +5215,14 @@
         </is>
       </c>
       <c r="O59" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="P59" t="n">
         <v>2</v>
       </c>
       <c r="Q59" t="inlineStr">
         <is>
-          <t>2023/135634b3c7c31d5d.pdf</t>
+          <t>2023/96a698008602b3d7.pdf</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5202,24 +5232,24 @@
       </c>
       <c r="S59" s="2" t="inlineStr">
         <is>
-          <t>Abstract Artificial intelligence (AI) has become a pervasive presence in almost every aspect of society and business: from assigning credit scores to people, to identifying the best candidates for an employment position, to ranking applicants for admission to university. One of the most striking innovations in the United States criminal justice system in the last three decades has been the introduction of risk-assessment software, powered by sophisticated algorithms, to predict whether individual offenders are likely to re-offend. The focus of this contribution is on the use of these risk-assessment tools in criminal sentencing. Apart from the broader social, ethical and legal considerations, to date, not much is known about how perceptions of technology influence cognition in decision-making, particularly in the legal context. What research does demonstrate is that humans are inclined to trust algorithms as objective, and, as such, as unobjectionable. This contribution examines two phenomena in this regard: (i) the “technology effect”—the human tendency towards excessive optimism when making decisions involving technology; and (ii) “automation bias”—the phenomenon whereby judges accept the recommendations of an automated decision-making system, and cease searching for confirmatory evidence, perhaps even transferring responsibility for decision-making onto the machine.</t>
+          <t>Abstract Social media are offering new opportunities for communication and interaction way beyond what was possible only a few years ago. However, social media are also virtual spaces where young people are exposed to a variety of threats. Digital addiction, discrimination, hate speech, misinformation, polarization as well as manipulative influences of algorithms, body stereotyping, and cyberbullying are examples of challenges that find fertile ground on social media. Educators and students are not adequately prepared to face these challenges. To this aim, the COURAGE project, presented in this paper, introduces new tools and learning methodologies that can be adopted within higher education learning paths to train educators to deal with social media threats. The overarching principles of the COURAGE project leverage the most recent advances in the fields of artificial intelligence and in the educational domain paired with social and media psychological insights to support the development of the COURAGE ecosystem. The results of the experiments currently implemented with teachers and students of secondary schools as well as the impact of the COURAGE project on societal changes and ethical questions are presented and discussed.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>7947ac0d82ac46e9</t>
+          <t>8f81d56c326a06d3</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Metabolism in Crisis? A New Interplay Between Physiology and Ecology</t>
+          <t>Transformer Language Model-Based Mobile Learning Solution for Higher Education</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Bognon-Küss, C.</t>
+          <t>Silvia García-Méndez; Francisco de Arriba-Pérez; Francisco J. González-Castaño</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -5232,22 +5262,7 @@
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>History, philosophy and theory of the life sciences</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Springer Nature (Netherlands)</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>book-chapter</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-031-12604-8_11</t>
+          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -5257,7 +5272,7 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -5269,66 +5284,58 @@
         <is>
           <t>Yes</t>
         </is>
-      </c>
-      <c r="N60" t="inlineStr">
-        <is>
-          <t>hybrid</t>
-        </is>
-      </c>
-      <c r="O60" t="n">
-        <v>2</v>
       </c>
       <c r="P60" t="n">
         <v>2</v>
       </c>
       <c r="Q60" t="inlineStr">
         <is>
-          <t>2023/7947ac0d82ac46e9.pdf</t>
+          <t>2023/8f81d56c326a06d3.pdf</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>eric</t>
         </is>
       </c>
       <c r="S60" s="2" t="inlineStr">
         <is>
-          <t>Abstract This chapter investigates the hybrid relationships between metabolism, broadly and a-historically understood as the set of processes through which alien matter is made homogeneous to that of the organism, and forms of vitalism from the eighteenth century on. While metabolic processes have long been modeled in a reductionist fashion as a straightforward function of repair and expansion of a given structure (either chemically, or mechanistically), a challenging vitalist view has characterized metabolism as a creative, organizing, vital faculty. I suggest that this tension was overcome in Claude Bernard’s works on “indirect nutrition”, in which nutrition, rightly conceived as a general vital phenomenon common to plants and animals, was both characterized as an instance of the general physico-chemical determinism of all phenomena and as the sign and condition of the “freedom and independence” of the organism with respect to the environment. I propose that Bernard’s theory of indirect nutrition was central in the elaboration of his general physiology and has, at the same time, underpinned a self-centered view of biological identity in which the organism creates itself continuously at the detriment of its external milieu . I further argue that this conception of biological individuality as metabolically constructed has since, and paradoxically, supported a view in which the organism appears as an autonomous and self-creating entity. I then contrast this classical view of the metabolic autonomy of the organism with the challenges raised by microbiome studies and suggest that these emerging fields contribute to sketch an ecological conception of the organism and its metabolism through the reconceptualization of its relationship with the environment. The recent focus on a “microbiota – host metabolism” axis contributes to shift the focus away from the classical concept of organism, somehow externalizing vitalism out of the autonomous individual in favor of an ecological, collaborative, and interactionist view of the living.</t>
+          <t>Mobile learning or mLearning has become an essential tool in many fields in this digital era, among the ones educational training deserves special attention, that is, applied to both basic and higher education towards active, flexible, effective high-quality and continuous learning. However, despite the advances in Natural Language Processing techniques, mLearning still does not take full advantage of the great potential of the latter techniques. It is the case of the transformer language models distributed in chatbot form. Accordingly, this work presents a mLearning application based on OpenAI GPT-3 model, which enables user-friendly interactions. The proposed system was tested in two evaluation scenarios, and the experimental results endorse its appropriateness toward learning experience enhancement. [For the full proceedings, see ED639391.]</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>3827a11b5b949e39</t>
+          <t>e3b815e1a83132e6</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Rebuilding After War and Genocide: Learning with and from Refugees in the Transnational Digital Classroom</t>
+          <t>About the Editor</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Brill-Carlat, M.; Höhn, M.</t>
+          <t>MBA, S.</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>post_chatgpt</t>
+          <t>pre_chatgpt</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Political pedagogies</t>
+          <t>Digital Health</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Springer International Publishing</t>
+          <t>SAGE Publishing</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
@@ -5338,7 +5345,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-12350-4_22</t>
+          <t>10.36255/exon-publications-digital-health.editor</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -5348,7 +5355,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5363,7 +5370,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>hybrid</t>
+          <t>gold</t>
         </is>
       </c>
       <c r="O61" t="n">
@@ -5374,7 +5381,7 @@
       </c>
       <c r="Q61" t="inlineStr">
         <is>
-          <t>2023/3827a11b5b949e39.pdf</t>
+          <t>2022/e3b815e1a83132e6.pdf</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5384,42 +5391,42 @@
       </c>
       <c r="S61" s="2" t="inlineStr">
         <is>
-          <t>Abstract The Covid-19 emergency spurred a flurry of teaching innovations as higher education institutions turned to online or blended learning models, and as international collaborations have moved nearly entirely online. These circumstances inspired us to revisit the digital transatlantic seminar, “Germany 1945: History and Memory in Germany after WWII,” taught by Höhn in Spring 2018 to a group of seven Vassar students (Brill-Carlat among them) and six advanced high-school students—between the ages of 17 and 22—who had come to Berlin as asylum seekers from Syria, Iraq, and Afghanistan. The course dealt with history and memory of World War II and the Holocaust in Germany. As such, it reflected a core commitment of the Consortium on Forced Migration, Displacement, and Education (CFMDE), founded by Höhn at Vassar and partners (Bard, Bennington, Sarah Lawrence, the New School, and the Council for European Studies): the importance of providing opportunities for our undergraduate students to learn with and from refugees and displaced individuals if they are to understand and tackle the global, multidimensional challenges of forced migration. As institutional resistance to digital teaching necessarily vanished with the Covid-19 pandemic in Spring 2020 and the direction of future online-learning policies is up for debate, we revisit the 2018 class to examine lessons learned and how this project points the way to another digital venture: digitally “hosting” displaced scholars at liberal arts campuses.</t>
+          <t>Professor Simon Lin Linwood, MD, MBA, is the Chief Medical Information Officer at the UCR Health and UCR School of Medicine, Riverside, CA, USA. He obtained his executive education in Artificial Intelligence Strategy and Implementation from Harvard University. He was named Innovator of the Year by CHIME in 2018. He is a national thought leader on digital transformation and acknowledged for providing vision and leadership in information technology to drive business growth in large, complex, and highly distributed environments. He has supervised and mentored many PhD students on data-driven innovation in healthcare, such as deep learning for risk prediction in population health to control costs, and methods to reduce physician documentation burden. He received Mentor of the Year Award in 2016. His areas of expertise include digital transformation, data-driven innovation, data science, data lake, artificial intelligence, and natural language processing, among others. He has extensively published on digital health, artificial intelligence/machine learning, data science, clinical informatics, genome informatics.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>c81bf633e42c7f19</t>
+          <t>246ac766bd6d1c42</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Survey of AI Tool Usage in Programming Course: Early Observations</t>
+          <t>List of Contributors</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Saari, M.; Rantanen, P.; Nurminen, M.; Kilamo, T.; Systä, K.; Abrahamsson, P.</t>
+          <t>Contributors, L.</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>2023</v>
+        <v>2022</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>post_chatgpt</t>
+          <t>pre_chatgpt</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lecture notes in business information processing</t>
+          <t>Digital Health</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Springer Science+Business Media</t>
+          <t>SAGE Publishing</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -5429,7 +5436,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-48550-3_18</t>
+          <t>10.36255/exon-publications-digital-health.contributors</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -5439,7 +5446,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -5454,18 +5461,18 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>hybrid</t>
+          <t>gold</t>
         </is>
       </c>
       <c r="O62" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="P62" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q62" t="inlineStr">
         <is>
-          <t>2023/c81bf633e42c7f19.pdf</t>
+          <t>2022/246ac766bd6d1c42.pdf</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -5475,42 +5482,42 @@
       </c>
       <c r="S62" s="2" t="inlineStr">
         <is>
-          <t>Abstract This study explores the role of artificial intelligence (AI) in university teaching, with a focus on the teaching of programming. Despite the growing use of AI in education, both students and teachers often struggle to understand its role and implications. To address this gap, we conducted a survey of a wide group of students (n = 200) to assess their experiences and perspectives on the use of AI in programming education. The survey results suggest that AI is becoming increasingly involved in university teaching, particularly in the teaching of programming. However, students require guidance from teachers in order to use AI tools effectively in their studies. The study concludes that the goal of teaching programming should be to guide students in the responsible use of AI. Overall, the study highlights the need for greater awareness and understanding of AI in university teaching and the fact that teachers have an important role to play in providing guidance to students on the responsible use of AI tools.</t>
+          <t>ABRAR-AHMAD ZULFIQAR, MDService de Médecine Interne, Diabète et Maladies métaboliques de la Clinique Médicale B, Hôpitaux Universitaires de Strasbourg et Equipe EA 3072 “Mitochondrie, Stress oxydant et Protection musculaire”, Faculté de Médecine-Université de Strasbourg, Strasbourg, France AIKO OSAWA, MD, PHDNational Center for Geriatrics and Gerontology, Aichi, Japan AMIR HAJJAM, PHDLaboratoire IRTES-SeT, Université de Technologie de Belfort-Montbéliard (UTBM), Belfort-Montbéliard, Belfort, France BRYONY MCGARRY, PHDPRECISE4Q, Predictive Modelling in Stroke, Technological University Dublin, Dublin, Ireland CEES TH. SMIT SIBINGA, MD, PHD, FRCP, FRCPATHIQM Consulting and University of Groningen, De Gast 46, 9801AE Zuidhorn, The Netherlands CLÁUDIA S. SOUSA, MDPulmonology Department, Central Hospital of Funchal, Portugal EMMANUEL ANDRÈS, MD, PHDLaboratoire IRTES-SeT, Université de Technologie de Belfort-Montbéliard (UTBM), Belfort-Montbéliard, Belfort, France EN-JU LIN, PHD, MPHResearch Information Solutions and Innovation, The Research Institute at Nationwide Children’s Hospital, Columbus, OH, USA ESRA ZIHNI, MSCPRECISE4Q, Predictive Modelling in Stroke, Technological University Dublin, Dublin, Ireland HIDENORI ARAI, MD, PHDNational Center for Geriatrics and Gerontology, Aichi, Japan IRVING D. KAPLAN, MDDepartment of Radiation Oncology, Beth Israel Deaconess Medical Center, Boston, MA, USA JENAY YUEN, BSKeck School of Medicine, University of Southern California, California, USA JESSAMINE P. WINER-JONES, PHDTriNetX, LLC, Cambridge, MA, USA JOHN KELLEHER, PHDPRECISE4Q, Predictive Modelling in Stroke, Technological University Dublin, Dublin, Ireland KATHARINE LAWRENCE, MD MPHNYU Grossman School of Medicine, Department of Population Health; NY, USA LIMOR APPELBAUM, MDDepartment of Radiation Oncology, Beth Israel Deaconess Medical Center, Boston, MA, USA MADELEINE SCHROEDER, MSResearch Information Solutions and Innovation, The Research Institute at Nationwide Children’s Hospital, Columbus, OH, USA MÁRIO MORAIS-ALMEIDA, MDAllergy Centre, CUF Descobertas Hospital, Lisboa, Portugal MARTIN RINARD, PHDComputer Science and Artificial Intelligence Laboratory, Massachusetts Institute of Technology, Cambridge, MA, USA MATVEY B. PALCHUK, MD, MSTriNetX, LLC, Cambridge, MA, USA MAURICE MARS, MBCHB, MDDepartment of TeleHealth, University of KwaZulu-Natal, Durban, South Africa MIGUEL T. BARBOSA, MDAllergy Centre, CUF Descobertas Hospital, Lisboa, Portugal MOHAMED HAJJAM, MDPredimed Technology, Schiltigheim, France RICHARD E. SCOTT, PHDDepartment of Community Health Sciences, University of Calgary, Calgary, Alberta, Canada SARAH PIKE, BAKeck School of Medicine, University of Southern California, California, USA SHINICHIRO MAESHIMA, MD, PHDKinjo University, Ishikawa, Japan SIMON LIN LINWOOD, MD, MBASchool of Medicine, University of California, Riverside, CA, USA STEVE KHACHIKYANDornsife College of Letters, Arts &amp;amp; Sciences, University of Southern California, California, USA STEVEN KUNDROT, BS, MBA&amp;nbsp;TriNetX, LLC, Cambridge, MA, USA SUDHA NALLASAMY, MDThe Vision Center at Children’s Hospital Los Angeles, California, USA; USC Roski Eye Institute, University of Southern California, California, USA YUNGUI HUANG, PHD, MBAResearch Information Solutions and Innovation, The Research Institute at Nationwide Children’s Hospital, Columbus, OH, USA</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>96a698008602b3d7</t>
+          <t>05cd11abf81f4c96</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>The Role of Educational Interventions in Facing Social Media Threats: Overarching Principles of the COURAGE Project</t>
+          <t>Artificial Intelligence and Machine Learning: An Instructor’s Exoskeleton in the Future of Education</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Taibi, D.; Börsting, J.; Hoppe, U.; Ognibene, D.; Hernández-Leo, D.; Eimler, S.; Kruschwitz, U.</t>
+          <t>August, S.; Tsaima, A.</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>post_chatgpt</t>
+          <t>pre_chatgpt</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Communications in computer and information science</t>
+          <t>SpringerBriefs in statistics</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Springer Science+Business Media</t>
+          <t>Springer International Publishing</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -5520,7 +5527,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>10.1007/978-3-031-29800-4_25</t>
+          <t>10.1007/978-3-030-58948-6_5</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -5549,54 +5556,49 @@
         </is>
       </c>
       <c r="O63" t="n">
-        <v>6</v>
+        <v>26</v>
       </c>
       <c r="P63" t="n">
         <v>2</v>
       </c>
       <c r="Q63" t="inlineStr">
         <is>
-          <t>2023/96a698008602b3d7.pdf</t>
+          <t>2021/05cd11abf81f4c96.pdf</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>openalex,s2</t>
         </is>
       </c>
       <c r="S63" s="2" t="inlineStr">
         <is>
-          <t>Abstract Social media are offering new opportunities for communication and interaction way beyond what was possible only a few years ago. However, social media are also virtual spaces where young people are exposed to a variety of threats. Digital addiction, discrimination, hate speech, misinformation, polarization as well as manipulative influences of algorithms, body stereotyping, and cyberbullying are examples of challenges that find fertile ground on social media. Educators and students are not adequately prepared to face these challenges. To this aim, the COURAGE project, presented in this paper, introduces new tools and learning methodologies that can be adopted within higher education learning paths to train educators to deal with social media threats. The overarching principles of the COURAGE project leverage the most recent advances in the fields of artificial intelligence and in the educational domain paired with social and media psychological insights to support the development of the COURAGE ecosystem. The results of the experiments currently implemented with teachers and students of secondary schools as well as the impact of the COURAGE project on societal changes and ethical questions are presented and discussed.</t>
+          <t>Abstract The role of artificial intelligence in US education is expanding. As education moves toward providing customized learning paths, the use of artificial intelligence (AI) and machine learning (ML) algorithms in learning systems increases. This can be viewed as growing metaphorical exoskeletons for instructors, enabling them to provide a higher level of guidance, feedback, and autonomy to learners. In turn, the instructor gains time to sense student needs and support authentic learning experiences that go beyond what AI and ML can provide. Applications of AI-based education technology support learning through automated tutoring, personalizing learning, assessing student knowledge, and automating tasks normally performed by the instructor. This technology raises questions about how it is best used, what data provides evidence of the impact of AI and ML on learning, and future directions in interactive learning systems. Exploration of the use of AI and ML for both co-curricular and independent learnings in content presentation and instruction; interactions, communications, and discussions; learner activities; assessment and evaluation; and co-curricular opportunities provide guidance for future research.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>8f81d56c326a06d3</t>
+          <t>6f715e2962c0cd6d</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Transformer Language Model-Based Mobile Learning Solution for Higher Education</t>
+          <t>Jobs at Risk of Automation in the USA: Implications for Community College</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Silvia García-Méndez; Francisco de Arriba-Pérez; Francisco J. González-Castaño</t>
+          <t>Yamashita, T.; Cummins, P.</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>post_chatgpt</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>International Association for the Development of the Information Society. e-mail: secretariat@iadis.org; Web site: http://www.iadisportal.org</t>
+          <t>pre_chatgpt</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -5620,11 +5622,11 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q64" t="inlineStr">
         <is>
-          <t>2023/8f81d56c326a06d3.pdf</t>
+          <t>2021/6f715e2962c0cd6d.pdf</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -5634,28 +5636,28 @@
       </c>
       <c r="S64" s="2" t="inlineStr">
         <is>
-          <t>Mobile learning or mLearning has become an essential tool in many fields in this digital era, among the ones educational training deserves special attention, that is, applied to both basic and higher education towards active, flexible, effective high-quality and continuous learning. However, despite the advances in Natural Language Processing techniques, mLearning still does not take full advantage of the great potential of the latter techniques. It is the case of the transformer language models distributed in chatbot form. Accordingly, this work presents a mLearning application based on OpenAI GPT-3 model, which enables user-friendly interactions. The proposed system was tested in two evaluation scenarios, and the experimental results endorse its appropriateness toward learning experience enhancement. [For the full proceedings, see ED639391.]</t>
+          <t>Advancing technology such as artificial intelligence and robots is steadily replacing jobs in the USA. Continuous skill-upgrading and re-skilling are critical for workers to remain employable throughout their careers. In these social and economic contexts, community colleges play significant roles to provide workforce education and training because of their open admission, lower tuition, and shorter and more specific occupational programs compared to four-year universities. However, the detailed data of jobs at risk of automation are currently unavailable. This study used the national occupation and risk-of-automation data (Frey &amp;amp; Osborne, 2017) to estimate specific numbers of jobs at risk by industries and age groups. Results showed that approximately 48% of the jobs could be replaced within two decades. Four industries (1) service; (2) sales and office; (3) natural resources, construction and maintenance; and (4) production, transportation, and material moving were at a particularly higher risk (up to 75%). At the same time, computer, engineering, and health care occupations had a lower risk (up to 12%). The estimated numbers of jobs at risk informs community colleges' strategic planning. [This is the advance online version of an article published in &amp;quot;Community College Journal of Research and Practice.&amp;quot;]</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>e3b815e1a83132e6</t>
+          <t>e4785c336fe78ec7</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>About the Editor</t>
+          <t>Personalized and Adaptive Learning</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>MBA, S.</t>
+          <t>Taylor, D.; Yeung, M.; Bashet, A.</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -5664,12 +5666,12 @@
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Digital Health</t>
+          <t>SpringerBriefs in statistics</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>SAGE Publishing</t>
+          <t>Springer International Publishing</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
@@ -5679,7 +5681,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>10.36255/exon-publications-digital-health.editor</t>
+          <t>10.1007/978-3-030-58948-6_2</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -5689,7 +5691,7 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
@@ -5704,49 +5706,49 @@
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="O65" t="n">
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="P65" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q65" t="inlineStr">
         <is>
-          <t>2022/e3b815e1a83132e6.pdf</t>
+          <t>2021/e4785c336fe78ec7.pdf</t>
         </is>
       </c>
       <c r="R65" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>openalex,s2</t>
         </is>
       </c>
       <c r="S65" s="2" t="inlineStr">
         <is>
-          <t>Professor Simon Lin Linwood, MD, MBA, is the Chief Medical Information Officer at the UCR Health and UCR School of Medicine, Riverside, CA, USA. He obtained his executive education in Artificial Intelligence Strategy and Implementation from Harvard University. He was named Innovator of the Year by CHIME in 2018. He is a national thought leader on digital transformation and acknowledged for providing vision and leadership in information technology to drive business growth in large, complex, and highly distributed environments. He has supervised and mentored many PhD students on data-driven innovation in healthcare, such as deep learning for risk prediction in population health to control costs, and methods to reduce physician documentation burden. He received Mentor of the Year Award in 2016. His areas of expertise include digital transformation, data-driven innovation, data science, data lake, artificial intelligence, and natural language processing, among others. He has extensively published on digital health, artificial intelligence/machine learning, data science, clinical informatics, genome informatics.</t>
+          <t>Abstract Personalized and adaptive learning has been touted to be one of the most promising emerging tools for increasing student learning and student success. Yet, the terms are neither precise nor clearly defined at this time, thus making it difficult for institutions of higher education to adopt and implement a learning approach using technology that is in its infancy and not clearly understood by those who will be utilizing it. One goal of this chapter is to define adaptive and personalized learning as it is used at this time in the hopes that as the technology evolves the promise of increased student learning can come to fruition. Adaptive learning personalizes learning by continuously evaluating each student’s performance in real time and creating an ever-changing individualized learning pathway as directed by artificial intelligence and machine learning, thus increasing learning and student satisfaction.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>246ac766bd6d1c42</t>
+          <t>085fa965ce157d51</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>List of Contributors</t>
+          <t>Robots as My Future Colleagues: Changing Attitudes Toward Collaborative Robots by Means of Experience-Based Workshops</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Contributors, L.</t>
+          <t>Leoste, J.; Viik, T.; López, J.; Kangur, M.; Vunder, V.; Mollard, Y.; Õun, T.; Tammo, H.; Paekivi, K.</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>2022</v>
+        <v>2021</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -5755,12 +5757,12 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Digital Health</t>
+          <t>Smart innovation, systems and technologies</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>SAGE Publishing</t>
+          <t>Springer Nature</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -5770,7 +5772,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>10.36255/exon-publications-digital-health.contributors</t>
+          <t>10.1007/978-981-16-3930-2_13</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -5780,7 +5782,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5795,18 +5797,18 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>gold</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="O66" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="P66" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q66" t="inlineStr">
         <is>
-          <t>2022/246ac766bd6d1c42.pdf</t>
+          <t>2021/085fa965ce157d51.pdf</t>
         </is>
       </c>
       <c r="R66" t="inlineStr">
@@ -5816,24 +5818,24 @@
       </c>
       <c r="S66" s="2" t="inlineStr">
         <is>
-          <t>ABRAR-AHMAD ZULFIQAR, MDService de Médecine Interne, Diabète et Maladies métaboliques de la Clinique Médicale B, Hôpitaux Universitaires de Strasbourg et Equipe EA 3072 “Mitochondrie, Stress oxydant et Protection musculaire”, Faculté de Médecine-Université de Strasbourg, Strasbourg, France AIKO OSAWA, MD, PHDNational Center for Geriatrics and Gerontology, Aichi, Japan AMIR HAJJAM, PHDLaboratoire IRTES-SeT, Université de Technologie de Belfort-Montbéliard (UTBM), Belfort-Montbéliard, Belfort, France BRYONY MCGARRY, PHDPRECISE4Q, Predictive Modelling in Stroke, Technological University Dublin, Dublin, Ireland CEES TH. SMIT SIBINGA, MD, PHD, FRCP, FRCPATHIQM Consulting and University of Groningen, De Gast 46, 9801AE Zuidhorn, The Netherlands CLÁUDIA S. SOUSA, MDPulmonology Department, Central Hospital of Funchal, Portugal EMMANUEL ANDRÈS, MD, PHDLaboratoire IRTES-SeT, Université de Technologie de Belfort-Montbéliard (UTBM), Belfort-Montbéliard, Belfort, France EN-JU LIN, PHD, MPHResearch Information Solutions and Innovation, The Research Institute at Nationwide Children’s Hospital, Columbus, OH, USA ESRA ZIHNI, MSCPRECISE4Q, Predictive Modelling in Stroke, Technological University Dublin, Dublin, Ireland HIDENORI ARAI, MD, PHDNational Center for Geriatrics and Gerontology, Aichi, Japan IRVING D. KAPLAN, MDDepartment of Radiation Oncology, Beth Israel Deaconess Medical Center, Boston, MA, USA JENAY YUEN, BSKeck School of Medicine, University of Southern California, California, USA JESSAMINE P. WINER-JONES, PHDTriNetX, LLC, Cambridge, MA, USA JOHN KELLEHER, PHDPRECISE4Q, Predictive Modelling in Stroke, Technological University Dublin, Dublin, Ireland KATHARINE LAWRENCE, MD MPHNYU Grossman School of Medicine, Department of Population Health; NY, USA LIMOR APPELBAUM, MDDepartment of Radiation Oncology, Beth Israel Deaconess Medical Center, Boston, MA, USA MADELEINE SCHROEDER, MSResearch Information Solutions and Innovation, The Research Institute at Nationwide Children’s Hospital, Columbus, OH, USA MÁRIO MORAIS-ALMEIDA, MDAllergy Centre, CUF Descobertas Hospital, Lisboa, Portugal MARTIN RINARD, PHDComputer Science and Artificial Intelligence Laboratory, Massachusetts Institute of Technology, Cambridge, MA, USA MATVEY B. PALCHUK, MD, MSTriNetX, LLC, Cambridge, MA, USA MAURICE MARS, MBCHB, MDDepartment of TeleHealth, University of KwaZulu-Natal, Durban, South Africa MIGUEL T. BARBOSA, MDAllergy Centre, CUF Descobertas Hospital, Lisboa, Portugal MOHAMED HAJJAM, MDPredimed Technology, Schiltigheim, France RICHARD E. SCOTT, PHDDepartment of Community Health Sciences, University of Calgary, Calgary, Alberta, Canada SARAH PIKE, BAKeck School of Medicine, University of Southern California, California, USA SHINICHIRO MAESHIMA, MD, PHDKinjo University, Ishikawa, Japan SIMON LIN LINWOOD, MD, MBASchool of Medicine, University of California, Riverside, CA, USA STEVE KHACHIKYANDornsife College of Letters, Arts &amp;amp; Sciences, University of Southern California, California, USA STEVEN KUNDROT, BS, MBA&amp;nbsp;TriNetX, LLC, Cambridge, MA, USA SUDHA NALLASAMY, MDThe Vision Center at Children’s Hospital Los Angeles, California, USA; USC Roski Eye Institute, University of Southern California, California, USA YUNGUI HUANG, PHD, MBAResearch Information Solutions and Innovation, The Research Institute at Nationwide Children’s Hospital, Columbus, OH, USA</t>
+          <t>Abstract Artificial intelligence-driven robots are increasingly being introduced in various workplaces. Research implies that people’s negative attitudes toward intelligent and collaborative robots might hinder their willingness to use them. We propose that interactive educational activities such as specialized workshops help people to overcome such negative attitudes. We designed a two-day workshop that introduced two quasi-industrial robots (Poppy Ergo Jr and ClearBot) to 16 university students. Students’ attitudes were qualitatively measured before and after the workshop. The results imply that the workshop helped students to increase their understanding of the nature of the intelligent collaborative robots. More precisely, robots became to be seen as empowering tools, rather than friends or enemies. Interestingly, there were significant gender differences, as the female participants had a greater tendency to view robots as animated objects. We concluded that specialized workshops effectively lead participants to become aware of various promising opportunities for their robotic co-workers in the possible future.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>05cd11abf81f4c96</t>
+          <t>0141788f9ac5d7cb</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Artificial Intelligence and Machine Learning: An Instructor’s Exoskeleton in the Future of Education</t>
+          <t>University Student Surveys Using Chatbots: Artificial Intelligence Conversational Agents</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>August, S.; Tsaima, A.</t>
+          <t>Abbas, N.; Pickard, T.; Atwell, E.; Walker, A.</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -5846,12 +5848,12 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>SpringerBriefs in statistics</t>
+          <t>Lecture notes in computer science</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Springer International Publishing</t>
+          <t>Springer Science+Business Media</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -5861,7 +5863,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>10.1007/978-3-030-58948-6_5</t>
+          <t>10.1007/978-3-030-77943-6_10</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -5886,18 +5888,18 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>hybrid</t>
+          <t>green</t>
         </is>
       </c>
       <c r="O67" t="n">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="P67" t="n">
         <v>2</v>
       </c>
       <c r="Q67" t="inlineStr">
         <is>
-          <t>2021/05cd11abf81f4c96.pdf</t>
+          <t>2021/0141788f9ac5d7cb.pdf</t>
         </is>
       </c>
       <c r="R67" t="inlineStr">
@@ -5905,36 +5907,52 @@
           <t>openalex,s2</t>
         </is>
       </c>
-      <c r="S67" s="2" t="inlineStr">
-        <is>
-          <t>Abstract The role of artificial intelligence in US education is expanding. As education moves toward providing customized learning paths, the use of artificial intelligence (AI) and machine learning (ML) algorithms in learning systems increases. This can be viewed as growing metaphorical exoskeletons for instructors, enabling them to provide a higher level of guidance, feedback, and autonomy to learners. In turn, the instructor gains time to sense student needs and support authentic learning experiences that go beyond what AI and ML can provide. Applications of AI-based education technology support learning through automated tutoring, personalizing learning, assessing student knowledge, and automating tasks normally performed by the instructor. This technology raises questions about how it is best used, what data provides evidence of the impact of AI and ML on learning, and future directions in interactive learning systems. Exploration of the use of AI and ML for both co-curricular and independent learnings in content presentation and instruction; interactions, communications, and discussions; learner activities; assessment and evaluation; and co-curricular opportunities provide guidance for future research.</t>
-        </is>
-      </c>
+      <c r="S67" s="2" t="n"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>6f715e2962c0cd6d</t>
+          <t>d0f022dbfc25bf9e</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Jobs at Risk of Automation in the USA: Implications for Community College</t>
+          <t>About the Book</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Yamashita, T.; Cummins, P.</t>
+          <t>Bartneck, C.; Lütge, C.; Wagner, A.; Welsh, S.</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
           <t>pre_chatgpt</t>
         </is>
       </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>SpringerBriefs in ethics</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Springer International Publishing</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>book-chapter</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>10.1007/978-3-030-51110-4_1</t>
+        </is>
+      </c>
       <c r="J68" t="inlineStr">
         <is>
           <t>en</t>
@@ -5942,7 +5960,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>No</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5955,43 +5973,51 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="N68" t="inlineStr">
+        <is>
+          <t>hybrid</t>
+        </is>
+      </c>
+      <c r="O68" t="n">
+        <v>1</v>
+      </c>
       <c r="P68" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Q68" t="inlineStr">
         <is>
-          <t>2021/6f715e2962c0cd6d.pdf</t>
+          <t>2020/d0f022dbfc25bf9e.pdf</t>
         </is>
       </c>
       <c r="R68" t="inlineStr">
         <is>
-          <t>eric</t>
+          <t>openalex</t>
         </is>
       </c>
       <c r="S68" s="2" t="inlineStr">
         <is>
-          <t>Advancing technology such as artificial intelligence and robots is steadily replacing jobs in the USA. Continuous skill-upgrading and re-skilling are critical for workers to remain employable throughout their careers. In these social and economic contexts, community colleges play significant roles to provide workforce education and training because of their open admission, lower tuition, and shorter and more specific occupational programs compared to four-year universities. However, the detailed data of jobs at risk of automation are currently unavailable. This study used the national occupation and risk-of-automation data (Frey &amp;amp; Osborne, 2017) to estimate specific numbers of jobs at risk by industries and age groups. Results showed that approximately 48% of the jobs could be replaced within two decades. Four industries (1) service; (2) sales and office; (3) natural resources, construction and maintenance; and (4) production, transportation, and material moving were at a particularly higher risk (up to 75%). At the same time, computer, engineering, and health care occupations had a lower risk (up to 12%). The estimated numbers of jobs at risk informs community colleges' strategic planning. [This is the advance online version of an article published in &amp;quot;Community College Journal of Research and Practice.&amp;quot;]</t>
+          <t>This book provides an introduction into the ethics of robots and artificial intelligence. The book was written with university students, policy makers, and professionals in mind but should be accessible for most adults. The book is meant to provide balanced and, at times, conflicting viewpoints as to the benefits and deficits of AI through the lens of ethics. As discussed in the chapters that follow, ethical questions are often not cut and dry. Nations, communities, and individuals may have unique and important perspectives on these topics that should be heard and considered. While the voices that compose this book are our own, we have attempted to represent the views of the broader AI, robotics, and ethics communities.</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>e4785c336fe78ec7</t>
+          <t>68c8ca7f7b8e293f</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Personalized and Adaptive Learning</t>
+          <t>Collaborative Innovation Between Shenzhen Municipal Government and Tsinghua University</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Taylor, D.; Yeung, M.; Bashet, A.</t>
+          <t>Kang, F.</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -6000,12 +6026,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>SpringerBriefs in statistics</t>
+          <t>Education in the Asia-Pacific region</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Springer International Publishing</t>
+          <t>Springer Nature</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -6015,7 +6041,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>10.1007/978-3-030-58948-6_2</t>
+          <t>10.1007/978-981-15-7018-6_20</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -6044,14 +6070,14 @@
         </is>
       </c>
       <c r="O69" t="n">
-        <v>136</v>
+        <v>4</v>
       </c>
       <c r="P69" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q69" t="inlineStr">
         <is>
-          <t>2021/e4785c336fe78ec7.pdf</t>
+          <t>2020/68c8ca7f7b8e293f.pdf</t>
         </is>
       </c>
       <c r="R69" t="inlineStr">
@@ -6061,28 +6087,28 @@
       </c>
       <c r="S69" s="2" t="inlineStr">
         <is>
-          <t>Abstract Personalized and adaptive learning has been touted to be one of the most promising emerging tools for increasing student learning and student success. Yet, the terms are neither precise nor clearly defined at this time, thus making it difficult for institutions of higher education to adopt and implement a learning approach using technology that is in its infancy and not clearly understood by those who will be utilizing it. One goal of this chapter is to define adaptive and personalized learning as it is used at this time in the hopes that as the technology evolves the promise of increased student learning can come to fruition. Adaptive learning personalizes learning by continuously evaluating each student’s performance in real time and creating an ever-changing individualized learning pathway as directed by artificial intelligence and machine learning, thus increasing learning and student satisfaction.</t>
+          <t>Global megatrendsGlobal megatrends—the rise of frontier technologies, the dramatic growth of information, sociopolitical landscape changes, and demographic changes—call for the need for ecosystem orchestration that requires collaboration. The People’s Republic of China has been heavily investing on Artificial Intelligence (AI) and Research and Development (R&amp;D) to become an innovation leader globally and to further leverage its position as a manufacturing powerhouse. The Chinese innovation ecosystemInnovation ecosystem has grown steadily in recent years as they tapped higher education and research institutes. University-research-industry linkagesUniversity-research-industry linkages have proven to be successful in achieving PRC’s innovation-driven endeavors as evidenced by the large number of firms and start-ups from such linkages have grown into large businesses and key technological leaders.</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>085fa965ce157d51</t>
+          <t>ccad16bc20847787</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Robots as My Future Colleagues: Changing Attitudes Toward Collaborative Robots by Means of Experience-Based Workshops</t>
+          <t>Correction to: Predictive Policing in 2025: A Scenario</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Leoste, J.; Viik, T.; López, J.; Kangur, M.; Vunder, V.; Mollard, Y.; Õun, T.; Tammo, H.; Paekivi, K.</t>
+          <t>Macnish, K.; Wright, D.; Jiya, T.</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -6091,12 +6117,12 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Smart innovation, systems and technologies</t>
+          <t>Advanced sciences and technologies for security applications</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Springer Nature</t>
+          <t>Springer International Publishing</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -6106,7 +6132,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>10.1007/978-981-16-3930-2_13</t>
+          <t>10.1007/978-3-030-50613-1_9</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6135,45 +6161,45 @@
         </is>
       </c>
       <c r="O70" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="P70" t="n">
         <v>2</v>
       </c>
       <c r="Q70" t="inlineStr">
         <is>
-          <t>2021/085fa965ce157d51.pdf</t>
+          <t>2020/ccad16bc20847787.pdf</t>
         </is>
       </c>
       <c r="R70" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>openalex,s2</t>
         </is>
       </c>
       <c r="S70" s="2" t="inlineStr">
         <is>
-          <t>Abstract Artificial intelligence-driven robots are increasingly being introduced in various workplaces. Research implies that people’s negative attitudes toward intelligent and collaborative robots might hinder their willingness to use them. We propose that interactive educational activities such as specialized workshops help people to overcome such negative attitudes. We designed a two-day workshop that introduced two quasi-industrial robots (Poppy Ergo Jr and ClearBot) to 16 university students. Students’ attitudes were qualitatively measured before and after the workshop. The results imply that the workshop helped students to increase their understanding of the nature of the intelligent collaborative robots. More precisely, robots became to be seen as empowering tools, rather than friends or enemies. Interestingly, there were significant gender differences, as the female participants had a greater tendency to view robots as animated objects. We concluded that specialized workshops effectively lead participants to become aware of various promising opportunities for their robotic co-workers in the possible future.</t>
+          <t>Abstract Law enforcement authorities (LEAs) have begun using artificial intelligence and predictive policing applications that are likely to raise ethical, data protection, social, political and economic issues. This paper describes application of a new scenario methodology for identifying issues that emerging technologies are likely to raise in a future six or seven years hence, but that deserve policymakers’ attention now. It often takes policymakers that long to develop a new policy, consult with stakeholders and implement the policy. Thus, policymakers need a structured, but concise framework in order to understand the issues and their various implications. At the same time, they also prefer policies that have stakeholder support. These considerations led the University of Twente in the Netherlands and the UK’s Trilateral Research to develop the scenario that follows. It is structured with several headings that policymakers need to consider in order to move toward a desired future and avoidance of an undesired future.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0141788f9ac5d7cb</t>
+          <t>e97796436a92a9c7</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>University Student Surveys Using Chatbots: Artificial Intelligence Conversational Agents</t>
+          <t>Creative Composition Problem: A Knowledge Graph Logical-Based AI Construction and Optimization Solution - Applied in Cecilia: An Architecture of a Digital Companion Artificial Intelligence (AI) Agent System Composer of Dialogue Scripts for Well-Being and Mental Health</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Abbas, N.; Pickard, T.; Atwell, E.; Walker, A.</t>
+          <t>Galindo, M.; Moreno, L.</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -6197,7 +6223,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>10.1007/978-3-030-77943-6_10</t>
+          <t>10.1007/978-3-030-72308-8_4</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -6222,18 +6248,18 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>green</t>
+          <t>hybrid</t>
         </is>
       </c>
       <c r="O71" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="P71" t="n">
         <v>2</v>
       </c>
       <c r="Q71" t="inlineStr">
         <is>
-          <t>2021/0141788f9ac5d7cb.pdf</t>
+          <t>2020/e97796436a92a9c7.pdf</t>
         </is>
       </c>
       <c r="R71" t="inlineStr">
@@ -6241,22 +6267,26 @@
           <t>openalex,s2</t>
         </is>
       </c>
-      <c r="S71" s="2" t="n"/>
+      <c r="S71" s="2" t="inlineStr">
+        <is>
+          <t>Abstract Contribution of this work is to Define the Creative Composition Problem (CCP) for Human Well-being Optimization by Construction of Knowledge Graph using Knowledge Representation and logic-based Artificial Intelligence reasoning-planning where the computation of the Optimal Solution is achieved by Dynamic Programming or Logic Programming. The Creative Composition Problem is embedded within Cecilia: an architecture of a digital companion artificial intelligence agent system composer of dialogue scripts for Well-being and Mental Health. Where Cecilia Framework is instantiated in Well-being and Mental Health domain for optimal well-being development of first year university students. We define the ‘The Problem of Creating a Dialogue Composition (PCDC)’ and we propose a feasible and optimal solution of it. CCP is instantiated in this applied domain to solve PCDC optimizing the Mental Health and Well-being of the student. CCP as PCDC is applied to optimize maximizing the mental health of the student but also maximizing the smoothness, coherence, enjoyment and engagement each time the dialogue session is composed. Cecilia helps students to manage stress/anxiety to attempt the prevention of depression. Students can interact through the digital companion making questions and answers. While the system “learns” from the user it allows the user to learn from herself. Once the student discovers elements that were unnoticed by her, she will find a better way to improve when discovering her points of improvement.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>d0f022dbfc25bf9e</t>
+          <t>8ed280224b419888</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>About the Book</t>
+          <t>Psychological Applications and Trends 2020</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Bartneck, C.; Lütge, C.; Wagner, A.; Welsh, S.</t>
+          <t>Pracana, C.; Wang, M.</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -6267,26 +6297,6 @@
           <t>pre_chatgpt</t>
         </is>
       </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>SpringerBriefs in ethics</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Springer International Publishing</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>book-chapter</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-030-51110-4_1</t>
-        </is>
-      </c>
       <c r="J72" t="inlineStr">
         <is>
           <t>en</t>
@@ -6294,7 +6304,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -6307,47 +6317,39 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="N72" t="inlineStr">
-        <is>
-          <t>hybrid</t>
-        </is>
-      </c>
-      <c r="O72" t="n">
-        <v>1</v>
-      </c>
       <c r="P72" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Q72" t="inlineStr">
         <is>
-          <t>2020/d0f022dbfc25bf9e.pdf</t>
+          <t>2020/8ed280224b419888.pdf</t>
         </is>
       </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>openalex</t>
+          <t>eric</t>
         </is>
       </c>
       <c r="S72" s="2" t="inlineStr">
         <is>
-          <t>This book provides an introduction into the ethics of robots and artificial intelligence. The book was written with university students, policy makers, and professionals in mind but should be accessible for most adults. The book is meant to provide balanced and, at times, conflicting viewpoints as to the benefits and deficits of AI through the lens of ethics. As discussed in the chapters that follow, ethical questions are often not cut and dry. Nations, communities, and individuals may have unique and important perspectives on these topics that should be heard and considered. While the voices that compose this book are our own, we have attempted to represent the views of the broader AI, robotics, and ethics communities.</t>
+          <t>This book contains a compilation of papers presented at the International Psychological Applications Conference and Trends (InPACT) 2020, organized by the World Institute for Advanced Research and Science (W.I.A.R.S.), that this year had to be transformed into a fully Virtual Conference as a result of the Coronavirus (COVID 19) pandemic. Modern psychology offers a large range of scientific fields where it can be applied. The goal of understanding individuals and groups (mental functions and behavioral standpoints), from this academic and practical scientific discipline, aims ultimately to benefit society. The International Conference seeks to provide some answers and explore the several areas within the Psychology field, new developments in studies and proposals for future scientific projects. The goal is to offer a worldwide connection between psychologists, researchers and lecturers, from a wide range of academic fields, interested in exploring and giving their contribution in psychological issues. We take pride in having been able to connect and bring together academics, scholars, practitioners and others interested in a field that is fertile in new perspectives, ideas and knowledge. We counted on an extensive variety of contributors and presenters, which can supplement the view of the human essence and behavior, showing the impact of their different personal, academic and cultural experiences. This is, certainly, one of the reasons there are nationalities and cultures represented, inspiring multi-disciplinary collaborative links, fomenting intellectual encounter and development. InPACT 2020 received 240 submissions, from more than 45 different countries from all over the world, reviewed by a double-blind process. Submissions were prepared to take form of Virtual Presentations and Posters. 75 submissions (overall, 31% acceptance rate) were accepted for presentation in the conference. The conference also included: - One keynote presentation by Prof. Dr. Michael Wang (Emeritus Professor of Clinical Psychology, University of Leicester; Chair, Association of Clinical Psychologists, United Kingdom). - One Special Talk by Prof. Dr. Matthias Ammann (PhD, Department of Social Sciences, Uminho; Psychotherapist and psychoanalyst at Equilibrium Oporto; Climate activist, Portugal). We would like to express our gratitude to our invitees. The Conference addresses different categories inside Applied Psychology area and papers fit broadly into one of the named themes and sub-themes. The conference program includes six main broad-ranging categories that cover diversified interest areas: (1) Clinical Psychology: Emotions and related psychological processes; Assessment; Psychotherapy and counseling; Addictive behaviors; Eating disorders; Personality disorders; Quality of life and mental health; Communication within relationships; Services of mental health; and Psychopathology. (2) Educational Psychology: Language and cognitive processes; School environment and childhood disorders; Parenting and parenting related processes; Learning and technology; Psychology in schools; Intelligence and creativity; Motivation in classroom; Perspectives on teaching; Assessment and evaluation; and Individual differences in learning. (3) Social Psychology: Cross-cultural dimensions of mental disorders; Employment issues and training; Organizational psychology; Psychology in politics and international issues; Social factors in adolescence and its development; Social anxiety and self-esteem; Immigration and social policy; Self-efficacy and identity development; Parenting and social support; Addiction and stigmatization; and Psychological and social impact of virtual networks. (4) Legal Psychology: Violence and trauma; Mass-media and aggression; Intra-familial violence; Juvenile delinquency; Aggressive behavior in childhood; Internet offending; Working with crime perpetrators; Forensic psychology; Violent risk assessment; and Law enforcement and stress. (5) Cognitive and Experimental Psychology: Perception, memory and attention; Decision making and problem-solving; Concept formation, reasoning and judgment; Language processing; Learning skills and education; Cognitive Neuroscience; Computer analogies and information processing (Artificial Intelligence and computer simulations); Social and cultural factors in the cognitive approach; Experimental methods, research and statistics; and Biopsychology. (6) Psychoanalysis and Psychoanalytical Psychotherapy: Psychoanalysis and psychology; The unconscious; The Oedipus complex; Psychoanalysis of children; Pathological mourning; Addictive personalities; Borderline organizations; Narcissistic personalities; Anxiety and phobias; Psychosis; Neuropsychoanalysis. This book contains the results of the different researches conducted by authors who focused on what they are passionate about: to study and develop research in areas related to Psychology and its applications. It includes an extensive variety of contributors and presenters that are hereby sharing with us their different personal, academic and cultural experiences. We would like to thank all the authors and participants, the members of the academic scientific committee, and of course, to the organizing and administration team for making and putting this conference together. [This document contains the proceedings of the virtual International Psychological Applications Conference and Trends (InPACT) 2020. The proceedings were published by InScience Press. Abstract modified to meet ERIC guidelines. For the 2019 proceedings, see ED604954.]</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>68c8ca7f7b8e293f</t>
+          <t>4f278c8b9ba9d758</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Collaborative Innovation Between Shenzhen Municipal Government and Tsinghua University</t>
+          <t>Teaching Programming for Mathematical Scientists</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Kang, F.</t>
+          <t>Betteridge, J.; Chan, E.; Corless, R.; Davenport, J.; Grant, J.</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -6360,12 +6362,12 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Education in the Asia-Pacific region</t>
+          <t>Mathematics education in the digital era</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Springer Nature</t>
+          <t>Springer Nature (Netherlands)</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -6375,7 +6377,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>10.1007/978-981-15-7018-6_20</t>
+          <t>10.1007/978-3-030-86909-0_12</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -6400,18 +6402,18 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>hybrid</t>
+          <t>green</t>
         </is>
       </c>
       <c r="O73" t="n">
         <v>4</v>
       </c>
       <c r="P73" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q73" t="inlineStr">
         <is>
-          <t>2020/68c8ca7f7b8e293f.pdf</t>
+          <t>2020/4f278c8b9ba9d758.pdf</t>
         </is>
       </c>
       <c r="R73" t="inlineStr">
@@ -6420,342 +6422,6 @@
         </is>
       </c>
       <c r="S73" s="2" t="inlineStr">
-        <is>
-          <t>Global megatrendsGlobal megatrends—the rise of frontier technologies, the dramatic growth of information, sociopolitical landscape changes, and demographic changes—call for the need for ecosystem orchestration that requires collaboration. The People’s Republic of China has been heavily investing on Artificial Intelligence (AI) and Research and Development (R&amp;D) to become an innovation leader globally and to further leverage its position as a manufacturing powerhouse. The Chinese innovation ecosystemInnovation ecosystem has grown steadily in recent years as they tapped higher education and research institutes. University-research-industry linkagesUniversity-research-industry linkages have proven to be successful in achieving PRC’s innovation-driven endeavors as evidenced by the large number of firms and start-ups from such linkages have grown into large businesses and key technological leaders.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>ccad16bc20847787</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Correction to: Predictive Policing in 2025: A Scenario</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Macnish, K.; Wright, D.; Jiya, T.</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>2020</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>pre_chatgpt</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>Advanced sciences and technologies for security applications</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Springer International Publishing</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>book-chapter</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-030-50613-1_9</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
-        <is>
-          <t>hybrid</t>
-        </is>
-      </c>
-      <c r="O74" t="n">
-        <v>10</v>
-      </c>
-      <c r="P74" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q74" t="inlineStr">
-        <is>
-          <t>2020/ccad16bc20847787.pdf</t>
-        </is>
-      </c>
-      <c r="R74" t="inlineStr">
-        <is>
-          <t>openalex,s2</t>
-        </is>
-      </c>
-      <c r="S74" s="2" t="inlineStr">
-        <is>
-          <t>Abstract Law enforcement authorities (LEAs) have begun using artificial intelligence and predictive policing applications that are likely to raise ethical, data protection, social, political and economic issues. This paper describes application of a new scenario methodology for identifying issues that emerging technologies are likely to raise in a future six or seven years hence, but that deserve policymakers’ attention now. It often takes policymakers that long to develop a new policy, consult with stakeholders and implement the policy. Thus, policymakers need a structured, but concise framework in order to understand the issues and their various implications. At the same time, they also prefer policies that have stakeholder support. These considerations led the University of Twente in the Netherlands and the UK’s Trilateral Research to develop the scenario that follows. It is structured with several headings that policymakers need to consider in order to move toward a desired future and avoidance of an undesired future.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>e97796436a92a9c7</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Creative Composition Problem: A Knowledge Graph Logical-Based AI Construction and Optimization Solution - Applied in Cecilia: An Architecture of a Digital Companion Artificial Intelligence (AI) Agent System Composer of Dialogue Scripts for Well-Being and Mental Health</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Galindo, M.; Moreno, L.</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>2020</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>pre_chatgpt</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>Lecture notes in computer science</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Springer Science+Business Media</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>book-chapter</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-030-72308-8_4</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
-        <is>
-          <t>hybrid</t>
-        </is>
-      </c>
-      <c r="O75" t="n">
-        <v>0</v>
-      </c>
-      <c r="P75" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q75" t="inlineStr">
-        <is>
-          <t>2020/e97796436a92a9c7.pdf</t>
-        </is>
-      </c>
-      <c r="R75" t="inlineStr">
-        <is>
-          <t>openalex,s2</t>
-        </is>
-      </c>
-      <c r="S75" s="2" t="inlineStr">
-        <is>
-          <t>Abstract Contribution of this work is to Define the Creative Composition Problem (CCP) for Human Well-being Optimization by Construction of Knowledge Graph using Knowledge Representation and logic-based Artificial Intelligence reasoning-planning where the computation of the Optimal Solution is achieved by Dynamic Programming or Logic Programming. The Creative Composition Problem is embedded within Cecilia: an architecture of a digital companion artificial intelligence agent system composer of dialogue scripts for Well-being and Mental Health. Where Cecilia Framework is instantiated in Well-being and Mental Health domain for optimal well-being development of first year university students. We define the ‘The Problem of Creating a Dialogue Composition (PCDC)’ and we propose a feasible and optimal solution of it. CCP is instantiated in this applied domain to solve PCDC optimizing the Mental Health and Well-being of the student. CCP as PCDC is applied to optimize maximizing the mental health of the student but also maximizing the smoothness, coherence, enjoyment and engagement each time the dialogue session is composed. Cecilia helps students to manage stress/anxiety to attempt the prevention of depression. Students can interact through the digital companion making questions and answers. While the system “learns” from the user it allows the user to learn from herself. Once the student discovers elements that were unnoticed by her, she will find a better way to improve when discovering her points of improvement.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>8ed280224b419888</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Psychological Applications and Trends 2020</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Pracana, C.; Wang, M.</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>2020</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>pre_chatgpt</t>
-        </is>
-      </c>
-      <c r="J76" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="K76" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L76" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P76" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q76" t="inlineStr">
-        <is>
-          <t>2020/8ed280224b419888.pdf</t>
-        </is>
-      </c>
-      <c r="R76" t="inlineStr">
-        <is>
-          <t>eric</t>
-        </is>
-      </c>
-      <c r="S76" s="2" t="inlineStr">
-        <is>
-          <t>This book contains a compilation of papers presented at the International Psychological Applications Conference and Trends (InPACT) 2020, organized by the World Institute for Advanced Research and Science (W.I.A.R.S.), that this year had to be transformed into a fully Virtual Conference as a result of the Coronavirus (COVID 19) pandemic. Modern psychology offers a large range of scientific fields where it can be applied. The goal of understanding individuals and groups (mental functions and behavioral standpoints), from this academic and practical scientific discipline, aims ultimately to benefit society. The International Conference seeks to provide some answers and explore the several areas within the Psychology field, new developments in studies and proposals for future scientific projects. The goal is to offer a worldwide connection between psychologists, researchers and lecturers, from a wide range of academic fields, interested in exploring and giving their contribution in psychological issues. We take pride in having been able to connect and bring together academics, scholars, practitioners and others interested in a field that is fertile in new perspectives, ideas and knowledge. We counted on an extensive variety of contributors and presenters, which can supplement the view of the human essence and behavior, showing the impact of their different personal, academic and cultural experiences. This is, certainly, one of the reasons there are nationalities and cultures represented, inspiring multi-disciplinary collaborative links, fomenting intellectual encounter and development. InPACT 2020 received 240 submissions, from more than 45 different countries from all over the world, reviewed by a double-blind process. Submissions were prepared to take form of Virtual Presentations and Posters. 75 submissions (overall, 31% acceptance rate) were accepted for presentation in the conference. The conference also included: - One keynote presentation by Prof. Dr. Michael Wang (Emeritus Professor of Clinical Psychology, University of Leicester; Chair, Association of Clinical Psychologists, United Kingdom). - One Special Talk by Prof. Dr. Matthias Ammann (PhD, Department of Social Sciences, Uminho; Psychotherapist and psychoanalyst at Equilibrium Oporto; Climate activist, Portugal). We would like to express our gratitude to our invitees. The Conference addresses different categories inside Applied Psychology area and papers fit broadly into one of the named themes and sub-themes. The conference program includes six main broad-ranging categories that cover diversified interest areas: (1) Clinical Psychology: Emotions and related psychological processes; Assessment; Psychotherapy and counseling; Addictive behaviors; Eating disorders; Personality disorders; Quality of life and mental health; Communication within relationships; Services of mental health; and Psychopathology. (2) Educational Psychology: Language and cognitive processes; School environment and childhood disorders; Parenting and parenting related processes; Learning and technology; Psychology in schools; Intelligence and creativity; Motivation in classroom; Perspectives on teaching; Assessment and evaluation; and Individual differences in learning. (3) Social Psychology: Cross-cultural dimensions of mental disorders; Employment issues and training; Organizational psychology; Psychology in politics and international issues; Social factors in adolescence and its development; Social anxiety and self-esteem; Immigration and social policy; Self-efficacy and identity development; Parenting and social support; Addiction and stigmatization; and Psychological and social impact of virtual networks. (4) Legal Psychology: Violence and trauma; Mass-media and aggression; Intra-familial violence; Juvenile delinquency; Aggressive behavior in childhood; Internet offending; Working with crime perpetrators; Forensic psychology; Violent risk assessment; and Law enforcement and stress. (5) Cognitive and Experimental Psychology: Perception, memory and attention; Decision making and problem-solving; Concept formation, reasoning and judgment; Language processing; Learning skills and education; Cognitive Neuroscience; Computer analogies and information processing (Artificial Intelligence and computer simulations); Social and cultural factors in the cognitive approach; Experimental methods, research and statistics; and Biopsychology. (6) Psychoanalysis and Psychoanalytical Psychotherapy: Psychoanalysis and psychology; The unconscious; The Oedipus complex; Psychoanalysis of children; Pathological mourning; Addictive personalities; Borderline organizations; Narcissistic personalities; Anxiety and phobias; Psychosis; Neuropsychoanalysis. This book contains the results of the different researches conducted by authors who focused on what they are passionate about: to study and develop research in areas related to Psychology and its applications. It includes an extensive variety of contributors and presenters that are hereby sharing with us their different personal, academic and cultural experiences. We would like to thank all the authors and participants, the members of the academic scientific committee, and of course, to the organizing and administration team for making and putting this conference together. [This document contains the proceedings of the virtual International Psychological Applications Conference and Trends (InPACT) 2020. The proceedings were published by InScience Press. Abstract modified to meet ERIC guidelines. For the 2019 proceedings, see ED604954.]</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>4f278c8b9ba9d758</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>Teaching Programming for Mathematical Scientists</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Betteridge, J.; Chan, E.; Corless, R.; Davenport, J.; Grant, J.</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>2020</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>pre_chatgpt</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>Mathematics education in the digital era</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Springer Nature (Netherlands)</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>book-chapter</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>10.1007/978-3-030-86909-0_12</t>
-        </is>
-      </c>
-      <c r="J77" t="inlineStr">
-        <is>
-          <t>en</t>
-        </is>
-      </c>
-      <c r="K77" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="L77" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="N77" t="inlineStr">
-        <is>
-          <t>green</t>
-        </is>
-      </c>
-      <c r="O77" t="n">
-        <v>4</v>
-      </c>
-      <c r="P77" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q77" t="inlineStr">
-        <is>
-          <t>2020/4f278c8b9ba9d758.pdf</t>
-        </is>
-      </c>
-      <c r="R77" t="inlineStr">
-        <is>
-          <t>openalex,s2</t>
-        </is>
-      </c>
-      <c r="S77" s="2" t="inlineStr">
         <is>
           <t>Over the past thirty years or so the authors have been teaching various programming for mathematics courses at our respective Universities, as well as incorporating computer algebra and numerical computation into traditional mathematics courses. These activities are, in some important ways, natural precursors to the use of Artificial Intelligence in Mathematics Education. This paper reflects on some of our course designs and experiences and is therefore a mix of theory and practice. Underlying both is a clear recognition of the value of computer programming for mathematics education. We use this theory and practice to suggest good techniques for and to raise questions about the use of AI in Mathematics Education.</t>
         </is>
@@ -6777,98 +6443,98 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I8" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I9" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I10" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I11" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I13" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I14" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I15" r:id="rId23"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I16" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I18" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId31"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId32"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId33"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId34"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" r:id="rId35"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I23" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId37"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q24" r:id="rId38"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I25" r:id="rId39"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q25" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q26" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I27" r:id="rId42"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q27" r:id="rId43"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q28" r:id="rId44"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I29" r:id="rId45"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q29" r:id="rId46"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I30" r:id="rId47"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q30" r:id="rId48"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q31" r:id="rId49"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q32" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q33" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q34" r:id="rId53"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I35" r:id="rId54"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q35" r:id="rId55"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId56"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q36" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q37" r:id="rId59"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q38" r:id="rId60"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q39" r:id="rId61"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId62"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q40" r:id="rId63"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q41" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I17" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I20" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I22" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I24" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q24" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q25" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I26" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q26" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q27" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I28" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q28" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q29" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q30" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I31" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q31" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I32" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q32" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I33" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q33" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q34" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q35" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I36" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q36" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I37" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q37" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q38" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I39" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q39" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I40" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q40" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I41" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q41" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I42" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q42" r:id="rId66"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I43" r:id="rId67"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q43" r:id="rId68"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId69"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q44" r:id="rId70"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I45" r:id="rId71"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q45" r:id="rId72"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I46" r:id="rId73"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q46" r:id="rId74"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q47" r:id="rId75"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I48" r:id="rId76"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q48" r:id="rId77"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q49" r:id="rId78"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q50" r:id="rId79"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q51" r:id="rId80"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q52" r:id="rId81"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q53" r:id="rId82"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q54" r:id="rId83"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId84"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q55" r:id="rId85"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q56" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q43" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I44" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q44" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q45" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q46" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q47" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q48" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q49" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q50" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I51" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q51" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q52" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q53" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I54" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q54" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I55" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q55" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I56" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q56" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I57" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q57" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I58" r:id="rId88"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q58" r:id="rId89"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I59" r:id="rId90"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q59" r:id="rId91"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I60" r:id="rId92"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q60" r:id="rId93"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId94"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q61" r:id="rId95"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId96"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q62" r:id="rId97"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId98"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q63" r:id="rId99"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q64" r:id="rId100"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId101"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q65" r:id="rId102"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId103"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q66" r:id="rId104"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId105"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q67" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q60" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I61" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q61" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I62" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q62" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I63" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q63" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q64" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I65" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q65" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I66" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q66" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I67" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q67" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I68" r:id="rId106"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q68" r:id="rId107"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I69" r:id="rId108"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q69" r:id="rId109"/>
@@ -6876,17 +6542,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q70" r:id="rId111"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I71" r:id="rId112"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q71" r:id="rId113"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I72" r:id="rId114"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q72" r:id="rId115"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId116"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q73" r:id="rId117"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I74" r:id="rId118"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q74" r:id="rId119"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I75" r:id="rId120"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q75" r:id="rId121"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q76" r:id="rId122"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I77" r:id="rId123"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q77" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q72" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I73" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q73" r:id="rId116"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
